--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1071" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="65">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,124 +41,133 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>120253058581610341</t>
+  </si>
+  <si>
+    <t>120253058581650341</t>
+  </si>
+  <si>
+    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>120253031332440341</t>
+  </si>
+  <si>
+    <t>120253031332450341</t>
+  </si>
+  <si>
+    <t>120253023460500341</t>
+  </si>
+  <si>
+    <t>120253023954770341</t>
+  </si>
+  <si>
+    <t>120253023954790341</t>
+  </si>
+  <si>
+    <t>120253028817940341</t>
+  </si>
+  <si>
+    <t>120253028817970341</t>
+  </si>
+  <si>
+    <t>120253028817980341</t>
+  </si>
+  <si>
+    <t>120253028817950341</t>
+  </si>
+  <si>
+    <t>120253031332470341</t>
+  </si>
+  <si>
+    <t>120253031402020341</t>
+  </si>
+  <si>
+    <t>120253031402030341</t>
+  </si>
+  <si>
+    <t>120253031402040341</t>
+  </si>
+  <si>
+    <t>120253058581630341</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>120253023460490341</t>
+  </si>
+  <si>
+    <t>120253023954740341</t>
+  </si>
+  <si>
+    <t>120253023954760341</t>
+  </si>
+  <si>
+    <t>120253023954780341</t>
+  </si>
+  <si>
+    <t>120253023954810341</t>
+  </si>
+  <si>
+    <t>120253028817960341</t>
+  </si>
+  <si>
+    <t>120253031332490341</t>
+  </si>
+  <si>
+    <t>120253028818100341</t>
+  </si>
+  <si>
+    <t>120253058581620341</t>
+  </si>
+  <si>
+    <t>120253031332460341</t>
+  </si>
+  <si>
+    <t>120253058581640341</t>
+  </si>
+  <si>
+    <t>120253058581660341</t>
+  </si>
+  <si>
+    <t>120253031402050341</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>120253023954750341</t>
+  </si>
+  <si>
+    <t>120253023954800341</t>
+  </si>
+  <si>
+    <t>120253031402010341</t>
+  </si>
+  <si>
+    <t>120253031332480341</t>
+  </si>
+  <si>
     <t>2026-08-10</t>
   </si>
   <si>
-    <t>120253058581610341</t>
-  </si>
-  <si>
-    <t>120253058581620341</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>120253031332440341</t>
-  </si>
-  <si>
-    <t>120253031332450341</t>
-  </si>
-  <si>
-    <t>120253031332490341</t>
-  </si>
-  <si>
-    <t>120253023460500341</t>
-  </si>
-  <si>
-    <t>120253023954760341</t>
-  </si>
-  <si>
-    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
-  </si>
-  <si>
-    <t>120253031402050341</t>
-  </si>
-  <si>
-    <t>120253031402040341</t>
-  </si>
-  <si>
-    <t>120253031332480341</t>
-  </si>
-  <si>
-    <t>120253031402010341</t>
-  </si>
-  <si>
-    <t>120253031332460341</t>
-  </si>
-  <si>
-    <t>120253023954770341</t>
-  </si>
-  <si>
-    <t>120253028817940341</t>
-  </si>
-  <si>
-    <t>120253028817960341</t>
-  </si>
-  <si>
-    <t>120253028817980341</t>
-  </si>
-  <si>
-    <t>120253031332470341</t>
-  </si>
-  <si>
-    <t>120253031402030341</t>
-  </si>
-  <si>
-    <t>120253058581650341</t>
-  </si>
-  <si>
-    <t>120253028817950341</t>
-  </si>
-  <si>
     <t>2026-08-09</t>
   </si>
   <si>
-    <t>120253031402020341</t>
-  </si>
-  <si>
-    <t>120253023954780341</t>
-  </si>
-  <si>
-    <t>120253023954740341</t>
-  </si>
-  <si>
-    <t>120253023460490341</t>
-  </si>
-  <si>
-    <t>120253028818100341</t>
-  </si>
-  <si>
-    <t>120253023954750341</t>
-  </si>
-  <si>
-    <t>120253023954790341</t>
-  </si>
-  <si>
-    <t>120253058581640341</t>
-  </si>
-  <si>
-    <t>120253058581660341</t>
-  </si>
-  <si>
-    <t>120253028817970341</t>
-  </si>
-  <si>
     <t>2026-08-08</t>
   </si>
   <si>
-    <t>120253023954800341</t>
-  </si>
-  <si>
-    <t>120253058581630341</t>
-  </si>
-  <si>
     <t>2026-08-07</t>
   </si>
   <si>
     <t>120253023954820341</t>
-  </si>
-  <si>
-    <t>120253023954810341</t>
   </si>
   <si>
     <t>2026-08-06</t>
@@ -561,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I140"/>
+  <dimension ref="A1:I195"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -616,13 +625,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>479.0</v>
+        <v>202562.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>12</v>
+      <c r="F2" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -631,7 +640,7 @@
         <v>9</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -639,19 +648,19 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>601.0</v>
+        <v>156.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
@@ -660,7 +669,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -668,19 +677,19 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>13248.0</v>
+        <v>420861.0</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>12</v>
+      <c r="F4" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -689,7 +698,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -700,16 +709,16 @@
         <v>16</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>97767.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -718,7 +727,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -726,19 +735,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5679.0</v>
+        <v>5275.0</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -747,7 +756,7 @@
         <v>9</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -755,19 +764,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>395.0</v>
+        <v>178666.0</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="7" t="s">
-        <v>12</v>
+      <c r="F7" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -776,7 +785,7 @@
         <v>9</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -784,19 +793,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>70.0</v>
+        <v>37984.0</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F8" s="7" t="s">
-        <v>12</v>
+      <c r="F8" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -805,7 +814,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -813,19 +822,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>969.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="7" t="s">
-        <v>12</v>
+      <c r="F9" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
@@ -834,7 +843,7 @@
         <v>9</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -842,19 +851,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5812.0</v>
+        <v>76.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -863,7 +872,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -871,16 +880,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>419695.0</v>
+        <v>410664.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F11" s="7" t="n">
         <v>10.0</v>
@@ -892,7 +901,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -900,19 +909,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>92920.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>9</v>
@@ -921,7 +930,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -929,19 +938,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>118141.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -950,2356 +959,2356 @@
         <v>9</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>353254.0</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>29827.0</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>9</v>
-      </c>
       <c r="H14" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>353607.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F15" s="7" t="n">
-        <v>10.0</v>
+        <v>13</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>231205.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>50847.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>3128.0</v>
+        <v>698463.0</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F18" s="7" t="s">
-        <v>12</v>
+      <c r="F18" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>8605.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>344.0</v>
+        <v>290.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>3200.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>22093.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>526.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4379.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>65819.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>806341.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>9408.0</v>
+        <v>383929.0</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>571.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>451.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>407243.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>11.0</v>
+        <v>13</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>456.0</v>
+        <v>696340.0</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F31" s="7" t="s">
-        <v>12</v>
+      <c r="F31" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>51830.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F32" s="7" t="n">
         <v>2.0</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>41</v>
+        <v>21</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>816.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="7" t="s">
-        <v>12</v>
+      <c r="F33" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>172.0</v>
+        <v>794.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>747712.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="7" t="n">
-        <v>16.0</v>
+        <v>13</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>24685.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="7" t="s">
-        <v>12</v>
+      <c r="F36" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>249629.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F37" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C38" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>928.0</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G38" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="D38" s="6" t="n">
-        <v>2994.0</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G38" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="H38" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>107118.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>2.0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>1186.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>85.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>325.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F42" s="7" t="s">
-        <v>12</v>
+      <c r="F42" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>197.0</v>
+        <v>889.0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>1164.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>12</v>
+      <c r="F44" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>5147.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>728.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F46" s="7" t="s">
-        <v>12</v>
+      <c r="F46" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1182.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>512430.0</v>
+        <v>633.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>40.0</v>
+        <v>13</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>952.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>5727.0</v>
+        <v>70.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>28983.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>283905.0</v>
+        <v>324.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>13629.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>506367.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>16.0</v>
+        <v>13</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>292130.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>1502.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="7" t="s">
-        <v>12</v>
+      <c r="F56" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>939.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>12</v>
+      <c r="F57" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>486.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F58" s="7" t="s">
-        <v>12</v>
+      <c r="F58" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>1542.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>12</v>
+      <c r="F59" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>5227.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>394262.0</v>
+        <v>601.0</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>7.0</v>
+        <v>13</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>252920.0</v>
+        <v>199.0</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>280988.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>477111.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>13.0</v>
+        <v>13</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>74515.0</v>
+        <v>969.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>12137.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>1644.0</v>
+        <v>395.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>7147.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F68" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>11734.0</v>
+        <v>479.0</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>23967.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>12</v>
+      <c r="F70" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>99098.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="D72" s="6" t="n">
-        <v>28978.0</v>
+        <v>70.0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>26497.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F73" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>2825.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>12</v>
+      <c r="F74" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>26146.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F75" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>4020.0</v>
+        <v>451.0</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>356.0</v>
+        <v>526.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F77" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>42880.0</v>
+        <v>806692.0</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F78" s="7" t="s">
-        <v>12</v>
+      <c r="F78" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>17054.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>5285.0</v>
+        <v>571.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>1685.0</v>
+        <v>344.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>1274.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>12</v>
+      <c r="F82" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>13942.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F83" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B84" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="C84" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="D84" s="6" t="n">
-        <v>17807.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F84" s="7" t="s">
-        <v>12</v>
+      <c r="F84" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>146.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F85" s="7" t="s">
-        <v>12</v>
+      <c r="F85" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>14588.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>5788.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F87" s="7" t="s">
-        <v>12</v>
+      <c r="F87" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>18799.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>773114.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>31.0</v>
+        <v>13</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>74182.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>37</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>19972.0</v>
+        <v>172.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>542175.0</v>
+        <v>456.0</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F92" s="7" t="n">
-        <v>9.0</v>
+        <v>13</v>
+      </c>
+      <c r="F92" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>36976.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F93" s="7" t="s">
-        <v>12</v>
+      <c r="F93" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>80351.0</v>
+        <v>816.0</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -3307,19 +3316,19 @@
         <v>49</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>173630.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F95" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>49</v>
@@ -3328,7 +3337,7 @@
         <v>49</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
@@ -3336,19 +3345,19 @@
         <v>49</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>61232.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>49</v>
@@ -3357,7 +3366,7 @@
         <v>49</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
@@ -3365,19 +3374,19 @@
         <v>49</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>30762.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F97" s="7" t="s">
-        <v>12</v>
+      <c r="F97" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>49</v>
@@ -3386,7 +3395,7 @@
         <v>49</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
@@ -3394,19 +3403,19 @@
         <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>48163.0</v>
+        <v>486.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>49</v>
@@ -3415,7 +3424,7 @@
         <v>49</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -3423,19 +3432,19 @@
         <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>26014.0</v>
+        <v>952.0</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F99" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>49</v>
@@ -3444,7 +3453,7 @@
         <v>49</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100">
@@ -3452,19 +3461,19 @@
         <v>49</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>23841.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>12</v>
+      <c r="F100" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>49</v>
@@ -3473,7 +3482,7 @@
         <v>49</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
@@ -3481,19 +3490,19 @@
         <v>49</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>35692.0</v>
+        <v>939.0</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>49</v>
@@ -3502,7 +3511,7 @@
         <v>49</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
@@ -3510,19 +3519,19 @@
         <v>49</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>64701.0</v>
+        <v>325.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>49</v>
@@ -3531,7 +3540,7 @@
         <v>49</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
@@ -3542,16 +3551,16 @@
         <v>16</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>2200.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F103" s="7" t="s">
-        <v>12</v>
+      <c r="F103" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>49</v>
@@ -3560,7 +3569,7 @@
         <v>49</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104">
@@ -3574,13 +3583,13 @@
         <v>44</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>16744.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>49</v>
@@ -3589,7 +3598,7 @@
         <v>49</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
@@ -3597,19 +3606,19 @@
         <v>49</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>35873.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>49</v>
@@ -3618,7 +3627,7 @@
         <v>49</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106">
@@ -3626,19 +3635,19 @@
         <v>49</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>6327.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>49</v>
@@ -3647,7 +3656,7 @@
         <v>49</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -3655,19 +3664,19 @@
         <v>49</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>274584.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>14.0</v>
+        <v>13</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>49</v>
@@ -3676,7 +3685,7 @@
         <v>49</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -3684,19 +3693,19 @@
         <v>49</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>32194.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F108" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F108" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>49</v>
@@ -3705,7 +3714,7 @@
         <v>49</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -3713,19 +3722,19 @@
         <v>49</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>126418.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F109" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F109" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>49</v>
@@ -3734,7 +3743,7 @@
         <v>49</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
@@ -3742,16 +3751,16 @@
         <v>49</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>38558.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F110" s="7" t="n">
         <v>1.0</v>
@@ -3763,7 +3772,7 @@
         <v>49</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111">
@@ -3771,19 +3780,19 @@
         <v>49</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>20617.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>49</v>
@@ -3792,7 +3801,7 @@
         <v>49</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
@@ -3800,19 +3809,19 @@
         <v>49</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>199153.0</v>
+        <v>728.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>49</v>
@@ -3821,7 +3830,7 @@
         <v>49</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
@@ -3829,19 +3838,19 @@
         <v>49</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>277603.0</v>
+        <v>197.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>12.0</v>
+        <v>13</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>49</v>
@@ -3850,7 +3859,7 @@
         <v>49</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
@@ -3858,19 +3867,19 @@
         <v>49</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>171789.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F114" s="7" t="n">
-        <v>5.0</v>
+        <v>16.0</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>49</v>
@@ -3879,7 +3888,7 @@
         <v>49</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
@@ -3887,19 +3896,19 @@
         <v>49</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>247735.0</v>
+        <v>85.0</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F115" s="7" t="n">
-        <v>10.0</v>
+        <v>13</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G115" s="8" t="s">
         <v>49</v>
@@ -3908,123 +3917,123 @@
         <v>49</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>15987.0</v>
+        <v>146.0</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F116" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>8810.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>2368.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F118" s="7" t="s">
-        <v>12</v>
+      <c r="F118" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>28702.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F119" s="7" t="s">
-        <v>12</v>
+      <c r="F119" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
@@ -4032,19 +4041,19 @@
         <v>50</v>
       </c>
       <c r="B120" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C120" s="5" t="s">
-        <v>52</v>
-      </c>
       <c r="D120" s="6" t="n">
-        <v>4103.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F120" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>50</v>
@@ -4053,7 +4062,7 @@
         <v>50</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
@@ -4061,19 +4070,19 @@
         <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>1291.0</v>
+        <v>356.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F121" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>50</v>
@@ -4082,7 +4091,7 @@
         <v>50</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122">
@@ -4090,19 +4099,19 @@
         <v>50</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>84082.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F122" s="7" t="s">
-        <v>12</v>
+      <c r="F122" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G122" s="8" t="s">
         <v>50</v>
@@ -4111,7 +4120,7 @@
         <v>50</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123">
@@ -4119,19 +4128,19 @@
         <v>50</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>1872.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>50</v>
@@ -4140,7 +4149,7 @@
         <v>50</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124">
@@ -4148,19 +4157,19 @@
         <v>50</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>71164.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>12</v>
+      <c r="F124" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>50</v>
@@ -4169,471 +4178,2066 @@
         <v>50</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>54</v>
+        <v>17</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>135520.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>2.0</v>
+        <v>31.0</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>158330.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>12</v>
+      <c r="F126" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>15111.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>9365.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>12000.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F129" s="7" t="s">
-        <v>12</v>
+      <c r="F129" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>235231.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F130" s="7" t="s">
-        <v>12</v>
+      <c r="F130" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>48329.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F131" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>844.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>1320.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F133" s="7" t="s">
-        <v>12</v>
+      <c r="F133" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>13.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F134" s="7" t="s">
-        <v>12</v>
+      <c r="F134" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="H134" s="8" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>17869.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F135" s="7" t="s">
-        <v>12</v>
+      <c r="F135" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>32631.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>61</v>
+        <v>27</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>121978.0</v>
+        <v>7147.0</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>85782.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>29625.0</v>
+        <v>26497.0</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F139" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D140" s="6" t="n">
+        <v>477111.0</v>
+      </c>
+      <c r="E140" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F140" s="7" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="G140" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H140" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D141" s="6" t="n">
+        <v>5285.0</v>
+      </c>
+      <c r="E141" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G141" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H141" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I141" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D142" s="6" t="n">
+        <v>5788.0</v>
+      </c>
+      <c r="E142" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G142" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H142" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D143" s="6" t="n">
+        <v>26146.0</v>
+      </c>
+      <c r="E143" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F143" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G143" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H143" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I143" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D144" s="6" t="n">
+        <v>14588.0</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="H144" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D145" s="6" t="n">
+        <v>16744.0</v>
+      </c>
+      <c r="E145" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G145" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H145" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I145" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D146" s="6" t="n">
+        <v>38558.0</v>
+      </c>
+      <c r="E146" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H146" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C147" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D147" s="6" t="n">
+        <v>20617.0</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G147" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H147" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I147" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C148" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D148" s="6" t="n">
+        <v>126418.0</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F148" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H148" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D149" s="6" t="n">
+        <v>2200.0</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G149" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H149" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I149" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D150" s="6" t="n">
+        <v>23841.0</v>
+      </c>
+      <c r="E150" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H150" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D151" s="6" t="n">
+        <v>48163.0</v>
+      </c>
+      <c r="E151" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F151" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G151" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H151" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I151" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D152" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E152" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F152" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H152" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I152" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D153" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G153" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H153" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I153" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D154" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H154" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I154" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D155" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G155" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H155" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I155" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D156" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H156" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I156" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D157" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G157" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H157" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I157" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C158" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D158" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F158" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H158" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I158" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D159" s="6" t="n">
+        <v>199153.0</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F159" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G159" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H159" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I159" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C160" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D160" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F160" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H160" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I160" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C161" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" s="6" t="n">
+        <v>35873.0</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G161" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H161" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I161" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D162" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H162" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I162" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C163" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D163" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G163" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H163" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I163" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C164" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D164" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E164" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F164" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G164" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H164" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I164" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C165" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D165" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E165" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G165" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H165" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I165" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C166" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D166" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E166" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F166" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G166" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H166" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I166" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C167" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D167" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E167" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F167" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G167" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H167" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I167" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D168" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E168" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H168" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I168" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C169" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D169" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E169" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G169" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H169" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I169" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C170" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D170" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E170" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H170" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I170" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C171" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D171" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E171" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G171" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H171" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I171" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C172" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D172" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E172" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H172" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I172" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C173" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D173" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E173" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G173" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H173" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I173" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C174" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D174" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E174" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G174" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="H174" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I174" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C175" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D175" s="6" t="n">
+        <v>4103.0</v>
+      </c>
+      <c r="E175" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G175" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H175" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I175" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C176" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D176" s="6" t="n">
+        <v>1291.0</v>
+      </c>
+      <c r="E176" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G176" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H176" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I176" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C177" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D177" s="6" t="n">
+        <v>84082.0</v>
+      </c>
+      <c r="E177" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G177" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H177" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I177" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C178" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D178" s="6" t="n">
+        <v>1872.0</v>
+      </c>
+      <c r="E178" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G178" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H178" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I178" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C179" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D179" s="6" t="n">
+        <v>71164.0</v>
+      </c>
+      <c r="E179" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G179" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="H179" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="I179" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B140" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C140" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="D140" s="6" t="n">
+      <c r="B180" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C180" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D180" s="6" t="n">
+        <v>135520.0</v>
+      </c>
+      <c r="E180" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F180" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G180" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H180" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I180" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C181" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D181" s="6" t="n">
+        <v>158330.0</v>
+      </c>
+      <c r="E181" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G181" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H181" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I181" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C182" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D182" s="6" t="n">
+        <v>15111.0</v>
+      </c>
+      <c r="E182" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F182" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G182" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H182" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I182" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C183" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D183" s="6" t="n">
+        <v>9365.0</v>
+      </c>
+      <c r="E183" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G183" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H183" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I183" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C184" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D184" s="6" t="n">
+        <v>12000.0</v>
+      </c>
+      <c r="E184" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G184" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H184" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I184" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C185" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D185" s="6" t="n">
+        <v>235231.0</v>
+      </c>
+      <c r="E185" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G185" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H185" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I185" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C186" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D186" s="6" t="n">
+        <v>48329.0</v>
+      </c>
+      <c r="E186" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G186" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H186" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I186" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C187" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D187" s="6" t="n">
+        <v>844.0</v>
+      </c>
+      <c r="E187" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G187" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H187" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I187" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C188" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D188" s="6" t="n">
+        <v>1320.0</v>
+      </c>
+      <c r="E188" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G188" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H188" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I188" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C189" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D189" s="6" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="E189" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F189" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G189" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="H189" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I189" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C190" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D190" s="6" t="n">
+        <v>17869.0</v>
+      </c>
+      <c r="E190" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G190" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H190" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I190" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C191" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="D191" s="6" t="n">
+        <v>32631.0</v>
+      </c>
+      <c r="E191" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F191" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G191" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H191" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I191" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C192" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D192" s="6" t="n">
+        <v>121978.0</v>
+      </c>
+      <c r="E192" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G192" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H192" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I192" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C193" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D193" s="6" t="n">
+        <v>85782.0</v>
+      </c>
+      <c r="E193" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F193" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G193" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H193" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I193" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C194" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D194" s="6" t="n">
+        <v>29625.0</v>
+      </c>
+      <c r="E194" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G194" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H194" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I194" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C195" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D195" s="6" t="n">
         <v>1619.0</v>
       </c>
-      <c r="E140" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="H140" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I140" s="7" t="s">
-        <v>12</v>
+      <c r="E195" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G195" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="H195" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="I195" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="55">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,16 +41,13 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-08-13</t>
+    <t>2026-08-15</t>
   </si>
   <si>
     <t>120253058581610341</t>
   </si>
   <si>
-    <t>120253058581650341</t>
-  </si>
-  <si>
-    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
+    <t>120253058581660341</t>
   </si>
   <si>
     <t/>
@@ -59,31 +56,43 @@
     <t>120253031332440341</t>
   </si>
   <si>
-    <t>120253031332450341</t>
+    <t>120253031332460341</t>
   </si>
   <si>
     <t>120253023460500341</t>
   </si>
   <si>
+    <t>120253023954760341</t>
+  </si>
+  <si>
+    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
+  </si>
+  <si>
     <t>120253023954770341</t>
   </si>
   <si>
-    <t>120253023954790341</t>
+    <t>120253023954800341</t>
+  </si>
+  <si>
+    <t>120253023954810341</t>
   </si>
   <si>
     <t>120253028817940341</t>
   </si>
   <si>
-    <t>120253028817970341</t>
+    <t>120253028817980341</t>
   </si>
   <si>
-    <t>120253028817980341</t>
+    <t>120253028818100341</t>
+  </si>
+  <si>
+    <t>120253031332450341</t>
   </si>
   <si>
     <t>120253028817950341</t>
   </si>
   <si>
-    <t>120253031332470341</t>
+    <t>120253031332480341</t>
   </si>
   <si>
     <t>120253031402020341</t>
@@ -92,67 +101,67 @@
     <t>120253031402030341</t>
   </si>
   <si>
-    <t>120253031402040341</t>
+    <t>120253031402050341</t>
+  </si>
+  <si>
+    <t>120253058581620341</t>
   </si>
   <si>
     <t>120253058581630341</t>
   </si>
   <si>
-    <t>2026-08-12</t>
+    <t>120253058581650341</t>
+  </si>
+  <si>
+    <t>120253031402010341</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
+  </si>
+  <si>
+    <t>120253023954780341</t>
+  </si>
+  <si>
+    <t>120253023954820341</t>
+  </si>
+  <si>
+    <t>120253023954790341</t>
   </si>
   <si>
     <t>120253023460490341</t>
   </si>
   <si>
-    <t>120253023954740341</t>
+    <t>120253023954750341</t>
   </si>
   <si>
-    <t>120253023954760341</t>
-  </si>
-  <si>
-    <t>120253023954780341</t>
-  </si>
-  <si>
-    <t>120253023954810341</t>
+    <t>120253023954740341</t>
   </si>
   <si>
     <t>120253028817960341</t>
   </si>
   <si>
-    <t>120253031332490341</t>
-  </si>
-  <si>
-    <t>120253028818100341</t>
-  </si>
-  <si>
-    <t>120253058581620341</t>
-  </si>
-  <si>
-    <t>120253031332460341</t>
+    <t>120253031402040341</t>
   </si>
   <si>
     <t>120253058581640341</t>
   </si>
   <si>
-    <t>120253058581660341</t>
+    <t>120253031332490341</t>
   </si>
   <si>
-    <t>120253031402050341</t>
+    <t>120253031332470341</t>
+  </si>
+  <si>
+    <t>2026-08-13</t>
+  </si>
+  <si>
+    <t>120253028817970341</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
   </si>
   <si>
     <t>2026-08-11</t>
-  </si>
-  <si>
-    <t>120253023954750341</t>
-  </si>
-  <si>
-    <t>120253023954800341</t>
-  </si>
-  <si>
-    <t>120253031402010341</t>
-  </si>
-  <si>
-    <t>120253031332480341</t>
   </si>
   <si>
     <t>2026-08-10</t>
@@ -167,46 +176,7 @@
     <t>2026-08-07</t>
   </si>
   <si>
-    <t>120253023954820341</t>
-  </si>
-  <si>
     <t>2026-08-06</t>
-  </si>
-  <si>
-    <t>2026-07-04</t>
-  </si>
-  <si>
-    <t>120251805122950341</t>
-  </si>
-  <si>
-    <t>120251806660850341</t>
-  </si>
-  <si>
-    <t>120251805122960341</t>
-  </si>
-  <si>
-    <t>120251935384290341</t>
-  </si>
-  <si>
-    <t>120251806689300341</t>
-  </si>
-  <si>
-    <t>120251806711770341</t>
-  </si>
-  <si>
-    <t>2026-07-03</t>
-  </si>
-  <si>
-    <t>Lượt đăng ký hoàn tất trên trang web</t>
-  </si>
-  <si>
-    <t>2026-07-02</t>
-  </si>
-  <si>
-    <t>2026-07-01</t>
-  </si>
-  <si>
-    <t>120251805122970341</t>
   </si>
 </sst>
 </file>
@@ -570,7 +540,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I195"/>
+  <dimension ref="A1:I220"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -625,13 +595,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>202562.0</v>
+        <v>772.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <v>2.0</v>
+      <c r="F2" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -640,7 +610,7 @@
         <v>9</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
@@ -648,19 +618,19 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" s="6" t="n">
-        <v>156.0</v>
+        <v>17276.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
@@ -669,7 +639,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -677,19 +647,19 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" s="6" t="n">
-        <v>420861.0</v>
+        <v>336995.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>10.0</v>
+        <v>14.0</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -698,7 +668,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -706,19 +676,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>5377.0</v>
+        <v>435395.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -727,7 +697,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -735,19 +705,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="D6" s="6" t="n">
-        <v>5275.0</v>
+        <v>5248.0</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -756,7 +726,7 @@
         <v>9</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7">
@@ -764,19 +734,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>178666.0</v>
+        <v>650.0</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <v>3.0</v>
+      <c r="F7" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -785,7 +755,7 @@
         <v>9</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8">
@@ -793,19 +763,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>37984.0</v>
+        <v>316097.0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -814,7 +784,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -822,19 +792,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>17021.0</v>
+        <v>819.0</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <v>2.0</v>
+      <c r="F9" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
@@ -843,7 +813,7 @@
         <v>9</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -851,19 +821,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>76.0</v>
+        <v>4802.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -872,7 +842,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11">
@@ -880,19 +850,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>410664.0</v>
+        <v>19816.0</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <v>10.0</v>
+      <c r="F11" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -901,7 +871,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -909,19 +879,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5104.0</v>
+        <v>29578.0</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>9</v>
@@ -930,7 +900,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -938,19 +908,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>3472.0</v>
+        <v>4237.0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -959,1636 +929,1636 @@
         <v>9</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D14" s="6" t="n">
-        <v>353254.0</v>
+        <v>852206.0</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>14.0</v>
+        <v>27.0</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>15807.0</v>
+        <v>2548.0</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2939.0</v>
+        <v>5801.0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>25848.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="7" t="n">
-        <v>1.0</v>
+      <c r="F17" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>698463.0</v>
+        <v>397792.0</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>20.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>3888.0</v>
+        <v>1439.0</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>290.0</v>
+        <v>228.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>16525.0</v>
+        <v>22960.0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3988.0</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>25346.0</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>33363.0</v>
+        <v>742.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>7643.0</v>
+        <v>8213.0</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>3642.0</v>
+        <v>461978.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>20739.0</v>
+        <v>378946.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>383929.0</v>
+        <v>2170.0</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="7" t="n">
-        <v>2.0</v>
+      <c r="F27" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7174.0</v>
+        <v>14351.0</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>40</v>
+        <v>22</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2276.0</v>
+        <v>324526.0</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F29" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C30" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>6325.0</v>
+        <v>14457.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>696340.0</v>
+        <v>51544.0</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>9025.0</v>
+        <v>1625.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="7" t="n">
-        <v>2.0</v>
+      <c r="F32" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D33" s="6" t="n">
-        <v>282217.0</v>
+        <v>8383.0</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F33" s="7" t="n">
-        <v>6.0</v>
+      <c r="F33" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>794.0</v>
+        <v>445496.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1474.0</v>
+        <v>412.0</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>83588.0</v>
+        <v>3011.0</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F36" s="7" t="n">
-        <v>4.0</v>
+      <c r="F36" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>3290.0</v>
+        <v>385.0</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>928.0</v>
+        <v>696176.0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>100569.0</v>
+        <v>2238.0</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F39" s="7" t="n">
-        <v>2.0</v>
+      <c r="F39" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C40" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>4481.0</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G40" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="D40" s="6" t="n">
-        <v>46118.0</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G40" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="H40" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>2673.0</v>
+        <v>5324.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>480911.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>889.0</v>
+        <v>893824.0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>621293.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="7" t="n">
-        <v>12.0</v>
+      <c r="F44" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>21813.0</v>
+        <v>1498.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>357571.0</v>
+        <v>43627.0</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F46" s="7" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>7945.0</v>
+        <v>379038.0</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>633.0</v>
+        <v>3659.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C49" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C49" s="5" t="s">
-        <v>24</v>
-      </c>
       <c r="D49" s="6" t="n">
-        <v>2220.0</v>
+        <v>7279.0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>70.0</v>
+        <v>5765.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>2029.0</v>
+        <v>1563.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C52" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D52" s="6" t="n">
+        <v>2256.0</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="6" t="n">
-        <v>324.0</v>
-      </c>
-      <c r="E52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G52" s="8" t="s">
-        <v>42</v>
-      </c>
       <c r="H52" s="8" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1812.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>5812.0</v>
+        <v>1293.0</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>112476.0</v>
+        <v>378762.0</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F55" s="7" t="n">
         <v>4.0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>730436.0</v>
+        <v>12172.0</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F56" s="7" t="n">
-        <v>24.0</v>
+      <c r="F56" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>58187.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="7" t="n">
-        <v>2.0</v>
+      <c r="F57" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>131368.0</v>
+        <v>935238.0</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F58" s="7" t="n">
-        <v>3.0</v>
+        <v>20.0</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>218816.0</v>
+        <v>76.0</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F59" s="7" t="n">
-        <v>6.0</v>
+      <c r="F59" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>3911.0</v>
+        <v>353476.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>601.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>199.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>33241.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>15780.0</v>
+        <v>700185.0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>969.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>637424.0</v>
+        <v>290.0</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F66" s="7" t="n">
-        <v>14.0</v>
+      <c r="F66" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>395.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C68" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>5851.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F68" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>479.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F69" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
@@ -2597,80 +2567,80 @@
         <v>11</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>386517.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="7" t="n">
-        <v>6.0</v>
+      <c r="F70" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>4729.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>70.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="73">
@@ -2678,19 +2648,19 @@
         <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>8605.0</v>
+        <v>697336.0</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F73" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>48</v>
@@ -2699,7 +2669,7 @@
         <v>48</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -2707,19 +2677,19 @@
         <v>48</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>107118.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="7" t="n">
-        <v>2.0</v>
+      <c r="F74" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>48</v>
@@ -2728,7 +2698,7 @@
         <v>48</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="75">
@@ -2736,19 +2706,19 @@
         <v>48</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>51830.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F75" s="7" t="n">
-        <v>2.0</v>
+      <c r="F75" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G75" s="8" t="s">
         <v>48</v>
@@ -2757,7 +2727,7 @@
         <v>48</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76">
@@ -2765,19 +2735,19 @@
         <v>48</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>451.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>48</v>
@@ -2786,7 +2756,7 @@
         <v>48</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
@@ -2794,19 +2764,19 @@
         <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>526.0</v>
+        <v>383981.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>48</v>
@@ -2815,7 +2785,7 @@
         <v>48</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="78">
@@ -2823,19 +2793,19 @@
         <v>48</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>806692.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="G78" s="8" t="s">
         <v>48</v>
@@ -2844,471 +2814,471 @@
         <v>48</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>65819.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F79" s="7" t="n">
-        <v>5.0</v>
+      <c r="F79" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>571.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>344.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B82" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C82" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D82" s="6" t="n">
-        <v>249629.0</v>
+        <v>928.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F82" s="7" t="n">
-        <v>4.0</v>
+      <c r="F82" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>2994.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>747712.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>16.0</v>
+        <v>14.0</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>9408.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>24685.0</v>
+        <v>794.0</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>22093.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F87" s="7" t="n">
-        <v>1.0</v>
+      <c r="F87" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>3128.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>3200.0</v>
+        <v>633.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>4379.0</v>
+        <v>889.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>172.0</v>
+        <v>324.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>456.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F92" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>407399.0</v>
+        <v>70.0</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F93" s="7" t="n">
-        <v>11.0</v>
+      <c r="F93" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>816.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F94" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="95">
@@ -3316,19 +3286,19 @@
         <v>49</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>1542.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>49</v>
@@ -3337,7 +3307,7 @@
         <v>49</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
@@ -3345,19 +3315,19 @@
         <v>49</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>1502.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F96" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>49</v>
@@ -3366,7 +3336,7 @@
         <v>49</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="97">
@@ -3377,16 +3347,16 @@
         <v>10</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>292130.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>49</v>
@@ -3395,7 +3365,7 @@
         <v>49</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98">
@@ -3403,19 +3373,19 @@
         <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>486.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G98" s="8" t="s">
         <v>49</v>
@@ -3424,500 +3394,500 @@
         <v>49</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>952.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>283905.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F100" s="7" t="n">
-        <v>6.0</v>
+      <c r="F100" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>939.0</v>
+        <v>70.0</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>325.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>512430.0</v>
+        <v>969.0</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F103" s="7" t="n">
-        <v>40.0</v>
+      <c r="F103" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>1164.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F104" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>28983.0</v>
+        <v>395.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F105" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>5727.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>5227.0</v>
+        <v>479.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>1182.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>13629.0</v>
+        <v>601.0</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F109" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B110" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C110" s="5" t="s">
-        <v>46</v>
-      </c>
       <c r="D110" s="6" t="n">
-        <v>5147.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F110" s="7" t="n">
-        <v>1.0</v>
+      <c r="F110" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>1186.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>728.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>197.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>506367.0</v>
+        <v>199.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F114" s="7" t="n">
-        <v>16.0</v>
+      <c r="F114" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>85.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F115" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F115" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="116">
@@ -3925,19 +3895,19 @@
         <v>50</v>
       </c>
       <c r="B116" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C116" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C116" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="D116" s="6" t="n">
-        <v>146.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F116" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F116" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G116" s="8" t="s">
         <v>50</v>
@@ -3946,7 +3916,7 @@
         <v>50</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="117">
@@ -3954,19 +3924,19 @@
         <v>50</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>23967.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F117" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>50</v>
@@ -3975,7 +3945,7 @@
         <v>50</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="118">
@@ -3983,19 +3953,19 @@
         <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>74515.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>50</v>
@@ -4004,761 +3974,761 @@
         <v>50</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C119" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>99098.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F119" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C120" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D120" s="6" t="n">
+        <v>806692.0</v>
+      </c>
+      <c r="E120" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F120" s="7" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G120" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D120" s="6" t="n">
-        <v>2825.0</v>
-      </c>
-      <c r="E120" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F120" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G120" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="H120" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>356.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>17054.0</v>
+        <v>451.0</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F122" s="7" t="n">
-        <v>1.0</v>
+      <c r="F122" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>4020.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>13942.0</v>
+        <v>526.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F124" s="7" t="n">
-        <v>2.0</v>
+      <c r="F124" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B125" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C125" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C125" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="D125" s="6" t="n">
-        <v>773114.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F125" s="7" t="n">
-        <v>31.0</v>
+        <v>5.0</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>28978.0</v>
+        <v>571.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F126" s="7" t="n">
-        <v>1.0</v>
+      <c r="F126" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>1274.0</v>
+        <v>344.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F127" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>17807.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>252920.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>280988.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F130" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>18799.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>42880.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F132" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>12137.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F133" s="7" t="n">
-        <v>1.0</v>
+      <c r="F133" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>1685.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H134" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>394262.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F135" s="7" t="n">
-        <v>7.0</v>
+      <c r="F135" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>11734.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F136" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>7147.0</v>
+        <v>172.0</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F137" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>1644.0</v>
+        <v>456.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>26497.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F139" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F139" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>477111.0</v>
+        <v>816.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F140" s="7" t="n">
-        <v>13.0</v>
+      <c r="F140" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>5285.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>5788.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>26146.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F143" s="7" t="n">
-        <v>1.0</v>
+      <c r="F143" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>14588.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="145">
@@ -4766,19 +4736,19 @@
         <v>52</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>16744.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F145" s="7" t="n">
-        <v>1.0</v>
+      <c r="F145" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>52</v>
@@ -4787,7 +4757,7 @@
         <v>52</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="146">
@@ -4795,19 +4765,19 @@
         <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>38558.0</v>
+        <v>952.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F146" s="7" t="n">
-        <v>1.0</v>
+      <c r="F146" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>52</v>
@@ -4816,7 +4786,7 @@
         <v>52</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147">
@@ -4824,19 +4794,19 @@
         <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>20617.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>52</v>
@@ -4845,7 +4815,7 @@
         <v>52</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="148">
@@ -4853,19 +4823,19 @@
         <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>126418.0</v>
+        <v>325.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F148" s="7" t="n">
-        <v>1.0</v>
+      <c r="F148" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>52</v>
@@ -4874,7 +4844,7 @@
         <v>52</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="149">
@@ -4882,19 +4852,19 @@
         <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>2200.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>52</v>
@@ -4903,7 +4873,7 @@
         <v>52</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150">
@@ -4911,19 +4881,19 @@
         <v>52</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>23841.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>52</v>
@@ -4932,7 +4902,7 @@
         <v>52</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151">
@@ -4940,19 +4910,19 @@
         <v>52</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>48163.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F151" s="7" t="n">
-        <v>1.0</v>
+      <c r="F151" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>52</v>
@@ -4961,7 +4931,7 @@
         <v>52</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="152">
@@ -4969,19 +4939,19 @@
         <v>52</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>32194.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>52</v>
@@ -4990,7 +4960,7 @@
         <v>52</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="153">
@@ -4998,19 +4968,19 @@
         <v>52</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>542175.0</v>
+        <v>728.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F153" s="7" t="n">
-        <v>9.0</v>
+      <c r="F153" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>52</v>
@@ -5019,7 +4989,7 @@
         <v>52</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154">
@@ -5027,19 +4997,19 @@
         <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>274584.0</v>
+        <v>197.0</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F154" s="7" t="n">
-        <v>14.0</v>
+      <c r="F154" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>52</v>
@@ -5048,7 +5018,7 @@
         <v>52</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155">
@@ -5056,19 +5026,19 @@
         <v>52</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>35692.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F155" s="7" t="n">
-        <v>3.0</v>
+        <v>16.0</v>
       </c>
       <c r="G155" s="8" t="s">
         <v>52</v>
@@ -5077,7 +5047,7 @@
         <v>52</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="156">
@@ -5085,19 +5055,19 @@
         <v>52</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>30762.0</v>
+        <v>85.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F156" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>52</v>
@@ -5106,7 +5076,7 @@
         <v>52</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="157">
@@ -5114,19 +5084,19 @@
         <v>52</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C157" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>36976.0</v>
+        <v>939.0</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F157" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G157" s="8" t="s">
         <v>52</v>
@@ -5135,7 +5105,7 @@
         <v>52</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="158">
@@ -5143,19 +5113,19 @@
         <v>52</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>19972.0</v>
+        <v>486.0</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G158" s="8" t="s">
         <v>52</v>
@@ -5164,7 +5134,7 @@
         <v>52</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="159">
@@ -5172,19 +5142,19 @@
         <v>52</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>199153.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F159" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G159" s="8" t="s">
         <v>52</v>
@@ -5193,7 +5163,7 @@
         <v>52</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="160">
@@ -5201,19 +5171,19 @@
         <v>52</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>247735.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F160" s="7" t="n">
-        <v>10.0</v>
+      <c r="F160" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>52</v>
@@ -5222,7 +5192,7 @@
         <v>52</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="161">
@@ -5230,19 +5200,19 @@
         <v>52</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>35873.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F161" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>52</v>
@@ -5251,384 +5221,384 @@
         <v>52</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>277603.0</v>
+        <v>146.0</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F162" s="7" t="n">
-        <v>12.0</v>
+      <c r="F162" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>61232.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E163" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F163" s="7" t="n">
-        <v>1.0</v>
+      <c r="F163" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>64701.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F164" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>6327.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F165" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>173630.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F166" s="7" t="n">
-        <v>3.0</v>
+      <c r="F166" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>171789.0</v>
+        <v>356.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F167" s="7" t="n">
-        <v>5.0</v>
+      <c r="F167" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H167" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>80351.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F168" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F168" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H168" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>26014.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F169" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H169" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>8810.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H170" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>2368.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F171" s="7" t="n">
+        <v>31.0</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>28702.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H172" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>15987.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>38</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>74182.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F174" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F174" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="175">
@@ -5636,19 +5606,19 @@
         <v>53</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>4103.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F175" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>53</v>
@@ -5657,7 +5627,7 @@
         <v>53</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="176">
@@ -5665,19 +5635,19 @@
         <v>53</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>1291.0</v>
+        <v>7147.0</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>53</v>
@@ -5686,7 +5656,7 @@
         <v>53</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177">
@@ -5694,19 +5664,19 @@
         <v>53</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>84082.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F177" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>53</v>
@@ -5715,7 +5685,7 @@
         <v>53</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="178">
@@ -5723,19 +5693,19 @@
         <v>53</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>1872.0</v>
+        <v>26497.0</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G178" s="8" t="s">
         <v>53</v>
@@ -5744,7 +5714,7 @@
         <v>53</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="179">
@@ -5752,19 +5722,19 @@
         <v>53</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>71164.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F179" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>53</v>
@@ -5773,471 +5743,1196 @@
         <v>53</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>135520.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>61</v>
+        <v>17</v>
       </c>
       <c r="F180" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>158330.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F181" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F181" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>15111.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>9365.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F183" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>12000.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>57</v>
+        <v>28</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>235231.0</v>
+        <v>477111.0</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F185" s="7" t="n">
+        <v>13.0</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>48329.0</v>
+        <v>5285.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>844.0</v>
+        <v>5788.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H187" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>1320.0</v>
+        <v>26146.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F188" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>56</v>
+        <v>26</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>13.0</v>
+        <v>14588.0</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="H189" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>17869.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H190" s="8" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>32631.0</v>
+        <v>23841.0</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F191" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H191" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>121978.0</v>
+        <v>199153.0</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F192" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F192" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>85782.0</v>
+        <v>20617.0</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H193" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>29625.0</v>
+        <v>38558.0</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F194" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>54</v>
+        <v>21</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>56</v>
+        <v>25</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>1619.0</v>
+        <v>126418.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F195" s="7" t="s">
-        <v>13</v>
+        <v>17</v>
+      </c>
+      <c r="F195" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C196" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D196" s="6" t="n">
+        <v>2200.0</v>
+      </c>
+      <c r="E196" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G196" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H196" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I196" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C197" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D197" s="6" t="n">
+        <v>35873.0</v>
+      </c>
+      <c r="E197" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G197" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H197" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I197" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C198" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D198" s="6" t="n">
+        <v>16744.0</v>
+      </c>
+      <c r="E198" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F198" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G198" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H198" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I198" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C199" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D199" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E199" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F199" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G199" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H199" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I199" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C200" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D200" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E200" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F200" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G200" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H200" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I200" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C201" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D201" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E201" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F201" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G201" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H201" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I201" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C202" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D202" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F202" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G202" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H202" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C203" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D203" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E203" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G203" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H203" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I203" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C204" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D204" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E204" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G204" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H204" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C205" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D205" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E205" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G205" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H205" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I205" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C206" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="D206" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E206" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G206" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H206" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C207" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D207" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E207" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F207" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G207" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H207" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I207" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C208" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D208" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E208" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G208" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H208" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D209" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E209" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F209" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G209" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H209" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I209" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C210" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D210" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E210" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G210" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H210" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C211" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D211" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E211" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F211" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G211" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H211" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I211" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D212" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E212" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F212" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G212" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H212" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I212" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C213" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D213" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E213" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G213" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H213" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I213" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C214" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D214" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E214" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G214" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H214" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I214" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C215" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D215" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E215" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G215" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H215" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I215" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D216" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E216" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G216" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H216" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I216" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C217" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D217" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E217" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G217" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H217" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I217" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C218" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D218" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E218" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F218" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G218" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H218" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I218" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C219" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D219" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E219" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G219" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H219" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I219" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>48163.0</v>
+      </c>
+      <c r="E220" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="H220" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="57">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,13 +41,16 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-08-15</t>
+    <t>2026-08-17</t>
   </si>
   <si>
     <t>120253058581610341</t>
   </si>
   <si>
-    <t>120253058581660341</t>
+    <t>120253058581650341</t>
+  </si>
+  <si>
+    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
   </si>
   <si>
     <t/>
@@ -56,7 +59,7 @@
     <t>120253031332440341</t>
   </si>
   <si>
-    <t>120253031332460341</t>
+    <t>120253031332470341</t>
   </si>
   <si>
     <t>120253023460500341</t>
@@ -65,31 +68,19 @@
     <t>120253023954760341</t>
   </si>
   <si>
-    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
+    <t>120253028817940341</t>
   </si>
   <si>
-    <t>120253023954770341</t>
-  </si>
-  <si>
-    <t>120253023954800341</t>
-  </si>
-  <si>
-    <t>120253023954810341</t>
-  </si>
-  <si>
-    <t>120253028817940341</t>
+    <t>120253028817950341</t>
   </si>
   <si>
     <t>120253028817980341</t>
   </si>
   <si>
-    <t>120253028818100341</t>
+    <t>120253031332460341</t>
   </si>
   <si>
-    <t>120253031332450341</t>
-  </si>
-  <si>
-    <t>120253028817950341</t>
+    <t>120253023954770341</t>
   </si>
   <si>
     <t>120253031332480341</t>
@@ -107,55 +98,70 @@
     <t>120253058581620341</t>
   </si>
   <si>
-    <t>120253058581630341</t>
+    <t>2026-08-16</t>
   </si>
   <si>
-    <t>120253058581650341</t>
+    <t>120253023954740341</t>
+  </si>
+  <si>
+    <t>120253023954750341</t>
+  </si>
+  <si>
+    <t>120253023954790341</t>
+  </si>
+  <si>
+    <t>120253023954800341</t>
+  </si>
+  <si>
+    <t>120253023954820341</t>
+  </si>
+  <si>
+    <t>120253028817960341</t>
+  </si>
+  <si>
+    <t>120253028817970341</t>
+  </si>
+  <si>
+    <t>120253023954780341</t>
+  </si>
+  <si>
+    <t>120253031332450341</t>
+  </si>
+  <si>
+    <t>120253058581640341</t>
+  </si>
+  <si>
+    <t>120253031402040341</t>
+  </si>
+  <si>
+    <t>120253058581630341</t>
   </si>
   <si>
     <t>120253031402010341</t>
   </si>
   <si>
-    <t>2026-08-14</t>
+    <t>120253031332490341</t>
   </si>
   <si>
-    <t>120253023954780341</t>
+    <t>2026-08-15</t>
   </si>
   <si>
-    <t>120253023954820341</t>
+    <t>120253023954810341</t>
   </si>
   <si>
-    <t>120253023954790341</t>
+    <t>120253028818100341</t>
+  </si>
+  <si>
+    <t>120253058581660341</t>
+  </si>
+  <si>
+    <t>2026-08-14</t>
   </si>
   <si>
     <t>120253023460490341</t>
   </si>
   <si>
-    <t>120253023954750341</t>
-  </si>
-  <si>
-    <t>120253023954740341</t>
-  </si>
-  <si>
-    <t>120253028817960341</t>
-  </si>
-  <si>
-    <t>120253031402040341</t>
-  </si>
-  <si>
-    <t>120253058581640341</t>
-  </si>
-  <si>
-    <t>120253031332490341</t>
-  </si>
-  <si>
-    <t>120253031332470341</t>
-  </si>
-  <si>
     <t>2026-08-13</t>
-  </si>
-  <si>
-    <t>120253028817970341</t>
   </si>
   <si>
     <t>2026-08-12</t>
@@ -540,7 +546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I220"/>
+  <dimension ref="A1:I256"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -595,13 +601,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>772.0</v>
+        <v>56132.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>12</v>
+      <c r="F2" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -610,7 +616,7 @@
         <v>9</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -618,19 +624,19 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>17276.0</v>
+        <v>158.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
@@ -639,7 +645,7 @@
         <v>9</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
@@ -647,19 +653,19 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>336995.0</v>
+        <v>79231.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -668,7 +674,7 @@
         <v>9</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -676,19 +682,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>435395.0</v>
+        <v>15684.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>12.0</v>
+        <v>13</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -697,7 +703,7 @@
         <v>9</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -705,19 +711,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5248.0</v>
+        <v>85947.0</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
+      <c r="F6" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -726,7 +732,7 @@
         <v>9</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -734,19 +740,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>650.0</v>
+        <v>612.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -755,7 +761,7 @@
         <v>9</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
@@ -763,19 +769,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>316097.0</v>
+        <v>37284.0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -784,7 +790,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -792,19 +798,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>819.0</v>
+        <v>16486.0</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
@@ -813,7 +819,7 @@
         <v>9</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -821,19 +827,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>4802.0</v>
+        <v>601.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -842,7 +848,7 @@
         <v>9</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -850,19 +856,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>19816.0</v>
+        <v>64289.0</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="7" t="s">
-        <v>12</v>
+      <c r="F11" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -871,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
@@ -879,19 +885,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>29578.0</v>
+        <v>623.0</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>9</v>
@@ -900,7 +906,7 @@
         <v>9</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -908,19 +914,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>4237.0</v>
+        <v>945.0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -929,1636 +935,1636 @@
         <v>9</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C14" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>357870.0</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="6" t="n">
-        <v>852206.0</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>27.0</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>9</v>
-      </c>
       <c r="H14" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I14" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2548.0</v>
+        <v>2527.0</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="7" t="s">
-        <v>12</v>
+      <c r="F15" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>5801.0</v>
+        <v>6618.0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1044.0</v>
+        <v>637081.0</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="7" t="s">
-        <v>12</v>
+      <c r="F17" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>397792.0</v>
+        <v>243818.0</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>4.0</v>
+        <v>11.0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>1439.0</v>
+        <v>10198.0</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I19" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>228.0</v>
+        <v>285.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>22960.0</v>
+        <v>383.0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>3988.0</v>
+        <v>24684.0</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F22" s="7" t="s">
-        <v>12</v>
+      <c r="F22" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="D23" s="6" t="n">
-        <v>742.0</v>
+        <v>11414.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>8213.0</v>
+        <v>8877.0</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>461978.0</v>
+        <v>18.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>14.0</v>
+        <v>13</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>378946.0</v>
+        <v>173.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>12.0</v>
+        <v>13</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>2170.0</v>
+        <v>699278.0</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F27" s="7" t="s">
-        <v>12</v>
+      <c r="F27" s="7" t="n">
+        <v>18.0</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>14351.0</v>
+        <v>384424.0</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>324526.0</v>
+        <v>2068.0</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>14457.0</v>
+        <v>12206.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>51544.0</v>
+        <v>772.0</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>1625.0</v>
+        <v>31361.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F32" s="7" t="s">
-        <v>12</v>
+      <c r="F32" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>8383.0</v>
+        <v>212.0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>445496.0</v>
+        <v>295.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>412.0</v>
+        <v>42524.0</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="7" t="s">
-        <v>12</v>
+      <c r="F35" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>3011.0</v>
+        <v>18008.0</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>385.0</v>
+        <v>392.0</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>696176.0</v>
+        <v>336995.0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>12.0</v>
+        <v>14.0</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>2238.0</v>
+        <v>17276.0</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I39" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>4481.0</v>
+        <v>435991.0</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F40" s="7" t="s">
-        <v>12</v>
+      <c r="F40" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>5324.0</v>
+        <v>5248.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>17021.0</v>
+        <v>650.0</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>893824.0</v>
+        <v>19816.0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F43" s="7" t="n">
-        <v>24.0</v>
+        <v>13</v>
+      </c>
+      <c r="F43" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>5377.0</v>
+        <v>317924.0</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F44" s="7" t="s">
-        <v>12</v>
+      <c r="F44" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1498.0</v>
+        <v>819.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>43627.0</v>
+        <v>4802.0</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>379038.0</v>
+        <v>1439.0</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>3659.0</v>
+        <v>29578.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>7279.0</v>
+        <v>853298.0</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F49" s="7" t="s">
-        <v>12</v>
+      <c r="F49" s="7" t="n">
+        <v>27.0</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>5765.0</v>
+        <v>2548.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>1563.0</v>
+        <v>5801.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F51" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I51" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>2256.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I52" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>3472.0</v>
+        <v>401629.0</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F53" s="7" t="s">
-        <v>12</v>
+      <c r="F53" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I53" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>1293.0</v>
+        <v>772.0</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I54" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>378762.0</v>
+        <v>4237.0</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I55" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>12172.0</v>
+        <v>228.0</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I56" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>5104.0</v>
+        <v>22960.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F57" s="7" t="s">
-        <v>12</v>
+      <c r="F57" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I57" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>935238.0</v>
+        <v>3988.0</v>
       </c>
       <c r="E58" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="7" t="n">
-        <v>20.0</v>
+        <v>13</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I58" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>76.0</v>
+        <v>742.0</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I59" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C60" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D60" s="6" t="n">
-        <v>353476.0</v>
+        <v>8213.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>14.0</v>
+        <v>13</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>15807.0</v>
+        <v>462054.0</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F61" s="7" t="s">
-        <v>12</v>
+      <c r="F61" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>2939.0</v>
+        <v>378946.0</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F62" s="7" t="s">
-        <v>12</v>
+      <c r="F62" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>25848.0</v>
+        <v>2170.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>700185.0</v>
+        <v>14351.0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3888.0</v>
+        <v>324526.0</v>
       </c>
       <c r="E65" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F65" s="7" t="s">
-        <v>12</v>
+      <c r="F65" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>290.0</v>
+        <v>14457.0</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>16525.0</v>
+        <v>5324.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I67" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>25346.0</v>
+        <v>1625.0</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I68" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>7643.0</v>
+        <v>696176.0</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F69" s="7" t="s">
-        <v>12</v>
+      <c r="F69" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I69" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
@@ -2567,254 +2573,254 @@
         <v>11</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>2276.0</v>
+        <v>445496.0</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F70" s="7" t="s">
-        <v>12</v>
+      <c r="F70" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I70" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>33363.0</v>
+        <v>3011.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I71" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>9025.0</v>
+        <v>8383.0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F72" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F72" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I72" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>697336.0</v>
+        <v>385.0</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>10.0</v>
+        <v>13</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I73" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>6325.0</v>
+        <v>51544.0</v>
       </c>
       <c r="E74" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F74" s="7" t="s">
-        <v>12</v>
+      <c r="F74" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I74" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>3642.0</v>
+        <v>2238.0</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F75" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I75" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>7174.0</v>
+        <v>4481.0</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F76" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I76" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>383981.0</v>
+        <v>412.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I77" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>20739.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F78" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I78" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -2822,19 +2828,19 @@
         <v>49</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>3290.0</v>
+        <v>893824.0</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F79" s="7" t="s">
-        <v>12</v>
+      <c r="F79" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G79" s="8" t="s">
         <v>49</v>
@@ -2843,7 +2849,7 @@
         <v>49</v>
       </c>
       <c r="I79" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -2851,19 +2857,19 @@
         <v>49</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>46118.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F80" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G80" s="8" t="s">
         <v>49</v>
@@ -2872,7 +2878,7 @@
         <v>49</v>
       </c>
       <c r="I80" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -2880,19 +2886,19 @@
         <v>49</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>100569.0</v>
+        <v>1498.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G81" s="8" t="s">
         <v>49</v>
@@ -2901,7 +2907,7 @@
         <v>49</v>
       </c>
       <c r="I81" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -2909,19 +2915,19 @@
         <v>49</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>928.0</v>
+        <v>43627.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F82" s="7" t="s">
-        <v>12</v>
+      <c r="F82" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G82" s="8" t="s">
         <v>49</v>
@@ -2930,7 +2936,7 @@
         <v>49</v>
       </c>
       <c r="I82" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -2938,19 +2944,19 @@
         <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>282217.0</v>
+        <v>5765.0</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F83" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F83" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G83" s="8" t="s">
         <v>49</v>
@@ -2959,7 +2965,7 @@
         <v>49</v>
       </c>
       <c r="I83" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="84">
@@ -2967,19 +2973,19 @@
         <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>480911.0</v>
+        <v>379038.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>14.0</v>
+        <v>5.0</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>49</v>
@@ -2988,7 +2994,7 @@
         <v>49</v>
       </c>
       <c r="I84" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="85">
@@ -2996,19 +3002,19 @@
         <v>49</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>83588.0</v>
+        <v>3659.0</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>49</v>
@@ -3017,7 +3023,7 @@
         <v>49</v>
       </c>
       <c r="I85" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="86">
@@ -3025,19 +3031,19 @@
         <v>49</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>794.0</v>
+        <v>7279.0</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F86" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>49</v>
@@ -3046,7 +3052,7 @@
         <v>49</v>
       </c>
       <c r="I86" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="87">
@@ -3054,19 +3060,19 @@
         <v>49</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>1474.0</v>
+        <v>12172.0</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G87" s="8" t="s">
         <v>49</v>
@@ -3075,7 +3081,7 @@
         <v>49</v>
       </c>
       <c r="I87" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="88">
@@ -3083,19 +3089,19 @@
         <v>49</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>2673.0</v>
+        <v>1563.0</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F88" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>49</v>
@@ -3104,7 +3110,7 @@
         <v>49</v>
       </c>
       <c r="I88" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -3112,19 +3118,19 @@
         <v>49</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>633.0</v>
+        <v>2256.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F89" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>49</v>
@@ -3133,7 +3139,7 @@
         <v>49</v>
       </c>
       <c r="I89" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
@@ -3141,19 +3147,19 @@
         <v>49</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>889.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F90" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>49</v>
@@ -3162,7 +3168,7 @@
         <v>49</v>
       </c>
       <c r="I90" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="91">
@@ -3170,19 +3176,19 @@
         <v>49</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>324.0</v>
+        <v>1293.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F91" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>49</v>
@@ -3191,7 +3197,7 @@
         <v>49</v>
       </c>
       <c r="I91" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="92">
@@ -3199,19 +3205,19 @@
         <v>49</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>2029.0</v>
+        <v>378762.0</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F92" s="7" t="s">
-        <v>12</v>
+      <c r="F92" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>49</v>
@@ -3220,7 +3226,7 @@
         <v>49</v>
       </c>
       <c r="I92" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -3228,19 +3234,19 @@
         <v>49</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>70.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F93" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G93" s="8" t="s">
         <v>49</v>
@@ -3249,7 +3255,7 @@
         <v>49</v>
       </c>
       <c r="I93" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94">
@@ -3257,19 +3263,19 @@
         <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>2220.0</v>
+        <v>935238.0</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F94" s="7" t="s">
-        <v>12</v>
+      <c r="F94" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>49</v>
@@ -3278,7 +3284,7 @@
         <v>49</v>
       </c>
       <c r="I94" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="95">
@@ -3286,19 +3292,19 @@
         <v>49</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>621293.0</v>
+        <v>76.0</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F95" s="7" t="n">
-        <v>12.0</v>
+        <v>13</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G95" s="8" t="s">
         <v>49</v>
@@ -3307,94 +3313,94 @@
         <v>49</v>
       </c>
       <c r="I95" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>7945.0</v>
+        <v>353476.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F96" s="7" t="s">
-        <v>12</v>
+      <c r="F96" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I96" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>357571.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F97" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I97" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>21813.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F98" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I98" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99">
@@ -3402,19 +3408,19 @@
         <v>50</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>637424.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G99" s="8" t="s">
         <v>50</v>
@@ -3423,7 +3429,7 @@
         <v>50</v>
       </c>
       <c r="I99" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100">
@@ -3431,19 +3437,19 @@
         <v>50</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>33241.0</v>
+        <v>700185.0</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F100" s="7" t="s">
-        <v>12</v>
+      <c r="F100" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>50</v>
@@ -3452,7 +3458,7 @@
         <v>50</v>
       </c>
       <c r="I100" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
@@ -3460,19 +3466,19 @@
         <v>50</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>70.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F101" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>50</v>
@@ -3481,7 +3487,7 @@
         <v>50</v>
       </c>
       <c r="I101" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102">
@@ -3489,19 +3495,19 @@
         <v>50</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C102" s="5" t="s">
         <v>44</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>15780.0</v>
+        <v>290.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F102" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G102" s="8" t="s">
         <v>50</v>
@@ -3510,7 +3516,7 @@
         <v>50</v>
       </c>
       <c r="I102" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103">
@@ -3518,19 +3524,19 @@
         <v>50</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>969.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F103" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G103" s="8" t="s">
         <v>50</v>
@@ -3539,7 +3545,7 @@
         <v>50</v>
       </c>
       <c r="I103" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104">
@@ -3547,19 +3553,19 @@
         <v>50</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>4729.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F104" s="7" t="s">
-        <v>12</v>
+      <c r="F104" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G104" s="8" t="s">
         <v>50</v>
@@ -3568,7 +3574,7 @@
         <v>50</v>
       </c>
       <c r="I104" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
@@ -3576,19 +3582,19 @@
         <v>50</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>42</v>
+        <v>11</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>395.0</v>
+        <v>383981.0</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F105" s="7" t="s">
-        <v>12</v>
+      <c r="F105" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>50</v>
@@ -3597,7 +3603,7 @@
         <v>50</v>
       </c>
       <c r="I105" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106">
@@ -3605,19 +3611,19 @@
         <v>50</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>5851.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F106" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>50</v>
@@ -3626,7 +3632,7 @@
         <v>50</v>
       </c>
       <c r="I106" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107">
@@ -3634,19 +3640,19 @@
         <v>50</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>479.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>50</v>
@@ -3655,7 +3661,7 @@
         <v>50</v>
       </c>
       <c r="I107" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108">
@@ -3663,19 +3669,19 @@
         <v>50</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>386517.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F108" s="7" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G108" s="8" t="s">
         <v>50</v>
@@ -3684,7 +3690,7 @@
         <v>50</v>
       </c>
       <c r="I108" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109">
@@ -3692,19 +3698,19 @@
         <v>50</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>601.0</v>
+        <v>697336.0</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F109" s="7" t="s">
-        <v>12</v>
+      <c r="F109" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>50</v>
@@ -3713,7 +3719,7 @@
         <v>50</v>
       </c>
       <c r="I109" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110">
@@ -3721,19 +3727,19 @@
         <v>50</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>5812.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F110" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>50</v>
@@ -3742,7 +3748,7 @@
         <v>50</v>
       </c>
       <c r="I110" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111">
@@ -3750,19 +3756,19 @@
         <v>50</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>3911.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F111" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>50</v>
@@ -3771,7 +3777,7 @@
         <v>50</v>
       </c>
       <c r="I111" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
@@ -3779,19 +3785,19 @@
         <v>50</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>131368.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>50</v>
@@ -3800,7 +3806,7 @@
         <v>50</v>
       </c>
       <c r="I112" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113">
@@ -3808,19 +3814,19 @@
         <v>50</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>58187.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F113" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F113" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>50</v>
@@ -3829,7 +3835,7 @@
         <v>50</v>
       </c>
       <c r="I113" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
@@ -3837,19 +3843,19 @@
         <v>50</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>199.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F114" s="7" t="s">
-        <v>12</v>
+      <c r="F114" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>50</v>
@@ -3858,123 +3864,123 @@
         <v>50</v>
       </c>
       <c r="I114" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>730436.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E115" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F115" s="7" t="n">
-        <v>24.0</v>
+        <v>13</v>
+      </c>
+      <c r="F115" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I115" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>112476.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E116" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F116" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F116" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I116" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>1812.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F117" s="7" t="s">
-        <v>12</v>
+      <c r="F117" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I117" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>218816.0</v>
+        <v>889.0</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F118" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F118" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I118" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119">
@@ -3982,19 +3988,19 @@
         <v>51</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>249629.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F119" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>51</v>
@@ -4003,7 +4009,7 @@
         <v>51</v>
       </c>
       <c r="I119" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120">
@@ -4011,19 +4017,19 @@
         <v>51</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>806692.0</v>
+        <v>324.0</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>40.0</v>
+        <v>13</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>51</v>
@@ -4032,7 +4038,7 @@
         <v>51</v>
       </c>
       <c r="I120" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="121">
@@ -4040,19 +4046,19 @@
         <v>51</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>51830.0</v>
+        <v>633.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F121" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>51</v>
@@ -4061,7 +4067,7 @@
         <v>51</v>
       </c>
       <c r="I121" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="122">
@@ -4069,19 +4075,19 @@
         <v>51</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>451.0</v>
+        <v>70.0</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F122" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G122" s="8" t="s">
         <v>51</v>
@@ -4090,7 +4096,7 @@
         <v>51</v>
       </c>
       <c r="I122" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="123">
@@ -4098,19 +4104,19 @@
         <v>51</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>8605.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F123" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G123" s="8" t="s">
         <v>51</v>
@@ -4119,7 +4125,7 @@
         <v>51</v>
       </c>
       <c r="I123" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="124">
@@ -4127,19 +4133,19 @@
         <v>51</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>526.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F124" s="7" t="s">
-        <v>12</v>
+      <c r="F124" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>51</v>
@@ -4148,7 +4154,7 @@
         <v>51</v>
       </c>
       <c r="I124" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="125">
@@ -4156,19 +4162,19 @@
         <v>51</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>65819.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G125" s="8" t="s">
         <v>51</v>
@@ -4177,7 +4183,7 @@
         <v>51</v>
       </c>
       <c r="I125" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126">
@@ -4185,19 +4191,19 @@
         <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>571.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F126" s="7" t="s">
-        <v>12</v>
+      <c r="F126" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>51</v>
@@ -4206,7 +4212,7 @@
         <v>51</v>
       </c>
       <c r="I126" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="127">
@@ -4214,19 +4220,19 @@
         <v>51</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>344.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E127" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F127" s="7" t="s">
-        <v>12</v>
+      <c r="F127" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>51</v>
@@ -4235,7 +4241,7 @@
         <v>51</v>
       </c>
       <c r="I127" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="128">
@@ -4243,19 +4249,19 @@
         <v>51</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>2994.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F128" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G128" s="8" t="s">
         <v>51</v>
@@ -4264,7 +4270,7 @@
         <v>51</v>
       </c>
       <c r="I128" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="129">
@@ -4272,19 +4278,19 @@
         <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>107118.0</v>
+        <v>928.0</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F129" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F129" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>51</v>
@@ -4293,7 +4299,7 @@
         <v>51</v>
       </c>
       <c r="I129" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="130">
@@ -4301,19 +4307,19 @@
         <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>22093.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G130" s="8" t="s">
         <v>51</v>
@@ -4322,7 +4328,7 @@
         <v>51</v>
       </c>
       <c r="I130" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="131">
@@ -4330,19 +4336,19 @@
         <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>9408.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F131" s="7" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>51</v>
@@ -4351,7 +4357,7 @@
         <v>51</v>
       </c>
       <c r="I131" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132">
@@ -4359,19 +4365,19 @@
         <v>51</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>24685.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F132" s="7" t="s">
-        <v>12</v>
+      <c r="F132" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>51</v>
@@ -4380,7 +4386,7 @@
         <v>51</v>
       </c>
       <c r="I132" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="133">
@@ -4388,19 +4394,19 @@
         <v>51</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>3128.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F133" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G133" s="8" t="s">
         <v>51</v>
@@ -4409,7 +4415,7 @@
         <v>51</v>
       </c>
       <c r="I133" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="134">
@@ -4417,19 +4423,19 @@
         <v>51</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>747712.0</v>
+        <v>794.0</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F134" s="7" t="n">
-        <v>16.0</v>
+        <v>13</v>
+      </c>
+      <c r="F134" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G134" s="8" t="s">
         <v>51</v>
@@ -4438,181 +4444,181 @@
         <v>51</v>
       </c>
       <c r="I134" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>3200.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F135" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I135" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>4379.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F136" s="7" t="s">
-        <v>12</v>
+      <c r="F136" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I136" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>172.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F137" s="7" t="s">
-        <v>12</v>
+      <c r="F137" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I137" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>456.0</v>
+        <v>199.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I138" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>407399.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>11.0</v>
+        <v>2.0</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I139" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>816.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F140" s="7" t="s">
-        <v>12</v>
+      <c r="F140" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="I140" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141">
@@ -4620,16 +4626,16 @@
         <v>52</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>283905.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F141" s="7" t="n">
         <v>6.0</v>
@@ -4641,7 +4647,7 @@
         <v>52</v>
       </c>
       <c r="I141" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142">
@@ -4649,19 +4655,19 @@
         <v>52</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1164.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F142" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>52</v>
@@ -4670,7 +4676,7 @@
         <v>52</v>
       </c>
       <c r="I142" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143">
@@ -4678,19 +4684,19 @@
         <v>52</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>5227.0</v>
+        <v>601.0</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F143" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G143" s="8" t="s">
         <v>52</v>
@@ -4699,7 +4705,7 @@
         <v>52</v>
       </c>
       <c r="I143" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144">
@@ -4707,19 +4713,19 @@
         <v>52</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>5727.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F144" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G144" s="8" t="s">
         <v>52</v>
@@ -4728,7 +4734,7 @@
         <v>52</v>
       </c>
       <c r="I144" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145">
@@ -4736,19 +4742,19 @@
         <v>52</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>28983.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F145" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>52</v>
@@ -4757,7 +4763,7 @@
         <v>52</v>
       </c>
       <c r="I145" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146">
@@ -4765,19 +4771,19 @@
         <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>952.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F146" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G146" s="8" t="s">
         <v>52</v>
@@ -4786,7 +4792,7 @@
         <v>52</v>
       </c>
       <c r="I146" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147">
@@ -4794,19 +4800,19 @@
         <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>512430.0</v>
+        <v>969.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>40.0</v>
+        <v>13</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>52</v>
@@ -4815,7 +4821,7 @@
         <v>52</v>
       </c>
       <c r="I147" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148">
@@ -4823,19 +4829,19 @@
         <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>325.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F148" s="7" t="s">
-        <v>12</v>
+      <c r="F148" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G148" s="8" t="s">
         <v>52</v>
@@ -4844,7 +4850,7 @@
         <v>52</v>
       </c>
       <c r="I148" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149">
@@ -4852,19 +4858,19 @@
         <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>13629.0</v>
+        <v>395.0</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F149" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>52</v>
@@ -4873,7 +4879,7 @@
         <v>52</v>
       </c>
       <c r="I149" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150">
@@ -4881,19 +4887,19 @@
         <v>52</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>1182.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F150" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>52</v>
@@ -4902,7 +4908,7 @@
         <v>52</v>
       </c>
       <c r="I150" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151">
@@ -4913,16 +4919,16 @@
         <v>10</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>1542.0</v>
+        <v>479.0</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F151" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>52</v>
@@ -4931,7 +4937,7 @@
         <v>52</v>
       </c>
       <c r="I151" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152">
@@ -4939,19 +4945,19 @@
         <v>52</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>5147.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>52</v>
@@ -4960,7 +4966,7 @@
         <v>52</v>
       </c>
       <c r="I152" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153">
@@ -4968,19 +4974,19 @@
         <v>52</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>728.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F153" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>52</v>
@@ -4989,7 +4995,7 @@
         <v>52</v>
       </c>
       <c r="I153" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="154">
@@ -4997,19 +5003,19 @@
         <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>197.0</v>
+        <v>70.0</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F154" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>52</v>
@@ -5018,210 +5024,210 @@
         <v>52</v>
       </c>
       <c r="I154" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>506367.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F155" s="7" t="n">
-        <v>16.0</v>
+        <v>13</v>
+      </c>
+      <c r="F155" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I155" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>85.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E156" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F156" s="7" t="s">
-        <v>12</v>
+      <c r="F156" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I156" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>939.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F157" s="7" t="s">
-        <v>12</v>
+      <c r="F157" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>486.0</v>
+        <v>451.0</v>
       </c>
       <c r="E158" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F158" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I158" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>292130.0</v>
+        <v>526.0</v>
       </c>
       <c r="E159" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F159" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F159" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I159" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>1186.0</v>
+        <v>806692.0</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F160" s="7" t="s">
-        <v>12</v>
+      <c r="F160" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I160" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>1502.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F161" s="7" t="s">
-        <v>12</v>
+      <c r="F161" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I161" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162">
@@ -5229,19 +5235,19 @@
         <v>53</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>146.0</v>
+        <v>571.0</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F162" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>53</v>
@@ -5250,7 +5256,7 @@
         <v>53</v>
       </c>
       <c r="I162" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163">
@@ -5258,19 +5264,19 @@
         <v>53</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>23967.0</v>
+        <v>344.0</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F163" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>53</v>
@@ -5279,7 +5285,7 @@
         <v>53</v>
       </c>
       <c r="I163" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164">
@@ -5287,19 +5293,19 @@
         <v>53</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>74515.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F164" s="7" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>53</v>
@@ -5308,7 +5314,7 @@
         <v>53</v>
       </c>
       <c r="I164" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="165">
@@ -5316,19 +5322,19 @@
         <v>53</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>99098.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F165" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>53</v>
@@ -5337,7 +5343,7 @@
         <v>53</v>
       </c>
       <c r="I165" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="166">
@@ -5345,19 +5351,19 @@
         <v>53</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>2825.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F166" s="7" t="s">
-        <v>12</v>
+      <c r="F166" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>53</v>
@@ -5366,7 +5372,7 @@
         <v>53</v>
       </c>
       <c r="I166" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="167">
@@ -5374,19 +5380,19 @@
         <v>53</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>356.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F167" s="7" t="s">
-        <v>12</v>
+      <c r="F167" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>53</v>
@@ -5395,7 +5401,7 @@
         <v>53</v>
       </c>
       <c r="I167" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="168">
@@ -5403,19 +5409,19 @@
         <v>53</v>
       </c>
       <c r="B168" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C168" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C168" s="5" t="s">
-        <v>16</v>
-      </c>
       <c r="D168" s="6" t="n">
-        <v>28978.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F168" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>53</v>
@@ -5424,7 +5430,7 @@
         <v>53</v>
       </c>
       <c r="I168" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="169">
@@ -5432,19 +5438,19 @@
         <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>4020.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F169" s="7" t="s">
-        <v>12</v>
+      <c r="F169" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>53</v>
@@ -5453,7 +5459,7 @@
         <v>53</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
@@ -5461,19 +5467,19 @@
         <v>53</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>13942.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F170" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>53</v>
@@ -5482,7 +5488,7 @@
         <v>53</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="171">
@@ -5490,19 +5496,19 @@
         <v>53</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>773114.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F171" s="7" t="n">
-        <v>31.0</v>
+        <v>13</v>
+      </c>
+      <c r="F171" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G171" s="8" t="s">
         <v>53</v>
@@ -5511,7 +5517,7 @@
         <v>53</v>
       </c>
       <c r="I171" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="172">
@@ -5519,19 +5525,19 @@
         <v>53</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>1274.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F172" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G172" s="8" t="s">
         <v>53</v>
@@ -5540,7 +5546,7 @@
         <v>53</v>
       </c>
       <c r="I172" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="173">
@@ -5548,19 +5554,19 @@
         <v>53</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>17807.0</v>
+        <v>172.0</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F173" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>53</v>
@@ -5569,7 +5575,7 @@
         <v>53</v>
       </c>
       <c r="I173" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="174">
@@ -5577,19 +5583,19 @@
         <v>53</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>17054.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F174" s="7" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G174" s="8" t="s">
         <v>53</v>
@@ -5598,7 +5604,7 @@
         <v>53</v>
       </c>
       <c r="I174" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="175">
@@ -5606,19 +5612,19 @@
         <v>53</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>252920.0</v>
+        <v>816.0</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F175" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>53</v>
@@ -5627,7 +5633,7 @@
         <v>53</v>
       </c>
       <c r="I175" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="176">
@@ -5638,16 +5644,16 @@
         <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>7147.0</v>
+        <v>456.0</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F176" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>53</v>
@@ -5656,413 +5662,413 @@
         <v>53</v>
       </c>
       <c r="I176" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>18799.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E177" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F177" s="7" t="s">
-        <v>12</v>
+      <c r="F177" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I177" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>26497.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F178" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>1685.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F179" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F179" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I179" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>12137.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F180" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I180" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C181" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>394262.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F181" s="7" t="n">
-        <v>7.0</v>
+        <v>13</v>
+      </c>
+      <c r="F181" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I181" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>11734.0</v>
+        <v>952.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F182" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>42880.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F183" s="7" t="s">
-        <v>12</v>
+      <c r="F183" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I183" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C184" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>1644.0</v>
+        <v>325.0</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F184" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I184" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>28</v>
+        <v>15</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>477111.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F185" s="7" t="n">
-        <v>13.0</v>
+        <v>13</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>5285.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F186" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I186" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>5788.0</v>
+        <v>197.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F187" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H187" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I187" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>26146.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F188" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>14588.0</v>
+        <v>486.0</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F189" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H189" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I189" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>280988.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F190" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H190" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I190" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="191">
@@ -6070,19 +6076,19 @@
         <v>54</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>23841.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F191" s="7" t="s">
-        <v>12</v>
+      <c r="F191" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>54</v>
@@ -6091,7 +6097,7 @@
         <v>54</v>
       </c>
       <c r="I191" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="192">
@@ -6099,19 +6105,19 @@
         <v>54</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>199153.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E192" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F192" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F192" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G192" s="8" t="s">
         <v>54</v>
@@ -6120,7 +6126,7 @@
         <v>54</v>
       </c>
       <c r="I192" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
@@ -6128,19 +6134,19 @@
         <v>54</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>20617.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E193" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F193" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G193" s="8" t="s">
         <v>54</v>
@@ -6149,7 +6155,7 @@
         <v>54</v>
       </c>
       <c r="I193" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="194">
@@ -6157,19 +6163,19 @@
         <v>54</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>38558.0</v>
+        <v>939.0</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F194" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F194" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>54</v>
@@ -6178,7 +6184,7 @@
         <v>54</v>
       </c>
       <c r="I194" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="195">
@@ -6186,19 +6192,19 @@
         <v>54</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>126418.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F195" s="7" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>54</v>
@@ -6207,7 +6213,7 @@
         <v>54</v>
       </c>
       <c r="I195" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="196">
@@ -6215,19 +6221,19 @@
         <v>54</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>2200.0</v>
+        <v>728.0</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F196" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>54</v>
@@ -6236,7 +6242,7 @@
         <v>54</v>
       </c>
       <c r="I196" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="197">
@@ -6244,19 +6250,19 @@
         <v>54</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>35873.0</v>
+        <v>85.0</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F197" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>54</v>
@@ -6265,674 +6271,1718 @@
         <v>54</v>
       </c>
       <c r="I197" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>16744.0</v>
+        <v>356.0</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F198" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I198" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>32194.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F199" s="7" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I199" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C200" s="5" t="s">
         <v>35</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>542175.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E200" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F200" s="7" t="n">
-        <v>9.0</v>
+        <v>13</v>
+      </c>
+      <c r="F200" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I200" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>274584.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F201" s="7" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I201" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>35692.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F202" s="7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I202" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>30762.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F203" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I203" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>19972.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F204" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I204" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>36976.0</v>
+        <v>146.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F205" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I205" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>74182.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F206" s="7" t="s">
-        <v>12</v>
+      <c r="F206" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I206" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>277603.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F207" s="7" t="n">
-        <v>12.0</v>
+        <v>31.0</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I207" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>61232.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I208" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>64701.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F209" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I209" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>6327.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F210" s="7" t="s">
-        <v>12</v>
+      <c r="F210" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I210" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>173630.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="F211" s="7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I211" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>171789.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F212" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I212" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>80351.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F213" s="7" t="s">
-        <v>12</v>
+      <c r="F213" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H213" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I213" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>26014.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F214" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I214" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>8810.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F215" s="7" t="s">
-        <v>12</v>
+      <c r="F215" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I215" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>2368.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F216" s="7" t="s">
-        <v>12</v>
+      <c r="F216" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I216" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>28702.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F217" s="7" t="s">
-        <v>12</v>
+      <c r="F217" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I217" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>247735.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F218" s="7" t="n">
-        <v>10.0</v>
+        <v>13</v>
+      </c>
+      <c r="F218" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H218" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I218" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>15987.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F219" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I219" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B220" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C220" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D220" s="6" t="n">
+        <v>7147.0</v>
+      </c>
+      <c r="E220" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G220" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H220" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I220" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C221" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D221" s="6" t="n">
+        <v>26497.0</v>
+      </c>
+      <c r="E221" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G221" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H221" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I221" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C222" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D222" s="6" t="n">
+        <v>477111.0</v>
+      </c>
+      <c r="E222" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F222" s="7" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="G222" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H222" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I222" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D223" s="6" t="n">
+        <v>5285.0</v>
+      </c>
+      <c r="E223" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G223" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H223" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I223" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D224" s="6" t="n">
+        <v>5788.0</v>
+      </c>
+      <c r="E224" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G224" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H224" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I224" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C225" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D225" s="6" t="n">
+        <v>26146.0</v>
+      </c>
+      <c r="E225" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G225" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H225" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I225" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D226" s="6" t="n">
+        <v>14588.0</v>
+      </c>
+      <c r="E226" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F226" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G226" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="H226" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I226" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C227" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D227" s="6" t="n">
+        <v>23841.0</v>
+      </c>
+      <c r="E227" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F227" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G227" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H227" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I227" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C228" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D228" s="6" t="n">
+        <v>199153.0</v>
+      </c>
+      <c r="E228" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F228" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G228" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H228" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I228" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C229" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D229" s="6" t="n">
+        <v>20617.0</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G229" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H229" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I229" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C230" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D230" s="6" t="n">
+        <v>38558.0</v>
+      </c>
+      <c r="E230" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F230" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G230" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H230" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I230" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C231" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D231" s="6" t="n">
+        <v>126418.0</v>
+      </c>
+      <c r="E231" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F231" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G231" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H231" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I231" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D232" s="6" t="n">
+        <v>2200.0</v>
+      </c>
+      <c r="E232" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H232" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I232" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>35873.0</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H233" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I233" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D234" s="6" t="n">
+        <v>16744.0</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H234" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D235" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H235" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I235" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D236" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F236" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H236" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D237" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E237" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F237" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H237" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I237" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D238" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E238" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F238" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H238" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I238" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D239" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H239" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I239" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D240" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E240" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H240" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D241" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E241" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H241" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I241" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D242" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E242" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F242" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H242" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I242" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C243" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C220" s="5" t="s">
+      <c r="D243" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E243" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F243" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G243" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H243" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I243" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D244" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E244" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F244" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G244" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H244" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I244" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D245" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E245" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H245" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I245" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D246" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E246" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H246" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I246" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D247" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E247" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H247" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I247" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D248" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E248" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F248" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H248" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D249" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E249" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F249" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H249" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I249" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D250" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E250" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H250" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I250" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D251" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F251" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H251" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I251" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D252" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E252" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H252" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I252" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C253" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D220" s="6" t="n">
+      <c r="D253" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E253" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H253" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I253" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D254" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E254" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F254" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H254" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D255" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E255" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F255" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H255" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I255" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D256" s="6" t="n">
         <v>48163.0</v>
       </c>
-      <c r="E220" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F220" s="7" t="n">
+      <c r="E256" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F256" s="7" t="n">
         <v>1.0</v>
       </c>
-      <c r="G220" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="H220" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="I220" s="7" t="s">
-        <v>12</v>
+      <c r="G256" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="H256" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1952" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2155" uniqueCount="58">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-08-17</t>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t>120253058581610341</t>
@@ -56,31 +56,37 @@
     <t/>
   </si>
   <si>
-    <t>120253031332440341</t>
+    <t>120253028817940341</t>
   </si>
   <si>
-    <t>120253031332470341</t>
+    <t>120253028817970341</t>
   </si>
   <si>
     <t>120253023460500341</t>
   </si>
   <si>
-    <t>120253023954760341</t>
+    <t>120253023954750341</t>
   </si>
   <si>
-    <t>120253028817940341</t>
+    <t>120253023954770341</t>
+  </si>
+  <si>
+    <t>120253023954790341</t>
   </si>
   <si>
     <t>120253028817950341</t>
   </si>
   <si>
+    <t>120253028817960341</t>
+  </si>
+  <si>
+    <t>120253023954760341</t>
+  </si>
+  <si>
     <t>120253028817980341</t>
   </si>
   <si>
-    <t>120253031332460341</t>
-  </si>
-  <si>
-    <t>120253023954770341</t>
+    <t>120253031332440341</t>
   </si>
   <si>
     <t>120253031332480341</t>
@@ -92,46 +98,58 @@
     <t>120253031402030341</t>
   </si>
   <si>
+    <t>120253031402040341</t>
+  </si>
+  <si>
+    <t>120253031332470341</t>
+  </si>
+  <si>
+    <t>2026-08-17</t>
+  </si>
+  <si>
+    <t>120253023954820341</t>
+  </si>
+  <si>
+    <t>120253023954810341</t>
+  </si>
+  <si>
+    <t>120253023954780341</t>
+  </si>
+  <si>
+    <t>120253023954740341</t>
+  </si>
+  <si>
+    <t>120253023460490341</t>
+  </si>
+  <si>
+    <t>120253028818100341</t>
+  </si>
+  <si>
+    <t>120253031332460341</t>
+  </si>
+  <si>
     <t>120253031402050341</t>
+  </si>
+  <si>
+    <t>120253058581640341</t>
   </si>
   <si>
     <t>120253058581620341</t>
   </si>
   <si>
-    <t>2026-08-16</t>
+    <t>120253058581660341</t>
   </si>
   <si>
-    <t>120253023954740341</t>
+    <t>120253031332490341</t>
   </si>
   <si>
-    <t>120253023954750341</t>
-  </si>
-  <si>
-    <t>120253023954790341</t>
+    <t>2026-08-16</t>
   </si>
   <si>
     <t>120253023954800341</t>
   </si>
   <si>
-    <t>120253023954820341</t>
-  </si>
-  <si>
-    <t>120253028817960341</t>
-  </si>
-  <si>
-    <t>120253028817970341</t>
-  </si>
-  <si>
-    <t>120253023954780341</t>
-  </si>
-  <si>
     <t>120253031332450341</t>
-  </si>
-  <si>
-    <t>120253058581640341</t>
-  </si>
-  <si>
-    <t>120253031402040341</t>
   </si>
   <si>
     <t>120253058581630341</t>
@@ -140,25 +158,10 @@
     <t>120253031402010341</t>
   </si>
   <si>
-    <t>120253031332490341</t>
-  </si>
-  <si>
     <t>2026-08-15</t>
   </si>
   <si>
-    <t>120253023954810341</t>
-  </si>
-  <si>
-    <t>120253028818100341</t>
-  </si>
-  <si>
-    <t>120253058581660341</t>
-  </si>
-  <si>
     <t>2026-08-14</t>
-  </si>
-  <si>
-    <t>120253023460490341</t>
   </si>
   <si>
     <t>2026-08-13</t>
@@ -546,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I256"/>
+  <dimension ref="A1:I283"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -601,13 +604,13 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>56132.0</v>
+        <v>139757.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>9</v>
@@ -630,7 +633,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>158.0</v>
+        <v>3533.0</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
@@ -659,13 +662,13 @@
         <v>17</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>79231.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -682,19 +685,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="5" t="s">
-        <v>19</v>
-      </c>
       <c r="D5" s="6" t="n">
-        <v>15684.0</v>
+        <v>85513.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F5" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -711,19 +714,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>85947.0</v>
+        <v>4442.0</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -743,16 +746,16 @@
         <v>14</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>612.0</v>
+        <v>38972.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -769,19 +772,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>37284.0</v>
+        <v>536.0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -798,19 +801,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>16486.0</v>
+        <v>80503.0</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
@@ -830,16 +833,16 @@
         <v>14</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>601.0</v>
+        <v>117214.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -856,19 +859,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>64289.0</v>
+        <v>10276.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -885,13 +888,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>623.0</v>
+        <v>12472.0</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
@@ -914,19 +917,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>945.0</v>
+        <v>133611.0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -940,28 +943,28 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="D14" s="6" t="n">
-        <v>357870.0</v>
+        <v>10207.0</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" s="7" t="n">
-        <v>9.0</v>
+        <v>13</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>13</v>
@@ -969,16 +972,16 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>2527.0</v>
+        <v>19172.0</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
@@ -987,10 +990,10 @@
         <v>1.0</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>13</v>
@@ -998,28 +1001,28 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G16" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="6" t="n">
-        <v>6618.0</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>28</v>
-      </c>
       <c r="H16" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>13</v>
@@ -1027,28 +1030,28 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>637081.0</v>
+        <v>7046.0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F17" s="7" t="n">
-        <v>20.0</v>
+        <v>13</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>13</v>
@@ -1056,28 +1059,28 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>243818.0</v>
+        <v>135942.0</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>13</v>
@@ -1085,7 +1088,7 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>16</v>
@@ -1094,7 +1097,7 @@
         <v>31</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>10198.0</v>
+        <v>147.0</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
@@ -1103,10 +1106,10 @@
         <v>13</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>13</v>
@@ -1114,7 +1117,7 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>16</v>
@@ -1123,7 +1126,7 @@
         <v>32</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>285.0</v>
+        <v>272.0</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
@@ -1132,10 +1135,10 @@
         <v>13</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>13</v>
@@ -1143,16 +1146,16 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>383.0</v>
+        <v>428.0</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
@@ -1161,10 +1164,10 @@
         <v>13</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>13</v>
@@ -1172,28 +1175,28 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>24684.0</v>
+        <v>1979.0</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>13</v>
@@ -1201,28 +1204,28 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B23" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>34</v>
-      </c>
       <c r="D23" s="6" t="n">
-        <v>11414.0</v>
+        <v>363600.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>13</v>
@@ -1230,16 +1233,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>8877.0</v>
+        <v>311.0</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
@@ -1248,10 +1251,10 @@
         <v>13</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>13</v>
@@ -1259,16 +1262,16 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>18.0</v>
+        <v>3882.0</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>13</v>
@@ -1277,10 +1280,10 @@
         <v>13</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>13</v>
@@ -1288,28 +1291,28 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>173.0</v>
+        <v>24918.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>13</v>
@@ -1317,28 +1320,28 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>699278.0</v>
+        <v>284309.0</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>13</v>
@@ -1346,28 +1349,28 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>384424.0</v>
+        <v>468648.0</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>13</v>
@@ -1375,16 +1378,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>2068.0</v>
+        <v>1815.0</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>13</v>
@@ -1393,10 +1396,10 @@
         <v>13</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>13</v>
@@ -1404,16 +1407,16 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>12206.0</v>
+        <v>1703.0</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>13</v>
@@ -1422,10 +1425,10 @@
         <v>13</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>13</v>
@@ -1433,16 +1436,16 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>772.0</v>
+        <v>7120.0</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>13</v>
@@ -1451,10 +1454,10 @@
         <v>13</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>13</v>
@@ -1462,28 +1465,28 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>31361.0</v>
+        <v>499768.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>13</v>
@@ -1491,16 +1494,16 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>212.0</v>
+        <v>11591.0</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>13</v>
@@ -1509,10 +1512,10 @@
         <v>13</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>13</v>
@@ -1520,16 +1523,16 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>295.0</v>
+        <v>945.0</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>13</v>
@@ -1538,10 +1541,10 @@
         <v>13</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>13</v>
@@ -1549,28 +1552,28 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>42524.0</v>
+        <v>3047.0</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>13</v>
@@ -1578,28 +1581,28 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="5" t="s">
-        <v>15</v>
-      </c>
       <c r="D36" s="6" t="n">
-        <v>18008.0</v>
+        <v>3904.0</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>13</v>
@@ -1607,16 +1610,16 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>392.0</v>
+        <v>167925.0</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>13</v>
@@ -1625,10 +1628,10 @@
         <v>13</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>13</v>
@@ -1636,28 +1639,28 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>336995.0</v>
+        <v>87472.0</v>
       </c>
       <c r="E38" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F38" s="7" t="n">
-        <v>14.0</v>
+        <v>4.0</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>13</v>
@@ -1665,16 +1668,16 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>17276.0</v>
+        <v>3746.0</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>13</v>
@@ -1683,10 +1686,10 @@
         <v>13</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>13</v>
@@ -1694,28 +1697,28 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>435991.0</v>
+        <v>712230.0</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>12.0</v>
+        <v>6.0</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>13</v>
@@ -1729,10 +1732,10 @@
         <v>16</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>5248.0</v>
+        <v>285.0</v>
       </c>
       <c r="E41" s="7" t="s">
         <v>13</v>
@@ -1755,13 +1758,13 @@
         <v>43</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>650.0</v>
+        <v>11414.0</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>13</v>
@@ -1784,19 +1787,19 @@
         <v>43</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>19816.0</v>
+        <v>24684.0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G43" s="8" t="s">
         <v>43</v>
@@ -1813,19 +1816,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>317924.0</v>
+        <v>383.0</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F44" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G44" s="8" t="s">
         <v>43</v>
@@ -1842,19 +1845,19 @@
         <v>43</v>
       </c>
       <c r="B45" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C45" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="D45" s="6" t="n">
-        <v>819.0</v>
+        <v>244115.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G45" s="8" t="s">
         <v>43</v>
@@ -1871,13 +1874,13 @@
         <v>43</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>4802.0</v>
+        <v>10198.0</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>13</v>
@@ -1900,13 +1903,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>1439.0</v>
+        <v>18.0</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>13</v>
@@ -1929,19 +1932,19 @@
         <v>43</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>29578.0</v>
+        <v>638501.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G48" s="8" t="s">
         <v>43</v>
@@ -1958,19 +1961,19 @@
         <v>43</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>853298.0</v>
+        <v>6618.0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>27.0</v>
+        <v>13</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G49" s="8" t="s">
         <v>43</v>
@@ -1990,16 +1993,16 @@
         <v>14</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>2548.0</v>
+        <v>358088.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G50" s="8" t="s">
         <v>43</v>
@@ -2016,19 +2019,19 @@
         <v>43</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>5801.0</v>
+        <v>2527.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G51" s="8" t="s">
         <v>43</v>
@@ -2045,13 +2048,13 @@
         <v>43</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>1044.0</v>
+        <v>8877.0</v>
       </c>
       <c r="E52" s="7" t="s">
         <v>13</v>
@@ -2074,19 +2077,19 @@
         <v>43</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>401629.0</v>
+        <v>18008.0</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G53" s="8" t="s">
         <v>43</v>
@@ -2103,13 +2106,13 @@
         <v>43</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>772.0</v>
+        <v>173.0</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>13</v>
@@ -2132,13 +2135,13 @@
         <v>43</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>4237.0</v>
+        <v>12318.0</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>13</v>
@@ -2158,16 +2161,16 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>228.0</v>
+        <v>392.0</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>13</v>
@@ -2176,10 +2179,10 @@
         <v>13</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>13</v>
@@ -2187,28 +2190,28 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>22960.0</v>
+        <v>2068.0</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>13</v>
@@ -2216,16 +2219,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>3988.0</v>
+        <v>772.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>13</v>
@@ -2234,10 +2237,10 @@
         <v>13</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>13</v>
@@ -2245,28 +2248,28 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>742.0</v>
+        <v>384990.0</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>13</v>
@@ -2274,28 +2277,28 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>8213.0</v>
+        <v>703357.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>18.0</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>13</v>
@@ -2303,28 +2306,28 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>462054.0</v>
+        <v>31421.0</v>
       </c>
       <c r="E61" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>13</v>
@@ -2332,28 +2335,28 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C62" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B62" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="D62" s="6" t="n">
-        <v>378946.0</v>
+        <v>212.0</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="7" t="n">
-        <v>12.0</v>
+        <v>13</v>
+      </c>
+      <c r="F62" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>13</v>
@@ -2361,16 +2364,16 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>2170.0</v>
+        <v>295.0</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>13</v>
@@ -2379,10 +2382,10 @@
         <v>13</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>13</v>
@@ -2390,28 +2393,28 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>14351.0</v>
+        <v>42524.0</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>13</v>
@@ -2419,28 +2422,28 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>324526.0</v>
+        <v>17276.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>13</v>
@@ -2448,28 +2451,28 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>14457.0</v>
+        <v>336995.0</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>13</v>
@@ -2477,28 +2480,28 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>5324.0</v>
+        <v>435991.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>13</v>
@@ -2506,16 +2509,16 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>1625.0</v>
+        <v>5248.0</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>13</v>
@@ -2524,10 +2527,10 @@
         <v>13</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>13</v>
@@ -2535,28 +2538,28 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>696176.0</v>
+        <v>650.0</v>
       </c>
       <c r="E69" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F69" s="7" t="n">
-        <v>12.0</v>
+        <v>13</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I69" s="7" t="s">
         <v>13</v>
@@ -2564,28 +2567,28 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>445496.0</v>
+        <v>19816.0</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>13</v>
@@ -2593,28 +2596,28 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>3011.0</v>
+        <v>317924.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F71" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>13</v>
@@ -2622,16 +2625,16 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>8383.0</v>
+        <v>819.0</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>13</v>
@@ -2640,10 +2643,10 @@
         <v>13</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>13</v>
@@ -2651,16 +2654,16 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>385.0</v>
+        <v>4802.0</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>13</v>
@@ -2669,10 +2672,10 @@
         <v>13</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>13</v>
@@ -2680,28 +2683,28 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>51544.0</v>
+        <v>4237.0</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>13</v>
@@ -2709,16 +2712,16 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>2238.0</v>
+        <v>29578.0</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>13</v>
@@ -2727,10 +2730,10 @@
         <v>13</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>13</v>
@@ -2738,16 +2741,16 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="D76" s="6" t="n">
-        <v>4481.0</v>
+        <v>1439.0</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>13</v>
@@ -2756,10 +2759,10 @@
         <v>13</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I76" s="7" t="s">
         <v>13</v>
@@ -2767,28 +2770,28 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>412.0</v>
+        <v>853298.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>27.0</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I77" s="7" t="s">
         <v>13</v>
@@ -2796,28 +2799,28 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>17021.0</v>
+        <v>2548.0</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I78" s="7" t="s">
         <v>13</v>
@@ -2825,28 +2828,28 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>893824.0</v>
+        <v>5801.0</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>24.0</v>
+        <v>13</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>13</v>
@@ -2854,16 +2857,16 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>5377.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>13</v>
@@ -2872,10 +2875,10 @@
         <v>13</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>13</v>
@@ -2883,28 +2886,28 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>1498.0</v>
+        <v>401629.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F81" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F81" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>13</v>
@@ -2912,28 +2915,28 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>43627.0</v>
+        <v>772.0</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F82" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>13</v>
@@ -2944,13 +2947,13 @@
         <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>5765.0</v>
+        <v>228.0</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>13</v>
@@ -2973,19 +2976,19 @@
         <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C84" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>379038.0</v>
+        <v>22960.0</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F84" s="7" t="n">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>49</v>
@@ -3002,19 +3005,19 @@
         <v>49</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>3659.0</v>
+        <v>3988.0</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>49</v>
@@ -3031,13 +3034,13 @@
         <v>49</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>7279.0</v>
+        <v>742.0</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>13</v>
@@ -3060,13 +3063,13 @@
         <v>49</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>12172.0</v>
+        <v>8213.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>13</v>
@@ -3089,19 +3092,19 @@
         <v>49</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>1563.0</v>
+        <v>462054.0</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F88" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F88" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G88" s="8" t="s">
         <v>49</v>
@@ -3118,19 +3121,19 @@
         <v>49</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>2256.0</v>
+        <v>378946.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>49</v>
@@ -3147,13 +3150,13 @@
         <v>49</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>3472.0</v>
+        <v>2170.0</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>13</v>
@@ -3176,19 +3179,19 @@
         <v>49</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>1293.0</v>
+        <v>14351.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F91" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F91" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G91" s="8" t="s">
         <v>49</v>
@@ -3205,13 +3208,13 @@
         <v>49</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>378762.0</v>
+        <v>324526.0</v>
       </c>
       <c r="E92" s="7" t="s">
         <v>12</v>
@@ -3237,10 +3240,10 @@
         <v>14</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>5104.0</v>
+        <v>14457.0</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>13</v>
@@ -3266,16 +3269,16 @@
         <v>14</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>935238.0</v>
+        <v>1625.0</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>20.0</v>
+        <v>13</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G94" s="8" t="s">
         <v>49</v>
@@ -3292,13 +3295,13 @@
         <v>49</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>76.0</v>
+        <v>385.0</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>13</v>
@@ -3318,28 +3321,28 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>353476.0</v>
+        <v>5324.0</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>14.0</v>
+        <v>13</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>13</v>
@@ -3347,16 +3350,16 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>2939.0</v>
+        <v>4481.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>13</v>
@@ -3365,10 +3368,10 @@
         <v>13</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I97" s="7" t="s">
         <v>13</v>
@@ -3376,16 +3379,16 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>15807.0</v>
+        <v>2238.0</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>13</v>
@@ -3394,10 +3397,10 @@
         <v>13</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>13</v>
@@ -3405,16 +3408,16 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>25848.0</v>
+        <v>51544.0</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>12</v>
@@ -3423,10 +3426,10 @@
         <v>1.0</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>13</v>
@@ -3434,28 +3437,28 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>700185.0</v>
+        <v>696176.0</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F100" s="7" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I100" s="7" t="s">
         <v>13</v>
@@ -3463,16 +3466,16 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>3888.0</v>
+        <v>8383.0</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>13</v>
@@ -3481,10 +3484,10 @@
         <v>13</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I101" s="7" t="s">
         <v>13</v>
@@ -3492,16 +3495,16 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>290.0</v>
+        <v>3011.0</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>13</v>
@@ -3510,10 +3513,10 @@
         <v>13</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>13</v>
@@ -3521,16 +3524,16 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>16525.0</v>
+        <v>412.0</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>13</v>
@@ -3539,10 +3542,10 @@
         <v>13</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>13</v>
@@ -3550,28 +3553,28 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>25346.0</v>
+        <v>445496.0</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F104" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>13</v>
@@ -3582,19 +3585,19 @@
         <v>50</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>383981.0</v>
+        <v>5765.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G105" s="8" t="s">
         <v>50</v>
@@ -3611,19 +3614,19 @@
         <v>50</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C106" s="5" t="s">
         <v>45</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>7643.0</v>
+        <v>3659.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F106" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F106" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>50</v>
@@ -3643,16 +3646,16 @@
         <v>14</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>33363.0</v>
+        <v>379038.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>50</v>
@@ -3669,13 +3672,13 @@
         <v>50</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>9025.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>12</v>
@@ -3701,16 +3704,16 @@
         <v>14</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>697336.0</v>
+        <v>43627.0</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>10.0</v>
+        <v>2.0</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>50</v>
@@ -3727,19 +3730,19 @@
         <v>50</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>6325.0</v>
+        <v>893824.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>50</v>
@@ -3756,13 +3759,13 @@
         <v>50</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>3642.0</v>
+        <v>1498.0</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>13</v>
@@ -3785,13 +3788,13 @@
         <v>50</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>7174.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>13</v>
@@ -3814,13 +3817,13 @@
         <v>50</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>2276.0</v>
+        <v>7279.0</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>13</v>
@@ -3843,19 +3846,19 @@
         <v>50</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>20739.0</v>
+        <v>1293.0</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>50</v>
@@ -3869,16 +3872,16 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>2029.0</v>
+        <v>1563.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>13</v>
@@ -3887,10 +3890,10 @@
         <v>13</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I115" s="7" t="s">
         <v>13</v>
@@ -3898,16 +3901,16 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>2673.0</v>
+        <v>76.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>13</v>
@@ -3916,10 +3919,10 @@
         <v>13</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>13</v>
@@ -3927,28 +3930,28 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>282217.0</v>
+        <v>935238.0</v>
       </c>
       <c r="E117" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F117" s="7" t="n">
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>13</v>
@@ -3956,16 +3959,16 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>889.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>13</v>
@@ -3974,10 +3977,10 @@
         <v>13</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>13</v>
@@ -3985,16 +3988,16 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>21813.0</v>
+        <v>2256.0</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>13</v>
@@ -4003,10 +4006,10 @@
         <v>13</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>13</v>
@@ -4014,16 +4017,16 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>324.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>13</v>
@@ -4032,10 +4035,10 @@
         <v>13</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>13</v>
@@ -4043,28 +4046,28 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>633.0</v>
+        <v>378762.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I121" s="7" t="s">
         <v>13</v>
@@ -4072,16 +4075,16 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>70.0</v>
+        <v>12172.0</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>13</v>
@@ -4090,10 +4093,10 @@
         <v>13</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I122" s="7" t="s">
         <v>13</v>
@@ -4107,10 +4110,10 @@
         <v>14</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>2220.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>13</v>
@@ -4133,19 +4136,19 @@
         <v>51</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>621293.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F124" s="7" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>51</v>
@@ -4162,19 +4165,19 @@
         <v>51</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>7945.0</v>
+        <v>700185.0</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G125" s="8" t="s">
         <v>51</v>
@@ -4191,19 +4194,19 @@
         <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>357571.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F126" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F126" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G126" s="8" t="s">
         <v>51</v>
@@ -4220,19 +4223,19 @@
         <v>51</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>100569.0</v>
+        <v>290.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>51</v>
@@ -4249,13 +4252,13 @@
         <v>51</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>46118.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>13</v>
@@ -4278,19 +4281,19 @@
         <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>928.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F129" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F129" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>51</v>
@@ -4307,19 +4310,19 @@
         <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>3290.0</v>
+        <v>353476.0</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F130" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F130" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G130" s="8" t="s">
         <v>51</v>
@@ -4336,19 +4339,19 @@
         <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>480911.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="7" t="n">
-        <v>14.0</v>
+        <v>13</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>51</v>
@@ -4365,19 +4368,19 @@
         <v>51</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>83588.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>51</v>
@@ -4394,13 +4397,13 @@
         <v>51</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>1474.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>13</v>
@@ -4423,19 +4426,19 @@
         <v>51</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>794.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F134" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G134" s="8" t="s">
         <v>51</v>
@@ -4449,28 +4452,28 @@
     </row>
     <row r="135">
       <c r="A135" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>5812.0</v>
+        <v>697336.0</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G135" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H135" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I135" s="7" t="s">
         <v>13</v>
@@ -4478,28 +4481,28 @@
     </row>
     <row r="136">
       <c r="A136" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>112476.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F136" s="7" t="n">
-        <v>4.0</v>
+        <v>13</v>
+      </c>
+      <c r="F136" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G136" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H136" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I136" s="7" t="s">
         <v>13</v>
@@ -4507,28 +4510,28 @@
     </row>
     <row r="137">
       <c r="A137" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>730436.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" s="7" t="n">
-        <v>24.0</v>
+        <v>13</v>
+      </c>
+      <c r="F137" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G137" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H137" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I137" s="7" t="s">
         <v>13</v>
@@ -4536,28 +4539,28 @@
     </row>
     <row r="138">
       <c r="A138" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>199.0</v>
+        <v>383981.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F138" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G138" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H138" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I138" s="7" t="s">
         <v>13</v>
@@ -4565,28 +4568,28 @@
     </row>
     <row r="139">
       <c r="A139" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>58187.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F139" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F139" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G139" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H139" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I139" s="7" t="s">
         <v>13</v>
@@ -4594,28 +4597,28 @@
     </row>
     <row r="140">
       <c r="A140" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>131368.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F140" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G140" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H140" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I140" s="7" t="s">
         <v>13</v>
@@ -4623,28 +4626,28 @@
     </row>
     <row r="141">
       <c r="A141" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>218816.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F141" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G141" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H141" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I141" s="7" t="s">
         <v>13</v>
@@ -4655,19 +4658,19 @@
         <v>52</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>3911.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F142" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>52</v>
@@ -4684,13 +4687,13 @@
         <v>52</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>601.0</v>
+        <v>928.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>13</v>
@@ -4713,13 +4716,13 @@
         <v>52</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>1812.0</v>
+        <v>633.0</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>13</v>
@@ -4742,13 +4745,13 @@
         <v>52</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>33241.0</v>
+        <v>794.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>13</v>
@@ -4771,13 +4774,13 @@
         <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>15780.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>13</v>
@@ -4800,19 +4803,19 @@
         <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>969.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>52</v>
@@ -4829,13 +4832,13 @@
         <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>637424.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4858,13 +4861,13 @@
         <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>395.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E149" s="7" t="s">
         <v>13</v>
@@ -4890,16 +4893,16 @@
         <v>14</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>5851.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>52</v>
@@ -4916,13 +4919,13 @@
         <v>52</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>479.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>13</v>
@@ -4945,19 +4948,19 @@
         <v>52</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>386517.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>52</v>
@@ -4974,19 +4977,19 @@
         <v>52</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>4729.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F153" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F153" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>52</v>
@@ -5003,13 +5006,13 @@
         <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>70.0</v>
+        <v>889.0</v>
       </c>
       <c r="E154" s="7" t="s">
         <v>13</v>
@@ -5029,16 +5032,16 @@
     </row>
     <row r="155">
       <c r="A155" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>8605.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>13</v>
@@ -5047,10 +5050,10 @@
         <v>13</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>13</v>
@@ -5058,28 +5061,28 @@
     </row>
     <row r="156">
       <c r="A156" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>107118.0</v>
+        <v>324.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F156" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F156" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>13</v>
@@ -5087,28 +5090,28 @@
     </row>
     <row r="157">
       <c r="A157" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>51830.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E157" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F157" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F157" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>13</v>
@@ -5116,16 +5119,16 @@
     </row>
     <row r="158">
       <c r="A158" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>451.0</v>
+        <v>70.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>13</v>
@@ -5134,10 +5137,10 @@
         <v>13</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I158" s="7" t="s">
         <v>13</v>
@@ -5145,16 +5148,16 @@
     </row>
     <row r="159">
       <c r="A159" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>526.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>13</v>
@@ -5163,10 +5166,10 @@
         <v>13</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>13</v>
@@ -5174,28 +5177,28 @@
     </row>
     <row r="160">
       <c r="A160" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>806692.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F160" s="7" t="n">
-        <v>40.0</v>
+        <v>12.0</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>13</v>
@@ -5203,28 +5206,28 @@
     </row>
     <row r="161">
       <c r="A161" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>65819.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F161" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F161" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>13</v>
@@ -5235,19 +5238,19 @@
         <v>53</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>571.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F162" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>53</v>
@@ -5264,19 +5267,19 @@
         <v>53</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>344.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>53</v>
@@ -5293,19 +5296,19 @@
         <v>53</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C164" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>249629.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F164" s="7" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>53</v>
@@ -5322,13 +5325,13 @@
         <v>53</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>2994.0</v>
+        <v>199.0</v>
       </c>
       <c r="E165" s="7" t="s">
         <v>13</v>
@@ -5351,19 +5354,19 @@
         <v>53</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>747712.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F166" s="7" t="n">
-        <v>16.0</v>
+        <v>24.0</v>
       </c>
       <c r="G166" s="8" t="s">
         <v>53</v>
@@ -5380,19 +5383,19 @@
         <v>53</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>9408.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F167" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>53</v>
@@ -5409,13 +5412,13 @@
         <v>53</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>24685.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>13</v>
@@ -5438,19 +5441,19 @@
         <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>22093.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F169" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>53</v>
@@ -5467,13 +5470,13 @@
         <v>53</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>3128.0</v>
+        <v>601.0</v>
       </c>
       <c r="E170" s="7" t="s">
         <v>13</v>
@@ -5499,10 +5502,10 @@
         <v>14</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>3200.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>13</v>
@@ -5525,13 +5528,13 @@
         <v>53</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>4379.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>13</v>
@@ -5554,13 +5557,13 @@
         <v>53</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>172.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>13</v>
@@ -5583,19 +5586,19 @@
         <v>53</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>407399.0</v>
+        <v>70.0</v>
       </c>
       <c r="E174" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F174" s="7" t="n">
-        <v>11.0</v>
+        <v>13</v>
+      </c>
+      <c r="F174" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G174" s="8" t="s">
         <v>53</v>
@@ -5615,16 +5618,16 @@
         <v>10</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>816.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F175" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>53</v>
@@ -5644,10 +5647,10 @@
         <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>456.0</v>
+        <v>479.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>13</v>
@@ -5667,28 +5670,28 @@
     </row>
     <row r="177">
       <c r="A177" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>283905.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>6.0</v>
+        <v>13</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G177" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I177" s="7" t="s">
         <v>13</v>
@@ -5696,16 +5699,16 @@
     </row>
     <row r="178">
       <c r="A178" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>28983.0</v>
+        <v>395.0</v>
       </c>
       <c r="E178" s="7" t="s">
         <v>13</v>
@@ -5714,10 +5717,10 @@
         <v>13</v>
       </c>
       <c r="G178" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I178" s="7" t="s">
         <v>13</v>
@@ -5725,28 +5728,28 @@
     </row>
     <row r="179">
       <c r="A179" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>5227.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F179" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G179" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I179" s="7" t="s">
         <v>13</v>
@@ -5754,16 +5757,16 @@
     </row>
     <row r="180">
       <c r="A180" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>5727.0</v>
+        <v>969.0</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>13</v>
@@ -5772,10 +5775,10 @@
         <v>13</v>
       </c>
       <c r="G180" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I180" s="7" t="s">
         <v>13</v>
@@ -5783,16 +5786,16 @@
     </row>
     <row r="181">
       <c r="A181" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>1164.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>13</v>
@@ -5801,10 +5804,10 @@
         <v>13</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>13</v>
@@ -5818,10 +5821,10 @@
         <v>16</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>952.0</v>
+        <v>526.0</v>
       </c>
       <c r="E182" s="7" t="s">
         <v>13</v>
@@ -5844,19 +5847,19 @@
         <v>54</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>512430.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>40.0</v>
+        <v>4.0</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>54</v>
@@ -5876,10 +5879,10 @@
         <v>16</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>325.0</v>
+        <v>344.0</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>13</v>
@@ -5902,13 +5905,13 @@
         <v>54</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>13629.0</v>
+        <v>571.0</v>
       </c>
       <c r="E185" s="7" t="s">
         <v>13</v>
@@ -5931,19 +5934,19 @@
         <v>54</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>1182.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G186" s="8" t="s">
         <v>54</v>
@@ -5960,19 +5963,19 @@
         <v>54</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>197.0</v>
+        <v>806692.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F187" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F187" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G187" s="8" t="s">
         <v>54</v>
@@ -5989,19 +5992,19 @@
         <v>54</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>5147.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G188" s="8" t="s">
         <v>54</v>
@@ -6018,13 +6021,13 @@
         <v>54</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>486.0</v>
+        <v>451.0</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>13</v>
@@ -6047,19 +6050,19 @@
         <v>54</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>1502.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>54</v>
@@ -6076,19 +6079,19 @@
         <v>54</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>292130.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>54</v>
@@ -6105,13 +6108,13 @@
         <v>54</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>1542.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>13</v>
@@ -6134,13 +6137,13 @@
         <v>54</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>1186.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>13</v>
@@ -6163,19 +6166,19 @@
         <v>54</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>939.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F194" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>54</v>
@@ -6192,19 +6195,19 @@
         <v>54</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>506367.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F195" s="7" t="n">
-        <v>16.0</v>
+        <v>13</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>54</v>
@@ -6221,19 +6224,19 @@
         <v>54</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>728.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F196" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F196" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>54</v>
@@ -6250,19 +6253,19 @@
         <v>54</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>85.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F197" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>54</v>
@@ -6276,16 +6279,16 @@
     </row>
     <row r="198">
       <c r="A198" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>356.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>13</v>
@@ -6294,10 +6297,10 @@
         <v>13</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I198" s="7" t="s">
         <v>13</v>
@@ -6305,28 +6308,28 @@
     </row>
     <row r="199">
       <c r="A199" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>252920.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F199" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I199" s="7" t="s">
         <v>13</v>
@@ -6334,16 +6337,16 @@
     </row>
     <row r="200">
       <c r="A200" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>23967.0</v>
+        <v>172.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>13</v>
@@ -6352,10 +6355,10 @@
         <v>13</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I200" s="7" t="s">
         <v>13</v>
@@ -6363,28 +6366,28 @@
     </row>
     <row r="201">
       <c r="A201" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>74515.0</v>
+        <v>456.0</v>
       </c>
       <c r="E201" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F201" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F201" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>13</v>
@@ -6392,28 +6395,28 @@
     </row>
     <row r="202">
       <c r="A202" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>99098.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E202" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F202" s="7" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>13</v>
@@ -6421,16 +6424,16 @@
     </row>
     <row r="203">
       <c r="A203" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>2825.0</v>
+        <v>816.0</v>
       </c>
       <c r="E203" s="7" t="s">
         <v>13</v>
@@ -6439,10 +6442,10 @@
         <v>13</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>13</v>
@@ -6453,13 +6456,13 @@
         <v>55</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>4020.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>13</v>
@@ -6482,19 +6485,19 @@
         <v>55</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>146.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F205" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F205" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>55</v>
@@ -6511,19 +6514,19 @@
         <v>55</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>13942.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F206" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>55</v>
@@ -6540,19 +6543,19 @@
         <v>55</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>773114.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F207" s="7" t="n">
-        <v>31.0</v>
+        <v>13</v>
+      </c>
+      <c r="F207" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G207" s="8" t="s">
         <v>55</v>
@@ -6569,13 +6572,13 @@
         <v>55</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>18799.0</v>
+        <v>728.0</v>
       </c>
       <c r="E208" s="7" t="s">
         <v>13</v>
@@ -6601,10 +6604,10 @@
         <v>16</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>1274.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>13</v>
@@ -6630,16 +6633,16 @@
         <v>16</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>17054.0</v>
+        <v>952.0</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F210" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>55</v>
@@ -6659,16 +6662,16 @@
         <v>16</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>28978.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F211" s="7" t="n">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>55</v>
@@ -6685,13 +6688,13 @@
         <v>55</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>17807.0</v>
+        <v>325.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>13</v>
@@ -6714,19 +6717,19 @@
         <v>55</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>1685.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F213" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G213" s="8" t="s">
         <v>55</v>
@@ -6743,13 +6746,13 @@
         <v>55</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>42880.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>13</v>
@@ -6772,19 +6775,19 @@
         <v>55</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>280988.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F215" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G215" s="8" t="s">
         <v>55</v>
@@ -6801,13 +6804,13 @@
         <v>55</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>12137.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6830,19 +6833,19 @@
         <v>55</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>394262.0</v>
+        <v>197.0</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F217" s="7" t="n">
-        <v>7.0</v>
+        <v>13</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G217" s="8" t="s">
         <v>55</v>
@@ -6859,19 +6862,19 @@
         <v>55</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>11734.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E218" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F218" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F218" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G218" s="8" t="s">
         <v>55</v>
@@ -6888,13 +6891,13 @@
         <v>55</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>1644.0</v>
+        <v>85.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>13</v>
@@ -6923,7 +6926,7 @@
         <v>40</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>7147.0</v>
+        <v>939.0</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>13</v>
@@ -6946,13 +6949,13 @@
         <v>55</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>26497.0</v>
+        <v>486.0</v>
       </c>
       <c r="E221" s="7" t="s">
         <v>13</v>
@@ -6975,19 +6978,19 @@
         <v>55</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>477111.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>13.0</v>
+        <v>13</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>55</v>
@@ -7004,19 +7007,19 @@
         <v>55</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>5285.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F223" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F223" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>55</v>
@@ -7033,13 +7036,13 @@
         <v>55</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>5788.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>13</v>
@@ -7059,28 +7062,28 @@
     </row>
     <row r="225">
       <c r="A225" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>26146.0</v>
+        <v>356.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>13</v>
@@ -7088,16 +7091,16 @@
     </row>
     <row r="226">
       <c r="A226" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>14</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>14588.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>13</v>
@@ -7106,10 +7109,10 @@
         <v>13</v>
       </c>
       <c r="G226" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I226" s="7" t="s">
         <v>13</v>
@@ -7120,19 +7123,19 @@
         <v>56</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>23841.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F227" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F227" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>56</v>
@@ -7149,19 +7152,19 @@
         <v>56</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C228" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>199153.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E228" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F228" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>56</v>
@@ -7178,13 +7181,13 @@
         <v>56</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>20617.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>13</v>
@@ -7207,13 +7210,13 @@
         <v>56</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>38558.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>12</v>
@@ -7236,19 +7239,19 @@
         <v>56</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>126418.0</v>
+        <v>146.0</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F231" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F231" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>56</v>
@@ -7268,10 +7271,10 @@
         <v>16</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>2200.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E232" s="7" t="s">
         <v>13</v>
@@ -7294,19 +7297,19 @@
         <v>56</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>35873.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E233" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F233" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F233" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G233" s="8" t="s">
         <v>56</v>
@@ -7326,16 +7329,16 @@
         <v>16</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>16744.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E234" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F234" s="7" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>56</v>
@@ -7352,19 +7355,19 @@
         <v>56</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>32194.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E235" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F235" s="7" t="n">
-        <v>2.0</v>
+        <v>13</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G235" s="8" t="s">
         <v>56</v>
@@ -7384,16 +7387,16 @@
         <v>16</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>542175.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E236" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F236" s="7" t="n">
-        <v>9.0</v>
+        <v>13</v>
+      </c>
+      <c r="F236" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G236" s="8" t="s">
         <v>56</v>
@@ -7413,16 +7416,16 @@
         <v>16</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>274584.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F237" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>56</v>
@@ -7439,19 +7442,19 @@
         <v>56</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>35692.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E238" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F238" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F238" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G238" s="8" t="s">
         <v>56</v>
@@ -7468,19 +7471,19 @@
         <v>56</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>30762.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F239" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F239" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>56</v>
@@ -7497,19 +7500,19 @@
         <v>56</v>
       </c>
       <c r="B240" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>19972.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E240" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F240" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F240" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G240" s="8" t="s">
         <v>56</v>
@@ -7526,13 +7529,13 @@
         <v>56</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>36976.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E241" s="7" t="s">
         <v>13</v>
@@ -7555,19 +7558,19 @@
         <v>56</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>74182.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E242" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F242" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F242" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G242" s="8" t="s">
         <v>56</v>
@@ -7584,19 +7587,19 @@
         <v>56</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>277603.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E243" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F243" s="7" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>56</v>
@@ -7613,19 +7616,19 @@
         <v>56</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>61232.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F244" s="7" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G244" s="8" t="s">
         <v>56</v>
@@ -7642,19 +7645,19 @@
         <v>56</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>64701.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F245" s="7" t="n">
-        <v>1.0</v>
+        <v>13</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>56</v>
@@ -7671,13 +7674,13 @@
         <v>56</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>6327.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>13</v>
@@ -7700,19 +7703,19 @@
         <v>56</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>173630.0</v>
+        <v>7147.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F247" s="7" t="n">
-        <v>3.0</v>
+        <v>13</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>56</v>
@@ -7729,19 +7732,19 @@
         <v>56</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>171789.0</v>
+        <v>26497.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F248" s="7" t="n">
-        <v>5.0</v>
+        <v>13</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>56</v>
@@ -7758,19 +7761,19 @@
         <v>56</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>80351.0</v>
+        <v>477111.0</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F249" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F249" s="7" t="n">
+        <v>13.0</v>
       </c>
       <c r="G249" s="8" t="s">
         <v>56</v>
@@ -7787,13 +7790,13 @@
         <v>56</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C250" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>26014.0</v>
+        <v>5285.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>13</v>
@@ -7816,13 +7819,13 @@
         <v>56</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>8810.0</v>
+        <v>5788.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>13</v>
@@ -7845,19 +7848,19 @@
         <v>56</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>2368.0</v>
+        <v>26146.0</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F252" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F252" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G252" s="8" t="s">
         <v>56</v>
@@ -7874,13 +7877,13 @@
         <v>56</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>28702.0</v>
+        <v>14588.0</v>
       </c>
       <c r="E253" s="7" t="s">
         <v>13</v>
@@ -7900,28 +7903,28 @@
     </row>
     <row r="254">
       <c r="A254" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>247735.0</v>
+        <v>23841.0</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F254" s="7" t="n">
-        <v>10.0</v>
+        <v>13</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>13</v>
       </c>
       <c r="G254" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H254" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I254" s="7" t="s">
         <v>13</v>
@@ -7929,28 +7932,28 @@
     </row>
     <row r="255">
       <c r="A255" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>15987.0</v>
+        <v>199153.0</v>
       </c>
       <c r="E255" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F255" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="F255" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G255" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H255" s="8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="I255" s="7" t="s">
         <v>13</v>
@@ -7958,30 +7961,813 @@
     </row>
     <row r="256">
       <c r="A256" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B256" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D256" s="6" t="n">
+        <v>20617.0</v>
+      </c>
+      <c r="E256" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H256" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D257" s="6" t="n">
+        <v>38558.0</v>
+      </c>
+      <c r="E257" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F257" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H257" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I257" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D258" s="6" t="n">
+        <v>126418.0</v>
+      </c>
+      <c r="E258" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F258" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H258" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I258" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B259" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C256" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D256" s="6" t="n">
+      <c r="C259" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D259" s="6" t="n">
+        <v>2200.0</v>
+      </c>
+      <c r="E259" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H259" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I259" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D260" s="6" t="n">
+        <v>35873.0</v>
+      </c>
+      <c r="E260" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H260" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D261" s="6" t="n">
+        <v>16744.0</v>
+      </c>
+      <c r="E261" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F261" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H261" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I261" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D262" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E262" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F262" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H262" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I262" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D263" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E263" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F263" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H263" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I263" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D264" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E264" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F264" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H264" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I264" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D265" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E265" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F265" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H265" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I265" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D266" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E266" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H266" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I266" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D267" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E267" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H267" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I267" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D268" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E268" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F268" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H268" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I268" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D269" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E269" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F269" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H269" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I269" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D270" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E270" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F270" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H270" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I270" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D271" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E271" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F271" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H271" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I271" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C272" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D272" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E272" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F272" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G272" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H272" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I272" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C273" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D273" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E273" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F273" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G273" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H273" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I273" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C274" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D274" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E274" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F274" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G274" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H274" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I274" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C275" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D275" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E275" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F275" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G275" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H275" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I275" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C276" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D276" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E276" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F276" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G276" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H276" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I276" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C277" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D277" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E277" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G277" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H277" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I277" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C278" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D278" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F278" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G278" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H278" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I278" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C279" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D279" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E279" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G279" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H279" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I279" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C280" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D280" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G280" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H280" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I280" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C281" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D281" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E281" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F281" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G281" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H281" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I281" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C282" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D282" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E282" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G282" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H282" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I282" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C283" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D283" s="6" t="n">
         <v>48163.0</v>
       </c>
-      <c r="E256" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F256" s="7" t="n">
+      <c r="E283" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F283" s="7" t="n">
         <v>1.0</v>
       </c>
-      <c r="G256" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="H256" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="I256" s="7" t="s">
+      <c r="G283" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H283" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I283" s="7" t="s">
         <v>13</v>
       </c>
     </row>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2297" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="60">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-08-19</t>
+    <t>2026-08-20</t>
   </si>
   <si>
     <t>120253031332440341</t>
@@ -56,19 +56,22 @@
     <t>120253028817940341</t>
   </si>
   <si>
-    <t>120253028817980341</t>
+    <t>120253028817970341</t>
+  </si>
+  <si>
+    <t>120253023460500341</t>
+  </si>
+  <si>
+    <t>120253023954760341</t>
   </si>
   <si>
     <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
   </si>
   <si>
-    <t>120253023460500341</t>
+    <t>120253023954770341</t>
   </si>
   <si>
-    <t>120253023460490341</t>
-  </si>
-  <si>
-    <t>120253023954770341</t>
+    <t>120253023954780341</t>
   </si>
   <si>
     <t>120253023954790341</t>
@@ -77,10 +80,16 @@
     <t>120253028817950341</t>
   </si>
   <si>
-    <t>120253023954760341</t>
+    <t>120253028817960341</t>
   </si>
   <si>
-    <t>120253028818100341</t>
+    <t>120253023954800341</t>
+  </si>
+  <si>
+    <t>120253028817980341</t>
+  </si>
+  <si>
+    <t>120253031332450341</t>
   </si>
   <si>
     <t>120253031332470341</t>
@@ -89,34 +98,40 @@
     <t>120253031332480341</t>
   </si>
   <si>
+    <t>120253031402010341</t>
+  </si>
+  <si>
     <t>120253031402020341</t>
   </si>
   <si>
     <t>120253031402030341</t>
   </si>
   <si>
-    <t>2026-08-18</t>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>120253023460490341</t>
   </si>
   <si>
     <t>120253023954750341</t>
   </si>
   <si>
-    <t>120253023954800341</t>
+    <t>120253023954820341</t>
   </si>
   <si>
-    <t>120253028817960341</t>
+    <t>120253023954740341</t>
   </si>
   <si>
-    <t>120253028817970341</t>
+    <t>120253031332490341</t>
+  </si>
+  <si>
+    <t>120253028818100341</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t>120253031332460341</t>
-  </si>
-  <si>
-    <t>120253031332450341</t>
-  </si>
-  <si>
-    <t>120253031402010341</t>
   </si>
   <si>
     <t>120253031402050341</t>
@@ -134,28 +149,16 @@
     <t>2026-08-17</t>
   </si>
   <si>
-    <t>120253023954780341</t>
-  </si>
-  <si>
-    <t>120253023954820341</t>
-  </si>
-  <si>
     <t>120253023954810341</t>
   </si>
   <si>
-    <t>120253023954740341</t>
-  </si>
-  <si>
-    <t>120253058581660341</t>
+    <t>120253058581620341</t>
   </si>
   <si>
     <t>120253058581640341</t>
   </si>
   <si>
-    <t>120253058581620341</t>
-  </si>
-  <si>
-    <t>120253031332490341</t>
+    <t>120253058581660341</t>
   </si>
   <si>
     <t>2026-08-16</t>
@@ -552,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I302"/>
+  <dimension ref="A1:I324"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -607,7 +610,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>320.0</v>
+        <v>2970.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -636,13 +639,13 @@
         <v>14</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>67808.0</v>
+        <v>52.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
@@ -659,19 +662,19 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" s="6" t="n">
-        <v>1908.0</v>
+        <v>103350.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -688,19 +691,19 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>52577.0</v>
+        <v>71458.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F5" s="7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -717,13 +720,13 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>790.0</v>
+        <v>37.0</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>12</v>
@@ -746,19 +749,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>32206.0</v>
+        <v>2292.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -775,19 +778,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>35593.0</v>
+        <v>521.0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -810,7 +813,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>215.0</v>
+        <v>4066.0</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>12</v>
@@ -833,13 +836,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1426.0</v>
+        <v>5440.0</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>12</v>
@@ -862,19 +865,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>19895.0</v>
+        <v>161144.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -897,13 +900,13 @@
         <v>25</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>13037.0</v>
+        <v>31738.0</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>9</v>
@@ -926,13 +929,13 @@
         <v>26</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>84802.0</v>
+        <v>7744.0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -946,16 +949,16 @@
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D14" s="6" t="n">
-        <v>902.0</v>
+        <v>10787.0</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>12</v>
@@ -964,10 +967,10 @@
         <v>12</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7" t="s">
         <v>12</v>
@@ -975,16 +978,16 @@
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1519.0</v>
+        <v>1130.0</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
@@ -993,10 +996,10 @@
         <v>12</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H15" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7" t="s">
         <v>12</v>
@@ -1004,28 +1007,28 @@
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>337193.0</v>
+        <v>4162.0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7" t="s">
         <v>12</v>
@@ -1033,28 +1036,28 @@
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>285141.0</v>
+        <v>185270.0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7" t="s">
         <v>12</v>
@@ -1062,28 +1065,28 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>15292.0</v>
+        <v>125559.0</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>12</v>
@@ -1091,28 +1094,28 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>7105.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F19" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>12</v>
@@ -1120,28 +1123,28 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>95272.0</v>
+        <v>8255.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>12</v>
@@ -1149,28 +1152,28 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>4415.0</v>
+        <v>353581.0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>12</v>
@@ -1178,28 +1181,28 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>357152.0</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G22" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D22" s="6" t="n">
-        <v>3958.0</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="H22" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>12</v>
@@ -1207,28 +1210,28 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>304259.0</v>
+        <v>43146.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>12</v>
@@ -1236,16 +1239,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>2724.0</v>
+        <v>15392.0</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>12</v>
@@ -1254,10 +1257,10 @@
         <v>12</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>12</v>
@@ -1265,16 +1268,16 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>9553.0</v>
+        <v>5128.0</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>12</v>
@@ -1283,10 +1286,10 @@
         <v>12</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>12</v>
@@ -1294,28 +1297,28 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>33470.0</v>
+        <v>4310.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>12</v>
@@ -1323,28 +1326,28 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>62451.0</v>
+        <v>26157.0</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>12</v>
@@ -1352,16 +1355,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>4352.0</v>
+        <v>13166.0</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>12</v>
@@ -1370,10 +1373,10 @@
         <v>12</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>12</v>
@@ -1381,28 +1384,28 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>33923.0</v>
+        <v>540962.0</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F29" s="7" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>12</v>
@@ -1410,28 +1413,28 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>437117.0</v>
+        <v>73604.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>12</v>
@@ -1439,7 +1442,7 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
@@ -1448,19 +1451,19 @@
         <v>11</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>31713.0</v>
+        <v>48756.0</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F31" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>12</v>
@@ -1468,16 +1471,16 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="D32" s="6" t="n">
-        <v>749.0</v>
+        <v>120888.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
@@ -1486,10 +1489,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>12</v>
@@ -1497,16 +1500,16 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>90.0</v>
+        <v>10204.0</v>
       </c>
       <c r="E33" s="7" t="s">
         <v>12</v>
@@ -1515,10 +1518,10 @@
         <v>12</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>12</v>
@@ -1526,28 +1529,28 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>160872.0</v>
+        <v>643.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>12</v>
@@ -1555,28 +1558,28 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1979.0</v>
+        <v>281884.0</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>12</v>
@@ -1584,28 +1587,28 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>135942.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>12</v>
@@ -1613,16 +1616,16 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>147.0</v>
+        <v>9553.0</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>12</v>
@@ -1631,10 +1634,10 @@
         <v>12</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>12</v>
@@ -1642,28 +1645,28 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="D38" s="6" t="n">
-        <v>272.0</v>
+        <v>337253.0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>12</v>
@@ -1671,28 +1674,28 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>48.0</v>
+        <v>285274.0</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>12</v>
@@ -1700,28 +1703,28 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>3882.0</v>
+        <v>15292.0</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>12</v>
@@ -1729,28 +1732,28 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>364072.0</v>
+        <v>7105.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F41" s="7" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>12</v>
@@ -1758,28 +1761,28 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>468850.0</v>
+        <v>95351.0</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F42" s="7" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>12</v>
@@ -1787,16 +1790,16 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>428.0</v>
+        <v>4415.0</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>12</v>
@@ -1805,10 +1808,10 @@
         <v>12</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>12</v>
@@ -1816,16 +1819,16 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>311.0</v>
+        <v>3958.0</v>
       </c>
       <c r="E44" s="7" t="s">
         <v>12</v>
@@ -1834,10 +1837,10 @@
         <v>12</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>12</v>
@@ -1845,28 +1848,28 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>284401.0</v>
+        <v>304338.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>12</v>
@@ -1874,16 +1877,16 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>7046.0</v>
+        <v>902.0</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>12</v>
@@ -1892,10 +1895,10 @@
         <v>12</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>12</v>
@@ -1903,28 +1906,28 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C47" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B47" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C47" s="5" t="s">
-        <v>44</v>
-      </c>
       <c r="D47" s="6" t="n">
-        <v>3047.0</v>
+        <v>2724.0</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F47" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>12</v>
@@ -1932,28 +1935,28 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>24918.0</v>
+        <v>62451.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F48" s="7" t="n">
         <v>2.0</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>12</v>
@@ -1961,28 +1964,28 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>3904.0</v>
+        <v>4352.0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>12</v>
@@ -1990,28 +1993,28 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>1815.0</v>
+        <v>33923.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>12</v>
@@ -2019,28 +2022,28 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>11591.0</v>
+        <v>437190.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F51" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F51" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>12</v>
@@ -2048,28 +2051,28 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>945.0</v>
+        <v>31713.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F52" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>12</v>
@@ -2077,16 +2080,16 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>1703.0</v>
+        <v>749.0</v>
       </c>
       <c r="E53" s="7" t="s">
         <v>12</v>
@@ -2095,10 +2098,10 @@
         <v>12</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>12</v>
@@ -2106,28 +2109,28 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C54" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D54" s="6" t="n">
-        <v>501017.0</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>39</v>
-      </c>
       <c r="H54" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>12</v>
@@ -2135,28 +2138,28 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>712387.0</v>
+        <v>160872.0</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F55" s="7" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>12</v>
@@ -2164,28 +2167,28 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>87472.0</v>
+        <v>33470.0</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F56" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>12</v>
@@ -2193,16 +2196,16 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>3746.0</v>
+        <v>48.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
@@ -2211,10 +2214,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>12</v>
@@ -2222,16 +2225,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>167988.0</v>
+        <v>7046.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
@@ -2240,10 +2243,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>12</v>
@@ -2251,28 +2254,28 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>7120.0</v>
+        <v>135942.0</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>12</v>
@@ -2280,28 +2283,28 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>358088.0</v>
+        <v>147.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>9.0</v>
+        <v>12</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>12</v>
@@ -2309,28 +2312,28 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>2527.0</v>
+        <v>272.0</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F61" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F61" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>12</v>
@@ -2338,16 +2341,16 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>6618.0</v>
+        <v>311.0</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>12</v>
@@ -2356,10 +2359,10 @@
         <v>12</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>12</v>
@@ -2367,28 +2370,28 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>638501.0</v>
+        <v>1979.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>20.0</v>
+        <v>12</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>12</v>
@@ -2396,28 +2399,28 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C64" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>244115.0</v>
+        <v>364072.0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F64" s="7" t="n">
         <v>11.0</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>12</v>
@@ -2425,28 +2428,28 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B65" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C65" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="D65" s="6" t="n">
-        <v>18.0</v>
+        <v>468850.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>12</v>
@@ -2454,16 +2457,16 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>10198.0</v>
+        <v>428.0</v>
       </c>
       <c r="E66" s="7" t="s">
         <v>12</v>
@@ -2472,10 +2475,10 @@
         <v>12</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>12</v>
@@ -2483,28 +2486,28 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>285.0</v>
+        <v>24918.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>12</v>
@@ -2512,28 +2515,28 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>24684.0</v>
+        <v>284401.0</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>12</v>
@@ -2541,16 +2544,16 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>11414.0</v>
+        <v>3882.0</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
@@ -2559,10 +2562,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I69" s="7" t="s">
         <v>12</v>
@@ -2570,16 +2573,16 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>8877.0</v>
+        <v>1815.0</v>
       </c>
       <c r="E70" s="7" t="s">
         <v>12</v>
@@ -2588,10 +2591,10 @@
         <v>12</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>12</v>
@@ -2599,16 +2602,16 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>383.0</v>
+        <v>167988.0</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>12</v>
@@ -2617,10 +2620,10 @@
         <v>12</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>12</v>
@@ -2628,16 +2631,16 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>173.0</v>
+        <v>3746.0</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
@@ -2646,10 +2649,10 @@
         <v>12</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>12</v>
@@ -2657,28 +2660,28 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>703357.0</v>
+        <v>87472.0</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>18.0</v>
+        <v>4.0</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>12</v>
@@ -2686,28 +2689,28 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>384990.0</v>
+        <v>712387.0</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>12</v>
@@ -2715,28 +2718,28 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>2068.0</v>
+        <v>3904.0</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>12</v>
@@ -2744,16 +2747,16 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>772.0</v>
+        <v>1703.0</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>12</v>
@@ -2762,10 +2765,10 @@
         <v>12</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I76" s="7" t="s">
         <v>12</v>
@@ -2773,16 +2776,16 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>12318.0</v>
+        <v>945.0</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>12</v>
@@ -2791,10 +2794,10 @@
         <v>12</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I77" s="7" t="s">
         <v>12</v>
@@ -2802,16 +2805,16 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>392.0</v>
+        <v>11591.0</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>12</v>
@@ -2820,10 +2823,10 @@
         <v>12</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I78" s="7" t="s">
         <v>12</v>
@@ -2831,28 +2834,28 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>31421.0</v>
+        <v>501017.0</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F79" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>12</v>
@@ -2860,28 +2863,28 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C80" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C80" s="5" t="s">
-        <v>47</v>
-      </c>
       <c r="D80" s="6" t="n">
-        <v>295.0</v>
+        <v>3047.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F80" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>12</v>
@@ -2889,28 +2892,28 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B81" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>42524.0</v>
+        <v>7120.0</v>
       </c>
       <c r="E81" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F81" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F81" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>12</v>
@@ -2918,16 +2921,16 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C82" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>18008.0</v>
+        <v>285.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
@@ -2936,10 +2939,10 @@
         <v>12</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>12</v>
@@ -2947,16 +2950,16 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>212.0</v>
+        <v>11414.0</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>12</v>
@@ -2965,10 +2968,10 @@
         <v>12</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>12</v>
@@ -2979,19 +2982,19 @@
         <v>49</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>17276.0</v>
+        <v>24684.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F84" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G84" s="8" t="s">
         <v>49</v>
@@ -3008,19 +3011,19 @@
         <v>49</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>336995.0</v>
+        <v>383.0</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F85" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F85" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G85" s="8" t="s">
         <v>49</v>
@@ -3037,19 +3040,19 @@
         <v>49</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>435991.0</v>
+        <v>2527.0</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G86" s="8" t="s">
         <v>49</v>
@@ -3066,13 +3069,13 @@
         <v>49</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>5248.0</v>
+        <v>10198.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
@@ -3095,13 +3098,13 @@
         <v>49</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>650.0</v>
+        <v>18.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3124,19 +3127,19 @@
         <v>49</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>19816.0</v>
+        <v>244115.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G89" s="8" t="s">
         <v>49</v>
@@ -3153,19 +3156,19 @@
         <v>49</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>317924.0</v>
+        <v>638501.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F90" s="7" t="n">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="G90" s="8" t="s">
         <v>49</v>
@@ -3182,13 +3185,13 @@
         <v>49</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C91" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>4802.0</v>
+        <v>6618.0</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>12</v>
@@ -3214,16 +3217,16 @@
         <v>13</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>819.0</v>
+        <v>358088.0</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G92" s="8" t="s">
         <v>49</v>
@@ -3240,13 +3243,13 @@
         <v>49</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>29578.0</v>
+        <v>8877.0</v>
       </c>
       <c r="E93" s="7" t="s">
         <v>12</v>
@@ -3269,13 +3272,13 @@
         <v>49</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>1044.0</v>
+        <v>18008.0</v>
       </c>
       <c r="E94" s="7" t="s">
         <v>12</v>
@@ -3298,13 +3301,13 @@
         <v>49</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>772.0</v>
+        <v>173.0</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>12</v>
@@ -3327,19 +3330,19 @@
         <v>49</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>38</v>
+        <v>11</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>401629.0</v>
+        <v>12318.0</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F96" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F96" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G96" s="8" t="s">
         <v>49</v>
@@ -3356,19 +3359,19 @@
         <v>49</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>1439.0</v>
+        <v>384990.0</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F97" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F97" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G97" s="8" t="s">
         <v>49</v>
@@ -3385,13 +3388,13 @@
         <v>49</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="D98" s="6" t="n">
-        <v>5801.0</v>
+        <v>392.0</v>
       </c>
       <c r="E98" s="7" t="s">
         <v>12</v>
@@ -3414,13 +3417,13 @@
         <v>49</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>2548.0</v>
+        <v>772.0</v>
       </c>
       <c r="E99" s="7" t="s">
         <v>12</v>
@@ -3443,19 +3446,19 @@
         <v>49</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>26</v>
+        <v>47</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>853298.0</v>
+        <v>2068.0</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F100" s="7" t="n">
-        <v>27.0</v>
+        <v>12</v>
+      </c>
+      <c r="F100" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G100" s="8" t="s">
         <v>49</v>
@@ -3475,16 +3478,16 @@
         <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>4237.0</v>
+        <v>703357.0</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F101" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F101" s="7" t="n">
+        <v>18.0</v>
       </c>
       <c r="G101" s="8" t="s">
         <v>49</v>
@@ -3498,28 +3501,28 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>8213.0</v>
+        <v>31421.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F102" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F102" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>12</v>
@@ -3527,28 +3530,28 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>324526.0</v>
+        <v>212.0</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F103" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F103" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>12</v>
@@ -3556,16 +3559,16 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>2170.0</v>
+        <v>295.0</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>12</v>
@@ -3574,10 +3577,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>12</v>
@@ -3585,28 +3588,28 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>378946.0</v>
+        <v>42524.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F105" s="7" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I105" s="7" t="s">
         <v>12</v>
@@ -3617,16 +3620,16 @@
         <v>50</v>
       </c>
       <c r="B106" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C106" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="D106" s="6" t="n">
-        <v>462054.0</v>
+        <v>336995.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F106" s="7" t="n">
         <v>14.0</v>
@@ -3646,19 +3649,19 @@
         <v>50</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>228.0</v>
+        <v>435991.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>50</v>
@@ -3675,13 +3678,13 @@
         <v>50</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>742.0</v>
+        <v>5248.0</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>12</v>
@@ -3704,13 +3707,13 @@
         <v>50</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>3988.0</v>
+        <v>650.0</v>
       </c>
       <c r="E109" s="7" t="s">
         <v>12</v>
@@ -3736,16 +3739,16 @@
         <v>13</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>22960.0</v>
+        <v>19816.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F110" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F110" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G110" s="8" t="s">
         <v>50</v>
@@ -3765,16 +3768,16 @@
         <v>13</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>14457.0</v>
+        <v>317924.0</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F111" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F111" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>50</v>
@@ -3791,19 +3794,19 @@
         <v>50</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>14351.0</v>
+        <v>819.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F112" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F112" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G112" s="8" t="s">
         <v>50</v>
@@ -3823,10 +3826,10 @@
         <v>10</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>412.0</v>
+        <v>4802.0</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>12</v>
@@ -3849,13 +3852,13 @@
         <v>50</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>1625.0</v>
+        <v>17276.0</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>12</v>
@@ -3881,10 +3884,10 @@
         <v>10</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>8383.0</v>
+        <v>29578.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3910,10 +3913,10 @@
         <v>10</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>5324.0</v>
+        <v>4237.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -3936,19 +3939,19 @@
         <v>50</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>385.0</v>
+        <v>853298.0</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>27.0</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>50</v>
@@ -3968,10 +3971,10 @@
         <v>10</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>3011.0</v>
+        <v>2548.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>12</v>
@@ -3994,19 +3997,19 @@
         <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>445496.0</v>
+        <v>5801.0</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F119" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>50</v>
@@ -4023,19 +4026,19 @@
         <v>50</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>696176.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F120" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F120" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G120" s="8" t="s">
         <v>50</v>
@@ -4052,19 +4055,19 @@
         <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>51544.0</v>
+        <v>401629.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F121" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>50</v>
@@ -4081,13 +4084,13 @@
         <v>50</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>2238.0</v>
+        <v>772.0</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>12</v>
@@ -4113,10 +4116,10 @@
         <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>4481.0</v>
+        <v>1439.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>12</v>
@@ -4139,19 +4142,19 @@
         <v>51</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>893824.0</v>
+        <v>228.0</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F124" s="7" t="n">
-        <v>24.0</v>
+        <v>12</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G124" s="8" t="s">
         <v>51</v>
@@ -4168,19 +4171,19 @@
         <v>51</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>5377.0</v>
+        <v>22960.0</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F125" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F125" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G125" s="8" t="s">
         <v>51</v>
@@ -4197,13 +4200,13 @@
         <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>1498.0</v>
+        <v>742.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
@@ -4226,19 +4229,19 @@
         <v>51</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>43627.0</v>
+        <v>8213.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F127" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G127" s="8" t="s">
         <v>51</v>
@@ -4255,19 +4258,19 @@
         <v>51</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>5765.0</v>
+        <v>462054.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F128" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F128" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G128" s="8" t="s">
         <v>51</v>
@@ -4284,19 +4287,19 @@
         <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>379038.0</v>
+        <v>378946.0</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>51</v>
@@ -4313,19 +4316,19 @@
         <v>51</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C130" s="5" t="s">
         <v>33</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>3659.0</v>
+        <v>2170.0</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G130" s="8" t="s">
         <v>51</v>
@@ -4342,19 +4345,19 @@
         <v>51</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>7279.0</v>
+        <v>14351.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>51</v>
@@ -4371,19 +4374,19 @@
         <v>51</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>17021.0</v>
+        <v>324526.0</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F132" s="7" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>51</v>
@@ -4400,13 +4403,13 @@
         <v>51</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>1563.0</v>
+        <v>14457.0</v>
       </c>
       <c r="E133" s="7" t="s">
         <v>12</v>
@@ -4429,13 +4432,13 @@
         <v>51</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C134" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>12172.0</v>
+        <v>3988.0</v>
       </c>
       <c r="E134" s="7" t="s">
         <v>12</v>
@@ -4458,19 +4461,19 @@
         <v>51</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>935238.0</v>
+        <v>1625.0</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F135" s="7" t="n">
-        <v>20.0</v>
+        <v>12</v>
+      </c>
+      <c r="F135" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>51</v>
@@ -4493,7 +4496,7 @@
         <v>11</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>5104.0</v>
+        <v>8383.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
@@ -4519,10 +4522,10 @@
         <v>10</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>2256.0</v>
+        <v>412.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
@@ -4545,19 +4548,19 @@
         <v>51</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>1293.0</v>
+        <v>445496.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F138" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F138" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G138" s="8" t="s">
         <v>51</v>
@@ -4574,13 +4577,13 @@
         <v>51</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>3472.0</v>
+        <v>3011.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4603,19 +4606,19 @@
         <v>51</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>378762.0</v>
+        <v>385.0</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F140" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G140" s="8" t="s">
         <v>51</v>
@@ -4635,16 +4638,16 @@
         <v>10</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>76.0</v>
+        <v>696176.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F141" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F141" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>51</v>
@@ -4658,28 +4661,28 @@
     </row>
     <row r="142">
       <c r="A142" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>6325.0</v>
+        <v>51544.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F142" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G142" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H142" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I142" s="7" t="s">
         <v>12</v>
@@ -4687,16 +4690,16 @@
     </row>
     <row r="143">
       <c r="A143" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>33363.0</v>
+        <v>2238.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4705,10 +4708,10 @@
         <v>12</v>
       </c>
       <c r="G143" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H143" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I143" s="7" t="s">
         <v>12</v>
@@ -4716,28 +4719,28 @@
     </row>
     <row r="144">
       <c r="A144" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>9025.0</v>
+        <v>4481.0</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F144" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G144" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H144" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I144" s="7" t="s">
         <v>12</v>
@@ -4745,7 +4748,7 @@
     </row>
     <row r="145">
       <c r="A145" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>10</v>
@@ -4754,19 +4757,19 @@
         <v>26</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>697336.0</v>
+        <v>5324.0</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F145" s="7" t="n">
-        <v>10.0</v>
+        <v>12</v>
+      </c>
+      <c r="F145" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G145" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H145" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I145" s="7" t="s">
         <v>12</v>
@@ -4777,13 +4780,13 @@
         <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>2276.0</v>
+        <v>1563.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
@@ -4806,19 +4809,19 @@
         <v>52</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>3642.0</v>
+        <v>43627.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F147" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>52</v>
@@ -4835,13 +4838,13 @@
         <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>45</v>
+        <v>14</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>7174.0</v>
+        <v>5765.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4864,19 +4867,19 @@
         <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>383981.0</v>
+        <v>379038.0</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>52</v>
@@ -4893,19 +4896,19 @@
         <v>52</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>7643.0</v>
+        <v>3659.0</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F150" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F150" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>52</v>
@@ -4925,16 +4928,16 @@
         <v>10</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>20739.0</v>
+        <v>7279.0</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F151" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F151" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>52</v>
@@ -4951,19 +4954,19 @@
         <v>52</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>353476.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F152" s="7" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>52</v>
@@ -4980,19 +4983,19 @@
         <v>52</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>25346.0</v>
+        <v>1293.0</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F153" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F153" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G153" s="8" t="s">
         <v>52</v>
@@ -5009,19 +5012,19 @@
         <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>700185.0</v>
+        <v>12172.0</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F154" s="7" t="n">
-        <v>20.0</v>
+        <v>12</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>52</v>
@@ -5038,13 +5041,13 @@
         <v>52</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>2939.0</v>
+        <v>76.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5067,19 +5070,19 @@
         <v>52</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>25848.0</v>
+        <v>935238.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>1.0</v>
+        <v>20.0</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>52</v>
@@ -5096,13 +5099,13 @@
         <v>52</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>15807.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>12</v>
@@ -5125,13 +5128,13 @@
         <v>52</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C158" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>3888.0</v>
+        <v>2256.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5154,13 +5157,13 @@
         <v>52</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C159" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>290.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>12</v>
@@ -5183,19 +5186,19 @@
         <v>52</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>16525.0</v>
+        <v>378762.0</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F160" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F160" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>52</v>
@@ -5209,16 +5212,16 @@
     </row>
     <row r="161">
       <c r="A161" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>2673.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>12</v>
@@ -5227,10 +5230,10 @@
         <v>12</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>12</v>
@@ -5238,16 +5241,16 @@
     </row>
     <row r="162">
       <c r="A162" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>794.0</v>
+        <v>1498.0</v>
       </c>
       <c r="E162" s="7" t="s">
         <v>12</v>
@@ -5256,10 +5259,10 @@
         <v>12</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>12</v>
@@ -5267,28 +5270,28 @@
     </row>
     <row r="163">
       <c r="A163" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>1474.0</v>
+        <v>893824.0</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>12</v>
@@ -5299,19 +5302,19 @@
         <v>53</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>83588.0</v>
+        <v>290.0</v>
       </c>
       <c r="E164" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F164" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F164" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G164" s="8" t="s">
         <v>53</v>
@@ -5328,19 +5331,19 @@
         <v>53</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>480911.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F165" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>53</v>
@@ -5357,13 +5360,13 @@
         <v>53</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>3290.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
@@ -5386,13 +5389,13 @@
         <v>53</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>928.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
@@ -5415,19 +5418,19 @@
         <v>53</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>100569.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F168" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>53</v>
@@ -5444,19 +5447,19 @@
         <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>46118.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F169" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F169" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>53</v>
@@ -5473,19 +5476,19 @@
         <v>53</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>282217.0</v>
+        <v>700185.0</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F170" s="7" t="n">
-        <v>6.0</v>
+        <v>20.0</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>53</v>
@@ -5502,13 +5505,13 @@
         <v>53</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>889.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>12</v>
@@ -5531,13 +5534,13 @@
         <v>53</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>2220.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>12</v>
@@ -5560,19 +5563,19 @@
         <v>53</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>633.0</v>
+        <v>353476.0</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F173" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F173" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>53</v>
@@ -5589,13 +5592,13 @@
         <v>53</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>7945.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5621,16 +5624,16 @@
         <v>10</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>621293.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F175" s="7" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>53</v>
@@ -5647,19 +5650,19 @@
         <v>53</v>
       </c>
       <c r="B176" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C176" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C176" s="5" t="s">
-        <v>38</v>
-      </c>
       <c r="D176" s="6" t="n">
-        <v>357571.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E176" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F176" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F176" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G176" s="8" t="s">
         <v>53</v>
@@ -5679,16 +5682,16 @@
         <v>10</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>70.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F177" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F177" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>53</v>
@@ -5708,16 +5711,16 @@
         <v>10</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>2029.0</v>
+        <v>697336.0</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G178" s="8" t="s">
         <v>53</v>
@@ -5737,10 +5740,10 @@
         <v>10</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>324.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>12</v>
@@ -5763,13 +5766,13 @@
         <v>53</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>21813.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E180" s="7" t="s">
         <v>12</v>
@@ -5789,16 +5792,16 @@
     </row>
     <row r="181">
       <c r="A181" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>5812.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>12</v>
@@ -5807,10 +5810,10 @@
         <v>12</v>
       </c>
       <c r="G181" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I181" s="7" t="s">
         <v>12</v>
@@ -5818,28 +5821,28 @@
     </row>
     <row r="182">
       <c r="A182" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>1812.0</v>
+        <v>383981.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F182" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F182" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G182" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I182" s="7" t="s">
         <v>12</v>
@@ -5850,19 +5853,19 @@
         <v>54</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>112476.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F183" s="7" t="n">
-        <v>4.0</v>
+        <v>14.0</v>
       </c>
       <c r="G183" s="8" t="s">
         <v>54</v>
@@ -5879,19 +5882,19 @@
         <v>54</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>730436.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F184" s="7" t="n">
-        <v>24.0</v>
+        <v>2.0</v>
       </c>
       <c r="G184" s="8" t="s">
         <v>54</v>
@@ -5908,13 +5911,13 @@
         <v>54</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>199.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E185" s="7" t="s">
         <v>12</v>
@@ -5937,19 +5940,19 @@
         <v>54</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>58187.0</v>
+        <v>928.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F186" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F186" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G186" s="8" t="s">
         <v>54</v>
@@ -5966,19 +5969,19 @@
         <v>54</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>131368.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F187" s="7" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G187" s="8" t="s">
         <v>54</v>
@@ -5995,19 +5998,19 @@
         <v>54</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>218816.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F188" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F188" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G188" s="8" t="s">
         <v>54</v>
@@ -6024,13 +6027,13 @@
         <v>54</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>3911.0</v>
+        <v>794.0</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>12</v>
@@ -6053,19 +6056,19 @@
         <v>54</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>601.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F190" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F190" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>54</v>
@@ -6082,13 +6085,13 @@
         <v>54</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>4729.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>12</v>
@@ -6111,13 +6114,13 @@
         <v>54</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>33241.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>12</v>
@@ -6143,10 +6146,10 @@
         <v>10</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>15780.0</v>
+        <v>889.0</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>12</v>
@@ -6172,10 +6175,10 @@
         <v>10</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>969.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E194" s="7" t="s">
         <v>12</v>
@@ -6204,13 +6207,13 @@
         <v>26</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>637424.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F195" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>54</v>
@@ -6233,7 +6236,7 @@
         <v>11</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>395.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E196" s="7" t="s">
         <v>12</v>
@@ -6259,16 +6262,16 @@
         <v>10</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>5851.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F197" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>54</v>
@@ -6285,13 +6288,13 @@
         <v>54</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>479.0</v>
+        <v>633.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>12</v>
@@ -6314,19 +6317,19 @@
         <v>54</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>386517.0</v>
+        <v>70.0</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F199" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>54</v>
@@ -6346,10 +6349,10 @@
         <v>10</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>70.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>12</v>
@@ -6369,16 +6372,16 @@
     </row>
     <row r="201">
       <c r="A201" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>8605.0</v>
+        <v>324.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>12</v>
@@ -6387,10 +6390,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>12</v>
@@ -6398,28 +6401,28 @@
     </row>
     <row r="202">
       <c r="A202" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>107118.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F202" s="7" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>12</v>
@@ -6430,19 +6433,19 @@
         <v>55</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>51830.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F203" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G203" s="8" t="s">
         <v>55</v>
@@ -6459,13 +6462,13 @@
         <v>55</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>451.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6488,16 +6491,16 @@
         <v>55</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>249629.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F205" s="7" t="n">
         <v>4.0</v>
@@ -6517,19 +6520,19 @@
         <v>55</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>806692.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F206" s="7" t="n">
-        <v>40.0</v>
+        <v>24.0</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>55</v>
@@ -6546,13 +6549,13 @@
         <v>55</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>571.0</v>
+        <v>199.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6575,19 +6578,19 @@
         <v>55</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>344.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F208" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>55</v>
@@ -6604,19 +6607,19 @@
         <v>55</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>526.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F209" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F209" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G209" s="8" t="s">
         <v>55</v>
@@ -6636,16 +6639,16 @@
         <v>13</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>2994.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F210" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F210" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>55</v>
@@ -6662,19 +6665,19 @@
         <v>55</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>65819.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F211" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F211" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>55</v>
@@ -6691,19 +6694,19 @@
         <v>55</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>9408.0</v>
+        <v>601.0</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F212" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G212" s="8" t="s">
         <v>55</v>
@@ -6720,13 +6723,13 @@
         <v>55</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>172.0</v>
+        <v>969.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6749,13 +6752,13 @@
         <v>55</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>816.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6781,10 +6784,10 @@
         <v>10</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>24685.0</v>
+        <v>70.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6807,13 +6810,13 @@
         <v>55</v>
       </c>
       <c r="B216" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C216" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C216" s="5" t="s">
-        <v>45</v>
-      </c>
       <c r="D216" s="6" t="n">
-        <v>456.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E216" s="7" t="s">
         <v>12</v>
@@ -6836,19 +6839,19 @@
         <v>55</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>407399.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F217" s="7" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G217" s="8" t="s">
         <v>55</v>
@@ -6868,10 +6871,10 @@
         <v>10</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>4379.0</v>
+        <v>395.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6897,10 +6900,10 @@
         <v>10</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>3200.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E219" s="7" t="s">
         <v>12</v>
@@ -6923,19 +6926,19 @@
         <v>55</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>747712.0</v>
+        <v>479.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F220" s="7" t="n">
-        <v>16.0</v>
+        <v>12</v>
+      </c>
+      <c r="F220" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>55</v>
@@ -6952,19 +6955,19 @@
         <v>55</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>3128.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F221" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>55</v>
@@ -6981,19 +6984,19 @@
         <v>55</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>22093.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>55</v>
@@ -7010,19 +7013,19 @@
         <v>56</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>325.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F223" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F223" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>56</v>
@@ -7039,19 +7042,19 @@
         <v>56</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>512430.0</v>
+        <v>451.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F224" s="7" t="n">
-        <v>40.0</v>
+        <v>12</v>
+      </c>
+      <c r="F224" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>56</v>
@@ -7068,19 +7071,19 @@
         <v>56</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>952.0</v>
+        <v>806692.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>56</v>
@@ -7097,13 +7100,13 @@
         <v>56</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>1164.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7126,13 +7129,13 @@
         <v>56</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>28983.0</v>
+        <v>344.0</v>
       </c>
       <c r="E227" s="7" t="s">
         <v>12</v>
@@ -7155,19 +7158,19 @@
         <v>56</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>13629.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F228" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F228" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>56</v>
@@ -7184,13 +7187,13 @@
         <v>56</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>5727.0</v>
+        <v>571.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7213,13 +7216,13 @@
         <v>56</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>5227.0</v>
+        <v>526.0</v>
       </c>
       <c r="E230" s="7" t="s">
         <v>12</v>
@@ -7245,16 +7248,16 @@
         <v>13</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>283905.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F231" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>56</v>
@@ -7271,19 +7274,19 @@
         <v>56</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>1182.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F232" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F232" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G232" s="8" t="s">
         <v>56</v>
@@ -7300,13 +7303,13 @@
         <v>56</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>939.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7329,16 +7332,16 @@
         <v>56</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>5147.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F234" s="7" t="n">
         <v>1.0</v>
@@ -7358,13 +7361,13 @@
         <v>56</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>486.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>12</v>
@@ -7387,13 +7390,13 @@
         <v>56</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>1502.0</v>
+        <v>816.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7416,19 +7419,19 @@
         <v>56</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>292130.0</v>
+        <v>456.0</v>
       </c>
       <c r="E237" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F237" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G237" s="8" t="s">
         <v>56</v>
@@ -7445,13 +7448,13 @@
         <v>56</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>1542.0</v>
+        <v>172.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7474,19 +7477,19 @@
         <v>56</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>1186.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F239" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F239" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>56</v>
@@ -7506,10 +7509,10 @@
         <v>10</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>85.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>12</v>
@@ -7535,16 +7538,16 @@
         <v>10</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>197.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F241" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F241" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>56</v>
@@ -7564,10 +7567,10 @@
         <v>10</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>728.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>12</v>
@@ -7593,16 +7596,16 @@
         <v>10</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>506367.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F243" s="7" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>56</v>
@@ -7616,16 +7619,16 @@
     </row>
     <row r="244">
       <c r="A244" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>356.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>12</v>
@@ -7634,10 +7637,10 @@
         <v>12</v>
       </c>
       <c r="G244" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H244" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I244" s="7" t="s">
         <v>12</v>
@@ -7648,19 +7651,19 @@
         <v>57</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>252920.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F245" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>57</v>
@@ -7677,13 +7680,13 @@
         <v>57</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>23967.0</v>
+        <v>325.0</v>
       </c>
       <c r="E246" s="7" t="s">
         <v>12</v>
@@ -7706,19 +7709,19 @@
         <v>57</v>
       </c>
       <c r="B247" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>74515.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F247" s="7" t="n">
-        <v>2.0</v>
+        <v>40.0</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>57</v>
@@ -7735,19 +7738,19 @@
         <v>57</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C248" s="5" t="s">
         <v>20</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>99098.0</v>
+        <v>952.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F248" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F248" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>57</v>
@@ -7764,13 +7767,13 @@
         <v>57</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>2825.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7793,13 +7796,13 @@
         <v>57</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>4020.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E250" s="7" t="s">
         <v>12</v>
@@ -7822,13 +7825,13 @@
         <v>57</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>146.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7851,19 +7854,19 @@
         <v>57</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>13942.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F252" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G252" s="8" t="s">
         <v>57</v>
@@ -7880,19 +7883,19 @@
         <v>57</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>773114.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F253" s="7" t="n">
-        <v>31.0</v>
+        <v>6.0</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>57</v>
@@ -7912,10 +7915,10 @@
         <v>10</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>18799.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E254" s="7" t="s">
         <v>12</v>
@@ -7938,13 +7941,13 @@
         <v>57</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>1274.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -7967,19 +7970,19 @@
         <v>57</v>
       </c>
       <c r="B256" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>17054.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E256" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F256" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F256" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G256" s="8" t="s">
         <v>57</v>
@@ -7996,19 +7999,19 @@
         <v>57</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>28978.0</v>
+        <v>728.0</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F257" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G257" s="8" t="s">
         <v>57</v>
@@ -8025,13 +8028,13 @@
         <v>57</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>17807.0</v>
+        <v>197.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8057,16 +8060,16 @@
         <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>1685.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F259" s="7" t="n">
-        <v>1.0</v>
+        <v>16.0</v>
       </c>
       <c r="G259" s="8" t="s">
         <v>57</v>
@@ -8086,10 +8089,10 @@
         <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>42880.0</v>
+        <v>85.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8112,19 +8115,19 @@
         <v>57</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>280988.0</v>
+        <v>939.0</v>
       </c>
       <c r="E261" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F261" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F261" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G261" s="8" t="s">
         <v>57</v>
@@ -8141,19 +8144,19 @@
         <v>57</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>12137.0</v>
+        <v>486.0</v>
       </c>
       <c r="E262" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F262" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F262" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G262" s="8" t="s">
         <v>57</v>
@@ -8170,19 +8173,19 @@
         <v>57</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>394262.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F263" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F263" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G263" s="8" t="s">
         <v>57</v>
@@ -8199,19 +8202,19 @@
         <v>57</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>11734.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F264" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F264" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G264" s="8" t="s">
         <v>57</v>
@@ -8228,13 +8231,13 @@
         <v>57</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>1644.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8254,16 +8257,16 @@
     </row>
     <row r="266">
       <c r="A266" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>7147.0</v>
+        <v>146.0</v>
       </c>
       <c r="E266" s="7" t="s">
         <v>12</v>
@@ -8272,10 +8275,10 @@
         <v>12</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>12</v>
@@ -8283,16 +8286,16 @@
     </row>
     <row r="267">
       <c r="A267" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>26497.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E267" s="7" t="s">
         <v>12</v>
@@ -8301,10 +8304,10 @@
         <v>12</v>
       </c>
       <c r="G267" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H267" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I267" s="7" t="s">
         <v>12</v>
@@ -8312,28 +8315,28 @@
     </row>
     <row r="268">
       <c r="A268" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>477111.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E268" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F268" s="7" t="n">
-        <v>13.0</v>
+        <v>2.0</v>
       </c>
       <c r="G268" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H268" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I268" s="7" t="s">
         <v>12</v>
@@ -8341,28 +8344,28 @@
     </row>
     <row r="269">
       <c r="A269" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>5285.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E269" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F269" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F269" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G269" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H269" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I269" s="7" t="s">
         <v>12</v>
@@ -8370,16 +8373,16 @@
     </row>
     <row r="270">
       <c r="A270" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B270" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C270" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>5788.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8388,10 +8391,10 @@
         <v>12</v>
       </c>
       <c r="G270" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H270" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I270" s="7" t="s">
         <v>12</v>
@@ -8399,28 +8402,28 @@
     </row>
     <row r="271">
       <c r="A271" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>26146.0</v>
+        <v>356.0</v>
       </c>
       <c r="E271" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F271" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F271" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G271" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H271" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I271" s="7" t="s">
         <v>12</v>
@@ -8428,28 +8431,28 @@
     </row>
     <row r="272">
       <c r="A272" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>14588.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E272" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F272" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F272" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G272" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H272" s="8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I272" s="7" t="s">
         <v>12</v>
@@ -8460,13 +8463,13 @@
         <v>58</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>23841.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>12</v>
@@ -8489,19 +8492,19 @@
         <v>58</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>199153.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E274" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F274" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G274" s="8" t="s">
         <v>58</v>
@@ -8518,19 +8521,19 @@
         <v>58</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>20617.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F275" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F275" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G275" s="8" t="s">
         <v>58</v>
@@ -8547,19 +8550,19 @@
         <v>58</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>38558.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E276" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F276" s="7" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="G276" s="8" t="s">
         <v>58</v>
@@ -8579,16 +8582,16 @@
         <v>13</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>126418.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E277" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F277" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F277" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G277" s="8" t="s">
         <v>58</v>
@@ -8605,13 +8608,13 @@
         <v>58</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D278" s="6" t="n">
-        <v>2200.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>12</v>
@@ -8634,19 +8637,19 @@
         <v>58</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>35873.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F279" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F279" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G279" s="8" t="s">
         <v>58</v>
@@ -8663,19 +8666,19 @@
         <v>58</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>16744.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E280" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F280" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F280" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G280" s="8" t="s">
         <v>58</v>
@@ -8692,19 +8695,19 @@
         <v>58</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>32194.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E281" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F281" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G281" s="8" t="s">
         <v>58</v>
@@ -8721,19 +8724,19 @@
         <v>58</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>542175.0</v>
+        <v>26497.0</v>
       </c>
       <c r="E282" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F282" s="7" t="n">
-        <v>9.0</v>
+        <v>12</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G282" s="8" t="s">
         <v>58</v>
@@ -8750,19 +8753,19 @@
         <v>58</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>274584.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F283" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G283" s="8" t="s">
         <v>58</v>
@@ -8779,19 +8782,19 @@
         <v>58</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>35692.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E284" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F284" s="7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G284" s="8" t="s">
         <v>58</v>
@@ -8808,19 +8811,19 @@
         <v>58</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>30762.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F285" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F285" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G285" s="8" t="s">
         <v>58</v>
@@ -8837,13 +8840,13 @@
         <v>58</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>19972.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E286" s="7" t="s">
         <v>12</v>
@@ -8866,13 +8869,13 @@
         <v>58</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>36976.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E287" s="7" t="s">
         <v>12</v>
@@ -8895,13 +8898,13 @@
         <v>58</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>74182.0</v>
+        <v>7147.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8927,16 +8930,16 @@
         <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>277603.0</v>
+        <v>477111.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F289" s="7" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>58</v>
@@ -8956,16 +8959,16 @@
         <v>10</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>61232.0</v>
+        <v>5285.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F290" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>58</v>
@@ -8985,16 +8988,16 @@
         <v>10</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D291" s="6" t="n">
-        <v>64701.0</v>
+        <v>5788.0</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F291" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F291" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G291" s="8" t="s">
         <v>58</v>
@@ -9014,16 +9017,16 @@
         <v>10</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D292" s="6" t="n">
-        <v>6327.0</v>
+        <v>26146.0</v>
       </c>
       <c r="E292" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F292" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F292" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G292" s="8" t="s">
         <v>58</v>
@@ -9043,16 +9046,16 @@
         <v>10</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>173630.0</v>
+        <v>14588.0</v>
       </c>
       <c r="E293" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F293" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F293" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G293" s="8" t="s">
         <v>58</v>
@@ -9075,10 +9078,10 @@
         <v>26</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>171789.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F294" s="7" t="n">
         <v>5.0</v>
@@ -9095,16 +9098,16 @@
     </row>
     <row r="295">
       <c r="A295" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>80351.0</v>
+        <v>23841.0</v>
       </c>
       <c r="E295" s="7" t="s">
         <v>12</v>
@@ -9113,10 +9116,10 @@
         <v>12</v>
       </c>
       <c r="G295" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H295" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I295" s="7" t="s">
         <v>12</v>
@@ -9124,28 +9127,28 @@
     </row>
     <row r="296">
       <c r="A296" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>26014.0</v>
+        <v>199153.0</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F296" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F296" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G296" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H296" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I296" s="7" t="s">
         <v>12</v>
@@ -9153,16 +9156,16 @@
     </row>
     <row r="297">
       <c r="A297" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>46</v>
+        <v>14</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>8810.0</v>
+        <v>20617.0</v>
       </c>
       <c r="E297" s="7" t="s">
         <v>12</v>
@@ -9171,10 +9174,10 @@
         <v>12</v>
       </c>
       <c r="G297" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H297" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I297" s="7" t="s">
         <v>12</v>
@@ -9182,28 +9185,28 @@
     </row>
     <row r="298">
       <c r="A298" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>2368.0</v>
+        <v>38558.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F298" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F298" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G298" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H298" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I298" s="7" t="s">
         <v>12</v>
@@ -9211,28 +9214,28 @@
     </row>
     <row r="299">
       <c r="A299" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>28702.0</v>
+        <v>126418.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F299" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F299" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G299" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H299" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I299" s="7" t="s">
         <v>12</v>
@@ -9240,28 +9243,28 @@
     </row>
     <row r="300">
       <c r="A300" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>247735.0</v>
+        <v>2200.0</v>
       </c>
       <c r="E300" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F300" s="7" t="n">
-        <v>10.0</v>
+        <v>12</v>
+      </c>
+      <c r="F300" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G300" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H300" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I300" s="7" t="s">
         <v>12</v>
@@ -9269,16 +9272,16 @@
     </row>
     <row r="301">
       <c r="A301" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>15987.0</v>
+        <v>35873.0</v>
       </c>
       <c r="E301" s="7" t="s">
         <v>12</v>
@@ -9287,10 +9290,10 @@
         <v>12</v>
       </c>
       <c r="G301" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H301" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I301" s="7" t="s">
         <v>12</v>
@@ -9298,30 +9301,668 @@
     </row>
     <row r="302">
       <c r="A302" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D302" s="6" t="n">
-        <v>48163.0</v>
+        <v>16744.0</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F302" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G302" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H302" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I302" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C303" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D303" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E303" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F303" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G303" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H303" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I303" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C304" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D304" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E304" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F304" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G304" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H304" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I304" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C305" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D305" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E305" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F305" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G305" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H305" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I305" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C306" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D306" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E306" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F306" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G306" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H306" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I306" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C307" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D307" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E307" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G307" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H307" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I307" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C308" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D308" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E308" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F308" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G308" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H308" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I308" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C309" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D309" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E309" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F309" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G309" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H309" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I309" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C310" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D310" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E310" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F310" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G310" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H310" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I310" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C311" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D311" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E311" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F311" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G311" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H311" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I311" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C312" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D312" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E312" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F312" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G312" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H312" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I312" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C313" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D313" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E313" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F313" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G313" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H313" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I313" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C314" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D314" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E314" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G314" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H314" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I314" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B315" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C315" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D315" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E315" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F315" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G315" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H315" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I315" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C316" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D316" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E316" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F316" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G316" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H316" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I316" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C317" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D317" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E317" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F317" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G317" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H317" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I317" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C318" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D318" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E318" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G318" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H318" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I318" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C319" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D319" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E319" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F319" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G319" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H319" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I319" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C320" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D320" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E320" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F320" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G320" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H320" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I320" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C321" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D321" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E321" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G321" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H321" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I321" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C322" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D322" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E322" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F322" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G322" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H322" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I322" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="C323" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D323" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E323" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F323" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G323" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H323" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I323" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C324" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D324" s="6" t="n">
+        <v>48163.0</v>
+      </c>
+      <c r="E324" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F324" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G324" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H324" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="I324" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2465" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="61">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-08-20</t>
+    <t>2026-08-21</t>
   </si>
   <si>
     <t>120253031332440341</t>
@@ -56,10 +56,16 @@
     <t>120253028817940341</t>
   </si>
   <si>
-    <t>120253028817970341</t>
+    <t>120253028817950341</t>
   </si>
   <si>
     <t>120253023460500341</t>
+  </si>
+  <si>
+    <t>120253023954740341</t>
+  </si>
+  <si>
+    <t>120253023954750341</t>
   </si>
   <si>
     <t>120253023954760341</t>
@@ -71,22 +77,16 @@
     <t>120253023954770341</t>
   </si>
   <si>
+    <t>120253023954790341</t>
+  </si>
+  <si>
+    <t>120253023954820341</t>
+  </si>
+  <si>
     <t>120253023954780341</t>
   </si>
   <si>
-    <t>120253023954790341</t>
-  </si>
-  <si>
-    <t>120253028817950341</t>
-  </si>
-  <si>
     <t>120253028817960341</t>
-  </si>
-  <si>
-    <t>120253023954800341</t>
-  </si>
-  <si>
-    <t>120253028817980341</t>
   </si>
   <si>
     <t>120253031332450341</t>
@@ -98,7 +98,7 @@
     <t>120253031332480341</t>
   </si>
   <si>
-    <t>120253031402010341</t>
+    <t>120253031332490341</t>
   </si>
   <si>
     <t>120253031402020341</t>
@@ -107,34 +107,40 @@
     <t>120253031402030341</t>
   </si>
   <si>
-    <t>2026-08-19</t>
+    <t>120253028817980341</t>
+  </si>
+  <si>
+    <t>2026-08-20</t>
+  </si>
+  <si>
+    <t>120253023954810341</t>
+  </si>
+  <si>
+    <t>120253023954800341</t>
   </si>
   <si>
     <t>120253023460490341</t>
   </si>
   <si>
-    <t>120253023954750341</t>
+    <t>120253028817970341</t>
   </si>
   <si>
-    <t>120253023954820341</t>
-  </si>
-  <si>
-    <t>120253023954740341</t>
-  </si>
-  <si>
-    <t>120253031332490341</t>
+    <t>120253031402050341</t>
   </si>
   <si>
     <t>120253028818100341</t>
   </si>
   <si>
-    <t>2026-08-18</t>
+    <t>120253031402010341</t>
   </si>
   <si>
     <t>120253031332460341</t>
   </si>
   <si>
-    <t>120253031402050341</t>
+    <t>2026-08-19</t>
+  </si>
+  <si>
+    <t>2026-08-18</t>
   </si>
   <si>
     <t>120253058581610341</t>
@@ -149,13 +155,10 @@
     <t>2026-08-17</t>
   </si>
   <si>
-    <t>120253023954810341</t>
+    <t>120253058581640341</t>
   </si>
   <si>
     <t>120253058581620341</t>
-  </si>
-  <si>
-    <t>120253058581640341</t>
   </si>
   <si>
     <t>120253058581660341</t>
@@ -555,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I324"/>
+  <dimension ref="A1:I346"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -610,7 +613,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>2970.0</v>
+        <v>58196.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -639,7 +642,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>52.0</v>
+        <v>10458.0</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>12</v>
@@ -668,13 +671,13 @@
         <v>16</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>103350.0</v>
+        <v>8781.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -694,16 +697,16 @@
         <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>71458.0</v>
+        <v>15162.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G5" s="8" t="s">
         <v>9</v>
@@ -723,16 +726,16 @@
         <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>37.0</v>
+        <v>150126.0</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -755,13 +758,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2292.0</v>
+        <v>205421.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -778,19 +781,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>521.0</v>
+        <v>8692.0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -807,13 +810,13 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>22</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4066.0</v>
+        <v>3201.0</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>12</v>
@@ -842,13 +845,13 @@
         <v>23</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>5440.0</v>
+        <v>11488.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -871,13 +874,13 @@
         <v>24</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>161144.0</v>
+        <v>2096.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -900,7 +903,7 @@
         <v>25</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>31738.0</v>
+        <v>15425.0</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
@@ -929,7 +932,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>7744.0</v>
+        <v>14903.0</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>12</v>
@@ -958,7 +961,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>10787.0</v>
+        <v>61152.0</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>12</v>
@@ -987,7 +990,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>1130.0</v>
+        <v>180.0</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
@@ -1016,13 +1019,13 @@
         <v>29</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>4162.0</v>
+        <v>31266.0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>9</v>
@@ -1045,10 +1048,10 @@
         <v>30</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>185270.0</v>
+        <v>228602.0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F17" s="7" t="n">
         <v>4.0</v>
@@ -1065,28 +1068,28 @@
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>125559.0</v>
+        <v>172144.0</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7" t="s">
         <v>12</v>
@@ -1094,28 +1097,28 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>8681.0</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="6" t="n">
-        <v>3681.0</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F19" s="7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="8" t="s">
-        <v>31</v>
-      </c>
       <c r="H19" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>12</v>
@@ -1123,28 +1126,28 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>8255.0</v>
+        <v>16546.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>12</v>
@@ -1152,28 +1155,28 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>353581.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H21" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>12</v>
@@ -1181,28 +1184,28 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>357152.0</v>
+        <v>5988.0</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>12</v>
@@ -1210,28 +1213,28 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>43146.0</v>
+        <v>16128.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F23" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>12</v>
@@ -1239,16 +1242,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>15392.0</v>
+        <v>22347.0</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>12</v>
@@ -1257,10 +1260,10 @@
         <v>12</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>12</v>
@@ -1268,28 +1271,28 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>5128.0</v>
+        <v>343161.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>12</v>
@@ -1297,28 +1300,28 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>4310.0</v>
+        <v>435968.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>12</v>
@@ -1326,16 +1329,16 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>26157.0</v>
+        <v>52.0</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>12</v>
@@ -1344,10 +1347,10 @@
         <v>12</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>12</v>
@@ -1355,16 +1358,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>13166.0</v>
+        <v>7421.0</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>12</v>
@@ -1373,10 +1376,10 @@
         <v>12</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>12</v>
@@ -1384,28 +1387,28 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>540962.0</v>
+        <v>63504.0</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>12</v>
@@ -1413,28 +1416,28 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="D30" s="6" t="n">
-        <v>73604.0</v>
+        <v>366264.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>12</v>
@@ -1442,28 +1445,28 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>48756.0</v>
+        <v>27003.0</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>12</v>
@@ -1471,16 +1474,16 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>120888.0</v>
+        <v>4714.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
@@ -1489,10 +1492,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>12</v>
@@ -1500,28 +1503,28 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>10204.0</v>
+        <v>4529.0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>12</v>
@@ -1529,28 +1532,28 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>643.0</v>
+        <v>603295.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>12</v>
@@ -1558,28 +1561,28 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>281884.0</v>
+        <v>37975.0</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>12</v>
@@ -1587,16 +1590,16 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1519.0</v>
+        <v>1379.0</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>12</v>
@@ -1605,10 +1608,10 @@
         <v>12</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>12</v>
@@ -1616,16 +1619,16 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>9553.0</v>
+        <v>19134.0</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>12</v>
@@ -1634,10 +1637,10 @@
         <v>12</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>12</v>
@@ -1645,28 +1648,28 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>337253.0</v>
+        <v>6788.0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>12</v>
@@ -1674,28 +1677,28 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>285274.0</v>
+        <v>88391.0</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F39" s="7" t="n">
-        <v>11.0</v>
+        <v>4.0</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>12</v>
@@ -1703,28 +1706,28 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>15292.0</v>
+        <v>125559.0</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>12</v>
@@ -1732,28 +1735,28 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>7105.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F41" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>12</v>
@@ -1761,28 +1764,28 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>95351.0</v>
+        <v>4310.0</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F42" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>12</v>
@@ -1790,16 +1793,16 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>4415.0</v>
+        <v>8255.0</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>12</v>
@@ -1808,10 +1811,10 @@
         <v>12</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>12</v>
@@ -1819,28 +1822,28 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>3958.0</v>
+        <v>353675.0</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>12</v>
@@ -1848,28 +1851,28 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>304338.0</v>
+        <v>357200.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F45" s="7" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>12</v>
@@ -1877,28 +1880,28 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>902.0</v>
+        <v>43146.0</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F46" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>12</v>
@@ -1906,16 +1909,16 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>2724.0</v>
+        <v>15392.0</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
@@ -1924,10 +1927,10 @@
         <v>12</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>12</v>
@@ -1935,28 +1938,28 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>62451.0</v>
+        <v>5128.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F48" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>12</v>
@@ -1964,16 +1967,16 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>4352.0</v>
+        <v>10758.0</v>
       </c>
       <c r="E49" s="7" t="s">
         <v>12</v>
@@ -1982,10 +1985,10 @@
         <v>12</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>12</v>
@@ -1993,28 +1996,28 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>33923.0</v>
+        <v>26157.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F50" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>12</v>
@@ -2022,28 +2025,28 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>437190.0</v>
+        <v>73604.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F51" s="7" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>12</v>
@@ -2051,7 +2054,7 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>10</v>
@@ -2060,19 +2063,19 @@
         <v>11</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>31713.0</v>
+        <v>48756.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F52" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>12</v>
@@ -2080,28 +2083,28 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>749.0</v>
+        <v>541580.0</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F53" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>12</v>
@@ -2109,28 +2112,28 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C54" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>284149.0</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G54" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C54" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="D54" s="6" t="n">
-        <v>90.0</v>
-      </c>
-      <c r="E54" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F54" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="H54" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>12</v>
@@ -2138,28 +2141,28 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C55" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>13166.0</v>
+      </c>
+      <c r="E55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C55" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D55" s="6" t="n">
-        <v>160872.0</v>
-      </c>
-      <c r="E55" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F55" s="7" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G55" s="8" t="s">
-        <v>38</v>
-      </c>
       <c r="H55" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>12</v>
@@ -2167,28 +2170,28 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>33470.0</v>
+        <v>120888.0</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F56" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>12</v>
@@ -2196,16 +2199,16 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>48.0</v>
+        <v>643.0</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>12</v>
@@ -2214,10 +2217,10 @@
         <v>12</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>12</v>
@@ -2225,16 +2228,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>7046.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
@@ -2243,10 +2246,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>12</v>
@@ -2254,28 +2257,28 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>135942.0</v>
+        <v>9553.0</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F59" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>12</v>
@@ -2283,28 +2286,28 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>147.0</v>
+        <v>287267.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>12</v>
@@ -2312,28 +2315,28 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>272.0</v>
+        <v>15292.0</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>12</v>
@@ -2341,28 +2344,28 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B62" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>311.0</v>
+        <v>7105.0</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>12</v>
@@ -2370,28 +2373,28 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>1979.0</v>
+        <v>95351.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>12</v>
@@ -2399,28 +2402,28 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>364072.0</v>
+        <v>4415.0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F64" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F64" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>12</v>
@@ -2428,28 +2431,28 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>468850.0</v>
+        <v>3958.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F65" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>12</v>
@@ -2457,28 +2460,28 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>428.0</v>
+        <v>304338.0</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>12</v>
@@ -2486,28 +2489,28 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>24918.0</v>
+        <v>337253.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>12</v>
@@ -2515,28 +2518,28 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>284401.0</v>
+        <v>902.0</v>
       </c>
       <c r="E68" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F68" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>12</v>
@@ -2544,16 +2547,16 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>3882.0</v>
+        <v>2724.0</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
@@ -2562,10 +2565,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I69" s="7" t="s">
         <v>12</v>
@@ -2573,28 +2576,28 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>1815.0</v>
+        <v>62451.0</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>12</v>
@@ -2602,16 +2605,16 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>167988.0</v>
+        <v>4352.0</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>12</v>
@@ -2620,10 +2623,10 @@
         <v>12</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>12</v>
@@ -2631,28 +2634,28 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>3746.0</v>
+        <v>33923.0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>12</v>
@@ -2660,28 +2663,28 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>87472.0</v>
+        <v>437190.0</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F73" s="7" t="n">
-        <v>4.0</v>
+        <v>12.0</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>12</v>
@@ -2689,28 +2692,28 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>712387.0</v>
+        <v>31713.0</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F74" s="7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>12</v>
@@ -2718,28 +2721,28 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>3904.0</v>
+        <v>749.0</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F75" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>12</v>
@@ -2747,16 +2750,16 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C76" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="D76" s="6" t="n">
-        <v>1703.0</v>
+        <v>90.0</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>12</v>
@@ -2765,10 +2768,10 @@
         <v>12</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I76" s="7" t="s">
         <v>12</v>
@@ -2776,28 +2779,28 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>945.0</v>
+        <v>160872.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F77" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F77" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I77" s="7" t="s">
         <v>12</v>
@@ -2805,28 +2808,28 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>11591.0</v>
+        <v>33470.0</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F78" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="I78" s="7" t="s">
         <v>12</v>
@@ -2834,28 +2837,28 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>501017.0</v>
+        <v>1979.0</v>
       </c>
       <c r="E79" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F79" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>12</v>
@@ -2863,28 +2866,28 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>3047.0</v>
+        <v>135942.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>12</v>
@@ -2892,16 +2895,16 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>7120.0</v>
+        <v>147.0</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>12</v>
@@ -2910,10 +2913,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>12</v>
@@ -2921,16 +2924,16 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>285.0</v>
+        <v>272.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
@@ -2939,10 +2942,10 @@
         <v>12</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>12</v>
@@ -2950,16 +2953,16 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>11414.0</v>
+        <v>48.0</v>
       </c>
       <c r="E83" s="7" t="s">
         <v>12</v>
@@ -2968,10 +2971,10 @@
         <v>12</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>12</v>
@@ -2979,28 +2982,28 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>24684.0</v>
+        <v>3882.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F84" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I84" s="7" t="s">
         <v>12</v>
@@ -3008,28 +3011,28 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>383.0</v>
+        <v>364072.0</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F85" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F85" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>12</v>
@@ -3037,28 +3040,28 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>2527.0</v>
+        <v>468850.0</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F86" s="7" t="n">
-        <v>1.0</v>
+        <v>11.0</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>12</v>
@@ -3066,16 +3069,16 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>10198.0</v>
+        <v>428.0</v>
       </c>
       <c r="E87" s="7" t="s">
         <v>12</v>
@@ -3084,10 +3087,10 @@
         <v>12</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>12</v>
@@ -3095,16 +3098,16 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B88" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>18.0</v>
+        <v>311.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3113,10 +3116,10 @@
         <v>12</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>12</v>
@@ -3124,28 +3127,28 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>244115.0</v>
+        <v>284401.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F89" s="7" t="n">
-        <v>11.0</v>
+        <v>3.0</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>12</v>
@@ -3153,28 +3156,28 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>638501.0</v>
+        <v>7046.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F90" s="7" t="n">
-        <v>20.0</v>
+        <v>12</v>
+      </c>
+      <c r="F90" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>12</v>
@@ -3182,16 +3185,16 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>6618.0</v>
+        <v>3746.0</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>12</v>
@@ -3200,10 +3203,10 @@
         <v>12</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>12</v>
@@ -3211,28 +3214,28 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B92" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>358088.0</v>
+        <v>24918.0</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F92" s="7" t="n">
-        <v>9.0</v>
+        <v>2.0</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>12</v>
@@ -3240,28 +3243,28 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>8877.0</v>
+        <v>3904.0</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>12</v>
@@ -3269,28 +3272,28 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D94" s="6" t="n">
-        <v>18008.0</v>
+        <v>501017.0</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F94" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I94" s="7" t="s">
         <v>12</v>
@@ -3298,16 +3301,16 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>173.0</v>
+        <v>11591.0</v>
       </c>
       <c r="E95" s="7" t="s">
         <v>12</v>
@@ -3316,10 +3319,10 @@
         <v>12</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I95" s="7" t="s">
         <v>12</v>
@@ -3327,16 +3330,16 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>11</v>
+        <v>48</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>12318.0</v>
+        <v>945.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -3345,10 +3348,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>12</v>
@@ -3356,28 +3359,28 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>384990.0</v>
+        <v>1703.0</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F97" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F97" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I97" s="7" t="s">
         <v>12</v>
@@ -3385,28 +3388,28 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="B98" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C98" s="5" t="s">
-        <v>39</v>
-      </c>
       <c r="D98" s="6" t="n">
-        <v>392.0</v>
+        <v>3047.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>12</v>
@@ -3414,28 +3417,28 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>772.0</v>
+        <v>712387.0</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F99" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F99" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>12</v>
@@ -3443,16 +3446,16 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>2068.0</v>
+        <v>1815.0</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>12</v>
@@ -3461,10 +3464,10 @@
         <v>12</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I100" s="7" t="s">
         <v>12</v>
@@ -3472,28 +3475,28 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>703357.0</v>
+        <v>167988.0</v>
       </c>
       <c r="E101" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F101" s="7" t="n">
-        <v>18.0</v>
+        <v>12</v>
+      </c>
+      <c r="F101" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I101" s="7" t="s">
         <v>12</v>
@@ -3501,28 +3504,28 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>31421.0</v>
+        <v>7120.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>12</v>
@@ -3530,28 +3533,28 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>212.0</v>
+        <v>87472.0</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F103" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F103" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>12</v>
@@ -3559,16 +3562,16 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>295.0</v>
+        <v>10198.0</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>12</v>
@@ -3577,10 +3580,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>12</v>
@@ -3588,28 +3591,28 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>42524.0</v>
+        <v>11414.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F105" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F105" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I105" s="7" t="s">
         <v>12</v>
@@ -3620,19 +3623,19 @@
         <v>50</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>336995.0</v>
+        <v>24684.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F106" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G106" s="8" t="s">
         <v>50</v>
@@ -3652,16 +3655,16 @@
         <v>15</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>435991.0</v>
+        <v>383.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F107" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F107" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G107" s="8" t="s">
         <v>50</v>
@@ -3681,10 +3684,10 @@
         <v>15</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>5248.0</v>
+        <v>285.0</v>
       </c>
       <c r="E108" s="7" t="s">
         <v>12</v>
@@ -3710,16 +3713,16 @@
         <v>15</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>650.0</v>
+        <v>638501.0</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G109" s="8" t="s">
         <v>50</v>
@@ -3736,13 +3739,13 @@
         <v>50</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>19816.0</v>
+        <v>18.0</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>12</v>
@@ -3765,19 +3768,19 @@
         <v>50</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>317924.0</v>
+        <v>244115.0</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F111" s="7" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G111" s="8" t="s">
         <v>50</v>
@@ -3794,13 +3797,13 @@
         <v>50</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>819.0</v>
+        <v>6618.0</v>
       </c>
       <c r="E112" s="7" t="s">
         <v>12</v>
@@ -3823,19 +3826,19 @@
         <v>50</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>4802.0</v>
+        <v>2527.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F113" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F113" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G113" s="8" t="s">
         <v>50</v>
@@ -3852,19 +3855,19 @@
         <v>50</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>17276.0</v>
+        <v>358088.0</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G114" s="8" t="s">
         <v>50</v>
@@ -3881,13 +3884,13 @@
         <v>50</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>29578.0</v>
+        <v>8877.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3913,10 +3916,10 @@
         <v>10</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>4237.0</v>
+        <v>18008.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -3942,16 +3945,16 @@
         <v>10</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>853298.0</v>
+        <v>173.0</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F117" s="7" t="n">
-        <v>27.0</v>
+        <v>12</v>
+      </c>
+      <c r="F117" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G117" s="8" t="s">
         <v>50</v>
@@ -3971,16 +3974,16 @@
         <v>10</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>2548.0</v>
+        <v>703357.0</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F118" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F118" s="7" t="n">
+        <v>18.0</v>
       </c>
       <c r="G118" s="8" t="s">
         <v>50</v>
@@ -3997,19 +4000,19 @@
         <v>50</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>5801.0</v>
+        <v>384990.0</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F119" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F119" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G119" s="8" t="s">
         <v>50</v>
@@ -4026,13 +4029,13 @@
         <v>50</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>1044.0</v>
+        <v>392.0</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>12</v>
@@ -4055,19 +4058,19 @@
         <v>50</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>401629.0</v>
+        <v>772.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F121" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F121" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G121" s="8" t="s">
         <v>50</v>
@@ -4084,13 +4087,13 @@
         <v>50</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>772.0</v>
+        <v>12318.0</v>
       </c>
       <c r="E122" s="7" t="s">
         <v>12</v>
@@ -4113,13 +4116,13 @@
         <v>50</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>1439.0</v>
+        <v>2068.0</v>
       </c>
       <c r="E123" s="7" t="s">
         <v>12</v>
@@ -4139,28 +4142,28 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>228.0</v>
+        <v>31421.0</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F124" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F124" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>12</v>
@@ -4168,28 +4171,28 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>22960.0</v>
+        <v>212.0</v>
       </c>
       <c r="E125" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F125" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F125" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>12</v>
@@ -4197,16 +4200,16 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>742.0</v>
+        <v>295.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
@@ -4215,10 +4218,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>12</v>
@@ -4226,28 +4229,28 @@
     </row>
     <row r="127">
       <c r="A127" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>8213.0</v>
+        <v>42524.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I127" s="7" t="s">
         <v>12</v>
@@ -4258,19 +4261,19 @@
         <v>51</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>462054.0</v>
+        <v>17276.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F128" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F128" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G128" s="8" t="s">
         <v>51</v>
@@ -4290,13 +4293,13 @@
         <v>15</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>378946.0</v>
+        <v>435991.0</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F129" s="7" t="n">
         <v>12.0</v>
@@ -4319,10 +4322,10 @@
         <v>15</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>2170.0</v>
+        <v>5248.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
@@ -4348,16 +4351,16 @@
         <v>15</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>14351.0</v>
+        <v>650.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F131" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F131" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>51</v>
@@ -4377,16 +4380,16 @@
         <v>13</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>324526.0</v>
+        <v>19816.0</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F132" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F132" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G132" s="8" t="s">
         <v>51</v>
@@ -4403,19 +4406,19 @@
         <v>51</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>14457.0</v>
+        <v>336995.0</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F133" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F133" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G133" s="8" t="s">
         <v>51</v>
@@ -4432,19 +4435,19 @@
         <v>51</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>3988.0</v>
+        <v>317924.0</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F134" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F134" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G134" s="8" t="s">
         <v>51</v>
@@ -4464,10 +4467,10 @@
         <v>13</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>1625.0</v>
+        <v>819.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
@@ -4493,10 +4496,10 @@
         <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>8383.0</v>
+        <v>4802.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
@@ -4522,10 +4525,10 @@
         <v>10</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>412.0</v>
+        <v>2548.0</v>
       </c>
       <c r="E137" s="7" t="s">
         <v>12</v>
@@ -4548,19 +4551,19 @@
         <v>51</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>445496.0</v>
+        <v>29578.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F138" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G138" s="8" t="s">
         <v>51</v>
@@ -4577,13 +4580,13 @@
         <v>51</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>3011.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4606,13 +4609,13 @@
         <v>51</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>385.0</v>
+        <v>772.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
@@ -4635,19 +4638,19 @@
         <v>51</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>696176.0</v>
+        <v>401629.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F141" s="7" t="n">
-        <v>12.0</v>
+        <v>5.0</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>51</v>
@@ -4667,16 +4670,16 @@
         <v>10</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>51544.0</v>
+        <v>1439.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F142" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>51</v>
@@ -4693,13 +4696,13 @@
         <v>51</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>2238.0</v>
+        <v>5801.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4725,16 +4728,16 @@
         <v>10</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>4481.0</v>
+        <v>853298.0</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F144" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F144" s="7" t="n">
+        <v>27.0</v>
       </c>
       <c r="G144" s="8" t="s">
         <v>51</v>
@@ -4754,10 +4757,10 @@
         <v>10</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>5324.0</v>
+        <v>4237.0</v>
       </c>
       <c r="E145" s="7" t="s">
         <v>12</v>
@@ -4780,13 +4783,13 @@
         <v>52</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>1563.0</v>
+        <v>8213.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
@@ -4812,16 +4815,16 @@
         <v>13</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>43627.0</v>
+        <v>324526.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F147" s="7" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G147" s="8" t="s">
         <v>52</v>
@@ -4838,13 +4841,13 @@
         <v>52</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>5765.0</v>
+        <v>2170.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4867,19 +4870,19 @@
         <v>52</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>379038.0</v>
+        <v>378946.0</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>52</v>
@@ -4896,19 +4899,19 @@
         <v>52</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>3659.0</v>
+        <v>462054.0</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F150" s="7" t="n">
-        <v>1.0</v>
+        <v>14.0</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>52</v>
@@ -4925,13 +4928,13 @@
         <v>52</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>7279.0</v>
+        <v>228.0</v>
       </c>
       <c r="E151" s="7" t="s">
         <v>12</v>
@@ -4954,19 +4957,19 @@
         <v>52</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>17021.0</v>
+        <v>742.0</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F152" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F152" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>52</v>
@@ -4983,13 +4986,13 @@
         <v>52</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>1293.0</v>
+        <v>3988.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5012,19 +5015,19 @@
         <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>12172.0</v>
+        <v>22960.0</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F154" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F154" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>52</v>
@@ -5041,13 +5044,13 @@
         <v>52</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>76.0</v>
+        <v>14457.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5070,19 +5073,19 @@
         <v>52</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>935238.0</v>
+        <v>14351.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>20.0</v>
+        <v>1.0</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>52</v>
@@ -5102,10 +5105,10 @@
         <v>10</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>5104.0</v>
+        <v>412.0</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>12</v>
@@ -5128,13 +5131,13 @@
         <v>52</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>2256.0</v>
+        <v>1625.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5157,13 +5160,13 @@
         <v>52</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>3472.0</v>
+        <v>5324.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>12</v>
@@ -5186,19 +5189,19 @@
         <v>52</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>378762.0</v>
+        <v>4481.0</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F160" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F160" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G160" s="8" t="s">
         <v>52</v>
@@ -5215,13 +5218,13 @@
         <v>52</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>5377.0</v>
+        <v>2238.0</v>
       </c>
       <c r="E161" s="7" t="s">
         <v>12</v>
@@ -5244,19 +5247,19 @@
         <v>52</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>1498.0</v>
+        <v>51544.0</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F162" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F162" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>52</v>
@@ -5273,19 +5276,19 @@
         <v>52</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>893824.0</v>
+        <v>696176.0</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F163" s="7" t="n">
-        <v>24.0</v>
+        <v>12.0</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>52</v>
@@ -5299,16 +5302,16 @@
     </row>
     <row r="164">
       <c r="A164" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>290.0</v>
+        <v>8383.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
@@ -5317,10 +5320,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>12</v>
@@ -5328,28 +5331,28 @@
     </row>
     <row r="165">
       <c r="A165" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>25346.0</v>
+        <v>3011.0</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F165" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F165" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>12</v>
@@ -5357,16 +5360,16 @@
     </row>
     <row r="166">
       <c r="A166" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>2276.0</v>
+        <v>385.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
@@ -5375,10 +5378,10 @@
         <v>12</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>12</v>
@@ -5386,28 +5389,28 @@
     </row>
     <row r="167">
       <c r="A167" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>15807.0</v>
+        <v>445496.0</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F167" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F167" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H167" s="8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>12</v>
@@ -5418,19 +5421,19 @@
         <v>53</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>2939.0</v>
+        <v>935238.0</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F168" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F168" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>53</v>
@@ -5447,19 +5450,19 @@
         <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>25848.0</v>
+        <v>378762.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F169" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>53</v>
@@ -5476,19 +5479,19 @@
         <v>53</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>700185.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F170" s="7" t="n">
-        <v>20.0</v>
+        <v>12</v>
+      </c>
+      <c r="F170" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>53</v>
@@ -5505,13 +5508,13 @@
         <v>53</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>3888.0</v>
+        <v>1293.0</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>12</v>
@@ -5534,13 +5537,13 @@
         <v>53</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>16525.0</v>
+        <v>2256.0</v>
       </c>
       <c r="E172" s="7" t="s">
         <v>12</v>
@@ -5563,19 +5566,19 @@
         <v>53</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>353476.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E173" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F173" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F173" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>53</v>
@@ -5592,13 +5595,13 @@
         <v>53</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>7643.0</v>
+        <v>76.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5621,19 +5624,19 @@
         <v>53</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>20739.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F175" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F175" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>53</v>
@@ -5653,10 +5656,10 @@
         <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>33363.0</v>
+        <v>1563.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>12</v>
@@ -5682,13 +5685,13 @@
         <v>10</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>9025.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F177" s="7" t="n">
         <v>2.0</v>
@@ -5711,16 +5714,16 @@
         <v>10</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>697336.0</v>
+        <v>7279.0</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F178" s="7" t="n">
-        <v>10.0</v>
+        <v>12</v>
+      </c>
+      <c r="F178" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G178" s="8" t="s">
         <v>53</v>
@@ -5740,16 +5743,16 @@
         <v>10</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>6325.0</v>
+        <v>3659.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F179" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F179" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>53</v>
@@ -5766,19 +5769,19 @@
         <v>53</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>3642.0</v>
+        <v>379038.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F180" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G180" s="8" t="s">
         <v>53</v>
@@ -5795,13 +5798,13 @@
         <v>53</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>7174.0</v>
+        <v>5765.0</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>12</v>
@@ -5824,16 +5827,16 @@
         <v>53</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>383981.0</v>
+        <v>43627.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F182" s="7" t="n">
         <v>2.0</v>
@@ -5850,28 +5853,28 @@
     </row>
     <row r="183">
       <c r="A183" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>480911.0</v>
+        <v>1498.0</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F183" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>12</v>
@@ -5879,28 +5882,28 @@
     </row>
     <row r="184">
       <c r="A184" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>100569.0</v>
+        <v>893824.0</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F184" s="7" t="n">
-        <v>2.0</v>
+        <v>24.0</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>12</v>
@@ -5908,16 +5911,16 @@
     </row>
     <row r="185">
       <c r="A185" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>3290.0</v>
+        <v>12172.0</v>
       </c>
       <c r="E185" s="7" t="s">
         <v>12</v>
@@ -5926,10 +5929,10 @@
         <v>12</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>12</v>
@@ -5943,16 +5946,16 @@
         <v>15</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>928.0</v>
+        <v>700185.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F186" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F186" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G186" s="8" t="s">
         <v>54</v>
@@ -5969,19 +5972,19 @@
         <v>54</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>83588.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F187" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G187" s="8" t="s">
         <v>54</v>
@@ -6004,7 +6007,7 @@
         <v>33</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>1474.0</v>
+        <v>290.0</v>
       </c>
       <c r="E188" s="7" t="s">
         <v>12</v>
@@ -6030,10 +6033,10 @@
         <v>15</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>794.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>12</v>
@@ -6056,19 +6059,19 @@
         <v>54</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>282217.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F190" s="7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>54</v>
@@ -6085,19 +6088,19 @@
         <v>54</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>46118.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F191" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F191" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>54</v>
@@ -6114,13 +6117,13 @@
         <v>54</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>2673.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>12</v>
@@ -6143,13 +6146,13 @@
         <v>54</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>889.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>12</v>
@@ -6172,19 +6175,19 @@
         <v>54</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>2220.0</v>
+        <v>353476.0</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F194" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>54</v>
@@ -6201,19 +6204,19 @@
         <v>54</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>21813.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F195" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F195" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>54</v>
@@ -6233,16 +6236,16 @@
         <v>10</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>7945.0</v>
+        <v>697336.0</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F196" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F196" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>54</v>
@@ -6259,19 +6262,19 @@
         <v>54</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>621293.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F197" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F197" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>54</v>
@@ -6288,13 +6291,13 @@
         <v>54</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>633.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>12</v>
@@ -6320,16 +6323,16 @@
         <v>10</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>70.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F199" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F199" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>54</v>
@@ -6349,10 +6352,10 @@
         <v>10</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>2029.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>12</v>
@@ -6375,13 +6378,13 @@
         <v>54</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>324.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>12</v>
@@ -6404,19 +6407,19 @@
         <v>54</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>357571.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F202" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G202" s="8" t="s">
         <v>54</v>
@@ -6430,28 +6433,28 @@
     </row>
     <row r="203">
       <c r="A203" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>1812.0</v>
+        <v>383981.0</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F203" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F203" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>12</v>
@@ -6459,16 +6462,16 @@
     </row>
     <row r="204">
       <c r="A204" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>5812.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6477,10 +6480,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>12</v>
@@ -6491,19 +6494,19 @@
         <v>55</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>112476.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F205" s="7" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G205" s="8" t="s">
         <v>55</v>
@@ -6523,16 +6526,16 @@
         <v>15</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>730436.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F206" s="7" t="n">
-        <v>24.0</v>
+        <v>14.0</v>
       </c>
       <c r="G206" s="8" t="s">
         <v>55</v>
@@ -6552,10 +6555,10 @@
         <v>15</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>199.0</v>
+        <v>928.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6578,19 +6581,19 @@
         <v>55</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>21</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>58187.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>55</v>
@@ -6607,19 +6610,19 @@
         <v>55</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>131368.0</v>
+        <v>889.0</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F209" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F209" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G209" s="8" t="s">
         <v>55</v>
@@ -6636,19 +6639,19 @@
         <v>55</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>218816.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F210" s="7" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>55</v>
@@ -6665,13 +6668,13 @@
         <v>55</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>3911.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E211" s="7" t="s">
         <v>12</v>
@@ -6694,13 +6697,13 @@
         <v>55</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>601.0</v>
+        <v>794.0</v>
       </c>
       <c r="E212" s="7" t="s">
         <v>12</v>
@@ -6723,13 +6726,13 @@
         <v>55</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>969.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6752,13 +6755,13 @@
         <v>55</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>33241.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6784,10 +6787,10 @@
         <v>10</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>70.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6810,19 +6813,19 @@
         <v>55</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>15780.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F216" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F216" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G216" s="8" t="s">
         <v>55</v>
@@ -6842,16 +6845,16 @@
         <v>10</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>637424.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F217" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F217" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G217" s="8" t="s">
         <v>55</v>
@@ -6874,7 +6877,7 @@
         <v>11</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>395.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6900,16 +6903,16 @@
         <v>10</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>5851.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F219" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F219" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G219" s="8" t="s">
         <v>55</v>
@@ -6926,13 +6929,13 @@
         <v>55</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>479.0</v>
+        <v>633.0</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>12</v>
@@ -6955,19 +6958,19 @@
         <v>55</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>386517.0</v>
+        <v>70.0</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F221" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F221" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>55</v>
@@ -6984,19 +6987,19 @@
         <v>55</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>4729.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F222" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F222" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>55</v>
@@ -7010,28 +7013,28 @@
     </row>
     <row r="223">
       <c r="A223" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>51830.0</v>
+        <v>324.0</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F223" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G223" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H223" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I223" s="7" t="s">
         <v>12</v>
@@ -7039,16 +7042,16 @@
     </row>
     <row r="224">
       <c r="A224" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>451.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>12</v>
@@ -7057,10 +7060,10 @@
         <v>12</v>
       </c>
       <c r="G224" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I224" s="7" t="s">
         <v>12</v>
@@ -7071,19 +7074,19 @@
         <v>56</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>806692.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F225" s="7" t="n">
-        <v>40.0</v>
+        <v>12</v>
+      </c>
+      <c r="F225" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G225" s="8" t="s">
         <v>56</v>
@@ -7103,10 +7106,10 @@
         <v>15</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>8605.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7132,16 +7135,16 @@
         <v>15</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>344.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F227" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F227" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>56</v>
@@ -7161,16 +7164,16 @@
         <v>15</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>65819.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F228" s="7" t="n">
-        <v>5.0</v>
+        <v>24.0</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>56</v>
@@ -7193,7 +7196,7 @@
         <v>33</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>571.0</v>
+        <v>199.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7216,19 +7219,19 @@
         <v>56</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>526.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F230" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F230" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>56</v>
@@ -7251,13 +7254,13 @@
         <v>24</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>249629.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F231" s="7" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>56</v>
@@ -7277,16 +7280,16 @@
         <v>13</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>107118.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F232" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G232" s="8" t="s">
         <v>56</v>
@@ -7306,10 +7309,10 @@
         <v>13</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>2994.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7332,19 +7335,19 @@
         <v>56</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>9408.0</v>
+        <v>601.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F234" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F234" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>56</v>
@@ -7364,10 +7367,10 @@
         <v>10</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>4379.0</v>
+        <v>969.0</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>12</v>
@@ -7390,13 +7393,13 @@
         <v>56</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>816.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7419,13 +7422,13 @@
         <v>56</v>
       </c>
       <c r="B237" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>456.0</v>
+        <v>70.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7448,13 +7451,13 @@
         <v>56</v>
       </c>
       <c r="B238" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>172.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7477,19 +7480,19 @@
         <v>56</v>
       </c>
       <c r="B239" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C239" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>407399.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F239" s="7" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>56</v>
@@ -7512,7 +7515,7 @@
         <v>11</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>3200.0</v>
+        <v>395.0</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>12</v>
@@ -7538,16 +7541,16 @@
         <v>10</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>747712.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E241" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F241" s="7" t="n">
-        <v>16.0</v>
+        <v>12</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G241" s="8" t="s">
         <v>56</v>
@@ -7564,13 +7567,13 @@
         <v>56</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>3128.0</v>
+        <v>479.0</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>12</v>
@@ -7593,19 +7596,19 @@
         <v>56</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>22093.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F243" s="7" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>56</v>
@@ -7622,13 +7625,13 @@
         <v>56</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>24685.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>12</v>
@@ -7651,19 +7654,19 @@
         <v>57</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>5147.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F245" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G245" s="8" t="s">
         <v>57</v>
@@ -7680,19 +7683,19 @@
         <v>57</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>325.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F246" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F246" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G246" s="8" t="s">
         <v>57</v>
@@ -7712,13 +7715,13 @@
         <v>15</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>512430.0</v>
+        <v>806692.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F247" s="7" t="n">
         <v>40.0</v>
@@ -7741,10 +7744,10 @@
         <v>15</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>952.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E248" s="7" t="s">
         <v>12</v>
@@ -7770,10 +7773,10 @@
         <v>15</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>1164.0</v>
+        <v>451.0</v>
       </c>
       <c r="E249" s="7" t="s">
         <v>12</v>
@@ -7796,19 +7799,19 @@
         <v>57</v>
       </c>
       <c r="B250" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>28983.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F250" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F250" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G250" s="8" t="s">
         <v>57</v>
@@ -7825,13 +7828,13 @@
         <v>57</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>5727.0</v>
+        <v>571.0</v>
       </c>
       <c r="E251" s="7" t="s">
         <v>12</v>
@@ -7854,13 +7857,13 @@
         <v>57</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>5227.0</v>
+        <v>344.0</v>
       </c>
       <c r="E252" s="7" t="s">
         <v>12</v>
@@ -7883,19 +7886,19 @@
         <v>57</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>283905.0</v>
+        <v>526.0</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F253" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F253" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>57</v>
@@ -7912,19 +7915,19 @@
         <v>57</v>
       </c>
       <c r="B254" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>1182.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F254" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F254" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G254" s="8" t="s">
         <v>57</v>
@@ -7941,13 +7944,13 @@
         <v>57</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>13629.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -7973,10 +7976,10 @@
         <v>10</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>1186.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>12</v>
@@ -7999,19 +8002,19 @@
         <v>57</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>728.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F257" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F257" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G257" s="8" t="s">
         <v>57</v>
@@ -8031,10 +8034,10 @@
         <v>10</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>197.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8057,19 +8060,19 @@
         <v>57</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>506367.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F259" s="7" t="n">
-        <v>16.0</v>
+        <v>11.0</v>
       </c>
       <c r="G259" s="8" t="s">
         <v>57</v>
@@ -8086,13 +8089,13 @@
         <v>57</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>85.0</v>
+        <v>456.0</v>
       </c>
       <c r="E260" s="7" t="s">
         <v>12</v>
@@ -8115,13 +8118,13 @@
         <v>57</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>939.0</v>
+        <v>172.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8144,13 +8147,13 @@
         <v>57</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>486.0</v>
+        <v>816.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8173,13 +8176,13 @@
         <v>57</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>47</v>
+        <v>11</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>1542.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8202,19 +8205,19 @@
         <v>57</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>292130.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F264" s="7" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="G264" s="8" t="s">
         <v>57</v>
@@ -8231,13 +8234,13 @@
         <v>57</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>1502.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8257,28 +8260,28 @@
     </row>
     <row r="266">
       <c r="A266" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B266" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C266" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>146.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F266" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F266" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G266" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H266" s="8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I266" s="7" t="s">
         <v>12</v>
@@ -8289,19 +8292,19 @@
         <v>58</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>23967.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F267" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F267" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G267" s="8" t="s">
         <v>58</v>
@@ -8318,19 +8321,19 @@
         <v>58</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>74515.0</v>
+        <v>325.0</v>
       </c>
       <c r="E268" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F268" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F268" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G268" s="8" t="s">
         <v>58</v>
@@ -8347,19 +8350,19 @@
         <v>58</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>99098.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E269" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F269" s="7" t="n">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="G269" s="8" t="s">
         <v>58</v>
@@ -8379,10 +8382,10 @@
         <v>15</v>
       </c>
       <c r="C270" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>2825.0</v>
+        <v>952.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8408,10 +8411,10 @@
         <v>15</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>356.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8434,19 +8437,19 @@
         <v>58</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>28978.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E272" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F272" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G272" s="8" t="s">
         <v>58</v>
@@ -8463,13 +8466,13 @@
         <v>58</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>4020.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E273" s="7" t="s">
         <v>12</v>
@@ -8492,19 +8495,19 @@
         <v>58</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>17054.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E274" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F274" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F274" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G274" s="8" t="s">
         <v>58</v>
@@ -8521,19 +8524,19 @@
         <v>58</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>13942.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F275" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G275" s="8" t="s">
         <v>58</v>
@@ -8550,19 +8553,19 @@
         <v>58</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>773114.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E276" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F276" s="7" t="n">
-        <v>31.0</v>
+        <v>12</v>
+      </c>
+      <c r="F276" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G276" s="8" t="s">
         <v>58</v>
@@ -8579,13 +8582,13 @@
         <v>58</v>
       </c>
       <c r="B277" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>17807.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8608,13 +8611,13 @@
         <v>58</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="D278" s="6" t="n">
-        <v>1274.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E278" s="7" t="s">
         <v>12</v>
@@ -8637,19 +8640,19 @@
         <v>58</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>252920.0</v>
+        <v>728.0</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F279" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F279" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G279" s="8" t="s">
         <v>58</v>
@@ -8666,13 +8669,13 @@
         <v>58</v>
       </c>
       <c r="B280" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>1644.0</v>
+        <v>197.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8698,16 +8701,16 @@
         <v>10</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>18799.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E281" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F281" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F281" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G281" s="8" t="s">
         <v>58</v>
@@ -8727,10 +8730,10 @@
         <v>10</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>26497.0</v>
+        <v>85.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8753,19 +8756,19 @@
         <v>58</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>1685.0</v>
+        <v>939.0</v>
       </c>
       <c r="E283" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F283" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F283" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G283" s="8" t="s">
         <v>58</v>
@@ -8782,19 +8785,19 @@
         <v>58</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>12137.0</v>
+        <v>486.0</v>
       </c>
       <c r="E284" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F284" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F284" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G284" s="8" t="s">
         <v>58</v>
@@ -8811,19 +8814,19 @@
         <v>58</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>394262.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E285" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F285" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F285" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G285" s="8" t="s">
         <v>58</v>
@@ -8840,19 +8843,19 @@
         <v>58</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>11734.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F286" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F286" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>58</v>
@@ -8869,13 +8872,13 @@
         <v>58</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>42880.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E287" s="7" t="s">
         <v>12</v>
@@ -8895,16 +8898,16 @@
     </row>
     <row r="288">
       <c r="A288" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>7147.0</v>
+        <v>146.0</v>
       </c>
       <c r="E288" s="7" t="s">
         <v>12</v>
@@ -8913,10 +8916,10 @@
         <v>12</v>
       </c>
       <c r="G288" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H288" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I288" s="7" t="s">
         <v>12</v>
@@ -8924,28 +8927,28 @@
     </row>
     <row r="289">
       <c r="A289" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>477111.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F289" s="7" t="n">
-        <v>13.0</v>
+        <v>12</v>
+      </c>
+      <c r="F289" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G289" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H289" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I289" s="7" t="s">
         <v>12</v>
@@ -8953,28 +8956,28 @@
     </row>
     <row r="290">
       <c r="A290" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>5285.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F290" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F290" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G290" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H290" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I290" s="7" t="s">
         <v>12</v>
@@ -8982,28 +8985,28 @@
     </row>
     <row r="291">
       <c r="A291" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="D291" s="6" t="n">
-        <v>5788.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F291" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F291" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G291" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H291" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I291" s="7" t="s">
         <v>12</v>
@@ -9011,28 +9014,28 @@
     </row>
     <row r="292">
       <c r="A292" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B292" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D292" s="6" t="n">
-        <v>26146.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E292" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F292" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F292" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G292" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H292" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I292" s="7" t="s">
         <v>12</v>
@@ -9040,16 +9043,16 @@
     </row>
     <row r="293">
       <c r="A293" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>14588.0</v>
+        <v>356.0</v>
       </c>
       <c r="E293" s="7" t="s">
         <v>12</v>
@@ -9058,10 +9061,10 @@
         <v>12</v>
       </c>
       <c r="G293" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H293" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I293" s="7" t="s">
         <v>12</v>
@@ -9069,28 +9072,28 @@
     </row>
     <row r="294">
       <c r="A294" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>280988.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F294" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G294" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H294" s="8" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="I294" s="7" t="s">
         <v>12</v>
@@ -9104,16 +9107,16 @@
         <v>15</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>23841.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F295" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F295" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>59</v>
@@ -9130,19 +9133,19 @@
         <v>59</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>199153.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E296" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F296" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F296" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G296" s="8" t="s">
         <v>59</v>
@@ -9159,19 +9162,19 @@
         <v>59</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>20617.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E297" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F297" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F297" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G297" s="8" t="s">
         <v>59</v>
@@ -9188,19 +9191,19 @@
         <v>59</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>38558.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F298" s="7" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>59</v>
@@ -9220,16 +9223,16 @@
         <v>13</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>126418.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E299" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F299" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F299" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G299" s="8" t="s">
         <v>59</v>
@@ -9249,10 +9252,10 @@
         <v>15</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>2200.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>12</v>
@@ -9275,19 +9278,19 @@
         <v>59</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>35873.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F301" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F301" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G301" s="8" t="s">
         <v>59</v>
@@ -9304,19 +9307,19 @@
         <v>59</v>
       </c>
       <c r="B302" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="D302" s="6" t="n">
-        <v>16744.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E302" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F302" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F302" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G302" s="8" t="s">
         <v>59</v>
@@ -9333,19 +9336,19 @@
         <v>59</v>
       </c>
       <c r="B303" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D303" s="6" t="n">
-        <v>32194.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F303" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F303" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G303" s="8" t="s">
         <v>59</v>
@@ -9362,19 +9365,19 @@
         <v>59</v>
       </c>
       <c r="B304" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C304" s="5" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D304" s="6" t="n">
-        <v>542175.0</v>
+        <v>26497.0</v>
       </c>
       <c r="E304" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F304" s="7" t="n">
-        <v>9.0</v>
+        <v>12</v>
+      </c>
+      <c r="F304" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G304" s="8" t="s">
         <v>59</v>
@@ -9391,19 +9394,19 @@
         <v>59</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>274584.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F305" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>59</v>
@@ -9420,19 +9423,19 @@
         <v>59</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>16</v>
+        <v>49</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>35692.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F306" s="7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G306" s="8" t="s">
         <v>59</v>
@@ -9449,19 +9452,19 @@
         <v>59</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>30762.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E307" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F307" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F307" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G307" s="8" t="s">
         <v>59</v>
@@ -9478,13 +9481,13 @@
         <v>59</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>19972.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E308" s="7" t="s">
         <v>12</v>
@@ -9507,13 +9510,13 @@
         <v>59</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="C309" s="5" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>36976.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9536,13 +9539,13 @@
         <v>59</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>74182.0</v>
+        <v>7147.0</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>12</v>
@@ -9568,16 +9571,16 @@
         <v>10</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>277603.0</v>
+        <v>477111.0</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F311" s="7" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G311" s="8" t="s">
         <v>59</v>
@@ -9597,16 +9600,16 @@
         <v>10</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>61232.0</v>
+        <v>5285.0</v>
       </c>
       <c r="E312" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F312" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F312" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G312" s="8" t="s">
         <v>59</v>
@@ -9626,16 +9629,16 @@
         <v>10</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>64701.0</v>
+        <v>5788.0</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F313" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F313" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G313" s="8" t="s">
         <v>59</v>
@@ -9658,13 +9661,13 @@
         <v>28</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>6327.0</v>
+        <v>26146.0</v>
       </c>
       <c r="E314" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F314" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F314" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G314" s="8" t="s">
         <v>59</v>
@@ -9684,16 +9687,16 @@
         <v>10</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>173630.0</v>
+        <v>14588.0</v>
       </c>
       <c r="E315" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F315" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F315" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G315" s="8" t="s">
         <v>59</v>
@@ -9713,13 +9716,13 @@
         <v>10</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>171789.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F316" s="7" t="n">
         <v>5.0</v>
@@ -9736,16 +9739,16 @@
     </row>
     <row r="317">
       <c r="A317" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B317" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>80351.0</v>
+        <v>23841.0</v>
       </c>
       <c r="E317" s="7" t="s">
         <v>12</v>
@@ -9754,10 +9757,10 @@
         <v>12</v>
       </c>
       <c r="G317" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H317" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I317" s="7" t="s">
         <v>12</v>
@@ -9765,28 +9768,28 @@
     </row>
     <row r="318">
       <c r="A318" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>26014.0</v>
+        <v>199153.0</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F318" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F318" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G318" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H318" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I318" s="7" t="s">
         <v>12</v>
@@ -9794,16 +9797,16 @@
     </row>
     <row r="319">
       <c r="A319" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>8810.0</v>
+        <v>20617.0</v>
       </c>
       <c r="E319" s="7" t="s">
         <v>12</v>
@@ -9812,10 +9815,10 @@
         <v>12</v>
       </c>
       <c r="G319" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H319" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I319" s="7" t="s">
         <v>12</v>
@@ -9823,28 +9826,28 @@
     </row>
     <row r="320">
       <c r="A320" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>2368.0</v>
+        <v>38558.0</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F320" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F320" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G320" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H320" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I320" s="7" t="s">
         <v>12</v>
@@ -9852,28 +9855,28 @@
     </row>
     <row r="321">
       <c r="A321" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B321" s="5" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>28702.0</v>
+        <v>126418.0</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F321" s="7" t="s">
-        <v>12</v>
+        <v>19</v>
+      </c>
+      <c r="F321" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G321" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H321" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I321" s="7" t="s">
         <v>12</v>
@@ -9881,28 +9884,28 @@
     </row>
     <row r="322">
       <c r="A322" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B322" s="5" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>247735.0</v>
+        <v>2200.0</v>
       </c>
       <c r="E322" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="F322" s="7" t="n">
-        <v>10.0</v>
+        <v>12</v>
+      </c>
+      <c r="F322" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G322" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H322" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I322" s="7" t="s">
         <v>12</v>
@@ -9910,16 +9913,16 @@
     </row>
     <row r="323">
       <c r="A323" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C323" s="5" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>15987.0</v>
+        <v>35873.0</v>
       </c>
       <c r="E323" s="7" t="s">
         <v>12</v>
@@ -9928,10 +9931,10 @@
         <v>12</v>
       </c>
       <c r="G323" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H323" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I323" s="7" t="s">
         <v>12</v>
@@ -9939,30 +9942,668 @@
     </row>
     <row r="324">
       <c r="A324" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>48163.0</v>
+        <v>16744.0</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F324" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G324" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H324" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I324" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C325" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D325" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E325" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F325" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G325" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H325" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I325" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C326" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D326" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E326" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F326" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G326" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H326" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I326" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C327" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D327" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E327" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F327" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G327" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H327" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I327" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C328" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D328" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E328" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F328" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G328" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H328" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I328" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C329" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D329" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E329" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F329" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G329" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H329" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I329" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C330" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D330" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E330" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F330" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G330" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H330" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I330" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C331" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D331" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E331" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F331" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G331" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H331" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I331" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C332" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D332" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E332" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F332" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G332" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H332" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I332" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C333" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D333" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E333" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F333" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G333" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H333" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I333" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C334" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D334" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E334" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F334" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G334" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H334" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I334" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C335" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D335" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E335" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F335" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G335" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H335" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I335" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C336" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D336" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E336" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F336" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G336" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H336" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I336" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C337" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D337" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E337" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F337" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G337" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H337" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I337" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C338" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D338" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E338" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F338" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G338" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H338" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I338" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C339" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D339" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E339" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F339" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G339" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H339" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I339" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C340" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D340" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E340" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F340" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G340" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H340" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I340" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C341" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D341" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E341" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F341" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G341" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H341" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I341" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C342" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D342" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E342" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F342" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G342" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H342" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I342" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C343" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D343" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E343" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F343" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G343" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H343" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I343" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C344" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D344" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E344" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F344" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G344" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H344" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I344" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C345" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D345" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E345" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F345" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G345" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H345" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I345" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C346" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D346" s="6" t="n">
+        <v>48163.0</v>
+      </c>
+      <c r="E346" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F346" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G346" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H346" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I346" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2799" uniqueCount="62">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,13 +41,13 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-08-21</t>
+    <t>2026-08-22</t>
   </si>
   <si>
     <t>120253031332440341</t>
   </si>
   <si>
-    <t>120253031402040341</t>
+    <t>120253031402050341</t>
   </si>
   <si>
     <t/>
@@ -56,13 +56,16 @@
     <t>120253028817940341</t>
   </si>
   <si>
-    <t>120253028817950341</t>
+    <t>120253028817960341</t>
   </si>
   <si>
     <t>120253023460500341</t>
   </si>
   <si>
-    <t>120253023954740341</t>
+    <t>120253023460490341</t>
+  </si>
+  <si>
+    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
   </si>
   <si>
     <t>120253023954750341</t>
@@ -71,25 +74,25 @@
     <t>120253023954760341</t>
   </si>
   <si>
-    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
-  </si>
-  <si>
     <t>120253023954770341</t>
   </si>
   <si>
     <t>120253023954790341</t>
   </si>
   <si>
-    <t>120253023954820341</t>
+    <t>120253023954800341</t>
+  </si>
+  <si>
+    <t>120253028817950341</t>
   </si>
   <si>
     <t>120253023954780341</t>
   </si>
   <si>
-    <t>120253028817960341</t>
+    <t>120253028817980341</t>
   </si>
   <si>
-    <t>120253031332450341</t>
+    <t>120253031332460341</t>
   </si>
   <si>
     <t>120253031332470341</t>
@@ -98,16 +101,34 @@
     <t>120253031332480341</t>
   </si>
   <si>
-    <t>120253031332490341</t>
-  </si>
-  <si>
     <t>120253031402020341</t>
   </si>
   <si>
     <t>120253031402030341</t>
   </si>
   <si>
-    <t>120253028817980341</t>
+    <t>120253031402040341</t>
+  </si>
+  <si>
+    <t>120253031332450341</t>
+  </si>
+  <si>
+    <t>2026-08-21</t>
+  </si>
+  <si>
+    <t>120253023954740341</t>
+  </si>
+  <si>
+    <t>120253023954820341</t>
+  </si>
+  <si>
+    <t>120253031402010341</t>
+  </si>
+  <si>
+    <t>120253028817970341</t>
+  </si>
+  <si>
+    <t>120253031332490341</t>
   </si>
   <si>
     <t>2026-08-20</t>
@@ -116,25 +137,7 @@
     <t>120253023954810341</t>
   </si>
   <si>
-    <t>120253023954800341</t>
-  </si>
-  <si>
-    <t>120253023460490341</t>
-  </si>
-  <si>
-    <t>120253028817970341</t>
-  </si>
-  <si>
-    <t>120253031402050341</t>
-  </si>
-  <si>
     <t>120253028818100341</t>
-  </si>
-  <si>
-    <t>120253031402010341</t>
-  </si>
-  <si>
-    <t>120253031332460341</t>
   </si>
   <si>
     <t>2026-08-19</t>
@@ -155,13 +158,13 @@
     <t>2026-08-17</t>
   </si>
   <si>
+    <t>120253058581660341</t>
+  </si>
+  <si>
     <t>120253058581640341</t>
   </si>
   <si>
     <t>120253058581620341</t>
-  </si>
-  <si>
-    <t>120253058581660341</t>
   </si>
   <si>
     <t>2026-08-16</t>
@@ -558,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I346"/>
+  <dimension ref="A1:I368"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -613,7 +616,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>58196.0</v>
+        <v>6351.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -642,7 +645,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>10458.0</v>
+        <v>378.0</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>12</v>
@@ -671,13 +674,13 @@
         <v>16</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>8781.0</v>
+        <v>24935.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -697,10 +700,10 @@
         <v>15</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>15162.0</v>
+        <v>5628.0</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>12</v>
@@ -726,16 +729,16 @@
         <v>15</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>150126.0</v>
+        <v>70028.0</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -758,13 +761,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>205421.0</v>
+        <v>45244.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -787,7 +790,7 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>8692.0</v>
+        <v>3497.0</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
@@ -816,7 +819,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3201.0</v>
+        <v>585.0</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>12</v>
@@ -839,19 +842,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>11488.0</v>
+        <v>7298.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -868,19 +871,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2096.0</v>
+        <v>4621.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -897,19 +900,19 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>15425.0</v>
+        <v>70896.0</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G12" s="8" t="s">
         <v>9</v>
@@ -932,7 +935,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>14903.0</v>
+        <v>1886.0</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>12</v>
@@ -961,7 +964,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>61152.0</v>
+        <v>3072.0</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>12</v>
@@ -990,7 +993,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>180.0</v>
+        <v>5426.0</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>12</v>
@@ -1019,13 +1022,13 @@
         <v>29</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>31266.0</v>
+        <v>7487.0</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F16" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>9</v>
@@ -1048,13 +1051,13 @@
         <v>30</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>228602.0</v>
+        <v>83155.0</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>9</v>
@@ -1071,19 +1074,19 @@
         <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>172144.0</v>
+        <v>4849.0</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>9</v>
@@ -1097,16 +1100,16 @@
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D19" s="6" t="n">
-        <v>8681.0</v>
+        <v>16766.0</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>12</v>
@@ -1115,10 +1118,10 @@
         <v>12</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7" t="s">
         <v>12</v>
@@ -1126,28 +1129,28 @@
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>16546.0</v>
+        <v>317621.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>1.0</v>
+        <v>9.0</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I20" s="7" t="s">
         <v>12</v>
@@ -1155,28 +1158,28 @@
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3994.0</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D21" s="6" t="n">
-        <v>1274.0</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F21" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>32</v>
-      </c>
       <c r="H21" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="7" t="s">
         <v>12</v>
@@ -1184,28 +1187,28 @@
     </row>
     <row r="22">
       <c r="A22" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>5988.0</v>
+        <v>32651.0</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H22" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I22" s="7" t="s">
         <v>12</v>
@@ -1213,28 +1216,28 @@
     </row>
     <row r="23">
       <c r="A23" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>16128.0</v>
+        <v>16899.0</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G23" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I23" s="7" t="s">
         <v>12</v>
@@ -1242,16 +1245,16 @@
     </row>
     <row r="24">
       <c r="A24" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>22347.0</v>
+        <v>3803.0</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>12</v>
@@ -1260,10 +1263,10 @@
         <v>12</v>
       </c>
       <c r="G24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H24" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I24" s="7" t="s">
         <v>12</v>
@@ -1271,28 +1274,28 @@
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>343161.0</v>
+        <v>379933.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>14.0</v>
+        <v>11.0</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H25" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I25" s="7" t="s">
         <v>12</v>
@@ -1300,7 +1303,7 @@
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>15</v>
@@ -1309,19 +1312,19 @@
         <v>18</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>435968.0</v>
+        <v>17848.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F26" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H26" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="7" t="s">
         <v>12</v>
@@ -1329,16 +1332,16 @@
     </row>
     <row r="27">
       <c r="A27" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>52.0</v>
+        <v>8781.0</v>
       </c>
       <c r="E27" s="7" t="s">
         <v>12</v>
@@ -1347,10 +1350,10 @@
         <v>12</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H27" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I27" s="7" t="s">
         <v>12</v>
@@ -1358,16 +1361,16 @@
     </row>
     <row r="28">
       <c r="A28" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>7421.0</v>
+        <v>22080.0</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>12</v>
@@ -1376,10 +1379,10 @@
         <v>12</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H28" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I28" s="7" t="s">
         <v>12</v>
@@ -1387,16 +1390,16 @@
     </row>
     <row r="29">
       <c r="A29" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>63504.0</v>
+        <v>3201.0</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>12</v>
@@ -1405,10 +1408,10 @@
         <v>12</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H29" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="7" t="s">
         <v>12</v>
@@ -1416,28 +1419,28 @@
     </row>
     <row r="30">
       <c r="A30" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>366264.0</v>
+        <v>76184.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F30" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G30" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H30" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I30" s="7" t="s">
         <v>12</v>
@@ -1445,28 +1448,28 @@
     </row>
     <row r="31">
       <c r="A31" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>27003.0</v>
+        <v>5345.0</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G31" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H31" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I31" s="7" t="s">
         <v>12</v>
@@ -1474,16 +1477,16 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>4714.0</v>
+        <v>875.0</v>
       </c>
       <c r="E32" s="7" t="s">
         <v>12</v>
@@ -1492,10 +1495,10 @@
         <v>12</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>12</v>
@@ -1503,28 +1506,28 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>4529.0</v>
+        <v>240.0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>12</v>
@@ -1532,7 +1535,7 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>10</v>
@@ -1541,19 +1544,19 @@
         <v>30</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>603295.0</v>
+        <v>486614.0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F34" s="7" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>12</v>
@@ -1561,28 +1564,28 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>37975.0</v>
+        <v>44164.0</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F35" s="7" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>12</v>
@@ -1590,16 +1593,16 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>1379.0</v>
+        <v>118009.0</v>
       </c>
       <c r="E36" s="7" t="s">
         <v>12</v>
@@ -1608,10 +1611,10 @@
         <v>12</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>12</v>
@@ -1619,16 +1622,16 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>19134.0</v>
+        <v>180.0</v>
       </c>
       <c r="E37" s="7" t="s">
         <v>12</v>
@@ -1637,10 +1640,10 @@
         <v>12</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>12</v>
@@ -1648,28 +1651,28 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>6788.0</v>
+        <v>27707.0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>12</v>
@@ -1677,28 +1680,28 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C39" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="D39" s="6" t="n">
-        <v>88391.0</v>
+        <v>27807.0</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F39" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>12</v>
@@ -1706,28 +1709,28 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>125559.0</v>
+        <v>337133.0</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F40" s="7" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>12</v>
@@ -1735,28 +1738,28 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D41" s="6" t="n">
-        <v>3681.0</v>
+        <v>52.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>12</v>
@@ -1764,7 +1767,7 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>15</v>
@@ -1773,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="D42" s="6" t="n">
-        <v>4310.0</v>
+        <v>16128.0</v>
       </c>
       <c r="E42" s="7" t="s">
         <v>12</v>
@@ -1782,10 +1785,10 @@
         <v>12</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>12</v>
@@ -1793,28 +1796,28 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>8255.0</v>
+        <v>435968.0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>12</v>
@@ -1822,28 +1825,28 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>353675.0</v>
+        <v>343217.0</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F44" s="7" t="n">
-        <v>11.0</v>
+        <v>14.0</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>12</v>
@@ -1851,28 +1854,28 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>357200.0</v>
+        <v>22347.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F45" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F45" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>12</v>
@@ -1880,28 +1883,28 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>43146.0</v>
+        <v>8681.0</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F46" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>12</v>
@@ -1909,16 +1912,16 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>15392.0</v>
+        <v>5988.0</v>
       </c>
       <c r="E47" s="7" t="s">
         <v>12</v>
@@ -1927,10 +1930,10 @@
         <v>12</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>12</v>
@@ -1938,16 +1941,16 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D48" s="6" t="n">
-        <v>5128.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E48" s="7" t="s">
         <v>12</v>
@@ -1956,10 +1959,10 @@
         <v>12</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>12</v>
@@ -1967,28 +1970,28 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>10758.0</v>
+        <v>16546.0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>12</v>
@@ -1996,16 +1999,16 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>26157.0</v>
+        <v>7421.0</v>
       </c>
       <c r="E50" s="7" t="s">
         <v>12</v>
@@ -2014,10 +2017,10 @@
         <v>12</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>12</v>
@@ -2025,28 +2028,28 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>73604.0</v>
+        <v>1379.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>12</v>
@@ -2054,28 +2057,28 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>48756.0</v>
+        <v>366264.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F52" s="7" t="n">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>12</v>
@@ -2083,28 +2086,28 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>541580.0</v>
+        <v>27003.0</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>12</v>
@@ -2112,28 +2115,28 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>284149.0</v>
+        <v>4714.0</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F54" s="7" t="n">
-        <v>10.0</v>
+        <v>12</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>12</v>
@@ -2141,28 +2144,28 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B55" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>28</v>
-      </c>
       <c r="D55" s="6" t="n">
-        <v>13166.0</v>
+        <v>4529.0</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F55" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>12</v>
@@ -2170,28 +2173,28 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>120888.0</v>
+        <v>603295.0</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F56" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>12</v>
@@ -2199,28 +2202,28 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>643.0</v>
+        <v>37975.0</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F57" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>12</v>
@@ -2228,16 +2231,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>1519.0</v>
+        <v>63504.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
@@ -2246,10 +2249,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>12</v>
@@ -2257,16 +2260,16 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>9553.0</v>
+        <v>19134.0</v>
       </c>
       <c r="E59" s="7" t="s">
         <v>12</v>
@@ -2275,10 +2278,10 @@
         <v>12</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>12</v>
@@ -2286,28 +2289,28 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>287267.0</v>
+        <v>6788.0</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F60" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F60" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>12</v>
@@ -2315,28 +2318,28 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>15292.0</v>
+        <v>88483.0</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F61" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>12</v>
@@ -2350,13 +2353,13 @@
         <v>15</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>7105.0</v>
+        <v>3681.0</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F62" s="7" t="n">
         <v>1.0</v>
@@ -2376,19 +2379,19 @@
         <v>42</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>95351.0</v>
+        <v>4310.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G63" s="8" t="s">
         <v>42</v>
@@ -2405,13 +2408,13 @@
         <v>42</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>4415.0</v>
+        <v>8255.0</v>
       </c>
       <c r="E64" s="7" t="s">
         <v>12</v>
@@ -2434,19 +2437,19 @@
         <v>42</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>3958.0</v>
+        <v>353675.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G65" s="8" t="s">
         <v>42</v>
@@ -2463,19 +2466,19 @@
         <v>42</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>304338.0</v>
+        <v>357200.0</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>5.0</v>
+        <v>12.0</v>
       </c>
       <c r="G66" s="8" t="s">
         <v>42</v>
@@ -2495,16 +2498,16 @@
         <v>15</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>337253.0</v>
+        <v>43146.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G67" s="8" t="s">
         <v>42</v>
@@ -2521,13 +2524,13 @@
         <v>42</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>902.0</v>
+        <v>15392.0</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>12</v>
@@ -2550,13 +2553,13 @@
         <v>42</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>2724.0</v>
+        <v>5128.0</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
@@ -2579,19 +2582,19 @@
         <v>42</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>62451.0</v>
+        <v>125559.0</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F70" s="7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G70" s="8" t="s">
         <v>42</v>
@@ -2608,13 +2611,13 @@
         <v>42</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>4352.0</v>
+        <v>26157.0</v>
       </c>
       <c r="E71" s="7" t="s">
         <v>12</v>
@@ -2637,19 +2640,19 @@
         <v>42</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>33923.0</v>
+        <v>284149.0</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F72" s="7" t="n">
-        <v>1.0</v>
+        <v>10.0</v>
       </c>
       <c r="G72" s="8" t="s">
         <v>42</v>
@@ -2669,16 +2672,16 @@
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>437190.0</v>
+        <v>10758.0</v>
       </c>
       <c r="E73" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F73" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G73" s="8" t="s">
         <v>42</v>
@@ -2698,16 +2701,16 @@
         <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>31713.0</v>
+        <v>120888.0</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G74" s="8" t="s">
         <v>42</v>
@@ -2727,10 +2730,10 @@
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>749.0</v>
+        <v>13166.0</v>
       </c>
       <c r="E75" s="7" t="s">
         <v>12</v>
@@ -2753,19 +2756,19 @@
         <v>42</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>90.0</v>
+        <v>73604.0</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F76" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G76" s="8" t="s">
         <v>42</v>
@@ -2782,19 +2785,19 @@
         <v>42</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>160872.0</v>
+        <v>541580.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F77" s="7" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="G77" s="8" t="s">
         <v>42</v>
@@ -2814,13 +2817,13 @@
         <v>10</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>33470.0</v>
+        <v>48756.0</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F78" s="7" t="n">
         <v>1.0</v>
@@ -2837,16 +2840,16 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>1979.0</v>
+        <v>643.0</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>12</v>
@@ -2855,10 +2858,10 @@
         <v>12</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>12</v>
@@ -2866,28 +2869,28 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>135942.0</v>
+        <v>7105.0</v>
       </c>
       <c r="E80" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F80" s="7" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>12</v>
@@ -2895,16 +2898,16 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>147.0</v>
+        <v>3958.0</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>12</v>
@@ -2913,10 +2916,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>12</v>
@@ -2924,16 +2927,16 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>272.0</v>
+        <v>4415.0</v>
       </c>
       <c r="E82" s="7" t="s">
         <v>12</v>
@@ -2942,10 +2945,10 @@
         <v>12</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>12</v>
@@ -2953,28 +2956,28 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>48.0</v>
+        <v>95351.0</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>12</v>
@@ -2982,16 +2985,16 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B84" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>3882.0</v>
+        <v>1519.0</v>
       </c>
       <c r="E84" s="7" t="s">
         <v>12</v>
@@ -3000,10 +3003,10 @@
         <v>12</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I84" s="7" t="s">
         <v>12</v>
@@ -3011,28 +3014,28 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>364072.0</v>
+        <v>15292.0</v>
       </c>
       <c r="E85" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F85" s="7" t="n">
-        <v>11.0</v>
+        <v>1.0</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>12</v>
@@ -3040,28 +3043,28 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>468850.0</v>
+        <v>287267.0</v>
       </c>
       <c r="E86" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F86" s="7" t="n">
         <v>11.0</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>12</v>
@@ -3069,28 +3072,28 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>428.0</v>
+        <v>337253.0</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F87" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>12</v>
@@ -3098,16 +3101,16 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>311.0</v>
+        <v>9553.0</v>
       </c>
       <c r="E88" s="7" t="s">
         <v>12</v>
@@ -3116,10 +3119,10 @@
         <v>12</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>12</v>
@@ -3127,28 +3130,28 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>284401.0</v>
+        <v>902.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F89" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F89" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>12</v>
@@ -3156,28 +3159,28 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B90" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>7046.0</v>
+        <v>304338.0</v>
       </c>
       <c r="E90" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F90" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F90" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>12</v>
@@ -3185,16 +3188,16 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B91" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>3746.0</v>
+        <v>2724.0</v>
       </c>
       <c r="E91" s="7" t="s">
         <v>12</v>
@@ -3203,10 +3206,10 @@
         <v>12</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>12</v>
@@ -3214,28 +3217,28 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>24918.0</v>
+        <v>62451.0</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F92" s="7" t="n">
         <v>2.0</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>12</v>
@@ -3243,28 +3246,28 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B93" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>3904.0</v>
+        <v>4352.0</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F93" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F93" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>12</v>
@@ -3272,28 +3275,28 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B94" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D94" s="6" t="n">
+        <v>33923.0</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F94" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G94" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C94" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="D94" s="6" t="n">
-        <v>501017.0</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="G94" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="H94" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I94" s="7" t="s">
         <v>12</v>
@@ -3301,28 +3304,28 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B95" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C95" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D95" s="6" t="n">
+        <v>437190.0</v>
+      </c>
+      <c r="E95" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F95" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G95" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C95" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D95" s="6" t="n">
-        <v>11591.0</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F95" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G95" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="H95" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I95" s="7" t="s">
         <v>12</v>
@@ -3330,28 +3333,28 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B96" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96" s="6" t="n">
+        <v>31713.0</v>
+      </c>
+      <c r="E96" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F96" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G96" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C96" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="D96" s="6" t="n">
-        <v>945.0</v>
-      </c>
-      <c r="E96" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F96" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="H96" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>12</v>
@@ -3359,16 +3362,16 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>1703.0</v>
+        <v>749.0</v>
       </c>
       <c r="E97" s="7" t="s">
         <v>12</v>
@@ -3377,10 +3380,10 @@
         <v>12</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I97" s="7" t="s">
         <v>12</v>
@@ -3388,28 +3391,28 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C98" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D98" s="6" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="E98" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="D98" s="6" t="n">
-        <v>3047.0</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F98" s="7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G98" s="8" t="s">
-        <v>46</v>
-      </c>
       <c r="H98" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>12</v>
@@ -3417,28 +3420,28 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C99" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="B99" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>30</v>
-      </c>
       <c r="D99" s="6" t="n">
-        <v>712387.0</v>
+        <v>160872.0</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F99" s="7" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>12</v>
@@ -3446,28 +3449,28 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>1815.0</v>
+        <v>33470.0</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F100" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F100" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="I100" s="7" t="s">
         <v>12</v>
@@ -3475,16 +3478,16 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>167988.0</v>
+        <v>48.0</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>12</v>
@@ -3493,10 +3496,10 @@
         <v>12</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I101" s="7" t="s">
         <v>12</v>
@@ -3504,16 +3507,16 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>7120.0</v>
+        <v>7046.0</v>
       </c>
       <c r="E102" s="7" t="s">
         <v>12</v>
@@ -3522,10 +3525,10 @@
         <v>12</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>12</v>
@@ -3533,28 +3536,28 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>87472.0</v>
+        <v>135942.0</v>
       </c>
       <c r="E103" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F103" s="7" t="n">
         <v>4.0</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>12</v>
@@ -3562,16 +3565,16 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>10198.0</v>
+        <v>147.0</v>
       </c>
       <c r="E104" s="7" t="s">
         <v>12</v>
@@ -3580,10 +3583,10 @@
         <v>12</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>12</v>
@@ -3591,16 +3594,16 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>11414.0</v>
+        <v>272.0</v>
       </c>
       <c r="E105" s="7" t="s">
         <v>12</v>
@@ -3609,10 +3612,10 @@
         <v>12</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I105" s="7" t="s">
         <v>12</v>
@@ -3620,28 +3623,28 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>24684.0</v>
+        <v>311.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I106" s="7" t="s">
         <v>12</v>
@@ -3649,16 +3652,16 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>383.0</v>
+        <v>1979.0</v>
       </c>
       <c r="E107" s="7" t="s">
         <v>12</v>
@@ -3667,10 +3670,10 @@
         <v>12</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I107" s="7" t="s">
         <v>12</v>
@@ -3678,28 +3681,28 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>285.0</v>
+        <v>364072.0</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F108" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F108" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I108" s="7" t="s">
         <v>12</v>
@@ -3707,28 +3710,28 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>638501.0</v>
+        <v>468850.0</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F109" s="7" t="n">
-        <v>20.0</v>
+        <v>11.0</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I109" s="7" t="s">
         <v>12</v>
@@ -3736,16 +3739,16 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>18.0</v>
+        <v>428.0</v>
       </c>
       <c r="E110" s="7" t="s">
         <v>12</v>
@@ -3754,10 +3757,10 @@
         <v>12</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>12</v>
@@ -3765,28 +3768,28 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>244115.0</v>
+        <v>3882.0</v>
       </c>
       <c r="E111" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F111" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F111" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>12</v>
@@ -3794,28 +3797,28 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>6618.0</v>
+        <v>284401.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F112" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F112" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I112" s="7" t="s">
         <v>12</v>
@@ -3823,28 +3826,28 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>2527.0</v>
+        <v>24918.0</v>
       </c>
       <c r="E113" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F113" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I113" s="7" t="s">
         <v>12</v>
@@ -3852,28 +3855,28 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>358088.0</v>
+        <v>1815.0</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F114" s="7" t="n">
-        <v>9.0</v>
+        <v>12</v>
+      </c>
+      <c r="F114" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I114" s="7" t="s">
         <v>12</v>
@@ -3881,16 +3884,16 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>8877.0</v>
+        <v>1703.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3899,10 +3902,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I115" s="7" t="s">
         <v>12</v>
@@ -3910,16 +3913,16 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>18008.0</v>
+        <v>7120.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -3928,10 +3931,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>12</v>
@@ -3939,28 +3942,28 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>173.0</v>
+        <v>3047.0</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>12</v>
@@ -3968,28 +3971,28 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>703357.0</v>
+        <v>501017.0</v>
       </c>
       <c r="E118" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F118" s="7" t="n">
-        <v>18.0</v>
+        <v>3.0</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>12</v>
@@ -3997,28 +4000,28 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>384990.0</v>
+        <v>11591.0</v>
       </c>
       <c r="E119" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F119" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F119" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>12</v>
@@ -4026,16 +4029,16 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C120" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B120" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C120" s="5" t="s">
-        <v>40</v>
-      </c>
       <c r="D120" s="6" t="n">
-        <v>392.0</v>
+        <v>945.0</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>12</v>
@@ -4044,10 +4047,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>12</v>
@@ -4055,28 +4058,28 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>772.0</v>
+        <v>3904.0</v>
       </c>
       <c r="E121" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F121" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F121" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I121" s="7" t="s">
         <v>12</v>
@@ -4084,28 +4087,28 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>12318.0</v>
+        <v>712387.0</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F122" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F122" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I122" s="7" t="s">
         <v>12</v>
@@ -4113,28 +4116,28 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D123" s="6" t="n">
+        <v>87472.0</v>
+      </c>
+      <c r="E123" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F123" s="7" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G123" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D123" s="6" t="n">
-        <v>2068.0</v>
-      </c>
-      <c r="E123" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F123" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="G123" s="8" t="s">
-        <v>50</v>
-      </c>
       <c r="H123" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>12</v>
@@ -4142,28 +4145,28 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>31421.0</v>
+        <v>3746.0</v>
       </c>
       <c r="E124" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F124" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F124" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>12</v>
@@ -4171,16 +4174,16 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>212.0</v>
+        <v>167988.0</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>12</v>
@@ -4189,10 +4192,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>12</v>
@@ -4200,16 +4203,16 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>295.0</v>
+        <v>285.0</v>
       </c>
       <c r="E126" s="7" t="s">
         <v>12</v>
@@ -4218,10 +4221,10 @@
         <v>12</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>12</v>
@@ -4229,28 +4232,28 @@
     </row>
     <row r="127">
       <c r="A127" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>42524.0</v>
+        <v>8877.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F127" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I127" s="7" t="s">
         <v>12</v>
@@ -4261,13 +4264,13 @@
         <v>51</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>17276.0</v>
+        <v>11414.0</v>
       </c>
       <c r="E128" s="7" t="s">
         <v>12</v>
@@ -4290,19 +4293,19 @@
         <v>51</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>435991.0</v>
+        <v>24684.0</v>
       </c>
       <c r="E129" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F129" s="7" t="n">
-        <v>12.0</v>
+        <v>1.0</v>
       </c>
       <c r="G129" s="8" t="s">
         <v>51</v>
@@ -4322,10 +4325,10 @@
         <v>15</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>5248.0</v>
+        <v>383.0</v>
       </c>
       <c r="E130" s="7" t="s">
         <v>12</v>
@@ -4351,16 +4354,16 @@
         <v>15</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>650.0</v>
+        <v>2527.0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F131" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F131" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G131" s="8" t="s">
         <v>51</v>
@@ -4377,13 +4380,13 @@
         <v>51</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>19816.0</v>
+        <v>10198.0</v>
       </c>
       <c r="E132" s="7" t="s">
         <v>12</v>
@@ -4409,16 +4412,16 @@
         <v>15</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>336995.0</v>
+        <v>18.0</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F133" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F133" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G133" s="8" t="s">
         <v>51</v>
@@ -4435,19 +4438,19 @@
         <v>51</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>317924.0</v>
+        <v>244115.0</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>5.0</v>
+        <v>11.0</v>
       </c>
       <c r="G134" s="8" t="s">
         <v>51</v>
@@ -4464,19 +4467,19 @@
         <v>51</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>819.0</v>
+        <v>638501.0</v>
       </c>
       <c r="E135" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F135" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F135" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G135" s="8" t="s">
         <v>51</v>
@@ -4493,13 +4496,13 @@
         <v>51</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>4802.0</v>
+        <v>6618.0</v>
       </c>
       <c r="E136" s="7" t="s">
         <v>12</v>
@@ -4522,19 +4525,19 @@
         <v>51</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>2548.0</v>
+        <v>358088.0</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F137" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F137" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G137" s="8" t="s">
         <v>51</v>
@@ -4554,10 +4557,10 @@
         <v>10</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>29578.0</v>
+        <v>173.0</v>
       </c>
       <c r="E138" s="7" t="s">
         <v>12</v>
@@ -4580,13 +4583,13 @@
         <v>51</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>1044.0</v>
+        <v>392.0</v>
       </c>
       <c r="E139" s="7" t="s">
         <v>12</v>
@@ -4609,13 +4612,13 @@
         <v>51</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C140" s="5" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>772.0</v>
+        <v>12318.0</v>
       </c>
       <c r="E140" s="7" t="s">
         <v>12</v>
@@ -4638,19 +4641,19 @@
         <v>51</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>401629.0</v>
+        <v>18008.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F141" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>51</v>
@@ -4667,19 +4670,19 @@
         <v>51</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>1439.0</v>
+        <v>384990.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F142" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F142" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>51</v>
@@ -4696,13 +4699,13 @@
         <v>51</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>5801.0</v>
+        <v>772.0</v>
       </c>
       <c r="E143" s="7" t="s">
         <v>12</v>
@@ -4725,19 +4728,19 @@
         <v>51</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>853298.0</v>
+        <v>2068.0</v>
       </c>
       <c r="E144" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F144" s="7" t="n">
-        <v>27.0</v>
+        <v>12</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G144" s="8" t="s">
         <v>51</v>
@@ -4757,16 +4760,16 @@
         <v>10</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>4237.0</v>
+        <v>703357.0</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>18.0</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>51</v>
@@ -4780,28 +4783,28 @@
     </row>
     <row r="146">
       <c r="A146" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>8213.0</v>
+        <v>31421.0</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F146" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F146" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G146" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H146" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I146" s="7" t="s">
         <v>12</v>
@@ -4809,28 +4812,28 @@
     </row>
     <row r="147">
       <c r="A147" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>324526.0</v>
+        <v>212.0</v>
       </c>
       <c r="E147" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F147" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F147" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G147" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H147" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I147" s="7" t="s">
         <v>12</v>
@@ -4838,16 +4841,16 @@
     </row>
     <row r="148">
       <c r="A148" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>2170.0</v>
+        <v>295.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4856,10 +4859,10 @@
         <v>12</v>
       </c>
       <c r="G148" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H148" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I148" s="7" t="s">
         <v>12</v>
@@ -4867,28 +4870,28 @@
     </row>
     <row r="149">
       <c r="A149" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>378946.0</v>
+        <v>42524.0</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F149" s="7" t="n">
-        <v>12.0</v>
+        <v>2.0</v>
       </c>
       <c r="G149" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H149" s="8" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I149" s="7" t="s">
         <v>12</v>
@@ -4899,19 +4902,19 @@
         <v>52</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>462054.0</v>
+        <v>17276.0</v>
       </c>
       <c r="E150" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F150" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G150" s="8" t="s">
         <v>52</v>
@@ -4931,16 +4934,16 @@
         <v>15</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>228.0</v>
+        <v>336995.0</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F151" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>52</v>
@@ -4960,16 +4963,16 @@
         <v>15</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>742.0</v>
+        <v>435991.0</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F152" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F152" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G152" s="8" t="s">
         <v>52</v>
@@ -4992,7 +4995,7 @@
         <v>22</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>3988.0</v>
+        <v>5248.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5015,19 +5018,19 @@
         <v>52</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>22960.0</v>
+        <v>650.0</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F154" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G154" s="8" t="s">
         <v>52</v>
@@ -5047,10 +5050,10 @@
         <v>13</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>14457.0</v>
+        <v>19816.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5073,19 +5076,19 @@
         <v>52</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>14351.0</v>
+        <v>317924.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G156" s="8" t="s">
         <v>52</v>
@@ -5105,10 +5108,10 @@
         <v>10</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>412.0</v>
+        <v>4802.0</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>12</v>
@@ -5134,10 +5137,10 @@
         <v>13</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>1625.0</v>
+        <v>819.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5163,10 +5166,10 @@
         <v>10</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>5324.0</v>
+        <v>29578.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>12</v>
@@ -5192,10 +5195,10 @@
         <v>10</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>4481.0</v>
+        <v>4237.0</v>
       </c>
       <c r="E160" s="7" t="s">
         <v>12</v>
@@ -5221,16 +5224,16 @@
         <v>10</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>2238.0</v>
+        <v>853298.0</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F161" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F161" s="7" t="n">
+        <v>27.0</v>
       </c>
       <c r="G161" s="8" t="s">
         <v>52</v>
@@ -5250,16 +5253,16 @@
         <v>10</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>51544.0</v>
+        <v>2548.0</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F162" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G162" s="8" t="s">
         <v>52</v>
@@ -5276,19 +5279,19 @@
         <v>52</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>696176.0</v>
+        <v>5801.0</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F163" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F163" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G163" s="8" t="s">
         <v>52</v>
@@ -5305,13 +5308,13 @@
         <v>52</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>8383.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
@@ -5334,19 +5337,19 @@
         <v>52</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>3011.0</v>
+        <v>401629.0</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F165" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G165" s="8" t="s">
         <v>52</v>
@@ -5363,13 +5366,13 @@
         <v>52</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>385.0</v>
+        <v>772.0</v>
       </c>
       <c r="E166" s="7" t="s">
         <v>12</v>
@@ -5392,19 +5395,19 @@
         <v>52</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>445496.0</v>
+        <v>1439.0</v>
       </c>
       <c r="E167" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F167" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F167" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G167" s="8" t="s">
         <v>52</v>
@@ -5424,16 +5427,16 @@
         <v>10</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>935238.0</v>
+        <v>5324.0</v>
       </c>
       <c r="E168" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F168" s="7" t="n">
-        <v>20.0</v>
+        <v>12</v>
+      </c>
+      <c r="F168" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G168" s="8" t="s">
         <v>53</v>
@@ -5450,19 +5453,19 @@
         <v>53</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>378762.0</v>
+        <v>3988.0</v>
       </c>
       <c r="E169" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F169" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F169" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G169" s="8" t="s">
         <v>53</v>
@@ -5479,19 +5482,19 @@
         <v>53</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>3472.0</v>
+        <v>22960.0</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>53</v>
@@ -5508,13 +5511,13 @@
         <v>53</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>1293.0</v>
+        <v>14457.0</v>
       </c>
       <c r="E171" s="7" t="s">
         <v>12</v>
@@ -5537,19 +5540,19 @@
         <v>53</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>2256.0</v>
+        <v>324526.0</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F172" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F172" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G172" s="8" t="s">
         <v>53</v>
@@ -5566,13 +5569,13 @@
         <v>53</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>5104.0</v>
+        <v>1625.0</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>12</v>
@@ -5598,10 +5601,10 @@
         <v>10</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>76.0</v>
+        <v>412.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5624,13 +5627,13 @@
         <v>53</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>5377.0</v>
+        <v>8383.0</v>
       </c>
       <c r="E175" s="7" t="s">
         <v>12</v>
@@ -5656,10 +5659,10 @@
         <v>10</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>1563.0</v>
+        <v>4481.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>12</v>
@@ -5685,16 +5688,16 @@
         <v>10</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>17021.0</v>
+        <v>2238.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F177" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F177" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>53</v>
@@ -5714,16 +5717,16 @@
         <v>10</v>
       </c>
       <c r="C178" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D178" s="6" t="n">
-        <v>7279.0</v>
+        <v>51544.0</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G178" s="8" t="s">
         <v>53</v>
@@ -5743,16 +5746,16 @@
         <v>10</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>3659.0</v>
+        <v>696176.0</v>
       </c>
       <c r="E179" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F179" s="7" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
       <c r="G179" s="8" t="s">
         <v>53</v>
@@ -5769,19 +5772,19 @@
         <v>53</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C180" s="5" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>379038.0</v>
+        <v>3011.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F180" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F180" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G180" s="8" t="s">
         <v>53</v>
@@ -5798,13 +5801,13 @@
         <v>53</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>5765.0</v>
+        <v>385.0</v>
       </c>
       <c r="E181" s="7" t="s">
         <v>12</v>
@@ -5827,19 +5830,19 @@
         <v>53</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>43627.0</v>
+        <v>445496.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F182" s="7" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>53</v>
@@ -5859,10 +5862,10 @@
         <v>15</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>1498.0</v>
+        <v>228.0</v>
       </c>
       <c r="E183" s="7" t="s">
         <v>12</v>
@@ -5888,16 +5891,16 @@
         <v>15</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>893824.0</v>
+        <v>742.0</v>
       </c>
       <c r="E184" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F184" s="7" t="n">
-        <v>24.0</v>
+        <v>12</v>
+      </c>
+      <c r="F184" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G184" s="8" t="s">
         <v>53</v>
@@ -5914,19 +5917,19 @@
         <v>53</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>12172.0</v>
+        <v>462054.0</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F185" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F185" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G185" s="8" t="s">
         <v>53</v>
@@ -5940,28 +5943,28 @@
     </row>
     <row r="186">
       <c r="A186" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>700185.0</v>
+        <v>378946.0</v>
       </c>
       <c r="E186" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F186" s="7" t="n">
-        <v>20.0</v>
+        <v>12.0</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>12</v>
@@ -5969,16 +5972,16 @@
     </row>
     <row r="187">
       <c r="A187" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>16525.0</v>
+        <v>2170.0</v>
       </c>
       <c r="E187" s="7" t="s">
         <v>12</v>
@@ -5987,10 +5990,10 @@
         <v>12</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H187" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>12</v>
@@ -5998,28 +6001,28 @@
     </row>
     <row r="188">
       <c r="A188" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B188" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>290.0</v>
+        <v>14351.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F188" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F188" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>12</v>
@@ -6027,16 +6030,16 @@
     </row>
     <row r="189">
       <c r="A189" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>3888.0</v>
+        <v>8213.0</v>
       </c>
       <c r="E189" s="7" t="s">
         <v>12</v>
@@ -6045,10 +6048,10 @@
         <v>12</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H189" s="8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I189" s="7" t="s">
         <v>12</v>
@@ -6062,16 +6065,16 @@
         <v>10</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>20739.0</v>
+        <v>17021.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F190" s="7" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G190" s="8" t="s">
         <v>54</v>
@@ -6091,16 +6094,16 @@
         <v>15</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>25848.0</v>
+        <v>893824.0</v>
       </c>
       <c r="E191" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F191" s="7" t="n">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G191" s="8" t="s">
         <v>54</v>
@@ -6120,10 +6123,10 @@
         <v>15</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>2939.0</v>
+        <v>5377.0</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>12</v>
@@ -6149,10 +6152,10 @@
         <v>15</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>15807.0</v>
+        <v>1498.0</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>12</v>
@@ -6178,16 +6181,16 @@
         <v>13</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>353476.0</v>
+        <v>43627.0</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F194" s="7" t="n">
-        <v>14.0</v>
+        <v>2.0</v>
       </c>
       <c r="G194" s="8" t="s">
         <v>54</v>
@@ -6207,16 +6210,16 @@
         <v>13</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>25346.0</v>
+        <v>5765.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F195" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F195" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G195" s="8" t="s">
         <v>54</v>
@@ -6233,19 +6236,19 @@
         <v>54</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>697336.0</v>
+        <v>379038.0</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F196" s="7" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G196" s="8" t="s">
         <v>54</v>
@@ -6262,19 +6265,19 @@
         <v>54</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>7643.0</v>
+        <v>3659.0</v>
       </c>
       <c r="E197" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F197" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F197" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G197" s="8" t="s">
         <v>54</v>
@@ -6294,10 +6297,10 @@
         <v>10</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>33363.0</v>
+        <v>7279.0</v>
       </c>
       <c r="E198" s="7" t="s">
         <v>12</v>
@@ -6323,16 +6326,16 @@
         <v>10</v>
       </c>
       <c r="C199" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>9025.0</v>
+        <v>1563.0</v>
       </c>
       <c r="E199" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F199" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F199" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G199" s="8" t="s">
         <v>54</v>
@@ -6352,10 +6355,10 @@
         <v>10</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>6325.0</v>
+        <v>2256.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>12</v>
@@ -6378,13 +6381,13 @@
         <v>54</v>
       </c>
       <c r="B201" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C201" s="5" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D201" s="6" t="n">
-        <v>3642.0</v>
+        <v>12172.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>12</v>
@@ -6407,13 +6410,13 @@
         <v>54</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D202" s="6" t="n">
-        <v>7174.0</v>
+        <v>3472.0</v>
       </c>
       <c r="E202" s="7" t="s">
         <v>12</v>
@@ -6436,19 +6439,19 @@
         <v>54</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>383981.0</v>
+        <v>1293.0</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F203" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F203" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G203" s="8" t="s">
         <v>54</v>
@@ -6465,19 +6468,19 @@
         <v>54</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>2276.0</v>
+        <v>378762.0</v>
       </c>
       <c r="E204" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F204" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F204" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G204" s="8" t="s">
         <v>54</v>
@@ -6491,28 +6494,28 @@
     </row>
     <row r="205">
       <c r="A205" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>100569.0</v>
+        <v>5104.0</v>
       </c>
       <c r="E205" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F205" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F205" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>12</v>
@@ -6520,28 +6523,28 @@
     </row>
     <row r="206">
       <c r="A206" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>480911.0</v>
+        <v>935238.0</v>
       </c>
       <c r="E206" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F206" s="7" t="n">
-        <v>14.0</v>
+        <v>20.0</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>12</v>
@@ -6549,16 +6552,16 @@
     </row>
     <row r="207">
       <c r="A207" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>928.0</v>
+        <v>76.0</v>
       </c>
       <c r="E207" s="7" t="s">
         <v>12</v>
@@ -6567,10 +6570,10 @@
         <v>12</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>12</v>
@@ -6581,19 +6584,19 @@
         <v>55</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>3290.0</v>
+        <v>353476.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F208" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F208" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G208" s="8" t="s">
         <v>55</v>
@@ -6610,13 +6613,13 @@
         <v>55</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>889.0</v>
+        <v>15807.0</v>
       </c>
       <c r="E209" s="7" t="s">
         <v>12</v>
@@ -6642,16 +6645,16 @@
         <v>15</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>83588.0</v>
+        <v>2939.0</v>
       </c>
       <c r="E210" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F210" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G210" s="8" t="s">
         <v>55</v>
@@ -6671,16 +6674,16 @@
         <v>15</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>1474.0</v>
+        <v>25848.0</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F211" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F211" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G211" s="8" t="s">
         <v>55</v>
@@ -6700,16 +6703,16 @@
         <v>15</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>794.0</v>
+        <v>700185.0</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F212" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F212" s="7" t="n">
+        <v>20.0</v>
       </c>
       <c r="G212" s="8" t="s">
         <v>55</v>
@@ -6726,13 +6729,13 @@
         <v>55</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>2673.0</v>
+        <v>3888.0</v>
       </c>
       <c r="E213" s="7" t="s">
         <v>12</v>
@@ -6755,13 +6758,13 @@
         <v>55</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>46118.0</v>
+        <v>290.0</v>
       </c>
       <c r="E214" s="7" t="s">
         <v>12</v>
@@ -6784,13 +6787,13 @@
         <v>55</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>2029.0</v>
+        <v>16525.0</v>
       </c>
       <c r="E215" s="7" t="s">
         <v>12</v>
@@ -6816,16 +6819,16 @@
         <v>13</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>282217.0</v>
+        <v>25346.0</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F216" s="7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G216" s="8" t="s">
         <v>55</v>
@@ -6842,13 +6845,13 @@
         <v>55</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>29</v>
+        <v>49</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>2220.0</v>
+        <v>7174.0</v>
       </c>
       <c r="E217" s="7" t="s">
         <v>12</v>
@@ -6871,13 +6874,13 @@
         <v>55</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>7945.0</v>
+        <v>7643.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6900,19 +6903,19 @@
         <v>55</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>621293.0</v>
+        <v>3642.0</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F219" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G219" s="8" t="s">
         <v>55</v>
@@ -6929,19 +6932,19 @@
         <v>55</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>633.0</v>
+        <v>20739.0</v>
       </c>
       <c r="E220" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F220" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F220" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G220" s="8" t="s">
         <v>55</v>
@@ -6958,19 +6961,19 @@
         <v>55</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>70.0</v>
+        <v>383981.0</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F221" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G221" s="8" t="s">
         <v>55</v>
@@ -6987,19 +6990,19 @@
         <v>55</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>357571.0</v>
+        <v>2276.0</v>
       </c>
       <c r="E222" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F222" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F222" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G222" s="8" t="s">
         <v>55</v>
@@ -7019,10 +7022,10 @@
         <v>10</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>324.0</v>
+        <v>6325.0</v>
       </c>
       <c r="E223" s="7" t="s">
         <v>12</v>
@@ -7048,16 +7051,16 @@
         <v>10</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>21813.0</v>
+        <v>697336.0</v>
       </c>
       <c r="E224" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F224" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F224" s="7" t="n">
+        <v>10.0</v>
       </c>
       <c r="G224" s="8" t="s">
         <v>55</v>
@@ -7071,28 +7074,28 @@
     </row>
     <row r="225">
       <c r="A225" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>5812.0</v>
+        <v>9025.0</v>
       </c>
       <c r="E225" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F225" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F225" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G225" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I225" s="7" t="s">
         <v>12</v>
@@ -7100,16 +7103,16 @@
     </row>
     <row r="226">
       <c r="A226" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>1812.0</v>
+        <v>33363.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7118,10 +7121,10 @@
         <v>12</v>
       </c>
       <c r="G226" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I226" s="7" t="s">
         <v>12</v>
@@ -7132,19 +7135,19 @@
         <v>56</v>
       </c>
       <c r="B227" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C227" s="5" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="D227" s="6" t="n">
-        <v>112476.0</v>
+        <v>282217.0</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F227" s="7" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>56</v>
@@ -7164,16 +7167,16 @@
         <v>15</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>730436.0</v>
+        <v>794.0</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F228" s="7" t="n">
-        <v>24.0</v>
+        <v>12</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>56</v>
@@ -7193,10 +7196,10 @@
         <v>15</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>199.0</v>
+        <v>1474.0</v>
       </c>
       <c r="E229" s="7" t="s">
         <v>12</v>
@@ -7219,19 +7222,19 @@
         <v>56</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>58187.0</v>
+        <v>83588.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F230" s="7" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>56</v>
@@ -7248,19 +7251,19 @@
         <v>56</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>131368.0</v>
+        <v>480911.0</v>
       </c>
       <c r="E231" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F231" s="7" t="n">
-        <v>3.0</v>
+        <v>14.0</v>
       </c>
       <c r="G231" s="8" t="s">
         <v>56</v>
@@ -7277,19 +7280,19 @@
         <v>56</v>
       </c>
       <c r="B232" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C232" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D232" s="6" t="n">
-        <v>218816.0</v>
+        <v>3290.0</v>
       </c>
       <c r="E232" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F232" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F232" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G232" s="8" t="s">
         <v>56</v>
@@ -7306,13 +7309,13 @@
         <v>56</v>
       </c>
       <c r="B233" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C233" s="5" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D233" s="6" t="n">
-        <v>3911.0</v>
+        <v>928.0</v>
       </c>
       <c r="E233" s="7" t="s">
         <v>12</v>
@@ -7335,19 +7338,19 @@
         <v>56</v>
       </c>
       <c r="B234" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C234" s="5" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D234" s="6" t="n">
-        <v>601.0</v>
+        <v>100569.0</v>
       </c>
       <c r="E234" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F234" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G234" s="8" t="s">
         <v>56</v>
@@ -7364,13 +7367,13 @@
         <v>56</v>
       </c>
       <c r="B235" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C235" s="5" t="s">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="D235" s="6" t="n">
-        <v>969.0</v>
+        <v>46118.0</v>
       </c>
       <c r="E235" s="7" t="s">
         <v>12</v>
@@ -7393,13 +7396,13 @@
         <v>56</v>
       </c>
       <c r="B236" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C236" s="5" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="D236" s="6" t="n">
-        <v>33241.0</v>
+        <v>2673.0</v>
       </c>
       <c r="E236" s="7" t="s">
         <v>12</v>
@@ -7425,10 +7428,10 @@
         <v>10</v>
       </c>
       <c r="C237" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D237" s="6" t="n">
-        <v>70.0</v>
+        <v>2220.0</v>
       </c>
       <c r="E237" s="7" t="s">
         <v>12</v>
@@ -7454,10 +7457,10 @@
         <v>10</v>
       </c>
       <c r="C238" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D238" s="6" t="n">
-        <v>15780.0</v>
+        <v>889.0</v>
       </c>
       <c r="E238" s="7" t="s">
         <v>12</v>
@@ -7486,13 +7489,13 @@
         <v>30</v>
       </c>
       <c r="D239" s="6" t="n">
-        <v>637424.0</v>
+        <v>621293.0</v>
       </c>
       <c r="E239" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F239" s="7" t="n">
-        <v>14.0</v>
+        <v>12.0</v>
       </c>
       <c r="G239" s="8" t="s">
         <v>56</v>
@@ -7512,10 +7515,10 @@
         <v>10</v>
       </c>
       <c r="C240" s="5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D240" s="6" t="n">
-        <v>395.0</v>
+        <v>21813.0</v>
       </c>
       <c r="E240" s="7" t="s">
         <v>12</v>
@@ -7538,13 +7541,13 @@
         <v>56</v>
       </c>
       <c r="B241" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C241" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D241" s="6" t="n">
-        <v>5851.0</v>
+        <v>633.0</v>
       </c>
       <c r="E241" s="7" t="s">
         <v>12</v>
@@ -7567,13 +7570,13 @@
         <v>56</v>
       </c>
       <c r="B242" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C242" s="5" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D242" s="6" t="n">
-        <v>479.0</v>
+        <v>7945.0</v>
       </c>
       <c r="E242" s="7" t="s">
         <v>12</v>
@@ -7596,19 +7599,19 @@
         <v>56</v>
       </c>
       <c r="B243" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C243" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D243" s="6" t="n">
-        <v>386517.0</v>
+        <v>357571.0</v>
       </c>
       <c r="E243" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F243" s="7" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="G243" s="8" t="s">
         <v>56</v>
@@ -7625,13 +7628,13 @@
         <v>56</v>
       </c>
       <c r="B244" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C244" s="5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D244" s="6" t="n">
-        <v>4729.0</v>
+        <v>70.0</v>
       </c>
       <c r="E244" s="7" t="s">
         <v>12</v>
@@ -7651,28 +7654,28 @@
     </row>
     <row r="245">
       <c r="A245" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B245" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C245" s="5" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="D245" s="6" t="n">
-        <v>107118.0</v>
+        <v>2029.0</v>
       </c>
       <c r="E245" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F245" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G245" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H245" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I245" s="7" t="s">
         <v>12</v>
@@ -7680,28 +7683,28 @@
     </row>
     <row r="246">
       <c r="A246" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B246" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C246" s="5" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="D246" s="6" t="n">
-        <v>51830.0</v>
+        <v>324.0</v>
       </c>
       <c r="E246" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F246" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G246" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H246" s="8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I246" s="7" t="s">
         <v>12</v>
@@ -7715,16 +7718,16 @@
         <v>15</v>
       </c>
       <c r="C247" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D247" s="6" t="n">
-        <v>806692.0</v>
+        <v>1812.0</v>
       </c>
       <c r="E247" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F247" s="7" t="n">
-        <v>40.0</v>
+        <v>12</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G247" s="8" t="s">
         <v>57</v>
@@ -7744,16 +7747,16 @@
         <v>15</v>
       </c>
       <c r="C248" s="5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="D248" s="6" t="n">
-        <v>8605.0</v>
+        <v>112476.0</v>
       </c>
       <c r="E248" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F248" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F248" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G248" s="8" t="s">
         <v>57</v>
@@ -7773,16 +7776,16 @@
         <v>15</v>
       </c>
       <c r="C249" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D249" s="6" t="n">
-        <v>451.0</v>
+        <v>730436.0</v>
       </c>
       <c r="E249" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F249" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F249" s="7" t="n">
+        <v>24.0</v>
       </c>
       <c r="G249" s="8" t="s">
         <v>57</v>
@@ -7802,16 +7805,16 @@
         <v>15</v>
       </c>
       <c r="C250" s="5" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D250" s="6" t="n">
-        <v>65819.0</v>
+        <v>199.0</v>
       </c>
       <c r="E250" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F250" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G250" s="8" t="s">
         <v>57</v>
@@ -7828,19 +7831,19 @@
         <v>57</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C251" s="5" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D251" s="6" t="n">
-        <v>571.0</v>
+        <v>58187.0</v>
       </c>
       <c r="E251" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F251" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F251" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G251" s="8" t="s">
         <v>57</v>
@@ -7857,19 +7860,19 @@
         <v>57</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C252" s="5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D252" s="6" t="n">
-        <v>344.0</v>
+        <v>131368.0</v>
       </c>
       <c r="E252" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F252" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F252" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G252" s="8" t="s">
         <v>57</v>
@@ -7886,19 +7889,19 @@
         <v>57</v>
       </c>
       <c r="B253" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C253" s="5" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D253" s="6" t="n">
-        <v>526.0</v>
+        <v>218816.0</v>
       </c>
       <c r="E253" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F253" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F253" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G253" s="8" t="s">
         <v>57</v>
@@ -7918,16 +7921,16 @@
         <v>13</v>
       </c>
       <c r="C254" s="5" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="D254" s="6" t="n">
-        <v>249629.0</v>
+        <v>3911.0</v>
       </c>
       <c r="E254" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F254" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F254" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G254" s="8" t="s">
         <v>57</v>
@@ -7944,13 +7947,13 @@
         <v>57</v>
       </c>
       <c r="B255" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C255" s="5" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D255" s="6" t="n">
-        <v>2994.0</v>
+        <v>601.0</v>
       </c>
       <c r="E255" s="7" t="s">
         <v>12</v>
@@ -7976,10 +7979,10 @@
         <v>10</v>
       </c>
       <c r="C256" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D256" s="6" t="n">
-        <v>3128.0</v>
+        <v>5812.0</v>
       </c>
       <c r="E256" s="7" t="s">
         <v>12</v>
@@ -8002,19 +8005,19 @@
         <v>57</v>
       </c>
       <c r="B257" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C257" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D257" s="6" t="n">
-        <v>9408.0</v>
+        <v>33241.0</v>
       </c>
       <c r="E257" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F257" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F257" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G257" s="8" t="s">
         <v>57</v>
@@ -8034,10 +8037,10 @@
         <v>10</v>
       </c>
       <c r="C258" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D258" s="6" t="n">
-        <v>4379.0</v>
+        <v>15780.0</v>
       </c>
       <c r="E258" s="7" t="s">
         <v>12</v>
@@ -8060,19 +8063,19 @@
         <v>57</v>
       </c>
       <c r="B259" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C259" s="5" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="D259" s="6" t="n">
-        <v>407399.0</v>
+        <v>969.0</v>
       </c>
       <c r="E259" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F259" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F259" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G259" s="8" t="s">
         <v>57</v>
@@ -8089,19 +8092,19 @@
         <v>57</v>
       </c>
       <c r="B260" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C260" s="5" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="D260" s="6" t="n">
-        <v>456.0</v>
+        <v>637424.0</v>
       </c>
       <c r="E260" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F260" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F260" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G260" s="8" t="s">
         <v>57</v>
@@ -8118,13 +8121,13 @@
         <v>57</v>
       </c>
       <c r="B261" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C261" s="5" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D261" s="6" t="n">
-        <v>172.0</v>
+        <v>395.0</v>
       </c>
       <c r="E261" s="7" t="s">
         <v>12</v>
@@ -8147,13 +8150,13 @@
         <v>57</v>
       </c>
       <c r="B262" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C262" s="5" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D262" s="6" t="n">
-        <v>816.0</v>
+        <v>5851.0</v>
       </c>
       <c r="E262" s="7" t="s">
         <v>12</v>
@@ -8176,13 +8179,13 @@
         <v>57</v>
       </c>
       <c r="B263" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C263" s="5" t="s">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="D263" s="6" t="n">
-        <v>3200.0</v>
+        <v>479.0</v>
       </c>
       <c r="E263" s="7" t="s">
         <v>12</v>
@@ -8205,19 +8208,19 @@
         <v>57</v>
       </c>
       <c r="B264" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C264" s="5" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D264" s="6" t="n">
-        <v>747712.0</v>
+        <v>386517.0</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F264" s="7" t="n">
-        <v>16.0</v>
+        <v>6.0</v>
       </c>
       <c r="G264" s="8" t="s">
         <v>57</v>
@@ -8234,13 +8237,13 @@
         <v>57</v>
       </c>
       <c r="B265" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C265" s="5" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="D265" s="6" t="n">
-        <v>24685.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E265" s="7" t="s">
         <v>12</v>
@@ -8269,13 +8272,13 @@
         <v>28</v>
       </c>
       <c r="D266" s="6" t="n">
-        <v>22093.0</v>
+        <v>70.0</v>
       </c>
       <c r="E266" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F266" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G266" s="8" t="s">
         <v>57</v>
@@ -8292,19 +8295,19 @@
         <v>58</v>
       </c>
       <c r="B267" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C267" s="5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D267" s="6" t="n">
-        <v>5147.0</v>
+        <v>8605.0</v>
       </c>
       <c r="E267" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F267" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G267" s="8" t="s">
         <v>58</v>
@@ -8321,19 +8324,19 @@
         <v>58</v>
       </c>
       <c r="B268" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C268" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D268" s="6" t="n">
-        <v>325.0</v>
+        <v>107118.0</v>
       </c>
       <c r="E268" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F268" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F268" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G268" s="8" t="s">
         <v>58</v>
@@ -8350,19 +8353,19 @@
         <v>58</v>
       </c>
       <c r="B269" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C269" s="5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D269" s="6" t="n">
-        <v>512430.0</v>
+        <v>51830.0</v>
       </c>
       <c r="E269" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F269" s="7" t="n">
-        <v>40.0</v>
+        <v>2.0</v>
       </c>
       <c r="G269" s="8" t="s">
         <v>58</v>
@@ -8385,7 +8388,7 @@
         <v>21</v>
       </c>
       <c r="D270" s="6" t="n">
-        <v>952.0</v>
+        <v>451.0</v>
       </c>
       <c r="E270" s="7" t="s">
         <v>12</v>
@@ -8408,13 +8411,13 @@
         <v>58</v>
       </c>
       <c r="B271" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C271" s="5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D271" s="6" t="n">
-        <v>1164.0</v>
+        <v>2994.0</v>
       </c>
       <c r="E271" s="7" t="s">
         <v>12</v>
@@ -8437,19 +8440,19 @@
         <v>58</v>
       </c>
       <c r="B272" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C272" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D272" s="6" t="n">
-        <v>28983.0</v>
+        <v>806692.0</v>
       </c>
       <c r="E272" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F272" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F272" s="7" t="n">
+        <v>40.0</v>
       </c>
       <c r="G272" s="8" t="s">
         <v>58</v>
@@ -8466,19 +8469,19 @@
         <v>58</v>
       </c>
       <c r="B273" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C273" s="5" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="D273" s="6" t="n">
-        <v>5727.0</v>
+        <v>65819.0</v>
       </c>
       <c r="E273" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F273" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F273" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G273" s="8" t="s">
         <v>58</v>
@@ -8495,13 +8498,13 @@
         <v>58</v>
       </c>
       <c r="B274" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C274" s="5" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="D274" s="6" t="n">
-        <v>5227.0</v>
+        <v>571.0</v>
       </c>
       <c r="E274" s="7" t="s">
         <v>12</v>
@@ -8524,19 +8527,19 @@
         <v>58</v>
       </c>
       <c r="B275" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C275" s="5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D275" s="6" t="n">
-        <v>283905.0</v>
+        <v>344.0</v>
       </c>
       <c r="E275" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F275" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F275" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G275" s="8" t="s">
         <v>58</v>
@@ -8553,13 +8556,13 @@
         <v>58</v>
       </c>
       <c r="B276" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C276" s="5" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D276" s="6" t="n">
-        <v>1182.0</v>
+        <v>526.0</v>
       </c>
       <c r="E276" s="7" t="s">
         <v>12</v>
@@ -8585,10 +8588,10 @@
         <v>10</v>
       </c>
       <c r="C277" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D277" s="6" t="n">
-        <v>13629.0</v>
+        <v>24685.0</v>
       </c>
       <c r="E277" s="7" t="s">
         <v>12</v>
@@ -8611,19 +8614,19 @@
         <v>58</v>
       </c>
       <c r="B278" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C278" s="5" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="D278" s="6" t="n">
-        <v>1186.0</v>
+        <v>407399.0</v>
       </c>
       <c r="E278" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F278" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F278" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G278" s="8" t="s">
         <v>58</v>
@@ -8640,19 +8643,19 @@
         <v>58</v>
       </c>
       <c r="B279" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C279" s="5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="D279" s="6" t="n">
-        <v>728.0</v>
+        <v>249629.0</v>
       </c>
       <c r="E279" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F279" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F279" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G279" s="8" t="s">
         <v>58</v>
@@ -8672,10 +8675,10 @@
         <v>10</v>
       </c>
       <c r="C280" s="5" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="D280" s="6" t="n">
-        <v>197.0</v>
+        <v>4379.0</v>
       </c>
       <c r="E280" s="7" t="s">
         <v>12</v>
@@ -8698,19 +8701,19 @@
         <v>58</v>
       </c>
       <c r="B281" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C281" s="5" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="D281" s="6" t="n">
-        <v>506367.0</v>
+        <v>9408.0</v>
       </c>
       <c r="E281" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F281" s="7" t="n">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="G281" s="8" t="s">
         <v>58</v>
@@ -8727,13 +8730,13 @@
         <v>58</v>
       </c>
       <c r="B282" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C282" s="5" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D282" s="6" t="n">
-        <v>85.0</v>
+        <v>456.0</v>
       </c>
       <c r="E282" s="7" t="s">
         <v>12</v>
@@ -8756,13 +8759,13 @@
         <v>58</v>
       </c>
       <c r="B283" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C283" s="5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D283" s="6" t="n">
-        <v>939.0</v>
+        <v>172.0</v>
       </c>
       <c r="E283" s="7" t="s">
         <v>12</v>
@@ -8785,13 +8788,13 @@
         <v>58</v>
       </c>
       <c r="B284" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C284" s="5" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D284" s="6" t="n">
-        <v>486.0</v>
+        <v>816.0</v>
       </c>
       <c r="E284" s="7" t="s">
         <v>12</v>
@@ -8814,13 +8817,13 @@
         <v>58</v>
       </c>
       <c r="B285" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C285" s="5" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="D285" s="6" t="n">
-        <v>1542.0</v>
+        <v>3200.0</v>
       </c>
       <c r="E285" s="7" t="s">
         <v>12</v>
@@ -8843,19 +8846,19 @@
         <v>58</v>
       </c>
       <c r="B286" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C286" s="5" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D286" s="6" t="n">
-        <v>292130.0</v>
+        <v>747712.0</v>
       </c>
       <c r="E286" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F286" s="7" t="n">
-        <v>6.0</v>
+        <v>16.0</v>
       </c>
       <c r="G286" s="8" t="s">
         <v>58</v>
@@ -8872,13 +8875,13 @@
         <v>58</v>
       </c>
       <c r="B287" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C287" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="D287" s="6" t="n">
-        <v>1502.0</v>
+        <v>3128.0</v>
       </c>
       <c r="E287" s="7" t="s">
         <v>12</v>
@@ -8898,28 +8901,28 @@
     </row>
     <row r="288">
       <c r="A288" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B288" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C288" s="5" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D288" s="6" t="n">
-        <v>146.0</v>
+        <v>22093.0</v>
       </c>
       <c r="E288" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F288" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F288" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G288" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="H288" s="8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I288" s="7" t="s">
         <v>12</v>
@@ -8930,19 +8933,19 @@
         <v>59</v>
       </c>
       <c r="B289" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C289" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="D289" s="6" t="n">
-        <v>23967.0</v>
+        <v>5147.0</v>
       </c>
       <c r="E289" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F289" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F289" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G289" s="8" t="s">
         <v>59</v>
@@ -8959,19 +8962,19 @@
         <v>59</v>
       </c>
       <c r="B290" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C290" s="5" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D290" s="6" t="n">
-        <v>74515.0</v>
+        <v>325.0</v>
       </c>
       <c r="E290" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F290" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F290" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G290" s="8" t="s">
         <v>59</v>
@@ -8988,19 +8991,19 @@
         <v>59</v>
       </c>
       <c r="B291" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C291" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D291" s="6" t="n">
-        <v>99098.0</v>
+        <v>512430.0</v>
       </c>
       <c r="E291" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F291" s="7" t="n">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="G291" s="8" t="s">
         <v>59</v>
@@ -9020,10 +9023,10 @@
         <v>15</v>
       </c>
       <c r="C292" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D292" s="6" t="n">
-        <v>2825.0</v>
+        <v>952.0</v>
       </c>
       <c r="E292" s="7" t="s">
         <v>12</v>
@@ -9049,10 +9052,10 @@
         <v>15</v>
       </c>
       <c r="C293" s="5" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D293" s="6" t="n">
-        <v>356.0</v>
+        <v>1164.0</v>
       </c>
       <c r="E293" s="7" t="s">
         <v>12</v>
@@ -9075,19 +9078,19 @@
         <v>59</v>
       </c>
       <c r="B294" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C294" s="5" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D294" s="6" t="n">
-        <v>28978.0</v>
+        <v>28983.0</v>
       </c>
       <c r="E294" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F294" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F294" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G294" s="8" t="s">
         <v>59</v>
@@ -9104,19 +9107,19 @@
         <v>59</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C295" s="5" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="D295" s="6" t="n">
-        <v>17054.0</v>
+        <v>5727.0</v>
       </c>
       <c r="E295" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F295" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F295" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G295" s="8" t="s">
         <v>59</v>
@@ -9133,13 +9136,13 @@
         <v>59</v>
       </c>
       <c r="B296" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C296" s="5" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="D296" s="6" t="n">
-        <v>4020.0</v>
+        <v>5227.0</v>
       </c>
       <c r="E296" s="7" t="s">
         <v>12</v>
@@ -9162,19 +9165,19 @@
         <v>59</v>
       </c>
       <c r="B297" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C297" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D297" s="6" t="n">
-        <v>13942.0</v>
+        <v>283905.0</v>
       </c>
       <c r="E297" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F297" s="7" t="n">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="G297" s="8" t="s">
         <v>59</v>
@@ -9191,19 +9194,19 @@
         <v>59</v>
       </c>
       <c r="B298" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C298" s="5" t="s">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="D298" s="6" t="n">
-        <v>773114.0</v>
+        <v>1182.0</v>
       </c>
       <c r="E298" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F298" s="7" t="n">
-        <v>31.0</v>
+        <v>12</v>
+      </c>
+      <c r="F298" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G298" s="8" t="s">
         <v>59</v>
@@ -9220,13 +9223,13 @@
         <v>59</v>
       </c>
       <c r="B299" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C299" s="5" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="D299" s="6" t="n">
-        <v>17807.0</v>
+        <v>13629.0</v>
       </c>
       <c r="E299" s="7" t="s">
         <v>12</v>
@@ -9249,13 +9252,13 @@
         <v>59</v>
       </c>
       <c r="B300" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C300" s="5" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D300" s="6" t="n">
-        <v>1274.0</v>
+        <v>1186.0</v>
       </c>
       <c r="E300" s="7" t="s">
         <v>12</v>
@@ -9278,19 +9281,19 @@
         <v>59</v>
       </c>
       <c r="B301" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C301" s="5" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D301" s="6" t="n">
-        <v>252920.0</v>
+        <v>728.0</v>
       </c>
       <c r="E301" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F301" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F301" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G301" s="8" t="s">
         <v>59</v>
@@ -9310,10 +9313,10 @@
         <v>10</v>
       </c>
       <c r="C302" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D302" s="6" t="n">
-        <v>42880.0</v>
+        <v>197.0</v>
       </c>
       <c r="E302" s="7" t="s">
         <v>12</v>
@@ -9339,16 +9342,16 @@
         <v>10</v>
       </c>
       <c r="C303" s="5" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D303" s="6" t="n">
-        <v>18799.0</v>
+        <v>506367.0</v>
       </c>
       <c r="E303" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F303" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F303" s="7" t="n">
+        <v>16.0</v>
       </c>
       <c r="G303" s="8" t="s">
         <v>59</v>
@@ -9371,7 +9374,7 @@
         <v>11</v>
       </c>
       <c r="D304" s="6" t="n">
-        <v>26497.0</v>
+        <v>85.0</v>
       </c>
       <c r="E304" s="7" t="s">
         <v>12</v>
@@ -9394,19 +9397,19 @@
         <v>59</v>
       </c>
       <c r="B305" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C305" s="5" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D305" s="6" t="n">
-        <v>1685.0</v>
+        <v>939.0</v>
       </c>
       <c r="E305" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F305" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F305" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G305" s="8" t="s">
         <v>59</v>
@@ -9423,19 +9426,19 @@
         <v>59</v>
       </c>
       <c r="B306" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C306" s="5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D306" s="6" t="n">
-        <v>12137.0</v>
+        <v>486.0</v>
       </c>
       <c r="E306" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F306" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F306" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G306" s="8" t="s">
         <v>59</v>
@@ -9452,19 +9455,19 @@
         <v>59</v>
       </c>
       <c r="B307" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C307" s="5" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D307" s="6" t="n">
-        <v>394262.0</v>
+        <v>1542.0</v>
       </c>
       <c r="E307" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F307" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F307" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G307" s="8" t="s">
         <v>59</v>
@@ -9481,19 +9484,19 @@
         <v>59</v>
       </c>
       <c r="B308" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C308" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D308" s="6" t="n">
-        <v>11734.0</v>
+        <v>292130.0</v>
       </c>
       <c r="E308" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F308" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F308" s="7" t="n">
+        <v>6.0</v>
       </c>
       <c r="G308" s="8" t="s">
         <v>59</v>
@@ -9510,13 +9513,13 @@
         <v>59</v>
       </c>
       <c r="B309" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C309" s="5" t="s">
         <v>48</v>
       </c>
       <c r="D309" s="6" t="n">
-        <v>1644.0</v>
+        <v>1502.0</v>
       </c>
       <c r="E309" s="7" t="s">
         <v>12</v>
@@ -9536,16 +9539,16 @@
     </row>
     <row r="310">
       <c r="A310" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B310" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C310" s="5" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D310" s="6" t="n">
-        <v>7147.0</v>
+        <v>146.0</v>
       </c>
       <c r="E310" s="7" t="s">
         <v>12</v>
@@ -9554,10 +9557,10 @@
         <v>12</v>
       </c>
       <c r="G310" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H310" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I310" s="7" t="s">
         <v>12</v>
@@ -9565,28 +9568,28 @@
     </row>
     <row r="311">
       <c r="A311" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B311" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C311" s="5" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="D311" s="6" t="n">
-        <v>477111.0</v>
+        <v>23967.0</v>
       </c>
       <c r="E311" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F311" s="7" t="n">
-        <v>13.0</v>
+        <v>12</v>
+      </c>
+      <c r="F311" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G311" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H311" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I311" s="7" t="s">
         <v>12</v>
@@ -9594,28 +9597,28 @@
     </row>
     <row r="312">
       <c r="A312" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B312" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C312" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="D312" s="6" t="n">
-        <v>5285.0</v>
+        <v>74515.0</v>
       </c>
       <c r="E312" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F312" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F312" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G312" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H312" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I312" s="7" t="s">
         <v>12</v>
@@ -9623,28 +9626,28 @@
     </row>
     <row r="313">
       <c r="A313" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B313" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C313" s="5" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="D313" s="6" t="n">
-        <v>5788.0</v>
+        <v>99098.0</v>
       </c>
       <c r="E313" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F313" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F313" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G313" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H313" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I313" s="7" t="s">
         <v>12</v>
@@ -9652,28 +9655,28 @@
     </row>
     <row r="314">
       <c r="A314" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B314" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C314" s="5" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="D314" s="6" t="n">
-        <v>26146.0</v>
+        <v>2825.0</v>
       </c>
       <c r="E314" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F314" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F314" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G314" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H314" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I314" s="7" t="s">
         <v>12</v>
@@ -9681,16 +9684,16 @@
     </row>
     <row r="315">
       <c r="A315" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B315" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C315" s="5" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D315" s="6" t="n">
-        <v>14588.0</v>
+        <v>356.0</v>
       </c>
       <c r="E315" s="7" t="s">
         <v>12</v>
@@ -9699,10 +9702,10 @@
         <v>12</v>
       </c>
       <c r="G315" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H315" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I315" s="7" t="s">
         <v>12</v>
@@ -9710,28 +9713,28 @@
     </row>
     <row r="316">
       <c r="A316" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B316" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C316" s="5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D316" s="6" t="n">
-        <v>280988.0</v>
+        <v>28978.0</v>
       </c>
       <c r="E316" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F316" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G316" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H316" s="8" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I316" s="7" t="s">
         <v>12</v>
@@ -9745,16 +9748,16 @@
         <v>15</v>
       </c>
       <c r="C317" s="5" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="D317" s="6" t="n">
-        <v>23841.0</v>
+        <v>17054.0</v>
       </c>
       <c r="E317" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F317" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F317" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G317" s="8" t="s">
         <v>60</v>
@@ -9771,19 +9774,19 @@
         <v>60</v>
       </c>
       <c r="B318" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C318" s="5" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="D318" s="6" t="n">
-        <v>199153.0</v>
+        <v>4020.0</v>
       </c>
       <c r="E318" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F318" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F318" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G318" s="8" t="s">
         <v>60</v>
@@ -9800,19 +9803,19 @@
         <v>60</v>
       </c>
       <c r="B319" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C319" s="5" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D319" s="6" t="n">
-        <v>20617.0</v>
+        <v>13942.0</v>
       </c>
       <c r="E319" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F319" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F319" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G319" s="8" t="s">
         <v>60</v>
@@ -9829,19 +9832,19 @@
         <v>60</v>
       </c>
       <c r="B320" s="5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C320" s="5" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D320" s="6" t="n">
-        <v>38558.0</v>
+        <v>773114.0</v>
       </c>
       <c r="E320" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F320" s="7" t="n">
-        <v>1.0</v>
+        <v>31.0</v>
       </c>
       <c r="G320" s="8" t="s">
         <v>60</v>
@@ -9861,16 +9864,16 @@
         <v>13</v>
       </c>
       <c r="C321" s="5" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="D321" s="6" t="n">
-        <v>126418.0</v>
+        <v>17807.0</v>
       </c>
       <c r="E321" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F321" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F321" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G321" s="8" t="s">
         <v>60</v>
@@ -9890,10 +9893,10 @@
         <v>15</v>
       </c>
       <c r="C322" s="5" t="s">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D322" s="6" t="n">
-        <v>2200.0</v>
+        <v>1274.0</v>
       </c>
       <c r="E322" s="7" t="s">
         <v>12</v>
@@ -9916,19 +9919,19 @@
         <v>60</v>
       </c>
       <c r="B323" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C323" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D323" s="6" t="n">
-        <v>35873.0</v>
+        <v>252920.0</v>
       </c>
       <c r="E323" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F323" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F323" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G323" s="8" t="s">
         <v>60</v>
@@ -9945,19 +9948,19 @@
         <v>60</v>
       </c>
       <c r="B324" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C324" s="5" t="s">
-        <v>34</v>
+        <v>11</v>
       </c>
       <c r="D324" s="6" t="n">
-        <v>16744.0</v>
+        <v>42880.0</v>
       </c>
       <c r="E324" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F324" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F324" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G324" s="8" t="s">
         <v>60</v>
@@ -9974,19 +9977,19 @@
         <v>60</v>
       </c>
       <c r="B325" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C325" s="5" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="D325" s="6" t="n">
-        <v>32194.0</v>
+        <v>18799.0</v>
       </c>
       <c r="E325" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F325" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F325" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G325" s="8" t="s">
         <v>60</v>
@@ -10003,19 +10006,19 @@
         <v>60</v>
       </c>
       <c r="B326" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C326" s="5" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D326" s="6" t="n">
-        <v>542175.0</v>
+        <v>26497.0</v>
       </c>
       <c r="E326" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F326" s="7" t="n">
-        <v>9.0</v>
+        <v>12</v>
+      </c>
+      <c r="F326" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G326" s="8" t="s">
         <v>60</v>
@@ -10032,19 +10035,19 @@
         <v>60</v>
       </c>
       <c r="B327" s="5" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C327" s="5" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D327" s="6" t="n">
-        <v>274584.0</v>
+        <v>1685.0</v>
       </c>
       <c r="E327" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F327" s="7" t="n">
-        <v>14.0</v>
+        <v>1.0</v>
       </c>
       <c r="G327" s="8" t="s">
         <v>60</v>
@@ -10061,19 +10064,19 @@
         <v>60</v>
       </c>
       <c r="B328" s="5" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C328" s="5" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D328" s="6" t="n">
-        <v>35692.0</v>
+        <v>12137.0</v>
       </c>
       <c r="E328" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F328" s="7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G328" s="8" t="s">
         <v>60</v>
@@ -10090,19 +10093,19 @@
         <v>60</v>
       </c>
       <c r="B329" s="5" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C329" s="5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="D329" s="6" t="n">
-        <v>30762.0</v>
+        <v>394262.0</v>
       </c>
       <c r="E329" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F329" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F329" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G329" s="8" t="s">
         <v>60</v>
@@ -10119,13 +10122,13 @@
         <v>60</v>
       </c>
       <c r="B330" s="5" t="s">
-        <v>13</v>
+        <v>44</v>
       </c>
       <c r="C330" s="5" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="D330" s="6" t="n">
-        <v>19972.0</v>
+        <v>11734.0</v>
       </c>
       <c r="E330" s="7" t="s">
         <v>12</v>
@@ -10148,13 +10151,13 @@
         <v>60</v>
       </c>
       <c r="B331" s="5" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C331" s="5" t="s">
-        <v>16</v>
+        <v>50</v>
       </c>
       <c r="D331" s="6" t="n">
-        <v>36976.0</v>
+        <v>1644.0</v>
       </c>
       <c r="E331" s="7" t="s">
         <v>12</v>
@@ -10177,13 +10180,13 @@
         <v>60</v>
       </c>
       <c r="B332" s="5" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C332" s="5" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D332" s="6" t="n">
-        <v>74182.0</v>
+        <v>7147.0</v>
       </c>
       <c r="E332" s="7" t="s">
         <v>12</v>
@@ -10209,16 +10212,16 @@
         <v>10</v>
       </c>
       <c r="C333" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="D333" s="6" t="n">
-        <v>277603.0</v>
+        <v>477111.0</v>
       </c>
       <c r="E333" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F333" s="7" t="n">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="G333" s="8" t="s">
         <v>60</v>
@@ -10238,16 +10241,16 @@
         <v>10</v>
       </c>
       <c r="C334" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D334" s="6" t="n">
-        <v>61232.0</v>
+        <v>5285.0</v>
       </c>
       <c r="E334" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F334" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F334" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G334" s="8" t="s">
         <v>60</v>
@@ -10267,16 +10270,16 @@
         <v>10</v>
       </c>
       <c r="C335" s="5" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D335" s="6" t="n">
-        <v>64701.0</v>
+        <v>5788.0</v>
       </c>
       <c r="E335" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F335" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F335" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G335" s="8" t="s">
         <v>60</v>
@@ -10296,16 +10299,16 @@
         <v>10</v>
       </c>
       <c r="C336" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D336" s="6" t="n">
-        <v>6327.0</v>
+        <v>26146.0</v>
       </c>
       <c r="E336" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F336" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F336" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G336" s="8" t="s">
         <v>60</v>
@@ -10325,16 +10328,16 @@
         <v>10</v>
       </c>
       <c r="C337" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D337" s="6" t="n">
-        <v>173630.0</v>
+        <v>14588.0</v>
       </c>
       <c r="E337" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F337" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F337" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G337" s="8" t="s">
         <v>60</v>
@@ -10354,13 +10357,13 @@
         <v>10</v>
       </c>
       <c r="C338" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D338" s="6" t="n">
-        <v>171789.0</v>
+        <v>280988.0</v>
       </c>
       <c r="E338" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F338" s="7" t="n">
         <v>5.0</v>
@@ -10377,16 +10380,16 @@
     </row>
     <row r="339">
       <c r="A339" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B339" s="5" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C339" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D339" s="6" t="n">
-        <v>80351.0</v>
+        <v>23841.0</v>
       </c>
       <c r="E339" s="7" t="s">
         <v>12</v>
@@ -10395,10 +10398,10 @@
         <v>12</v>
       </c>
       <c r="G339" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H339" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I339" s="7" t="s">
         <v>12</v>
@@ -10406,28 +10409,28 @@
     </row>
     <row r="340">
       <c r="A340" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B340" s="5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C340" s="5" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D340" s="6" t="n">
-        <v>26014.0</v>
+        <v>199153.0</v>
       </c>
       <c r="E340" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F340" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F340" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G340" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H340" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I340" s="7" t="s">
         <v>12</v>
@@ -10435,16 +10438,16 @@
     </row>
     <row r="341">
       <c r="A341" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B341" s="5" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C341" s="5" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="D341" s="6" t="n">
-        <v>8810.0</v>
+        <v>20617.0</v>
       </c>
       <c r="E341" s="7" t="s">
         <v>12</v>
@@ -10453,10 +10456,10 @@
         <v>12</v>
       </c>
       <c r="G341" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H341" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I341" s="7" t="s">
         <v>12</v>
@@ -10464,28 +10467,28 @@
     </row>
     <row r="342">
       <c r="A342" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B342" s="5" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C342" s="5" t="s">
-        <v>44</v>
+        <v>14</v>
       </c>
       <c r="D342" s="6" t="n">
-        <v>2368.0</v>
+        <v>38558.0</v>
       </c>
       <c r="E342" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F342" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F342" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G342" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H342" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I342" s="7" t="s">
         <v>12</v>
@@ -10493,28 +10496,28 @@
     </row>
     <row r="343">
       <c r="A343" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B343" s="5" t="s">
-        <v>43</v>
+        <v>13</v>
       </c>
       <c r="C343" s="5" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="D343" s="6" t="n">
-        <v>28702.0</v>
+        <v>126418.0</v>
       </c>
       <c r="E343" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F343" s="7" t="s">
-        <v>12</v>
+        <v>17</v>
+      </c>
+      <c r="F343" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G343" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H343" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I343" s="7" t="s">
         <v>12</v>
@@ -10522,28 +10525,28 @@
     </row>
     <row r="344">
       <c r="A344" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B344" s="5" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C344" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D344" s="6" t="n">
-        <v>247735.0</v>
+        <v>2200.0</v>
       </c>
       <c r="E344" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F344" s="7" t="n">
-        <v>10.0</v>
+        <v>12</v>
+      </c>
+      <c r="F344" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G344" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H344" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I344" s="7" t="s">
         <v>12</v>
@@ -10551,16 +10554,16 @@
     </row>
     <row r="345">
       <c r="A345" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B345" s="5" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C345" s="5" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="D345" s="6" t="n">
-        <v>15987.0</v>
+        <v>35873.0</v>
       </c>
       <c r="E345" s="7" t="s">
         <v>12</v>
@@ -10569,10 +10572,10 @@
         <v>12</v>
       </c>
       <c r="G345" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H345" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I345" s="7" t="s">
         <v>12</v>
@@ -10580,30 +10583,668 @@
     </row>
     <row r="346">
       <c r="A346" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>15</v>
       </c>
       <c r="C346" s="5" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D346" s="6" t="n">
-        <v>48163.0</v>
+        <v>16744.0</v>
       </c>
       <c r="E346" s="7" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F346" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G346" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="H346" s="8" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I346" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B347" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C347" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D347" s="6" t="n">
+        <v>32194.0</v>
+      </c>
+      <c r="E347" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F347" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G347" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H347" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I347" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C348" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D348" s="6" t="n">
+        <v>542175.0</v>
+      </c>
+      <c r="E348" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F348" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G348" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H348" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I348" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C349" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D349" s="6" t="n">
+        <v>274584.0</v>
+      </c>
+      <c r="E349" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F349" s="7" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="G349" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H349" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I349" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C350" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D350" s="6" t="n">
+        <v>35692.0</v>
+      </c>
+      <c r="E350" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F350" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G350" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H350" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I350" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C351" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D351" s="6" t="n">
+        <v>30762.0</v>
+      </c>
+      <c r="E351" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F351" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G351" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H351" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I351" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D352" s="6" t="n">
+        <v>19972.0</v>
+      </c>
+      <c r="E352" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F352" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G352" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H352" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I352" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D353" s="6" t="n">
+        <v>36976.0</v>
+      </c>
+      <c r="E353" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F353" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G353" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H353" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I353" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C354" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D354" s="6" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="E354" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F354" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G354" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H354" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I354" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C355" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D355" s="6" t="n">
+        <v>277603.0</v>
+      </c>
+      <c r="E355" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F355" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G355" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H355" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I355" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C356" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D356" s="6" t="n">
+        <v>61232.0</v>
+      </c>
+      <c r="E356" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F356" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G356" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H356" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I356" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C357" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D357" s="6" t="n">
+        <v>64701.0</v>
+      </c>
+      <c r="E357" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F357" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G357" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H357" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I357" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C358" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D358" s="6" t="n">
+        <v>6327.0</v>
+      </c>
+      <c r="E358" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F358" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G358" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H358" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I358" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C359" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D359" s="6" t="n">
+        <v>173630.0</v>
+      </c>
+      <c r="E359" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F359" s="7" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G359" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H359" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I359" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C360" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D360" s="6" t="n">
+        <v>171789.0</v>
+      </c>
+      <c r="E360" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F360" s="7" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="G360" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H360" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I360" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C361" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D361" s="6" t="n">
+        <v>80351.0</v>
+      </c>
+      <c r="E361" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F361" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G361" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H361" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I361" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C362" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D362" s="6" t="n">
+        <v>26014.0</v>
+      </c>
+      <c r="E362" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F362" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G362" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H362" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I362" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C363" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D363" s="6" t="n">
+        <v>8810.0</v>
+      </c>
+      <c r="E363" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F363" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G363" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H363" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I363" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C364" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="D364" s="6" t="n">
+        <v>2368.0</v>
+      </c>
+      <c r="E364" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F364" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G364" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H364" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I364" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C365" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D365" s="6" t="n">
+        <v>28702.0</v>
+      </c>
+      <c r="E365" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F365" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G365" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H365" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I365" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C366" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D366" s="6" t="n">
+        <v>247735.0</v>
+      </c>
+      <c r="E366" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F366" s="7" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="G366" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H366" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I366" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C367" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D367" s="6" t="n">
+        <v>15987.0</v>
+      </c>
+      <c r="E367" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F367" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G367" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H367" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I367" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C368" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D368" s="6" t="n">
+        <v>48163.0</v>
+      </c>
+      <c r="E368" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F368" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G368" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H368" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I368" s="7" t="s">
         <v>12</v>
       </c>
     </row>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -643,7 +643,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>30069.0</v>
+        <v>31080.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -672,7 +672,7 @@
         <v>15</v>
       </c>
       <c r="D3" s="6" t="n">
-        <v>126573.0</v>
+        <v>153483.0</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>12</v>
@@ -701,7 +701,7 @@
         <v>17</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>2086.0</v>
+        <v>2171.0</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
@@ -730,7 +730,7 @@
         <v>18</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>33931.0</v>
+        <v>38629.0</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
@@ -759,7 +759,7 @@
         <v>19</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>11016.0</v>
+        <v>11354.0</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
@@ -788,13 +788,13 @@
         <v>20</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>177276.0</v>
+        <v>233144.0</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -817,13 +817,13 @@
         <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>375415.0</v>
+        <v>504680.0</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>5.0</v>
+        <v>7.0</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -846,7 +846,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>15465.0</v>
+        <v>15995.0</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
@@ -875,7 +875,7 @@
         <v>23</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>59934.0</v>
+        <v>72671.0</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
@@ -962,7 +962,7 @@
         <v>26</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>101291.0</v>
+        <v>129988.0</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>12</v>
@@ -991,7 +991,7 @@
         <v>27</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>53804.0</v>
+        <v>69026.0</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>12</v>
@@ -1020,7 +1020,7 @@
         <v>28</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>767.0</v>
+        <v>792.0</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
@@ -1078,7 +1078,7 @@
         <v>30</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>9529.0</v>
+        <v>9623.0</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
@@ -1107,7 +1107,7 @@
         <v>31</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>176843.0</v>
+        <v>212818.0</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>12</v>
@@ -1136,13 +1136,13 @@
         <v>32</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>302491.0</v>
+        <v>368994.0</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F19" s="7" t="n">
-        <v>7.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>9</v>
@@ -1165,7 +1165,7 @@
         <v>33</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>16479.0</v>
+        <v>19413.0</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
@@ -1194,13 +1194,13 @@
         <v>34</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>177654.0</v>
+        <v>250175.0</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>12</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="G21" s="8" t="s">
         <v>9</v>
@@ -1223,7 +1223,7 @@
         <v>35</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>55229.0</v>
+        <v>68998.0</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
@@ -1252,7 +1252,7 @@
         <v>36</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>196092.0</v>
+        <v>248522.0</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>12</v>
@@ -1310,7 +1310,7 @@
         <v>38</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>19134.0</v>
+        <v>21238.0</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>12</v>
@@ -1339,7 +1339,7 @@
         <v>39</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>4089.0</v>
+        <v>4406.0</v>
       </c>
       <c r="E26" s="7" t="s">
         <v>13</v>
@@ -1455,7 +1455,7 @@
         <v>20</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>304795.0</v>
+        <v>304877.0</v>
       </c>
       <c r="E30" s="7" t="s">
         <v>12</v>
@@ -1484,7 +1484,7 @@
         <v>21</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>481417.0</v>
+        <v>482493.0</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>12</v>
@@ -1716,7 +1716,7 @@
         <v>31</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>265858.0</v>
+        <v>266037.0</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>12</v>
@@ -1832,7 +1832,7 @@
         <v>32</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>255729.0</v>
+        <v>256885.0</v>
       </c>
       <c r="E43" s="7" t="s">
         <v>12</v>

--- a/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
+++ b/DATA-Mess-WS-tệp-trung-1917455875136727.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1764" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2068" uniqueCount="77">
   <si>
     <t>Ngày</t>
   </si>
@@ -41,7 +41,7 @@
     <t>Kết quả (ban đầu)</t>
   </si>
   <si>
-    <t>2026-09-07</t>
+    <t>2026-09-08</t>
   </si>
   <si>
     <t>120253759731680341</t>
@@ -53,82 +53,70 @@
     <t/>
   </si>
   <si>
+    <t>120253762151910341</t>
+  </si>
+  <si>
+    <t>120253023460500341</t>
+  </si>
+  <si>
+    <t>120253023460490341</t>
+  </si>
+  <si>
+    <t>120253023954740341</t>
+  </si>
+  <si>
+    <t>120253023954760341</t>
+  </si>
+  <si>
+    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
+  </si>
+  <si>
+    <t>120253023954770341</t>
+  </si>
+  <si>
     <t>120253028817940341</t>
+  </si>
+  <si>
+    <t>120253028817950341</t>
+  </si>
+  <si>
+    <t>120253028817960341</t>
   </si>
   <si>
     <t>120253028817980341</t>
   </si>
   <si>
-    <t>Lượt bắt đầu cuộc trò chuyện qua tin nhắn</t>
-  </si>
-  <si>
-    <t>120253761757650341</t>
-  </si>
-  <si>
-    <t>120253023460500341</t>
-  </si>
-  <si>
-    <t>120253721770850341</t>
-  </si>
-  <si>
     <t>120253031332440341</t>
   </si>
   <si>
-    <t>120253031402040341</t>
+    <t>120253031332470341</t>
+  </si>
+  <si>
+    <t>120253031332480341</t>
+  </si>
+  <si>
+    <t>120253031332490341</t>
+  </si>
+  <si>
+    <t>120253031402020341</t>
   </si>
   <si>
     <t>120253031402030341</t>
   </si>
   <si>
-    <t>120253031402020341</t>
-  </si>
-  <si>
-    <t>120253031332470341</t>
-  </si>
-  <si>
-    <t>120253028817970341</t>
-  </si>
-  <si>
-    <t>120253761757670341</t>
-  </si>
-  <si>
-    <t>120253028817960341</t>
+    <t>120253721770870341</t>
   </si>
   <si>
     <t>120253023954790341</t>
   </si>
   <si>
-    <t>120253023954770341</t>
+    <t>120253762151840341</t>
   </si>
   <si>
-    <t>120253023954760341</t>
+    <t>120253762152000341</t>
   </si>
   <si>
-    <t>120253023954750341</t>
-  </si>
-  <si>
-    <t>120253023954740341</t>
-  </si>
-  <si>
-    <t>120253023460490341</t>
-  </si>
-  <si>
-    <t>120253761757660341</t>
-  </si>
-  <si>
-    <t>120253028817950341</t>
-  </si>
-  <si>
-    <t>120253762151810341</t>
-  </si>
-  <si>
-    <t>120253762151970341</t>
-  </si>
-  <si>
-    <t>120253762151860341</t>
-  </si>
-  <si>
-    <t>120253762151870341</t>
+    <t>120253762151830341</t>
   </si>
   <si>
     <t>120253762151990341</t>
@@ -137,61 +125,94 @@
     <t>120253762151960341</t>
   </si>
   <si>
+    <t>120253762151970341</t>
+  </si>
+  <si>
+    <t>120253762151820341</t>
+  </si>
+  <si>
     <t>120253762151880341</t>
   </si>
   <si>
-    <t>120253762151840341</t>
+    <t>120253762151860341</t>
   </si>
   <si>
-    <t>120253762151910341</t>
+    <t>120253762151810341</t>
+  </si>
+  <si>
+    <t>120253761757670341</t>
+  </si>
+  <si>
+    <t>120253761757660341</t>
+  </si>
+  <si>
+    <t>120253761757650341</t>
+  </si>
+  <si>
+    <t>120253762151980341</t>
+  </si>
+  <si>
+    <t>2026-09-07</t>
+  </si>
+  <si>
+    <t>120253721770850341</t>
+  </si>
+  <si>
+    <t>120253031332450341</t>
+  </si>
+  <si>
+    <t>120253031402050341</t>
+  </si>
+  <si>
+    <t>120253031402040341</t>
+  </si>
+  <si>
+    <t>120253031402010341</t>
+  </si>
+  <si>
+    <t>120253031332460341</t>
+  </si>
+  <si>
+    <t>120253023954800341</t>
+  </si>
+  <si>
+    <t>120253023954750341</t>
+  </si>
+  <si>
+    <t>120253762151870341</t>
+  </si>
+  <si>
+    <t>120253721770860341</t>
+  </si>
+  <si>
+    <t>120253028817970341</t>
+  </si>
+  <si>
+    <t>120253759731700341</t>
+  </si>
+  <si>
+    <t>120253762151900341</t>
   </si>
   <si>
     <t>120253762151890341</t>
   </si>
   <si>
-    <t>120253762151900341</t>
+    <t>120253762151850341</t>
   </si>
   <si>
-    <t>120253762151820341</t>
-  </si>
-  <si>
-    <t>120253762152000341</t>
+    <t>120253762151940341</t>
   </si>
   <si>
     <t>120253762151950341</t>
   </si>
   <si>
-    <t>120253762151980341</t>
-  </si>
-  <si>
     <t>120253762151930341</t>
-  </si>
-  <si>
-    <t>120253762151850341</t>
   </si>
   <si>
     <t>2026-09-06</t>
   </si>
   <si>
-    <t>120253031332480341</t>
-  </si>
-  <si>
-    <t>120253031332490341</t>
-  </si>
-  <si>
-    <t>120253721770870341</t>
-  </si>
-  <si>
-    <t>120253031402050341</t>
-  </si>
-  <si>
-    <t>120253031332450341</t>
-  </si>
-  <si>
     <t>120253721770840341</t>
-  </si>
-  <si>
-    <t>120253031332460341</t>
   </si>
   <si>
     <t>120253028818100341</t>
@@ -200,28 +221,10 @@
     <t>120253023954820341</t>
   </si>
   <si>
-    <t>120253023954800341</t>
-  </si>
-  <si>
-    <t>120253721770860341</t>
-  </si>
-  <si>
-    <t>120253759731700341</t>
-  </si>
-  <si>
     <t>120253762151920341</t>
   </si>
   <si>
-    <t>120253762151940341</t>
-  </si>
-  <si>
-    <t>120253762151830341</t>
-  </si>
-  <si>
     <t>2026-09-05</t>
-  </si>
-  <si>
-    <t>120253031402010341</t>
   </si>
   <si>
     <t>2026-09-04</t>
@@ -603,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I231"/>
+  <dimension ref="A1:I271"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="10" max="16384" style="1" width="12.7109375"/>
@@ -658,7 +661,7 @@
         <v>11</v>
       </c>
       <c r="D2" s="6" t="n">
-        <v>473.0</v>
+        <v>2186.0</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>12</v>
@@ -681,19 +684,19 @@
         <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="D3" s="6" t="n">
-        <v>59655.0</v>
+        <v>14858.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>9</v>
@@ -710,19 +713,19 @@
         <v>9</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>41579.0</v>
+        <v>1535.0</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G4" s="8" t="s">
         <v>9</v>
@@ -739,13 +742,13 @@
         <v>9</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>173.0</v>
+        <v>182.0</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>12</v>
@@ -768,19 +771,19 @@
         <v>9</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>616.0</v>
+        <v>23452.0</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G6" s="8" t="s">
         <v>9</v>
@@ -797,19 +800,19 @@
         <v>9</v>
       </c>
       <c r="B7" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="s">
-        <v>21</v>
-      </c>
       <c r="D7" s="6" t="n">
-        <v>84913.0</v>
+        <v>141291.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="G7" s="8" t="s">
         <v>9</v>
@@ -826,19 +829,19 @@
         <v>9</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>28350.0</v>
+        <v>14472.0</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>9</v>
@@ -855,19 +858,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>23869.0</v>
+        <v>29426.0</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G9" s="8" t="s">
         <v>9</v>
@@ -884,19 +887,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>1731.0</v>
+        <v>73454.0</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G10" s="8" t="s">
         <v>9</v>
@@ -913,19 +916,19 @@
         <v>9</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2740.0</v>
+        <v>5918.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G11" s="8" t="s">
         <v>9</v>
@@ -942,13 +945,13 @@
         <v>9</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>26</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>5968.0</v>
+        <v>268.0</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>12</v>
@@ -971,19 +974,19 @@
         <v>9</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>27</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>19697.0</v>
+        <v>623.0</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G13" s="8" t="s">
         <v>9</v>
@@ -1000,19 +1003,19 @@
         <v>9</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>101324.0</v>
+        <v>17524.0</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G14" s="8" t="s">
         <v>9</v>
@@ -1029,19 +1032,19 @@
         <v>9</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>36846.0</v>
+        <v>99259.0</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G15" s="8" t="s">
         <v>9</v>
@@ -1058,13 +1061,13 @@
         <v>9</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>1710.0</v>
+        <v>1760.0</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>12</v>
@@ -1087,13 +1090,13 @@
         <v>9</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>3971.0</v>
+        <v>21467.0</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>12</v>
@@ -1116,13 +1119,13 @@
         <v>9</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>32</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>5609.0</v>
+        <v>129.0</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>12</v>
@@ -1151,13 +1154,13 @@
         <v>33</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>2497.0</v>
+        <v>111334.0</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>9</v>
@@ -1174,19 +1177,19 @@
         <v>9</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>34</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>27335.0</v>
+        <v>1656.0</v>
       </c>
       <c r="E20" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>9</v>
@@ -1209,7 +1212,7 @@
         <v>35</v>
       </c>
       <c r="D21" s="6" t="n">
-        <v>6037.0</v>
+        <v>6270.0</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>12</v>
@@ -1238,7 +1241,7 @@
         <v>36</v>
       </c>
       <c r="D22" s="6" t="n">
-        <v>69562.0</v>
+        <v>3700.0</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>12</v>
@@ -1267,7 +1270,7 @@
         <v>37</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>42062.0</v>
+        <v>132962.0</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>12</v>
@@ -1296,7 +1299,7 @@
         <v>38</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>830.0</v>
+        <v>1166.0</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>12</v>
@@ -1325,13 +1328,13 @@
         <v>39</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>6271.0</v>
+        <v>177779.0</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G25" s="8" t="s">
         <v>9</v>
@@ -1354,13 +1357,13 @@
         <v>40</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>7307.0</v>
+        <v>67368.0</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G26" s="8" t="s">
         <v>9</v>
@@ -1383,13 +1386,13 @@
         <v>41</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>165854.0</v>
+        <v>3616.0</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F27" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G27" s="8" t="s">
         <v>9</v>
@@ -1412,7 +1415,7 @@
         <v>42</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>86.0</v>
+        <v>8944.0</v>
       </c>
       <c r="E28" s="7" t="s">
         <v>12</v>
@@ -1441,7 +1444,7 @@
         <v>43</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>4796.0</v>
+        <v>2798.0</v>
       </c>
       <c r="E29" s="7" t="s">
         <v>12</v>
@@ -1470,13 +1473,13 @@
         <v>44</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>80.0</v>
+        <v>39402.0</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G30" s="8" t="s">
         <v>9</v>
@@ -1499,7 +1502,7 @@
         <v>45</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>288.0</v>
+        <v>4071.0</v>
       </c>
       <c r="E31" s="7" t="s">
         <v>12</v>
@@ -1519,28 +1522,28 @@
     </row>
     <row r="32">
       <c r="A32" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>5927.0</v>
+        <v>173.0</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H32" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I32" s="7" t="s">
         <v>12</v>
@@ -1548,28 +1551,28 @@
     </row>
     <row r="33">
       <c r="A33" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>107040.0</v>
+        <v>11128.0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H33" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I33" s="7" t="s">
         <v>12</v>
@@ -1577,16 +1580,16 @@
     </row>
     <row r="34">
       <c r="A34" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>1066.0</v>
+        <v>2835.0</v>
       </c>
       <c r="E34" s="7" t="s">
         <v>12</v>
@@ -1595,10 +1598,10 @@
         <v>12</v>
       </c>
       <c r="G34" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H34" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I34" s="7" t="s">
         <v>12</v>
@@ -1606,16 +1609,16 @@
     </row>
     <row r="35">
       <c r="A35" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>1762.0</v>
+        <v>11408.0</v>
       </c>
       <c r="E35" s="7" t="s">
         <v>12</v>
@@ -1624,10 +1627,10 @@
         <v>12</v>
       </c>
       <c r="G35" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H35" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I35" s="7" t="s">
         <v>12</v>
@@ -1635,28 +1638,28 @@
     </row>
     <row r="36">
       <c r="A36" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>143.0</v>
+        <v>408424.0</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>12.0</v>
       </c>
       <c r="G36" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H36" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I36" s="7" t="s">
         <v>12</v>
@@ -1664,28 +1667,28 @@
     </row>
     <row r="37">
       <c r="A37" s="4" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>761.0</v>
+        <v>254307.0</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F37" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G37" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="H37" s="8" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I37" s="7" t="s">
         <v>12</v>
@@ -1693,28 +1696,28 @@
     </row>
     <row r="38">
       <c r="A38" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="D38" s="6" t="n">
-        <v>143232.0</v>
+        <v>1950.0</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G38" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H38" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I38" s="7" t="s">
         <v>12</v>
@@ -1722,16 +1725,16 @@
     </row>
     <row r="39">
       <c r="A39" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="D39" s="6" t="n">
-        <v>299.0</v>
+        <v>34983.0</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>12</v>
@@ -1740,10 +1743,10 @@
         <v>12</v>
       </c>
       <c r="G39" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H39" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I39" s="7" t="s">
         <v>12</v>
@@ -1751,16 +1754,16 @@
     </row>
     <row r="40">
       <c r="A40" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="D40" s="6" t="n">
-        <v>4433.0</v>
+        <v>124816.0</v>
       </c>
       <c r="E40" s="7" t="s">
         <v>12</v>
@@ -1769,10 +1772,10 @@
         <v>12</v>
       </c>
       <c r="G40" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H40" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I40" s="7" t="s">
         <v>12</v>
@@ -1780,28 +1783,28 @@
     </row>
     <row r="41">
       <c r="A41" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B41" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C41" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D41" s="6" t="n">
-        <v>262150.0</v>
+        <v>453.0</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F41" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F41" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G41" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H41" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I41" s="7" t="s">
         <v>12</v>
@@ -1809,28 +1812,28 @@
     </row>
     <row r="42">
       <c r="A42" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B42" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C42" s="5" t="s">
-        <v>55</v>
-      </c>
       <c r="D42" s="6" t="n">
-        <v>1711.0</v>
+        <v>307697.0</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G42" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H42" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I42" s="7" t="s">
         <v>12</v>
@@ -1838,28 +1841,28 @@
     </row>
     <row r="43">
       <c r="A43" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D43" s="6" t="n">
-        <v>628634.0</v>
+        <v>255896.0</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F43" s="7" t="n">
-        <v>14.0</v>
+        <v>3.0</v>
       </c>
       <c r="G43" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H43" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I43" s="7" t="s">
         <v>12</v>
@@ -1867,28 +1870,28 @@
     </row>
     <row r="44">
       <c r="A44" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D44" s="6" t="n">
-        <v>2535.0</v>
+        <v>63984.0</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G44" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H44" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I44" s="7" t="s">
         <v>12</v>
@@ -1896,28 +1899,28 @@
     </row>
     <row r="45">
       <c r="A45" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="D45" s="6" t="n">
-        <v>1277.0</v>
+        <v>154556.0</v>
       </c>
       <c r="E45" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F45" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G45" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H45" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I45" s="7" t="s">
         <v>12</v>
@@ -1925,16 +1928,16 @@
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D46" s="6" t="n">
-        <v>2177.0</v>
+        <v>17323.0</v>
       </c>
       <c r="E46" s="7" t="s">
         <v>12</v>
@@ -1943,10 +1946,10 @@
         <v>12</v>
       </c>
       <c r="G46" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H46" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I46" s="7" t="s">
         <v>12</v>
@@ -1954,28 +1957,28 @@
     </row>
     <row r="47">
       <c r="A47" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="D47" s="6" t="n">
-        <v>230.0</v>
+        <v>93394.0</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F47" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G47" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H47" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I47" s="7" t="s">
         <v>12</v>
@@ -1983,28 +1986,28 @@
     </row>
     <row r="48">
       <c r="A48" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B48" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>59</v>
-      </c>
       <c r="D48" s="6" t="n">
-        <v>5595.0</v>
+        <v>499116.0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F48" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>19.0</v>
       </c>
       <c r="G48" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H48" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I48" s="7" t="s">
         <v>12</v>
@@ -2012,28 +2015,28 @@
     </row>
     <row r="49">
       <c r="A49" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="D49" s="6" t="n">
-        <v>284612.0</v>
+        <v>15739.0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F49" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G49" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H49" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I49" s="7" t="s">
         <v>12</v>
@@ -2041,28 +2044,28 @@
     </row>
     <row r="50">
       <c r="A50" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="D50" s="6" t="n">
-        <v>7371.0</v>
+        <v>14918.0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F50" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G50" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H50" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I50" s="7" t="s">
         <v>12</v>
@@ -2070,28 +2073,28 @@
     </row>
     <row r="51">
       <c r="A51" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D51" s="6" t="n">
-        <v>379556.0</v>
+        <v>9238.0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F51" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G51" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H51" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I51" s="7" t="s">
         <v>12</v>
@@ -2099,28 +2102,28 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="D52" s="6" t="n">
-        <v>50997.0</v>
+        <v>1703.0</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F52" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F52" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G52" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H52" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I52" s="7" t="s">
         <v>12</v>
@@ -2128,28 +2131,28 @@
     </row>
     <row r="53">
       <c r="A53" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D53" s="6" t="n">
-        <v>109331.0</v>
+        <v>4620.0</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F53" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G53" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H53" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I53" s="7" t="s">
         <v>12</v>
@@ -2157,16 +2160,16 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>716.0</v>
+        <v>1977.0</v>
       </c>
       <c r="E54" s="7" t="s">
         <v>12</v>
@@ -2175,10 +2178,10 @@
         <v>12</v>
       </c>
       <c r="G54" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H54" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I54" s="7" t="s">
         <v>12</v>
@@ -2186,16 +2189,16 @@
     </row>
     <row r="55">
       <c r="A55" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D55" s="6" t="n">
-        <v>1152.0</v>
+        <v>2700.0</v>
       </c>
       <c r="E55" s="7" t="s">
         <v>12</v>
@@ -2204,10 +2207,10 @@
         <v>12</v>
       </c>
       <c r="G55" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H55" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I55" s="7" t="s">
         <v>12</v>
@@ -2215,16 +2218,16 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="D56" s="6" t="n">
-        <v>11242.0</v>
+        <v>1777.0</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>12</v>
@@ -2233,10 +2236,10 @@
         <v>12</v>
       </c>
       <c r="G56" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H56" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I56" s="7" t="s">
         <v>12</v>
@@ -2244,28 +2247,28 @@
     </row>
     <row r="57">
       <c r="A57" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D57" s="6" t="n">
-        <v>640933.0</v>
+        <v>18850.0</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F57" s="7" t="n">
-        <v>24.0</v>
+        <v>12</v>
+      </c>
+      <c r="F57" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G57" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H57" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I57" s="7" t="s">
         <v>12</v>
@@ -2273,16 +2276,16 @@
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D58" s="6" t="n">
-        <v>11629.0</v>
+        <v>15532.0</v>
       </c>
       <c r="E58" s="7" t="s">
         <v>12</v>
@@ -2291,10 +2294,10 @@
         <v>12</v>
       </c>
       <c r="G58" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H58" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I58" s="7" t="s">
         <v>12</v>
@@ -2302,28 +2305,28 @@
     </row>
     <row r="59">
       <c r="A59" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D59" s="6" t="n">
-        <v>22898.0</v>
+        <v>92652.0</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F59" s="7" t="n">
         <v>2.0</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H59" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I59" s="7" t="s">
         <v>12</v>
@@ -2331,16 +2334,16 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D60" s="6" t="n">
-        <v>41999.0</v>
+        <v>14273.0</v>
       </c>
       <c r="E60" s="7" t="s">
         <v>12</v>
@@ -2349,10 +2352,10 @@
         <v>12</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H60" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I60" s="7" t="s">
         <v>12</v>
@@ -2360,28 +2363,28 @@
     </row>
     <row r="61">
       <c r="A61" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="D61" s="6" t="n">
-        <v>891.0</v>
+        <v>755333.0</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H61" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I61" s="7" t="s">
         <v>12</v>
@@ -2389,28 +2392,28 @@
     </row>
     <row r="62">
       <c r="A62" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>283.0</v>
+        <v>270624.0</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H62" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I62" s="7" t="s">
         <v>12</v>
@@ -2418,28 +2421,28 @@
     </row>
     <row r="63">
       <c r="A63" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="D63" s="6" t="n">
-        <v>75516.0</v>
+        <v>5654.0</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F63" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F63" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H63" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I63" s="7" t="s">
         <v>12</v>
@@ -2447,28 +2450,28 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D64" s="6" t="n">
-        <v>127.0</v>
+        <v>15395.0</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H64" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I64" s="7" t="s">
         <v>12</v>
@@ -2476,28 +2479,28 @@
     </row>
     <row r="65">
       <c r="A65" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="D65" s="6" t="n">
-        <v>16347.0</v>
+        <v>339954.0</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H65" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I65" s="7" t="s">
         <v>12</v>
@@ -2505,28 +2508,28 @@
     </row>
     <row r="66">
       <c r="A66" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B66" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="5" t="s">
-        <v>16</v>
+        <v>61</v>
       </c>
       <c r="D66" s="6" t="n">
-        <v>53873.0</v>
+        <v>4647.0</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H66" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I66" s="7" t="s">
         <v>12</v>
@@ -2534,28 +2537,28 @@
     </row>
     <row r="67">
       <c r="A67" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C67" s="5" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="D67" s="6" t="n">
-        <v>11399.0</v>
+        <v>132961.0</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H67" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I67" s="7" t="s">
         <v>12</v>
@@ -2563,16 +2566,16 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B68" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C68" s="5" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D68" s="6" t="n">
-        <v>3762.0</v>
+        <v>4359.0</v>
       </c>
       <c r="E68" s="7" t="s">
         <v>12</v>
@@ -2581,10 +2584,10 @@
         <v>12</v>
       </c>
       <c r="G68" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I68" s="7" t="s">
         <v>12</v>
@@ -2592,16 +2595,16 @@
     </row>
     <row r="69">
       <c r="A69" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C69" s="5" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="D69" s="6" t="n">
-        <v>4229.0</v>
+        <v>387.0</v>
       </c>
       <c r="E69" s="7" t="s">
         <v>12</v>
@@ -2610,10 +2613,10 @@
         <v>12</v>
       </c>
       <c r="G69" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H69" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I69" s="7" t="s">
         <v>12</v>
@@ -2621,28 +2624,28 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B70" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C70" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D70" s="6" t="n">
-        <v>29705.0</v>
+        <v>40926.0</v>
       </c>
       <c r="E70" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F70" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F70" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G70" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H70" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I70" s="7" t="s">
         <v>12</v>
@@ -2650,28 +2653,28 @@
     </row>
     <row r="71">
       <c r="A71" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B71" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C71" s="5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D71" s="6" t="n">
-        <v>79599.0</v>
+        <v>2512.0</v>
       </c>
       <c r="E71" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F71" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G71" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H71" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I71" s="7" t="s">
         <v>12</v>
@@ -2679,16 +2682,16 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C72" s="5" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="D72" s="6" t="n">
-        <v>32531.0</v>
+        <v>3079.0</v>
       </c>
       <c r="E72" s="7" t="s">
         <v>12</v>
@@ -2697,10 +2700,10 @@
         <v>12</v>
       </c>
       <c r="G72" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H72" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I72" s="7" t="s">
         <v>12</v>
@@ -2708,16 +2711,16 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B73" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C73" s="5" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="D73" s="6" t="n">
-        <v>975.0</v>
+        <v>14912.0</v>
       </c>
       <c r="E73" s="7" t="s">
         <v>12</v>
@@ -2726,10 +2729,10 @@
         <v>12</v>
       </c>
       <c r="G73" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H73" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I73" s="7" t="s">
         <v>12</v>
@@ -2737,28 +2740,28 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B74" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C74" s="5" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D74" s="6" t="n">
-        <v>313139.0</v>
+        <v>8493.0</v>
       </c>
       <c r="E74" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F74" s="7" t="n">
-        <v>9.0</v>
+        <v>12</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G74" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H74" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I74" s="7" t="s">
         <v>12</v>
@@ -2766,28 +2769,28 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C75" s="5" t="s">
-        <v>66</v>
+        <v>44</v>
       </c>
       <c r="D75" s="6" t="n">
-        <v>400.0</v>
+        <v>98010.0</v>
       </c>
       <c r="E75" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F75" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G75" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H75" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I75" s="7" t="s">
         <v>12</v>
@@ -2795,28 +2798,28 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B76" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C76" s="5" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D76" s="6" t="n">
-        <v>727254.0</v>
+        <v>10838.0</v>
       </c>
       <c r="E76" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F76" s="7" t="n">
-        <v>13.0</v>
+        <v>12</v>
+      </c>
+      <c r="F76" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G76" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H76" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I76" s="7" t="s">
         <v>12</v>
@@ -2824,28 +2827,28 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C77" s="5" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="D77" s="6" t="n">
-        <v>16667.0</v>
+        <v>25071.0</v>
       </c>
       <c r="E77" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F77" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G77" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="H77" s="8" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I77" s="7" t="s">
         <v>12</v>
@@ -2853,28 +2856,28 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C78" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D78" s="6" t="n">
-        <v>540180.0</v>
+        <v>2177.0</v>
       </c>
       <c r="E78" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F78" s="7" t="n">
-        <v>15.0</v>
+        <v>12</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G78" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H78" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I78" s="7" t="s">
         <v>12</v>
@@ -2882,16 +2885,16 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="D79" s="6" t="n">
-        <v>13697.0</v>
+        <v>230.0</v>
       </c>
       <c r="E79" s="7" t="s">
         <v>12</v>
@@ -2900,10 +2903,10 @@
         <v>12</v>
       </c>
       <c r="G79" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H79" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I79" s="7" t="s">
         <v>12</v>
@@ -2911,16 +2914,16 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="D80" s="6" t="n">
-        <v>6523.0</v>
+        <v>1277.0</v>
       </c>
       <c r="E80" s="7" t="s">
         <v>12</v>
@@ -2929,10 +2932,10 @@
         <v>12</v>
       </c>
       <c r="G80" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H80" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I80" s="7" t="s">
         <v>12</v>
@@ -2940,16 +2943,16 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D81" s="6" t="n">
-        <v>16644.0</v>
+        <v>2535.0</v>
       </c>
       <c r="E81" s="7" t="s">
         <v>12</v>
@@ -2958,10 +2961,10 @@
         <v>12</v>
       </c>
       <c r="G81" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H81" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I81" s="7" t="s">
         <v>12</v>
@@ -2969,28 +2972,28 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D82" s="6" t="n">
-        <v>8361.0</v>
+        <v>629793.0</v>
       </c>
       <c r="E82" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G82" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H82" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I82" s="7" t="s">
         <v>12</v>
@@ -2998,28 +3001,28 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D83" s="6" t="n">
-        <v>4729.0</v>
+        <v>262939.0</v>
       </c>
       <c r="E83" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F83" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F83" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G83" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H83" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I83" s="7" t="s">
         <v>12</v>
@@ -3027,28 +3030,28 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D84" s="6" t="n">
-        <v>234875.0</v>
+        <v>891.0</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F84" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F84" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G84" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H84" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I84" s="7" t="s">
         <v>12</v>
@@ -3056,16 +3059,16 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D85" s="6" t="n">
-        <v>45885.0</v>
+        <v>4433.0</v>
       </c>
       <c r="E85" s="7" t="s">
         <v>12</v>
@@ -3074,10 +3077,10 @@
         <v>12</v>
       </c>
       <c r="G85" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H85" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I85" s="7" t="s">
         <v>12</v>
@@ -3085,16 +3088,16 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>46</v>
+        <v>26</v>
       </c>
       <c r="D86" s="6" t="n">
-        <v>58570.0</v>
+        <v>299.0</v>
       </c>
       <c r="E86" s="7" t="s">
         <v>12</v>
@@ -3103,10 +3106,10 @@
         <v>12</v>
       </c>
       <c r="G86" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H86" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I86" s="7" t="s">
         <v>12</v>
@@ -3114,28 +3117,28 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="D87" s="6" t="n">
-        <v>23742.0</v>
+        <v>143540.0</v>
       </c>
       <c r="E87" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F87" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G87" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="H87" s="8" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I87" s="7" t="s">
         <v>12</v>
@@ -3143,28 +3146,28 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D88" s="6" t="n">
-        <v>287203.0</v>
+        <v>5595.0</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F88" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F88" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G88" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H88" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I88" s="7" t="s">
         <v>12</v>
@@ -3172,28 +3175,28 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="D89" s="6" t="n">
-        <v>36571.0</v>
+        <v>22898.0</v>
       </c>
       <c r="E89" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F89" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F89" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G89" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H89" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I89" s="7" t="s">
         <v>12</v>
@@ -3201,16 +3204,16 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="D90" s="6" t="n">
-        <v>14342.0</v>
+        <v>7371.0</v>
       </c>
       <c r="E90" s="7" t="s">
         <v>12</v>
@@ -3219,10 +3222,10 @@
         <v>12</v>
       </c>
       <c r="G90" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H90" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I90" s="7" t="s">
         <v>12</v>
@@ -3230,28 +3233,28 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="D91" s="6" t="n">
-        <v>47217.0</v>
+        <v>382081.0</v>
       </c>
       <c r="E91" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F91" s="7" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G91" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H91" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I91" s="7" t="s">
         <v>12</v>
@@ -3259,28 +3262,28 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D92" s="6" t="n">
-        <v>65872.0</v>
+        <v>50997.0</v>
       </c>
       <c r="E92" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F92" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F92" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G92" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H92" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I92" s="7" t="s">
         <v>12</v>
@@ -3288,28 +3291,28 @@
     </row>
     <row r="93">
       <c r="A93" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="D93" s="6" t="n">
-        <v>16990.0</v>
+        <v>109432.0</v>
       </c>
       <c r="E93" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F93" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F93" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G93" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H93" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I93" s="7" t="s">
         <v>12</v>
@@ -3317,28 +3320,28 @@
     </row>
     <row r="94">
       <c r="A94" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B94" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="5" t="s">
-        <v>35</v>
-      </c>
       <c r="D94" s="6" t="n">
-        <v>155352.0</v>
+        <v>716.0</v>
       </c>
       <c r="E94" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F94" s="7" t="n">
-        <v>5.0</v>
+        <v>12</v>
+      </c>
+      <c r="F94" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G94" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H94" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I94" s="7" t="s">
         <v>12</v>
@@ -3346,28 +3349,28 @@
     </row>
     <row r="95">
       <c r="A95" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="D95" s="6" t="n">
-        <v>70613.0</v>
+        <v>1152.0</v>
       </c>
       <c r="E95" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F95" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F95" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G95" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H95" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I95" s="7" t="s">
         <v>12</v>
@@ -3375,16 +3378,16 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D96" s="6" t="n">
-        <v>14906.0</v>
+        <v>11242.0</v>
       </c>
       <c r="E96" s="7" t="s">
         <v>12</v>
@@ -3393,10 +3396,10 @@
         <v>12</v>
       </c>
       <c r="G96" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H96" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I96" s="7" t="s">
         <v>12</v>
@@ -3404,28 +3407,28 @@
     </row>
     <row r="97">
       <c r="A97" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D97" s="6" t="n">
-        <v>114488.0</v>
+        <v>642318.0</v>
       </c>
       <c r="E97" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F97" s="7" t="n">
-        <v>1.0</v>
+        <v>24.0</v>
       </c>
       <c r="G97" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H97" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I97" s="7" t="s">
         <v>12</v>
@@ -3433,28 +3436,28 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B98" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C98" s="5" t="s">
-        <v>18</v>
-      </c>
       <c r="D98" s="6" t="n">
-        <v>7517.0</v>
+        <v>284612.0</v>
       </c>
       <c r="E98" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F98" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F98" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G98" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H98" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I98" s="7" t="s">
         <v>12</v>
@@ -3462,28 +3465,28 @@
     </row>
     <row r="99">
       <c r="A99" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="D99" s="6" t="n">
-        <v>233499.0</v>
+        <v>11629.0</v>
       </c>
       <c r="E99" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F99" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F99" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G99" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H99" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I99" s="7" t="s">
         <v>12</v>
@@ -3491,16 +3494,16 @@
     </row>
     <row r="100">
       <c r="A100" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="D100" s="6" t="n">
-        <v>36573.0</v>
+        <v>1711.0</v>
       </c>
       <c r="E100" s="7" t="s">
         <v>12</v>
@@ -3509,10 +3512,10 @@
         <v>12</v>
       </c>
       <c r="G100" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H100" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I100" s="7" t="s">
         <v>12</v>
@@ -3520,16 +3523,16 @@
     </row>
     <row r="101">
       <c r="A101" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>65</v>
+        <v>15</v>
       </c>
       <c r="D101" s="6" t="n">
-        <v>1225.0</v>
+        <v>41999.0</v>
       </c>
       <c r="E101" s="7" t="s">
         <v>12</v>
@@ -3538,10 +3541,10 @@
         <v>12</v>
       </c>
       <c r="G101" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H101" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I101" s="7" t="s">
         <v>12</v>
@@ -3549,28 +3552,28 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D102" s="6" t="n">
-        <v>114556.0</v>
+        <v>283.0</v>
       </c>
       <c r="E102" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F102" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F102" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G102" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H102" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I102" s="7" t="s">
         <v>12</v>
@@ -3578,16 +3581,16 @@
     </row>
     <row r="103">
       <c r="A103" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D103" s="6" t="n">
-        <v>25020.0</v>
+        <v>400.0</v>
       </c>
       <c r="E103" s="7" t="s">
         <v>12</v>
@@ -3596,10 +3599,10 @@
         <v>12</v>
       </c>
       <c r="G103" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H103" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I103" s="7" t="s">
         <v>12</v>
@@ -3607,28 +3610,28 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="D104" s="6" t="n">
-        <v>95912.0</v>
+        <v>4229.0</v>
       </c>
       <c r="E104" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F104" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F104" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G104" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H104" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I104" s="7" t="s">
         <v>12</v>
@@ -3636,28 +3639,28 @@
     </row>
     <row r="105">
       <c r="A105" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="D105" s="6" t="n">
-        <v>9042.0</v>
+        <v>234937.0</v>
       </c>
       <c r="E105" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F105" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F105" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G105" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H105" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I105" s="7" t="s">
         <v>12</v>
@@ -3665,28 +3668,28 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="D106" s="6" t="n">
-        <v>277175.0</v>
+        <v>11399.0</v>
       </c>
       <c r="E106" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F106" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F106" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G106" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H106" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I106" s="7" t="s">
         <v>12</v>
@@ -3694,28 +3697,28 @@
     </row>
     <row r="107">
       <c r="A107" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="D107" s="6" t="n">
-        <v>18894.0</v>
+        <v>29705.0</v>
       </c>
       <c r="E107" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F107" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F107" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G107" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H107" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I107" s="7" t="s">
         <v>12</v>
@@ -3723,28 +3726,28 @@
     </row>
     <row r="108">
       <c r="A108" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="D108" s="6" t="n">
-        <v>91926.0</v>
+        <v>79599.0</v>
       </c>
       <c r="E108" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F108" s="7" t="n">
         <v>2.0</v>
       </c>
       <c r="G108" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H108" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I108" s="7" t="s">
         <v>12</v>
@@ -3752,28 +3755,28 @@
     </row>
     <row r="109">
       <c r="A109" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D109" s="6" t="n">
-        <v>3755.0</v>
+        <v>730586.0</v>
       </c>
       <c r="E109" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F109" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F109" s="7" t="n">
+        <v>13.0</v>
       </c>
       <c r="G109" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H109" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I109" s="7" t="s">
         <v>12</v>
@@ -3781,28 +3784,28 @@
     </row>
     <row r="110">
       <c r="A110" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D110" s="6" t="n">
-        <v>195070.0</v>
+        <v>313139.0</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F110" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F110" s="7" t="n">
+        <v>9.0</v>
       </c>
       <c r="G110" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H110" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I110" s="7" t="s">
         <v>12</v>
@@ -3810,16 +3813,16 @@
     </row>
     <row r="111">
       <c r="A111" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D111" s="6" t="n">
-        <v>45684.0</v>
+        <v>16347.0</v>
       </c>
       <c r="E111" s="7" t="s">
         <v>12</v>
@@ -3828,10 +3831,10 @@
         <v>12</v>
       </c>
       <c r="G111" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H111" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I111" s="7" t="s">
         <v>12</v>
@@ -3839,28 +3842,28 @@
     </row>
     <row r="112">
       <c r="A112" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>38</v>
+        <v>61</v>
       </c>
       <c r="D112" s="6" t="n">
-        <v>26183.0</v>
+        <v>16667.0</v>
       </c>
       <c r="E112" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F112" s="7" t="n">
         <v>1.0</v>
       </c>
       <c r="G112" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H112" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I112" s="7" t="s">
         <v>12</v>
@@ -3868,16 +3871,16 @@
     </row>
     <row r="113">
       <c r="A113" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="D113" s="6" t="n">
-        <v>3258.0</v>
+        <v>127.0</v>
       </c>
       <c r="E113" s="7" t="s">
         <v>12</v>
@@ -3886,10 +3889,10 @@
         <v>12</v>
       </c>
       <c r="G113" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H113" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I113" s="7" t="s">
         <v>12</v>
@@ -3897,28 +3900,28 @@
     </row>
     <row r="114">
       <c r="A114" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D114" s="6" t="n">
-        <v>2948.0</v>
+        <v>542033.0</v>
       </c>
       <c r="E114" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F114" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F114" s="7" t="n">
+        <v>15.0</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H114" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I114" s="7" t="s">
         <v>12</v>
@@ -3926,16 +3929,16 @@
     </row>
     <row r="115">
       <c r="A115" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D115" s="6" t="n">
-        <v>2627.0</v>
+        <v>4729.0</v>
       </c>
       <c r="E115" s="7" t="s">
         <v>12</v>
@@ -3944,10 +3947,10 @@
         <v>12</v>
       </c>
       <c r="G115" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H115" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I115" s="7" t="s">
         <v>12</v>
@@ -3955,16 +3958,16 @@
     </row>
     <row r="116">
       <c r="A116" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="D116" s="6" t="n">
-        <v>3941.0</v>
+        <v>58618.0</v>
       </c>
       <c r="E116" s="7" t="s">
         <v>12</v>
@@ -3973,10 +3976,10 @@
         <v>12</v>
       </c>
       <c r="G116" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H116" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I116" s="7" t="s">
         <v>12</v>
@@ -3984,28 +3987,28 @@
     </row>
     <row r="117">
       <c r="A117" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="D117" s="6" t="n">
-        <v>14642.0</v>
+        <v>75516.0</v>
       </c>
       <c r="E117" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F117" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F117" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G117" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H117" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I117" s="7" t="s">
         <v>12</v>
@@ -4013,16 +4016,16 @@
     </row>
     <row r="118">
       <c r="A118" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>26</v>
+        <v>64</v>
       </c>
       <c r="D118" s="6" t="n">
-        <v>2894.0</v>
+        <v>8361.0</v>
       </c>
       <c r="E118" s="7" t="s">
         <v>12</v>
@@ -4031,10 +4034,10 @@
         <v>12</v>
       </c>
       <c r="G118" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H118" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I118" s="7" t="s">
         <v>12</v>
@@ -4042,16 +4045,16 @@
     </row>
     <row r="119">
       <c r="A119" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C119" s="5" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="D119" s="6" t="n">
-        <v>13222.0</v>
+        <v>3762.0</v>
       </c>
       <c r="E119" s="7" t="s">
         <v>12</v>
@@ -4060,10 +4063,10 @@
         <v>12</v>
       </c>
       <c r="G119" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H119" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I119" s="7" t="s">
         <v>12</v>
@@ -4071,16 +4074,16 @@
     </row>
     <row r="120">
       <c r="A120" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C120" s="5" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="D120" s="6" t="n">
-        <v>17093.0</v>
+        <v>46007.0</v>
       </c>
       <c r="E120" s="7" t="s">
         <v>12</v>
@@ -4089,10 +4092,10 @@
         <v>12</v>
       </c>
       <c r="G120" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H120" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I120" s="7" t="s">
         <v>12</v>
@@ -4100,16 +4103,16 @@
     </row>
     <row r="121">
       <c r="A121" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C121" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D121" s="6" t="n">
-        <v>14051.0</v>
+        <v>975.0</v>
       </c>
       <c r="E121" s="7" t="s">
         <v>12</v>
@@ -4118,10 +4121,10 @@
         <v>12</v>
       </c>
       <c r="G121" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H121" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I121" s="7" t="s">
         <v>12</v>
@@ -4129,28 +4132,28 @@
     </row>
     <row r="122">
       <c r="A122" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C122" s="5" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="D122" s="6" t="n">
-        <v>212335.0</v>
+        <v>32531.0</v>
       </c>
       <c r="E122" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F122" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F122" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G122" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H122" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I122" s="7" t="s">
         <v>12</v>
@@ -4158,28 +4161,28 @@
     </row>
     <row r="123">
       <c r="A123" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C123" s="5" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D123" s="6" t="n">
-        <v>509443.0</v>
+        <v>6523.0</v>
       </c>
       <c r="E123" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F123" s="7" t="n">
-        <v>14.0</v>
+        <v>12</v>
+      </c>
+      <c r="F123" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G123" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H123" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I123" s="7" t="s">
         <v>12</v>
@@ -4187,16 +4190,16 @@
     </row>
     <row r="124">
       <c r="A124" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C124" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D124" s="6" t="n">
-        <v>7498.0</v>
+        <v>13697.0</v>
       </c>
       <c r="E124" s="7" t="s">
         <v>12</v>
@@ -4205,10 +4208,10 @@
         <v>12</v>
       </c>
       <c r="G124" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H124" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I124" s="7" t="s">
         <v>12</v>
@@ -4216,16 +4219,16 @@
     </row>
     <row r="125">
       <c r="A125" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C125" s="5" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="D125" s="6" t="n">
-        <v>7233.0</v>
+        <v>16644.0</v>
       </c>
       <c r="E125" s="7" t="s">
         <v>12</v>
@@ -4234,10 +4237,10 @@
         <v>12</v>
       </c>
       <c r="G125" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H125" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I125" s="7" t="s">
         <v>12</v>
@@ -4245,28 +4248,28 @@
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C126" s="5" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="D126" s="6" t="n">
-        <v>139189.0</v>
+        <v>54559.0</v>
       </c>
       <c r="E126" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F126" s="7" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="G126" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H126" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I126" s="7" t="s">
         <v>12</v>
@@ -4274,28 +4277,28 @@
     </row>
     <row r="127">
       <c r="A127" s="4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C127" s="5" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="D127" s="6" t="n">
-        <v>1218.0</v>
+        <v>23742.0</v>
       </c>
       <c r="E127" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F127" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F127" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G127" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H127" s="8" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="I127" s="7" t="s">
         <v>12</v>
@@ -4303,28 +4306,28 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C128" s="5" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D128" s="6" t="n">
-        <v>230828.0</v>
+        <v>114556.0</v>
       </c>
       <c r="E128" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F128" s="7" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G128" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H128" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I128" s="7" t="s">
         <v>12</v>
@@ -4332,16 +4335,16 @@
     </row>
     <row r="129">
       <c r="A129" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C129" s="5" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="D129" s="6" t="n">
-        <v>8139.0</v>
+        <v>3258.0</v>
       </c>
       <c r="E129" s="7" t="s">
         <v>12</v>
@@ -4350,10 +4353,10 @@
         <v>12</v>
       </c>
       <c r="G129" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H129" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I129" s="7" t="s">
         <v>12</v>
@@ -4361,28 +4364,28 @@
     </row>
     <row r="130">
       <c r="A130" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C130" s="5" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="D130" s="6" t="n">
-        <v>160049.0</v>
+        <v>45684.0</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F130" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F130" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G130" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H130" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I130" s="7" t="s">
         <v>12</v>
@@ -4390,16 +4393,16 @@
     </row>
     <row r="131">
       <c r="A131" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C131" s="5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="D131" s="6" t="n">
-        <v>2654.0</v>
+        <v>195070.0</v>
       </c>
       <c r="E131" s="7" t="s">
         <v>12</v>
@@ -4408,10 +4411,10 @@
         <v>12</v>
       </c>
       <c r="G131" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H131" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I131" s="7" t="s">
         <v>12</v>
@@ -4419,28 +4422,28 @@
     </row>
     <row r="132">
       <c r="A132" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C132" s="5" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="D132" s="6" t="n">
-        <v>74.0</v>
+        <v>91926.0</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F132" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F132" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G132" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H132" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I132" s="7" t="s">
         <v>12</v>
@@ -4448,28 +4451,28 @@
     </row>
     <row r="133">
       <c r="A133" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C133" s="5" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="D133" s="6" t="n">
-        <v>195883.0</v>
+        <v>277175.0</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F133" s="7" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="G133" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H133" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I133" s="7" t="s">
         <v>12</v>
@@ -4477,28 +4480,28 @@
     </row>
     <row r="134">
       <c r="A134" s="4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C134" s="5" t="s">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="D134" s="6" t="n">
-        <v>370451.0</v>
+        <v>95912.0</v>
       </c>
       <c r="E134" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F134" s="7" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="G134" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H134" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I134" s="7" t="s">
         <v>12</v>
@@ -4509,13 +4512,13 @@
         <v>70</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C135" s="5" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="D135" s="6" t="n">
-        <v>619.0</v>
+        <v>25020.0</v>
       </c>
       <c r="E135" s="7" t="s">
         <v>12</v>
@@ -4538,19 +4541,19 @@
         <v>70</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C136" s="5" t="s">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="D136" s="6" t="n">
-        <v>320554.0</v>
+        <v>233499.0</v>
       </c>
       <c r="E136" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F136" s="7" t="n">
-        <v>8.0</v>
+        <v>7.0</v>
       </c>
       <c r="G136" s="8" t="s">
         <v>70</v>
@@ -4567,19 +4570,19 @@
         <v>70</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C137" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D137" s="6" t="n">
-        <v>3597.0</v>
+        <v>212335.0</v>
       </c>
       <c r="E137" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F137" s="7" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G137" s="8" t="s">
         <v>70</v>
@@ -4596,19 +4599,19 @@
         <v>70</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C138" s="5" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D138" s="6" t="n">
-        <v>15061.0</v>
+        <v>1218.0</v>
       </c>
       <c r="E138" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F138" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F138" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G138" s="8" t="s">
         <v>70</v>
@@ -4625,19 +4628,19 @@
         <v>70</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C139" s="5" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D139" s="6" t="n">
-        <v>24694.0</v>
+        <v>370451.0</v>
       </c>
       <c r="E139" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F139" s="7" t="n">
-        <v>1.0</v>
+        <v>7.0</v>
       </c>
       <c r="G139" s="8" t="s">
         <v>70</v>
@@ -4654,19 +4657,19 @@
         <v>70</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C140" s="5" t="s">
         <v>28</v>
       </c>
       <c r="D140" s="6" t="n">
-        <v>321912.0</v>
+        <v>195883.0</v>
       </c>
       <c r="E140" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F140" s="7" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="G140" s="8" t="s">
         <v>70</v>
@@ -4683,19 +4686,19 @@
         <v>70</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C141" s="5" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="D141" s="6" t="n">
-        <v>125228.0</v>
+        <v>74.0</v>
       </c>
       <c r="E141" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F141" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F141" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G141" s="8" t="s">
         <v>70</v>
@@ -4712,19 +4715,19 @@
         <v>70</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C142" s="5" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="D142" s="6" t="n">
-        <v>3005.0</v>
+        <v>2654.0</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F142" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G142" s="8" t="s">
         <v>70</v>
@@ -4741,19 +4744,19 @@
         <v>70</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C143" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D143" s="6" t="n">
-        <v>3414.0</v>
+        <v>160049.0</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F143" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F143" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G143" s="8" t="s">
         <v>70</v>
@@ -4770,13 +4773,13 @@
         <v>70</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C144" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D144" s="6" t="n">
-        <v>2767.0</v>
+        <v>8139.0</v>
       </c>
       <c r="E144" s="7" t="s">
         <v>12</v>
@@ -4799,19 +4802,19 @@
         <v>70</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C145" s="5" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="D145" s="6" t="n">
-        <v>35783.0</v>
+        <v>230828.0</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F145" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G145" s="8" t="s">
         <v>70</v>
@@ -4828,13 +4831,13 @@
         <v>70</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C146" s="5" t="s">
-        <v>59</v>
+        <v>22</v>
       </c>
       <c r="D146" s="6" t="n">
-        <v>4174.0</v>
+        <v>2894.0</v>
       </c>
       <c r="E146" s="7" t="s">
         <v>12</v>
@@ -4857,13 +4860,13 @@
         <v>70</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C147" s="5" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="D147" s="6" t="n">
-        <v>29704.0</v>
+        <v>2948.0</v>
       </c>
       <c r="E147" s="7" t="s">
         <v>12</v>
@@ -4886,13 +4889,13 @@
         <v>70</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C148" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D148" s="6" t="n">
-        <v>3240.0</v>
+        <v>7233.0</v>
       </c>
       <c r="E148" s="7" t="s">
         <v>12</v>
@@ -4915,19 +4918,19 @@
         <v>70</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C149" s="5" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D149" s="6" t="n">
-        <v>584131.0</v>
+        <v>7498.0</v>
       </c>
       <c r="E149" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F149" s="7" t="n">
-        <v>11.0</v>
+        <v>12</v>
+      </c>
+      <c r="F149" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G149" s="8" t="s">
         <v>70</v>
@@ -4944,13 +4947,13 @@
         <v>70</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C150" s="5" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="D150" s="6" t="n">
-        <v>5761.0</v>
+        <v>14642.0</v>
       </c>
       <c r="E150" s="7" t="s">
         <v>12</v>
@@ -4973,19 +4976,19 @@
         <v>70</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C151" s="5" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="D151" s="6" t="n">
-        <v>17608.0</v>
+        <v>509443.0</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F151" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F151" s="7" t="n">
+        <v>14.0</v>
       </c>
       <c r="G151" s="8" t="s">
         <v>70</v>
@@ -5002,13 +5005,13 @@
         <v>70</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C152" s="5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="D152" s="6" t="n">
-        <v>30381.0</v>
+        <v>14051.0</v>
       </c>
       <c r="E152" s="7" t="s">
         <v>12</v>
@@ -5031,13 +5034,13 @@
         <v>70</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C153" s="5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D153" s="6" t="n">
-        <v>85424.0</v>
+        <v>17093.0</v>
       </c>
       <c r="E153" s="7" t="s">
         <v>12</v>
@@ -5057,28 +5060,28 @@
     </row>
     <row r="154">
       <c r="A154" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C154" s="5" t="s">
-        <v>26</v>
+        <v>59</v>
       </c>
       <c r="D154" s="6" t="n">
-        <v>39931.0</v>
+        <v>65872.0</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F154" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F154" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G154" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H154" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I154" s="7" t="s">
         <v>12</v>
@@ -5086,16 +5089,16 @@
     </row>
     <row r="155">
       <c r="A155" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C155" s="5" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="D155" s="6" t="n">
-        <v>30333.0</v>
+        <v>13222.0</v>
       </c>
       <c r="E155" s="7" t="s">
         <v>12</v>
@@ -5104,10 +5107,10 @@
         <v>12</v>
       </c>
       <c r="G155" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H155" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I155" s="7" t="s">
         <v>12</v>
@@ -5115,28 +5118,28 @@
     </row>
     <row r="156">
       <c r="A156" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C156" s="5" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="D156" s="6" t="n">
-        <v>55894.0</v>
+        <v>139189.0</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F156" s="7" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G156" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H156" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I156" s="7" t="s">
         <v>12</v>
@@ -5144,16 +5147,16 @@
     </row>
     <row r="157">
       <c r="A157" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C157" s="5" t="s">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="D157" s="6" t="n">
-        <v>59.0</v>
+        <v>7517.0</v>
       </c>
       <c r="E157" s="7" t="s">
         <v>12</v>
@@ -5162,10 +5165,10 @@
         <v>12</v>
       </c>
       <c r="G157" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H157" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I157" s="7" t="s">
         <v>12</v>
@@ -5173,16 +5176,16 @@
     </row>
     <row r="158">
       <c r="A158" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C158" s="5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D158" s="6" t="n">
-        <v>2758.0</v>
+        <v>36573.0</v>
       </c>
       <c r="E158" s="7" t="s">
         <v>12</v>
@@ -5191,10 +5194,10 @@
         <v>12</v>
       </c>
       <c r="G158" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H158" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I158" s="7" t="s">
         <v>12</v>
@@ -5202,16 +5205,16 @@
     </row>
     <row r="159">
       <c r="A159" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C159" s="5" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D159" s="6" t="n">
-        <v>1934.0</v>
+        <v>2627.0</v>
       </c>
       <c r="E159" s="7" t="s">
         <v>12</v>
@@ -5220,10 +5223,10 @@
         <v>12</v>
       </c>
       <c r="G159" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H159" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I159" s="7" t="s">
         <v>12</v>
@@ -5231,28 +5234,28 @@
     </row>
     <row r="160">
       <c r="A160" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C160" s="5" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="D160" s="6" t="n">
-        <v>570.0</v>
+        <v>155352.0</v>
       </c>
       <c r="E160" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F160" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F160" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G160" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H160" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I160" s="7" t="s">
         <v>12</v>
@@ -5260,28 +5263,28 @@
     </row>
     <row r="161">
       <c r="A161" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C161" s="5" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="D161" s="6" t="n">
-        <v>321509.0</v>
+        <v>70613.0</v>
       </c>
       <c r="E161" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F161" s="7" t="n">
-        <v>6.0</v>
+        <v>1.0</v>
       </c>
       <c r="G161" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H161" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I161" s="7" t="s">
         <v>12</v>
@@ -5289,28 +5292,28 @@
     </row>
     <row r="162">
       <c r="A162" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B162" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C162" s="5" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D162" s="6" t="n">
-        <v>222565.0</v>
+        <v>14906.0</v>
       </c>
       <c r="E162" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F162" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F162" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G162" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H162" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I162" s="7" t="s">
         <v>12</v>
@@ -5318,28 +5321,28 @@
     </row>
     <row r="163">
       <c r="A163" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B163" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C163" s="5" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D163" s="6" t="n">
-        <v>3184.0</v>
+        <v>114488.0</v>
       </c>
       <c r="E163" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F163" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F163" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G163" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H163" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I163" s="7" t="s">
         <v>12</v>
@@ -5347,16 +5350,16 @@
     </row>
     <row r="164">
       <c r="A164" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C164" s="5" t="s">
-        <v>31</v>
+        <v>62</v>
       </c>
       <c r="D164" s="6" t="n">
-        <v>7379.0</v>
+        <v>9042.0</v>
       </c>
       <c r="E164" s="7" t="s">
         <v>12</v>
@@ -5365,10 +5368,10 @@
         <v>12</v>
       </c>
       <c r="G164" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H164" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I164" s="7" t="s">
         <v>12</v>
@@ -5376,28 +5379,28 @@
     </row>
     <row r="165">
       <c r="A165" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B165" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C165" s="5" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="D165" s="6" t="n">
-        <v>8170.0</v>
+        <v>287203.0</v>
       </c>
       <c r="E165" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F165" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F165" s="7" t="n">
+        <v>5.0</v>
       </c>
       <c r="G165" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H165" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I165" s="7" t="s">
         <v>12</v>
@@ -5405,28 +5408,28 @@
     </row>
     <row r="166">
       <c r="A166" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="D166" s="6" t="n">
-        <v>320265.0</v>
+        <v>14342.0</v>
       </c>
       <c r="E166" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F166" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F166" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G166" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H166" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I166" s="7" t="s">
         <v>12</v>
@@ -5434,16 +5437,16 @@
     </row>
     <row r="167">
       <c r="A167" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B167" s="5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C167" s="5" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D167" s="6" t="n">
-        <v>180.0</v>
+        <v>36571.0</v>
       </c>
       <c r="E167" s="7" t="s">
         <v>12</v>
@@ -5452,10 +5455,10 @@
         <v>12</v>
       </c>
       <c r="G167" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H167" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I167" s="7" t="s">
         <v>12</v>
@@ -5463,16 +5466,16 @@
     </row>
     <row r="168">
       <c r="A168" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D168" s="6" t="n">
-        <v>2379.0</v>
+        <v>16990.0</v>
       </c>
       <c r="E168" s="7" t="s">
         <v>12</v>
@@ -5481,10 +5484,10 @@
         <v>12</v>
       </c>
       <c r="G168" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H168" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I168" s="7" t="s">
         <v>12</v>
@@ -5492,16 +5495,16 @@
     </row>
     <row r="169">
       <c r="A169" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B169" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C169" s="5" t="s">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="D169" s="6" t="n">
-        <v>1508.0</v>
+        <v>3941.0</v>
       </c>
       <c r="E169" s="7" t="s">
         <v>12</v>
@@ -5510,10 +5513,10 @@
         <v>12</v>
       </c>
       <c r="G169" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H169" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I169" s="7" t="s">
         <v>12</v>
@@ -5521,28 +5524,28 @@
     </row>
     <row r="170">
       <c r="A170" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C170" s="5" t="s">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="D170" s="6" t="n">
-        <v>3221.0</v>
+        <v>47217.0</v>
       </c>
       <c r="E170" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F170" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F170" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G170" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H170" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I170" s="7" t="s">
         <v>12</v>
@@ -5550,28 +5553,28 @@
     </row>
     <row r="171">
       <c r="A171" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B171" s="5" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C171" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D171" s="6" t="n">
-        <v>2031.0</v>
+        <v>26183.0</v>
       </c>
       <c r="E171" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F171" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F171" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G171" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I171" s="7" t="s">
         <v>12</v>
@@ -5579,28 +5582,28 @@
     </row>
     <row r="172">
       <c r="A172" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="D172" s="6" t="n">
-        <v>18449.0</v>
+        <v>1225.0</v>
       </c>
       <c r="E172" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F172" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F172" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G172" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H172" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I172" s="7" t="s">
         <v>12</v>
@@ -5608,16 +5611,16 @@
     </row>
     <row r="173">
       <c r="A173" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B173" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C173" s="5" t="s">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="D173" s="6" t="n">
-        <v>17448.0</v>
+        <v>3755.0</v>
       </c>
       <c r="E173" s="7" t="s">
         <v>12</v>
@@ -5626,10 +5629,10 @@
         <v>12</v>
       </c>
       <c r="G173" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H173" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I173" s="7" t="s">
         <v>12</v>
@@ -5637,16 +5640,16 @@
     </row>
     <row r="174">
       <c r="A174" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C174" s="5" t="s">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="D174" s="6" t="n">
-        <v>5269.0</v>
+        <v>18894.0</v>
       </c>
       <c r="E174" s="7" t="s">
         <v>12</v>
@@ -5655,10 +5658,10 @@
         <v>12</v>
       </c>
       <c r="G174" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I174" s="7" t="s">
         <v>12</v>
@@ -5669,19 +5672,19 @@
         <v>71</v>
       </c>
       <c r="B175" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C175" s="5" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="D175" s="6" t="n">
-        <v>1675.0</v>
+        <v>3005.0</v>
       </c>
       <c r="E175" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F175" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F175" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G175" s="8" t="s">
         <v>71</v>
@@ -5698,13 +5701,13 @@
         <v>71</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C176" s="5" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D176" s="6" t="n">
-        <v>24915.0</v>
+        <v>3414.0</v>
       </c>
       <c r="E176" s="7" t="s">
         <v>12</v>
@@ -5727,19 +5730,19 @@
         <v>71</v>
       </c>
       <c r="B177" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C177" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D177" s="6" t="n">
-        <v>329014.0</v>
+        <v>125228.0</v>
       </c>
       <c r="E177" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F177" s="7" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="G177" s="8" t="s">
         <v>71</v>
@@ -5756,19 +5759,19 @@
         <v>71</v>
       </c>
       <c r="B178" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C178" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C178" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D178" s="6" t="n">
-        <v>6951.0</v>
+        <v>321912.0</v>
       </c>
       <c r="E178" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F178" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F178" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G178" s="8" t="s">
         <v>71</v>
@@ -5785,13 +5788,13 @@
         <v>71</v>
       </c>
       <c r="B179" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C179" s="5" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D179" s="6" t="n">
-        <v>5201.0</v>
+        <v>619.0</v>
       </c>
       <c r="E179" s="7" t="s">
         <v>12</v>
@@ -5814,19 +5817,19 @@
         <v>71</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C180" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D180" s="6" t="n">
-        <v>1653.0</v>
+        <v>15061.0</v>
       </c>
       <c r="E180" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F180" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F180" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G180" s="8" t="s">
         <v>71</v>
@@ -5843,19 +5846,19 @@
         <v>71</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C181" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D181" s="6" t="n">
-        <v>173545.0</v>
+        <v>3597.0</v>
       </c>
       <c r="E181" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F181" s="7" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G181" s="8" t="s">
         <v>71</v>
@@ -5872,19 +5875,19 @@
         <v>71</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C182" s="5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D182" s="6" t="n">
-        <v>238945.0</v>
+        <v>320554.0</v>
       </c>
       <c r="E182" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F182" s="7" t="n">
-        <v>5.0</v>
+        <v>8.0</v>
       </c>
       <c r="G182" s="8" t="s">
         <v>71</v>
@@ -5898,28 +5901,28 @@
     </row>
     <row r="183">
       <c r="A183" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C183" s="5" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="D183" s="6" t="n">
-        <v>29224.0</v>
+        <v>2767.0</v>
       </c>
       <c r="E183" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F183" s="7" t="n">
-        <v>3.0</v>
+        <v>12</v>
+      </c>
+      <c r="F183" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G183" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I183" s="7" t="s">
         <v>12</v>
@@ -5927,16 +5930,16 @@
     </row>
     <row r="184">
       <c r="A184" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C184" s="5" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="D184" s="6" t="n">
-        <v>4101.0</v>
+        <v>85424.0</v>
       </c>
       <c r="E184" s="7" t="s">
         <v>12</v>
@@ -5945,10 +5948,10 @@
         <v>12</v>
       </c>
       <c r="G184" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I184" s="7" t="s">
         <v>12</v>
@@ -5956,28 +5959,28 @@
     </row>
     <row r="185">
       <c r="A185" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B185" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C185" s="5" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D185" s="6" t="n">
-        <v>69107.0</v>
+        <v>4174.0</v>
       </c>
       <c r="E185" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F185" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F185" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G185" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I185" s="7" t="s">
         <v>12</v>
@@ -5985,16 +5988,16 @@
     </row>
     <row r="186">
       <c r="A186" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C186" s="5" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="D186" s="6" t="n">
-        <v>3578.0</v>
+        <v>29704.0</v>
       </c>
       <c r="E186" s="7" t="s">
         <v>12</v>
@@ -6003,10 +6006,10 @@
         <v>12</v>
       </c>
       <c r="G186" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I186" s="7" t="s">
         <v>12</v>
@@ -6014,28 +6017,28 @@
     </row>
     <row r="187">
       <c r="A187" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C187" s="5" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="D187" s="6" t="n">
-        <v>8732.0</v>
+        <v>3240.0</v>
       </c>
       <c r="E187" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F187" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F187" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G187" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H187" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I187" s="7" t="s">
         <v>12</v>
@@ -6043,28 +6046,28 @@
     </row>
     <row r="188">
       <c r="A188" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C188" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D188" s="6" t="n">
-        <v>257668.0</v>
+        <v>24694.0</v>
       </c>
       <c r="E188" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F188" s="7" t="n">
-        <v>13.0</v>
+        <v>1.0</v>
       </c>
       <c r="G188" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H188" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I188" s="7" t="s">
         <v>12</v>
@@ -6072,28 +6075,28 @@
     </row>
     <row r="189">
       <c r="A189" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C189" s="5" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="D189" s="6" t="n">
-        <v>1044.0</v>
+        <v>584131.0</v>
       </c>
       <c r="E189" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F189" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F189" s="7" t="n">
+        <v>11.0</v>
       </c>
       <c r="G189" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H189" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I189" s="7" t="s">
         <v>12</v>
@@ -6101,28 +6104,28 @@
     </row>
     <row r="190">
       <c r="A190" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C190" s="5" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D190" s="6" t="n">
-        <v>503076.0</v>
+        <v>5761.0</v>
       </c>
       <c r="E190" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F190" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F190" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G190" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H190" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I190" s="7" t="s">
         <v>12</v>
@@ -6130,16 +6133,16 @@
     </row>
     <row r="191">
       <c r="A191" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C191" s="5" t="s">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D191" s="6" t="n">
-        <v>2926.0</v>
+        <v>35783.0</v>
       </c>
       <c r="E191" s="7" t="s">
         <v>12</v>
@@ -6148,10 +6151,10 @@
         <v>12</v>
       </c>
       <c r="G191" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H191" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>12</v>
@@ -6159,16 +6162,16 @@
     </row>
     <row r="192">
       <c r="A192" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C192" s="5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D192" s="6" t="n">
-        <v>1810.0</v>
+        <v>30381.0</v>
       </c>
       <c r="E192" s="7" t="s">
         <v>12</v>
@@ -6177,10 +6180,10 @@
         <v>12</v>
       </c>
       <c r="G192" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H192" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>12</v>
@@ -6188,16 +6191,16 @@
     </row>
     <row r="193">
       <c r="A193" s="4" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C193" s="5" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D193" s="6" t="n">
-        <v>829.0</v>
+        <v>17608.0</v>
       </c>
       <c r="E193" s="7" t="s">
         <v>12</v>
@@ -6206,10 +6209,10 @@
         <v>12</v>
       </c>
       <c r="G193" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H193" s="8" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>12</v>
@@ -6217,28 +6220,28 @@
     </row>
     <row r="194">
       <c r="A194" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C194" s="5" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D194" s="6" t="n">
-        <v>22718.0</v>
+        <v>39931.0</v>
       </c>
       <c r="E194" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F194" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F194" s="7" t="n">
+        <v>2.0</v>
       </c>
       <c r="G194" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H194" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>12</v>
@@ -6246,28 +6249,28 @@
     </row>
     <row r="195">
       <c r="A195" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B195" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C195" s="5" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="D195" s="6" t="n">
-        <v>17895.0</v>
+        <v>55894.0</v>
       </c>
       <c r="E195" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F195" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F195" s="7" t="n">
+        <v>4.0</v>
       </c>
       <c r="G195" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H195" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>12</v>
@@ -6275,28 +6278,28 @@
     </row>
     <row r="196">
       <c r="A196" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C196" s="5" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="D196" s="6" t="n">
-        <v>237487.0</v>
+        <v>1934.0</v>
       </c>
       <c r="E196" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F196" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F196" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G196" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H196" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I196" s="7" t="s">
         <v>12</v>
@@ -6304,16 +6307,16 @@
     </row>
     <row r="197">
       <c r="A197" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B197" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C197" s="5" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="D197" s="6" t="n">
-        <v>3935.0</v>
+        <v>30333.0</v>
       </c>
       <c r="E197" s="7" t="s">
         <v>12</v>
@@ -6322,10 +6325,10 @@
         <v>12</v>
       </c>
       <c r="G197" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I197" s="7" t="s">
         <v>12</v>
@@ -6333,28 +6336,28 @@
     </row>
     <row r="198">
       <c r="A198" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C198" s="5" t="s">
-        <v>23</v>
+        <v>73</v>
       </c>
       <c r="D198" s="6" t="n">
-        <v>118180.0</v>
+        <v>59.0</v>
       </c>
       <c r="E198" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F198" s="7" t="n">
-        <v>4.0</v>
+        <v>12</v>
+      </c>
+      <c r="F198" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G198" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H198" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I198" s="7" t="s">
         <v>12</v>
@@ -6362,16 +6365,16 @@
     </row>
     <row r="199">
       <c r="A199" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B199" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C199" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D199" s="6" t="n">
-        <v>19998.0</v>
+        <v>2758.0</v>
       </c>
       <c r="E199" s="7" t="s">
         <v>12</v>
@@ -6380,10 +6383,10 @@
         <v>12</v>
       </c>
       <c r="G199" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H199" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I199" s="7" t="s">
         <v>12</v>
@@ -6391,16 +6394,16 @@
     </row>
     <row r="200">
       <c r="A200" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C200" s="5" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="D200" s="6" t="n">
-        <v>362.0</v>
+        <v>5201.0</v>
       </c>
       <c r="E200" s="7" t="s">
         <v>12</v>
@@ -6409,10 +6412,10 @@
         <v>12</v>
       </c>
       <c r="G200" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H200" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I200" s="7" t="s">
         <v>12</v>
@@ -6420,16 +6423,16 @@
     </row>
     <row r="201">
       <c r="A201" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C201" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B201" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="C201" s="5" t="s">
-        <v>69</v>
-      </c>
       <c r="D201" s="6" t="n">
-        <v>2814.0</v>
+        <v>570.0</v>
       </c>
       <c r="E201" s="7" t="s">
         <v>12</v>
@@ -6438,10 +6441,10 @@
         <v>12</v>
       </c>
       <c r="G201" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H201" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I201" s="7" t="s">
         <v>12</v>
@@ -6449,28 +6452,28 @@
     </row>
     <row r="202">
       <c r="A202" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B202" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C202" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C202" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D202" s="6" t="n">
-        <v>285842.0</v>
+        <v>321509.0</v>
       </c>
       <c r="E202" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F202" s="7" t="n">
-        <v>8.0</v>
+        <v>6.0</v>
       </c>
       <c r="G202" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H202" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I202" s="7" t="s">
         <v>12</v>
@@ -6478,28 +6481,28 @@
     </row>
     <row r="203">
       <c r="A203" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D203" s="6" t="n">
-        <v>266600.0</v>
+        <v>222565.0</v>
       </c>
       <c r="E203" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F203" s="7" t="n">
-        <v>9.0</v>
+        <v>6.0</v>
       </c>
       <c r="G203" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H203" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I203" s="7" t="s">
         <v>12</v>
@@ -6507,16 +6510,16 @@
     </row>
     <row r="204">
       <c r="A204" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="D204" s="6" t="n">
-        <v>6142.0</v>
+        <v>3184.0</v>
       </c>
       <c r="E204" s="7" t="s">
         <v>12</v>
@@ -6525,10 +6528,10 @@
         <v>12</v>
       </c>
       <c r="G204" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H204" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I204" s="7" t="s">
         <v>12</v>
@@ -6536,16 +6539,16 @@
     </row>
     <row r="205">
       <c r="A205" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C205" s="5" t="s">
-        <v>56</v>
+        <v>16</v>
       </c>
       <c r="D205" s="6" t="n">
-        <v>14008.0</v>
+        <v>7379.0</v>
       </c>
       <c r="E205" s="7" t="s">
         <v>12</v>
@@ -6554,10 +6557,10 @@
         <v>12</v>
       </c>
       <c r="G205" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H205" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I205" s="7" t="s">
         <v>12</v>
@@ -6565,16 +6568,16 @@
     </row>
     <row r="206">
       <c r="A206" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C206" s="5" t="s">
-        <v>60</v>
+        <v>15</v>
       </c>
       <c r="D206" s="6" t="n">
-        <v>1634.0</v>
+        <v>8170.0</v>
       </c>
       <c r="E206" s="7" t="s">
         <v>12</v>
@@ -6583,10 +6586,10 @@
         <v>12</v>
       </c>
       <c r="G206" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="H206" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="I206" s="7" t="s">
         <v>12</v>
@@ -6594,28 +6597,28 @@
     </row>
     <row r="207">
       <c r="A207" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C207" s="5" t="s">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="D207" s="6" t="n">
-        <v>17945.0</v>
+        <v>320265.0</v>
       </c>
       <c r="E207" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F207" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F207" s="7" t="n">
+        <v>7.0</v>
       </c>
       <c r="G207" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H207" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I207" s="7" t="s">
         <v>12</v>
@@ -6623,28 +6626,28 @@
     </row>
     <row r="208">
       <c r="A208" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="C208" s="5" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D208" s="6" t="n">
-        <v>82973.0</v>
+        <v>180.0</v>
       </c>
       <c r="E208" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F208" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G208" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H208" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I208" s="7" t="s">
         <v>12</v>
@@ -6652,28 +6655,28 @@
     </row>
     <row r="209">
       <c r="A209" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C209" s="5" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D209" s="6" t="n">
-        <v>452.0</v>
+        <v>18449.0</v>
       </c>
       <c r="E209" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F209" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F209" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G209" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I209" s="7" t="s">
         <v>12</v>
@@ -6681,16 +6684,16 @@
     </row>
     <row r="210">
       <c r="A210" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C210" s="5" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="D210" s="6" t="n">
-        <v>146.0</v>
+        <v>1508.0</v>
       </c>
       <c r="E210" s="7" t="s">
         <v>12</v>
@@ -6699,10 +6702,10 @@
         <v>12</v>
       </c>
       <c r="G210" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I210" s="7" t="s">
         <v>12</v>
@@ -6710,28 +6713,28 @@
     </row>
     <row r="211">
       <c r="A211" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C211" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="D211" s="6" t="n">
-        <v>463.0</v>
+        <v>329014.0</v>
       </c>
       <c r="E211" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F211" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F211" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G211" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H211" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I211" s="7" t="s">
         <v>12</v>
@@ -6739,28 +6742,28 @@
     </row>
     <row r="212">
       <c r="A212" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C212" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D212" s="6" t="n">
-        <v>59949.0</v>
+        <v>5269.0</v>
       </c>
       <c r="E212" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F212" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F212" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G212" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H212" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I212" s="7" t="s">
         <v>12</v>
@@ -6768,28 +6771,28 @@
     </row>
     <row r="213">
       <c r="A213" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C213" s="5" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="D213" s="6" t="n">
-        <v>15327.0</v>
+        <v>17448.0</v>
       </c>
       <c r="E213" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F213" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F213" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G213" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H213" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I213" s="7" t="s">
         <v>12</v>
@@ -6797,28 +6800,28 @@
     </row>
     <row r="214">
       <c r="A214" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C214" s="5" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="D214" s="6" t="n">
-        <v>420055.0</v>
+        <v>1675.0</v>
       </c>
       <c r="E214" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F214" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F214" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G214" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H214" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I214" s="7" t="s">
         <v>12</v>
@@ -6826,28 +6829,28 @@
     </row>
     <row r="215">
       <c r="A215" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C215" s="5" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="D215" s="6" t="n">
-        <v>289870.0</v>
+        <v>3221.0</v>
       </c>
       <c r="E215" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F215" s="7" t="n">
-        <v>12.0</v>
+        <v>12</v>
+      </c>
+      <c r="F215" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G215" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H215" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I215" s="7" t="s">
         <v>12</v>
@@ -6855,28 +6858,28 @@
     </row>
     <row r="216">
       <c r="A216" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C216" s="5" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="D216" s="6" t="n">
-        <v>5459.0</v>
+        <v>24915.0</v>
       </c>
       <c r="E216" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F216" s="7" t="n">
-        <v>1.0</v>
+        <v>12</v>
+      </c>
+      <c r="F216" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G216" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H216" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I216" s="7" t="s">
         <v>12</v>
@@ -6884,28 +6887,28 @@
     </row>
     <row r="217">
       <c r="A217" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C217" s="5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D217" s="6" t="n">
-        <v>78919.0</v>
+        <v>238945.0</v>
       </c>
       <c r="E217" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F217" s="7" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="G217" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H217" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I217" s="7" t="s">
         <v>12</v>
@@ -6913,16 +6916,16 @@
     </row>
     <row r="218">
       <c r="A218" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C218" s="5" t="s">
-        <v>31</v>
+        <v>52</v>
       </c>
       <c r="D218" s="6" t="n">
-        <v>25601.0</v>
+        <v>2379.0</v>
       </c>
       <c r="E218" s="7" t="s">
         <v>12</v>
@@ -6931,10 +6934,10 @@
         <v>12</v>
       </c>
       <c r="G218" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H218" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I218" s="7" t="s">
         <v>12</v>
@@ -6942,28 +6945,28 @@
     </row>
     <row r="219">
       <c r="A219" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C219" s="5" t="s">
-        <v>14</v>
+        <v>51</v>
       </c>
       <c r="D219" s="6" t="n">
-        <v>216687.0</v>
+        <v>6951.0</v>
       </c>
       <c r="E219" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F219" s="7" t="n">
-        <v>6.0</v>
+        <v>12</v>
+      </c>
+      <c r="F219" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G219" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H219" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I219" s="7" t="s">
         <v>12</v>
@@ -6971,16 +6974,16 @@
     </row>
     <row r="220">
       <c r="A220" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C220" s="5" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="D220" s="6" t="n">
-        <v>3509.0</v>
+        <v>2031.0</v>
       </c>
       <c r="E220" s="7" t="s">
         <v>12</v>
@@ -6989,10 +6992,10 @@
         <v>12</v>
       </c>
       <c r="G220" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H220" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I220" s="7" t="s">
         <v>12</v>
@@ -7000,28 +7003,28 @@
     </row>
     <row r="221">
       <c r="A221" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C221" s="5" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="D221" s="6" t="n">
-        <v>12122.0</v>
+        <v>173545.0</v>
       </c>
       <c r="E221" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F221" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F221" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G221" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H221" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I221" s="7" t="s">
         <v>12</v>
@@ -7029,16 +7032,16 @@
     </row>
     <row r="222">
       <c r="A222" s="4" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C222" s="5" t="s">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="D222" s="6" t="n">
-        <v>1176.0</v>
+        <v>1653.0</v>
       </c>
       <c r="E222" s="7" t="s">
         <v>12</v>
@@ -7047,10 +7050,10 @@
         <v>12</v>
       </c>
       <c r="G222" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="I222" s="7" t="s">
         <v>12</v>
@@ -7061,19 +7064,19 @@
         <v>75</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C223" s="5" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D223" s="6" t="n">
-        <v>140722.0</v>
+        <v>4101.0</v>
       </c>
       <c r="E223" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F223" s="7" t="n">
-        <v>2.0</v>
+        <v>12</v>
+      </c>
+      <c r="F223" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G223" s="8" t="s">
         <v>75</v>
@@ -7090,13 +7093,13 @@
         <v>75</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C224" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D224" s="6" t="n">
-        <v>59681.0</v>
+        <v>829.0</v>
       </c>
       <c r="E224" s="7" t="s">
         <v>12</v>
@@ -7119,13 +7122,13 @@
         <v>75</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C225" s="5" t="s">
-        <v>54</v>
+        <v>16</v>
       </c>
       <c r="D225" s="6" t="n">
-        <v>639.0</v>
+        <v>1810.0</v>
       </c>
       <c r="E225" s="7" t="s">
         <v>12</v>
@@ -7148,13 +7151,13 @@
         <v>75</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C226" s="5" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D226" s="6" t="n">
-        <v>12619.0</v>
+        <v>2926.0</v>
       </c>
       <c r="E226" s="7" t="s">
         <v>12</v>
@@ -7177,19 +7180,19 @@
         <v>75</v>
       </c>
       <c r="B227" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C227" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C227" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="D227" s="6" t="n">
-        <v>295668.0</v>
+        <v>503076.0</v>
       </c>
       <c r="E227" s="7" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F227" s="7" t="n">
-        <v>7.0</v>
+        <v>12.0</v>
       </c>
       <c r="G227" s="8" t="s">
         <v>75</v>
@@ -7206,19 +7209,19 @@
         <v>75</v>
       </c>
       <c r="B228" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C228" s="5" t="s">
-        <v>21</v>
+        <v>74</v>
       </c>
       <c r="D228" s="6" t="n">
-        <v>252587.0</v>
+        <v>1044.0</v>
       </c>
       <c r="E228" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F228" s="7" t="n">
-        <v>7.0</v>
+        <v>12</v>
+      </c>
+      <c r="F228" s="7" t="s">
+        <v>12</v>
       </c>
       <c r="G228" s="8" t="s">
         <v>75</v>
@@ -7235,19 +7238,19 @@
         <v>75</v>
       </c>
       <c r="B229" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C229" s="5" t="s">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="D229" s="6" t="n">
-        <v>2780.0</v>
+        <v>29224.0</v>
       </c>
       <c r="E229" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F229" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F229" s="7" t="n">
+        <v>3.0</v>
       </c>
       <c r="G229" s="8" t="s">
         <v>75</v>
@@ -7264,19 +7267,19 @@
         <v>75</v>
       </c>
       <c r="B230" s="5" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C230" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="D230" s="6" t="n">
-        <v>35153.0</v>
+        <v>8732.0</v>
       </c>
       <c r="E230" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F230" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
+      </c>
+      <c r="F230" s="7" t="n">
+        <v>1.0</v>
       </c>
       <c r="G230" s="8" t="s">
         <v>75</v>
@@ -7293,13 +7296,13 @@
         <v>75</v>
       </c>
       <c r="B231" s="5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C231" s="5" t="s">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="D231" s="6" t="n">
-        <v>1221.0</v>
+        <v>3578.0</v>
       </c>
       <c r="E231" s="7" t="s">
         <v>12</v>
@@ -7314,6 +7317,1166 @@
         <v>75</v>
       </c>
       <c r="I231" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D232" s="6" t="n">
+        <v>69107.0</v>
+      </c>
+      <c r="E232" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F232" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G232" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H232" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I232" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C233" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D233" s="6" t="n">
+        <v>22718.0</v>
+      </c>
+      <c r="E233" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F233" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G233" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H233" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I233" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D234" s="6" t="n">
+        <v>257668.0</v>
+      </c>
+      <c r="E234" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F234" s="7" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="G234" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H234" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I234" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C235" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D235" s="6" t="n">
+        <v>1634.0</v>
+      </c>
+      <c r="E235" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F235" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G235" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H235" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I235" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C236" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D236" s="6" t="n">
+        <v>237487.0</v>
+      </c>
+      <c r="E236" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F236" s="7" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G236" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H236" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I236" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C237" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D237" s="6" t="n">
+        <v>3935.0</v>
+      </c>
+      <c r="E237" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F237" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G237" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H237" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I237" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C238" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D238" s="6" t="n">
+        <v>118180.0</v>
+      </c>
+      <c r="E238" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F238" s="7" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G238" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H238" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I238" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C239" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D239" s="6" t="n">
+        <v>19998.0</v>
+      </c>
+      <c r="E239" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F239" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G239" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H239" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I239" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C240" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D240" s="6" t="n">
+        <v>362.0</v>
+      </c>
+      <c r="E240" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F240" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G240" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H240" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I240" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C241" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D241" s="6" t="n">
+        <v>2814.0</v>
+      </c>
+      <c r="E241" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F241" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G241" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H241" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I241" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C242" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D242" s="6" t="n">
+        <v>285842.0</v>
+      </c>
+      <c r="E242" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F242" s="7" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="G242" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H242" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I242" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C243" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D243" s="6" t="n">
+        <v>266600.0</v>
+      </c>
+      <c r="E243" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F243" s="7" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="G243" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H243" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I243" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C244" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D244" s="6" t="n">
+        <v>6142.0</v>
+      </c>
+      <c r="E244" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F244" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G244" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H244" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I244" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C245" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D245" s="6" t="n">
+        <v>14008.0</v>
+      </c>
+      <c r="E245" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F245" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G245" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H245" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I245" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C246" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D246" s="6" t="n">
+        <v>17895.0</v>
+      </c>
+      <c r="E246" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F246" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G246" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H246" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="I246" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C247" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D247" s="6" t="n">
+        <v>17945.0</v>
+      </c>
+      <c r="E247" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F247" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G247" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H247" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I247" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C248" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D248" s="6" t="n">
+        <v>82973.0</v>
+      </c>
+      <c r="E248" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F248" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G248" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H248" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I248" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C249" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" s="6" t="n">
+        <v>452.0</v>
+      </c>
+      <c r="E249" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F249" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H249" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I249" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C250" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D250" s="6" t="n">
+        <v>146.0</v>
+      </c>
+      <c r="E250" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F250" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G250" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H250" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I250" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D251" s="6" t="n">
+        <v>463.0</v>
+      </c>
+      <c r="E251" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F251" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G251" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H251" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I251" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C252" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D252" s="6" t="n">
+        <v>59949.0</v>
+      </c>
+      <c r="E252" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F252" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G252" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H252" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I252" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C253" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D253" s="6" t="n">
+        <v>15327.0</v>
+      </c>
+      <c r="E253" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F253" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G253" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H253" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I253" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C254" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D254" s="6" t="n">
+        <v>420055.0</v>
+      </c>
+      <c r="E254" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F254" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G254" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H254" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I254" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C255" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D255" s="6" t="n">
+        <v>289870.0</v>
+      </c>
+      <c r="E255" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F255" s="7" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="G255" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H255" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I255" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C256" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D256" s="6" t="n">
+        <v>5459.0</v>
+      </c>
+      <c r="E256" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F256" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G256" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H256" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I256" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C257" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="D257" s="6" t="n">
+        <v>78919.0</v>
+      </c>
+      <c r="E257" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F257" s="7" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="G257" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H257" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I257" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C258" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D258" s="6" t="n">
+        <v>25601.0</v>
+      </c>
+      <c r="E258" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F258" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G258" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H258" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I258" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C259" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D259" s="6" t="n">
+        <v>216687.0</v>
+      </c>
+      <c r="E259" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F259" s="7" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="G259" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H259" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I259" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C260" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D260" s="6" t="n">
+        <v>3509.0</v>
+      </c>
+      <c r="E260" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F260" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G260" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H260" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I260" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C261" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D261" s="6" t="n">
+        <v>12122.0</v>
+      </c>
+      <c r="E261" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F261" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G261" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H261" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I261" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C262" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D262" s="6" t="n">
+        <v>1176.0</v>
+      </c>
+      <c r="E262" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F262" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G262" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H262" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I262" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C263" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D263" s="6" t="n">
+        <v>140722.0</v>
+      </c>
+      <c r="E263" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F263" s="7" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G263" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H263" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I263" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C264" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D264" s="6" t="n">
+        <v>59681.0</v>
+      </c>
+      <c r="E264" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F264" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G264" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H264" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I264" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C265" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D265" s="6" t="n">
+        <v>639.0</v>
+      </c>
+      <c r="E265" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F265" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G265" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H265" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I265" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C266" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D266" s="6" t="n">
+        <v>12619.0</v>
+      </c>
+      <c r="E266" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G266" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H266" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I266" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C267" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D267" s="6" t="n">
+        <v>295668.0</v>
+      </c>
+      <c r="E267" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F267" s="7" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="G267" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H267" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I267" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C268" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D268" s="6" t="n">
+        <v>252587.0</v>
+      </c>
+      <c r="E268" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F268" s="7" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="G268" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H268" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I268" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C269" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D269" s="6" t="n">
+        <v>2780.0</v>
+      </c>
+      <c r="E269" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F269" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G269" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H269" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I269" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C270" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D270" s="6" t="n">
+        <v>35153.0</v>
+      </c>
+      <c r="E270" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F270" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G270" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H270" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I270" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C271" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D271" s="6" t="n">
+        <v>1221.0</v>
+      </c>
+      <c r="E271" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F271" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G271" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="H271" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I271" s="7" t="s">
         <v>12</v>
       </c>
     </row>
